--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G18">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G25">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G57">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G65">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G80">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G90">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G78">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G57">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G71">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G78">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G71">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G87">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G88">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G126">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G129">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU135"/>
+  <dimension ref="A1:AU139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-30 09:55:00</t>
+          <t>2026-10-30 09:15:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:00:00</t>
+          <t>2026-10-30 09:55:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:15:00</t>
+          <t>2026-10-30 10:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:30:00</t>
+          <t>2026-10-30 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:45:00</t>
+          <t>2026-10-30 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00:00</t>
+          <t>2026-10-30 10:45:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-30 11:15:00</t>
+          <t>2026-10-30 11:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-10-30 11:30:00</t>
+          <t>2026-10-30 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-30 11:30:00</t>
+          <t>2026-10-30 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-10-30 11:50:00</t>
+          <t>2026-10-30 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-30 12:00:00</t>
+          <t>2026-10-30 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-30 12:00:00</t>
+          <t>2026-10-30 11:50:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G37">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-30 12:35:00</t>
+          <t>2026-10-30 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-30 13:00:00</t>
+          <t>2026-10-30 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-30 13:30:00</t>
+          <t>2026-10-30 12:35:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-30 13:45:00</t>
+          <t>2026-10-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 13:45:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G47">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-10-30 14:15:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,12 +8086,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G49">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G50">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>7.11</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>7.11</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9971,10 +9971,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G60">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-30 15:30:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-30 15:30:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-30 15:30:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G66">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G76">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G78">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13302,12 +13302,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G81">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G84">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14372,10 +14372,10 @@
         <v>0</v>
       </c>
       <c r="AC86">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE86">
         <v>0</v>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>0</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15100,22 +15100,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G91">
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G95">
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-10-30 17:05:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-30 17:15:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-30 19:00:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-30 19:00:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-30 19:00:00</t>
+          <t>2026-10-30 17:05:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-30 19:30:00</t>
+          <t>2026-10-30 17:15:00</t>
         </is>
       </c>
     </row>
@@ -17540,12 +17540,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-30 20:00:00</t>
+          <t>2026-10-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,27 +17703,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G107">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,22 +21457,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,22 +21620,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G134">
@@ -22267,156 +22267,808 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Vardar</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Struga</t>
+        </is>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="R135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="T135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>0</v>
+      </c>
+      <c r="V135">
+        <v>0</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <v>0</v>
+      </c>
+      <c r="Y135">
+        <v>0</v>
+      </c>
+      <c r="Z135">
+        <v>0</v>
+      </c>
+      <c r="AA135">
+        <v>0</v>
+      </c>
+      <c r="AB135">
+        <v>0</v>
+      </c>
+      <c r="AC135">
+        <v>0</v>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135">
+        <v>0</v>
+      </c>
+      <c r="AF135">
+        <v>0</v>
+      </c>
+      <c r="AG135">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+      <c r="AK135">
+        <v>0</v>
+      </c>
+      <c r="AL135">
+        <v>0</v>
+      </c>
+      <c r="AM135">
+        <v>-1</v>
+      </c>
+      <c r="AN135">
+        <v>-1</v>
+      </c>
+      <c r="AO135">
+        <v>-1</v>
+      </c>
+      <c r="AP135">
+        <v>-1</v>
+      </c>
+      <c r="AQ135">
+        <v>0</v>
+      </c>
+      <c r="AR135">
+        <v>0</v>
+      </c>
+      <c r="AS135">
+        <v>0</v>
+      </c>
+      <c r="AT135">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Shkëndija Haraçinë</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Tikveš</t>
+        </is>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>0</v>
+      </c>
+      <c r="R136">
+        <v>0</v>
+      </c>
+      <c r="S136">
+        <v>0</v>
+      </c>
+      <c r="T136">
+        <v>0</v>
+      </c>
+      <c r="U136">
+        <v>0</v>
+      </c>
+      <c r="V136">
+        <v>0</v>
+      </c>
+      <c r="W136">
+        <v>0</v>
+      </c>
+      <c r="X136">
+        <v>0</v>
+      </c>
+      <c r="Y136">
+        <v>0</v>
+      </c>
+      <c r="Z136">
+        <v>0</v>
+      </c>
+      <c r="AA136">
+        <v>0</v>
+      </c>
+      <c r="AB136">
+        <v>0</v>
+      </c>
+      <c r="AC136">
+        <v>0</v>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136">
+        <v>0</v>
+      </c>
+      <c r="AF136">
+        <v>0</v>
+      </c>
+      <c r="AG136">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+      <c r="AK136">
+        <v>0</v>
+      </c>
+      <c r="AL136">
+        <v>0</v>
+      </c>
+      <c r="AM136">
+        <v>-1</v>
+      </c>
+      <c r="AN136">
+        <v>-1</v>
+      </c>
+      <c r="AO136">
+        <v>-1</v>
+      </c>
+      <c r="AP136">
+        <v>-1</v>
+      </c>
+      <c r="AQ136">
+        <v>0</v>
+      </c>
+      <c r="AR136">
+        <v>0</v>
+      </c>
+      <c r="AS136">
+        <v>0</v>
+      </c>
+      <c r="AT136">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Bregalnica Štip</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>0</v>
+      </c>
+      <c r="R137">
+        <v>0</v>
+      </c>
+      <c r="S137">
+        <v>0</v>
+      </c>
+      <c r="T137">
+        <v>0</v>
+      </c>
+      <c r="U137">
+        <v>0</v>
+      </c>
+      <c r="V137">
+        <v>0</v>
+      </c>
+      <c r="W137">
+        <v>0</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+      <c r="AA137">
+        <v>0</v>
+      </c>
+      <c r="AB137">
+        <v>0</v>
+      </c>
+      <c r="AC137">
+        <v>0</v>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137">
+        <v>0</v>
+      </c>
+      <c r="AF137">
+        <v>0</v>
+      </c>
+      <c r="AG137">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+      <c r="AK137">
+        <v>0</v>
+      </c>
+      <c r="AL137">
+        <v>0</v>
+      </c>
+      <c r="AM137">
+        <v>-1</v>
+      </c>
+      <c r="AN137">
+        <v>-1</v>
+      </c>
+      <c r="AO137">
+        <v>-1</v>
+      </c>
+      <c r="AP137">
+        <v>-1</v>
+      </c>
+      <c r="AQ137">
+        <v>0</v>
+      </c>
+      <c r="AR137">
+        <v>0</v>
+      </c>
+      <c r="AS137">
+        <v>0</v>
+      </c>
+      <c r="AT137">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>FK Bashkimi Kumanovo</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Aresimi</t>
+        </is>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>21:15</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Curicó Unido</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Deportes Temuco</t>
         </is>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-10-30 21:15:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G69">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G133">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G43">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G92">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G133">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G54">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G92">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.55</v>
+        <v>1.84</v>
       </c>
       <c r="O55">
         <v>3.75</v>
       </c>
       <c r="P55">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="O56">
         <v>3.75</v>
       </c>
       <c r="P56">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q65">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q84">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G128">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G133">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G138">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -970,34 +970,34 @@
         <v>2.14</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
@@ -1006,19 +1006,19 @@
         <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>6.32</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q86">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU139"/>
+  <dimension ref="A1:AU138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G9">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Sheger Ketema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G10">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sheger Ketema</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-30 09:00:00</t>
+          <t>2026-10-30 09:15:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-30 09:15:00</t>
+          <t>2026-10-30 09:55:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,17 +2750,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>8.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-30 09:55:00</t>
+          <t>2026-10-30 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G21">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G22">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:00:00</t>
+          <t>2026-10-30 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:15:00</t>
+          <t>2026-10-30 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:30:00</t>
+          <t>2026-10-30 10:45:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:45:00</t>
+          <t>2026-10-30 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G29">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G30">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00:00</t>
+          <t>2026-10-30 11:15:00</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G31">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N31">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-30 11:15:00</t>
+          <t>2026-10-30 11:30:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G33">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-30 11:30:00</t>
+          <t>2026-10-30 11:50:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Asyut Petroleum</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-30 11:50:00</t>
+          <t>2026-10-30 12:00:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Asyut Petroleum</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>6.32</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="G38">
@@ -6499,68 +6499,68 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>6.32</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-30 12:00:00</t>
+          <t>2026-10-30 12:35:00</t>
         </is>
       </c>
     </row>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="G39">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-10-30 12:35:00</t>
+          <t>2026-10-30 13:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-10-30 13:00:00</t>
+          <t>2026-10-30 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G42">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-30 13:30:00</t>
+          <t>2026-10-30 13:45:00</t>
         </is>
       </c>
     </row>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-30 13:45:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G49">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-30 14:15:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="O55">
         <v>3.75</v>
       </c>
       <c r="P55">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>7.11</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>7.11</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9971,10 +9971,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>4.55</v>
+        <v>3.06</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P66">
-        <v>3.06</v>
+        <v>3.68</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="O69">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="P69">
-        <v>4.94</v>
+        <v>8</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,17 +11715,17 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N70">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-30 15:30:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="O73">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="P73">
-        <v>3.48</v>
+        <v>6.57</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.46</v>
+        <v>3.09</v>
       </c>
       <c r="O74">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="P74">
-        <v>6.57</v>
+        <v>2.24</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.09</v>
+        <v>2.1</v>
       </c>
       <c r="O75">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="P75">
-        <v>2.24</v>
+        <v>3.06</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P84">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.13</v>
+        <v>3.19</v>
       </c>
       <c r="O86">
-        <v>3.59</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>3.04</v>
+        <v>2.17</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.19</v>
+        <v>2.3</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P87">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14861,10 +14861,10 @@
         <v>0</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE89">
         <v>0</v>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.34</v>
+        <v>1.76</v>
       </c>
       <c r="O90">
-        <v>4.07</v>
+        <v>3.8</v>
       </c>
       <c r="P90">
-        <v>2.13</v>
+        <v>3.98</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15024,10 +15024,10 @@
         <v>0</v>
       </c>
       <c r="AC90">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD90">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.18</v>
+        <v>3.23</v>
       </c>
       <c r="O93">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P93">
-        <v>3.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>3.23</v>
+        <v>2.09</v>
       </c>
       <c r="O94">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>2.07</v>
+        <v>3.27</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.09</v>
+        <v>4.84</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P95">
-        <v>3.27</v>
+        <v>1.63</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.84</v>
+        <v>1.87</v>
       </c>
       <c r="O96">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P96">
-        <v>1.63</v>
+        <v>3.57</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.87</v>
+        <v>3.46</v>
       </c>
       <c r="O97">
-        <v>3.92</v>
+        <v>3.48</v>
       </c>
       <c r="P97">
-        <v>3.57</v>
+        <v>1.99</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.46</v>
+        <v>4.97</v>
       </c>
       <c r="O98">
-        <v>3.48</v>
+        <v>4.25</v>
       </c>
       <c r="P98">
-        <v>1.99</v>
+        <v>1.64</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 17:05:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-30 17:05:00</t>
+          <t>2026-10-30 17:15:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G105">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-30 17:15:00</t>
+          <t>2026-10-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G107">
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -17958,10 +17958,10 @@
         <v>0</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-30 19:00:00</t>
+          <t>2026-10-30 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-30 19:30:00</t>
+          <t>2026-10-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>5.93</v>
+        <v>0</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-30 20:00:00</t>
+          <t>2026-10-30 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G137">
@@ -22756,27 +22756,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G138">
@@ -22906,169 +22906,6 @@
         <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-10-30 21:15:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>8.710000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q82">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>2.24</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>3.42</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8468,34 +8468,34 @@
         <v>6.1</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AA50">
         <v>1.82</v>
@@ -8504,19 +8504,19 @@
         <v>1.94</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>3.8</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,55 +9283,55 @@
         <v>2.38</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>2.3</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9772,40 +9772,40 @@
         <v>1.28</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC58">
         <v>1.82</v>
@@ -9814,13 +9814,13 @@
         <v>1.97</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="O60">
-        <v>2.53</v>
+        <v>2.82</v>
       </c>
       <c r="P60">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10587,55 +10587,55 @@
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>3.06</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>3.68</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>2.9</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>4.94</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,55 +11565,55 @@
         <v>8</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12054,34 +12054,34 @@
         <v>3.48</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA72">
         <v>1.83</v>
@@ -12090,19 +12090,19 @@
         <v>1.96</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12217,55 +12217,55 @@
         <v>6.57</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>2.24</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>3.06</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>3.13</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13847,55 +13847,55 @@
         <v>2.2</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.17</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>2.89</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14825,40 +14825,40 @@
         <v>2.13</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC89">
         <v>2.2</v>
@@ -14867,13 +14867,13 @@
         <v>1.6</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>3.98</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16129,34 +16129,34 @@
         <v>1.99</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA97">
         <v>1.81</v>
@@ -16165,19 +16165,19 @@
         <v>1.95</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>1.64</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16781,55 +16781,55 @@
         <v>2.7</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>3</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17922,40 +17922,40 @@
         <v>30</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AC108">
         <v>1.9</v>
@@ -17964,13 +17964,13 @@
         <v>1.77</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -10424,55 +10424,55 @@
         <v>4.44</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>4.55</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="O67">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="P67">
-        <v>2.9</v>
+        <v>4.94</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="R67">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V67">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z67">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA67">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AB67">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="AC67">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AD67">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AE67">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF67">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="P68">
-        <v>4.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q68">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="R68">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="S68">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="V68">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="W68">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z68">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA68">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AB68">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="AC68">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AD68">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AE68">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
+        <v>1.46</v>
+      </c>
+      <c r="O72">
+        <v>4.3</v>
+      </c>
+      <c r="P72">
+        <v>6.57</v>
+      </c>
+      <c r="Q72">
         <v>1.99</v>
       </c>
-      <c r="O72">
-        <v>3.58</v>
-      </c>
-      <c r="P72">
-        <v>3.48</v>
-      </c>
-      <c r="Q72">
-        <v>2.65</v>
-      </c>
       <c r="R72">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S72">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="U72">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V72">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W72">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AA72">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB72">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC72">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD72">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF72">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AG72">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK72">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.46</v>
+        <v>3.09</v>
       </c>
       <c r="O73">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="P73">
-        <v>6.57</v>
+        <v>2.24</v>
       </c>
       <c r="Q73">
-        <v>1.99</v>
+        <v>3.84</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U73">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z73">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AB73">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AC73">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD73">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF73">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK73">
-        <v>2.62</v>
+        <v>1.33</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.09</v>
+        <v>1.99</v>
       </c>
       <c r="O74">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="P74">
-        <v>2.24</v>
+        <v>3.48</v>
       </c>
       <c r="Q74">
-        <v>3.84</v>
+        <v>2.65</v>
       </c>
       <c r="R74">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="U74">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V74">
+        <v>1.5</v>
+      </c>
+      <c r="W74">
+        <v>1.11</v>
+      </c>
+      <c r="X74">
+        <v>1.02</v>
+      </c>
+      <c r="Y74">
+        <v>1.19</v>
+      </c>
+      <c r="Z74">
+        <v>3.74</v>
+      </c>
+      <c r="AA74">
+        <v>1.83</v>
+      </c>
+      <c r="AB74">
+        <v>1.96</v>
+      </c>
+      <c r="AC74">
+        <v>2.78</v>
+      </c>
+      <c r="AD74">
         <v>1.4</v>
       </c>
-      <c r="W74">
-        <v>1.08</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>1.28</v>
-      </c>
-      <c r="Z74">
-        <v>3.08</v>
-      </c>
-      <c r="AA74">
-        <v>1.98</v>
-      </c>
-      <c r="AB74">
-        <v>1.77</v>
-      </c>
-      <c r="AC74">
-        <v>3.34</v>
-      </c>
-      <c r="AD74">
-        <v>1.24</v>
-      </c>
       <c r="AE74">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG74">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="O78">
+        <v>3.85</v>
+      </c>
+      <c r="P78">
+        <v>2.87</v>
+      </c>
+      <c r="Q78">
+        <v>2.55</v>
+      </c>
+      <c r="R78">
+        <v>2.45</v>
+      </c>
+      <c r="S78">
+        <v>1.17</v>
+      </c>
+      <c r="T78">
         <v>4.1</v>
       </c>
-      <c r="P78">
-        <v>2.94</v>
-      </c>
-      <c r="Q78">
-        <v>2.44</v>
-      </c>
-      <c r="R78">
-        <v>2.61</v>
-      </c>
-      <c r="S78">
-        <v>1.15</v>
-      </c>
-      <c r="T78">
-        <v>4.45</v>
-      </c>
       <c r="U78">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="V78">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="W78">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA78">
+        <v>1.37</v>
+      </c>
+      <c r="AB78">
+        <v>2.66</v>
+      </c>
+      <c r="AC78">
+        <v>2.01</v>
+      </c>
+      <c r="AD78">
+        <v>1.74</v>
+      </c>
+      <c r="AE78">
+        <v>1.28</v>
+      </c>
+      <c r="AF78">
+        <v>1.4</v>
+      </c>
+      <c r="AG78">
+        <v>2.8</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.25</v>
       </c>
-      <c r="AB78">
-        <v>3.28</v>
-      </c>
-      <c r="AC78">
-        <v>1.72</v>
-      </c>
-      <c r="AD78">
-        <v>2.03</v>
-      </c>
-      <c r="AE78">
-        <v>1.42</v>
-      </c>
-      <c r="AF78">
-        <v>1.28</v>
-      </c>
-      <c r="AG78">
-        <v>3.34</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.19</v>
-      </c>
       <c r="AK78">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P79">
-        <v>2.87</v>
+        <v>4.09</v>
       </c>
       <c r="Q79">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="R79">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S79">
+        <v>1.16</v>
+      </c>
+      <c r="T79">
+        <v>4.15</v>
+      </c>
+      <c r="U79">
+        <v>2.02</v>
+      </c>
+      <c r="V79">
+        <v>1.72</v>
+      </c>
+      <c r="W79">
         <v>1.17</v>
       </c>
-      <c r="T79">
-        <v>4.1</v>
-      </c>
-      <c r="U79">
-        <v>1.98</v>
-      </c>
-      <c r="V79">
-        <v>1.75</v>
-      </c>
-      <c r="W79">
-        <v>1.2</v>
-      </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA79">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC79">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AD79">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AE79">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF79">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG79">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,80 +13349,80 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="O80">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="P80">
-        <v>4.09</v>
+        <v>3.08</v>
       </c>
       <c r="Q80">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="R80">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S80">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="U80">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="V80">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="W80">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z80">
-        <v>5.55</v>
+        <v>4.3</v>
       </c>
       <c r="AA80">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AB80">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC80">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="AD80">
+        <v>1.46</v>
+      </c>
+      <c r="AE80">
+        <v>1.16</v>
+      </c>
+      <c r="AF80">
+        <v>1.51</v>
+      </c>
+      <c r="AG80">
+        <v>2.39</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
+        <v>1.24</v>
+      </c>
+      <c r="AK80">
         <v>1.7</v>
-      </c>
-      <c r="AE80">
-        <v>1.25</v>
-      </c>
-      <c r="AF80">
-        <v>1.43</v>
-      </c>
-      <c r="AG80">
-        <v>2.62</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ80">
-        <v>1.22</v>
-      </c>
-      <c r="AK80">
-        <v>2.1</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O81">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="P81">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="Q81">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="R81">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T81">
-        <v>3.5</v>
+        <v>4.45</v>
       </c>
       <c r="U81">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="W81">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Z81">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AA81">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="AB81">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AC81">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="AD81">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="AE81">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="AF81">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AG81">
-        <v>2.39</v>
+        <v>3.34</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK81">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P82">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q82">
-        <v>2.51</v>
+        <v>3.22</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U82">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V82">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W82">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z82">
-        <v>5.22</v>
+        <v>5.35</v>
       </c>
       <c r="AA82">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB82">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC82">
         <v>2.15</v>
       </c>
       <c r="AD82">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE82">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF82">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG82">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.67</v>
+        <v>1.94</v>
       </c>
       <c r="O83">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
+        <v>3.13</v>
+      </c>
+      <c r="Q83">
+        <v>2.51</v>
+      </c>
+      <c r="R83">
+        <v>2.38</v>
+      </c>
+      <c r="S83">
+        <v>1.22</v>
+      </c>
+      <c r="T83">
+        <v>3.8</v>
+      </c>
+      <c r="U83">
         <v>2.2</v>
       </c>
-      <c r="Q83">
-        <v>3.22</v>
-      </c>
-      <c r="R83">
-        <v>2.36</v>
-      </c>
-      <c r="S83">
-        <v>1.2</v>
-      </c>
-      <c r="T83">
-        <v>3.9</v>
-      </c>
-      <c r="U83">
-        <v>2.14</v>
-      </c>
       <c r="V83">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z83">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="AA83">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB83">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC83">
         <v>2.15</v>
       </c>
       <c r="AD83">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE83">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF83">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AG83">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK83">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>3.05</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>2.07</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
+        <v>4.84</v>
+      </c>
+      <c r="O94">
+        <v>4</v>
+      </c>
+      <c r="P94">
+        <v>1.63</v>
+      </c>
+      <c r="Q94">
+        <v>5.38</v>
+      </c>
+      <c r="R94">
+        <v>2.43</v>
+      </c>
+      <c r="S94">
+        <v>1.29</v>
+      </c>
+      <c r="T94">
+        <v>3.08</v>
+      </c>
+      <c r="U94">
+        <v>2.58</v>
+      </c>
+      <c r="V94">
+        <v>1.47</v>
+      </c>
+      <c r="W94">
+        <v>1.08</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
+        <v>1.23</v>
+      </c>
+      <c r="Z94">
+        <v>4.02</v>
+      </c>
+      <c r="AA94">
+        <v>1.72</v>
+      </c>
+      <c r="AB94">
         <v>2.09</v>
       </c>
-      <c r="O94">
-        <v>3.5</v>
-      </c>
-      <c r="P94">
-        <v>3.27</v>
-      </c>
-      <c r="Q94">
-        <v>0</v>
-      </c>
-      <c r="R94">
-        <v>0</v>
-      </c>
-      <c r="S94">
-        <v>0</v>
-      </c>
-      <c r="T94">
-        <v>0</v>
-      </c>
-      <c r="U94">
-        <v>0</v>
-      </c>
-      <c r="V94">
-        <v>0</v>
-      </c>
-      <c r="W94">
-        <v>0</v>
-      </c>
-      <c r="X94">
-        <v>0</v>
-      </c>
-      <c r="Y94">
-        <v>0</v>
-      </c>
-      <c r="Z94">
-        <v>0</v>
-      </c>
-      <c r="AA94">
-        <v>0</v>
-      </c>
-      <c r="AB94">
-        <v>0</v>
-      </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>4.84</v>
+        <v>1.87</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P95">
-        <v>1.63</v>
+        <v>3.57</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="O96">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>3.57</v>
+        <v>3.27</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18085,55 +18085,55 @@
         <v>5.93</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL109">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="O54">
         <v>3.75</v>
       </c>
       <c r="P54">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q54">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R54">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T54">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U54">
         <v>2.17</v>
       </c>
       <c r="V54">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W54">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X54">
         <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z54">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA54">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB54">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC54">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AD54">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG54">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK54">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.55</v>
+        <v>1.84</v>
       </c>
       <c r="O55">
         <v>3.75</v>
       </c>
       <c r="P55">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="Q55">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="S55">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T55">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U55">
         <v>2.17</v>
       </c>
       <c r="V55">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA55">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AB55">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC55">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="AD55">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG55">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>2.03</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.23</v>
+        <v>4.84</v>
       </c>
       <c r="O93">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="P93">
-        <v>2.07</v>
+        <v>1.63</v>
       </c>
       <c r="Q93">
-        <v>3.91</v>
+        <v>5.38</v>
       </c>
       <c r="R93">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="U93">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W93">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>4.25</v>
+        <v>4.02</v>
       </c>
       <c r="AA93">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC93">
-        <v>2.69</v>
+        <v>2.81</v>
       </c>
       <c r="AD93">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
         <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AG93">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>4.84</v>
+        <v>1.87</v>
       </c>
       <c r="O94">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P94">
-        <v>1.63</v>
+        <v>3.57</v>
       </c>
       <c r="Q94">
-        <v>5.38</v>
+        <v>2.36</v>
       </c>
       <c r="R94">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="V94">
+        <v>1.6</v>
+      </c>
+      <c r="W94">
+        <v>1.13</v>
+      </c>
+      <c r="X94">
+        <v>1.01</v>
+      </c>
+      <c r="Y94">
+        <v>1.16</v>
+      </c>
+      <c r="Z94">
+        <v>5.07</v>
+      </c>
+      <c r="AA94">
+        <v>1.53</v>
+      </c>
+      <c r="AB94">
+        <v>2.49</v>
+      </c>
+      <c r="AC94">
+        <v>2.31</v>
+      </c>
+      <c r="AD94">
+        <v>1.61</v>
+      </c>
+      <c r="AE94">
+        <v>1.25</v>
+      </c>
+      <c r="AF94">
         <v>1.47</v>
       </c>
-      <c r="W94">
-        <v>1.08</v>
-      </c>
-      <c r="X94">
-        <v>1</v>
-      </c>
-      <c r="Y94">
-        <v>1.23</v>
-      </c>
-      <c r="Z94">
-        <v>4.02</v>
-      </c>
-      <c r="AA94">
-        <v>1.72</v>
-      </c>
-      <c r="AB94">
-        <v>2.09</v>
-      </c>
-      <c r="AC94">
-        <v>2.81</v>
-      </c>
-      <c r="AD94">
-        <v>1.42</v>
-      </c>
-      <c r="AE94">
-        <v>1.12</v>
-      </c>
-      <c r="AF94">
-        <v>1.72</v>
-      </c>
       <c r="AG94">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="O95">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>3.57</v>
+        <v>3.27</v>
       </c>
       <c r="Q95">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="R95">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="S95">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="V95">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W95">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z95">
-        <v>5.07</v>
+        <v>3.88</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB95">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC95">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="AD95">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AG95">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.09</v>
+        <v>3.23</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P96">
-        <v>3.27</v>
+        <v>2.07</v>
       </c>
       <c r="Q96">
-        <v>2.65</v>
+        <v>3.91</v>
       </c>
       <c r="R96">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U96">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z96">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB96">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC96">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AD96">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF96">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG96">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK96">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="R105">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U105">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="V105">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.02</v>
       </c>
       <c r="Y105">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>5.68</v>
+        <v>3.2</v>
       </c>
       <c r="AA105">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AB105">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC105">
-        <v>2.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD105">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG105">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G106">
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="S106">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T106">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U106">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="V106">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X106">
         <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z106">
-        <v>3.2</v>
+        <v>5.68</v>
       </c>
       <c r="AA106">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="AB106">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="AC106">
-        <v>3.28</v>
+        <v>2.17</v>
       </c>
       <c r="AD106">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AE106">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG106">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK106">
-        <v>2.15</v>
+        <v>3.5</v>
       </c>
       <c r="AL106">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.18</v>
+        <v>4.84</v>
       </c>
       <c r="O92">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="P92">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="Q92">
-        <v>2.8</v>
+        <v>5.38</v>
       </c>
       <c r="R92">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="S92">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T92">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="V92">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W92">
         <v>1.08</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z92">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="AA92">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB92">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AC92">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD92">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE92">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AG92">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>4.84</v>
+        <v>1.87</v>
       </c>
       <c r="O93">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P93">
-        <v>1.63</v>
+        <v>3.57</v>
       </c>
       <c r="Q93">
-        <v>5.38</v>
+        <v>2.36</v>
       </c>
       <c r="R93">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="U93">
-        <v>2.58</v>
+        <v>2.2</v>
       </c>
       <c r="V93">
+        <v>1.6</v>
+      </c>
+      <c r="W93">
+        <v>1.13</v>
+      </c>
+      <c r="X93">
+        <v>1.01</v>
+      </c>
+      <c r="Y93">
+        <v>1.16</v>
+      </c>
+      <c r="Z93">
+        <v>5.07</v>
+      </c>
+      <c r="AA93">
+        <v>1.53</v>
+      </c>
+      <c r="AB93">
+        <v>2.49</v>
+      </c>
+      <c r="AC93">
+        <v>2.31</v>
+      </c>
+      <c r="AD93">
+        <v>1.61</v>
+      </c>
+      <c r="AE93">
+        <v>1.25</v>
+      </c>
+      <c r="AF93">
         <v>1.47</v>
       </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1</v>
-      </c>
-      <c r="Y93">
-        <v>1.23</v>
-      </c>
-      <c r="Z93">
-        <v>4.02</v>
-      </c>
-      <c r="AA93">
-        <v>1.72</v>
-      </c>
-      <c r="AB93">
-        <v>2.09</v>
-      </c>
-      <c r="AC93">
-        <v>2.81</v>
-      </c>
-      <c r="AD93">
-        <v>1.42</v>
-      </c>
-      <c r="AE93">
-        <v>1.12</v>
-      </c>
-      <c r="AF93">
-        <v>1.72</v>
-      </c>
       <c r="AG93">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.17</v>
+        <v>1.88</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="O94">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>3.57</v>
+        <v>3.27</v>
       </c>
       <c r="Q94">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="R94">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U94">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="V94">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W94">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z94">
-        <v>5.07</v>
+        <v>3.88</v>
       </c>
       <c r="AA94">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AB94">
-        <v>2.49</v>
+        <v>1.93</v>
       </c>
       <c r="AC94">
-        <v>2.31</v>
+        <v>2.99</v>
       </c>
       <c r="AD94">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE94">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF94">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AG94">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.09</v>
+        <v>3.23</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P95">
-        <v>3.27</v>
+        <v>2.07</v>
       </c>
       <c r="Q95">
-        <v>2.65</v>
+        <v>3.91</v>
       </c>
       <c r="R95">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U95">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V95">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z95">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AB95">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC95">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AD95">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG95">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK95">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.23</v>
+        <v>2.18</v>
       </c>
       <c r="O96">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="P96">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="Q96">
-        <v>3.91</v>
+        <v>2.8</v>
       </c>
       <c r="R96">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="S96">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T96">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U96">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="V96">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="AA96">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB96">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AC96">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD96">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE96">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF96">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG96">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AL96">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU138"/>
+  <dimension ref="A1:AU139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G25">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-30 14:00:00</t>
+          <t>2026-10-30 13:45:00</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.98</v>
+        <v>4.84</v>
       </c>
       <c r="O45">
-        <v>3.54</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>3.42</v>
+        <v>1.62</v>
       </c>
       <c r="Q45">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="R45">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S45">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T45">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V45">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W45">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y45">
+        <v>1.19</v>
+      </c>
+      <c r="Z45">
+        <v>4.34</v>
+      </c>
+      <c r="AA45">
+        <v>1.67</v>
+      </c>
+      <c r="AB45">
+        <v>2.31</v>
+      </c>
+      <c r="AC45">
+        <v>2.52</v>
+      </c>
+      <c r="AD45">
+        <v>1.5</v>
+      </c>
+      <c r="AE45">
         <v>1.18</v>
       </c>
-      <c r="Z45">
-        <v>4.33</v>
-      </c>
-      <c r="AA45">
-        <v>1.64</v>
-      </c>
-      <c r="AB45">
-        <v>2.08</v>
-      </c>
-      <c r="AC45">
-        <v>2.63</v>
-      </c>
-      <c r="AD45">
-        <v>1.44</v>
-      </c>
-      <c r="AE45">
-        <v>1.14</v>
-      </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AG45">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.25</v>
       </c>
       <c r="AK45">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G47">
@@ -7979,55 +7979,55 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G48">
@@ -8142,55 +8142,55 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G49">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-10-30 14:15:00</t>
+          <t>2026-10-30 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-10-30 14:30:00</t>
+          <t>2026-10-30 14:15:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.84</v>
+        <v>2.55</v>
       </c>
       <c r="O55">
         <v>3.75</v>
       </c>
       <c r="P55">
-        <v>3.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q55">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R55">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T55">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U55">
         <v>2.17</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X55">
         <v>1.02</v>
       </c>
       <c r="Y55">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z55">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AB55">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AD55">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AG55">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>2.03</v>
+        <v>1.33</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>1.84</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="Q56">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="R56">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="S56">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U56">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W56">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.18</v>
       </c>
       <c r="Z56">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="AA56">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AB56">
+        <v>2.4</v>
+      </c>
+      <c r="AC56">
+        <v>2.38</v>
+      </c>
+      <c r="AD56">
+        <v>1.53</v>
+      </c>
+      <c r="AE56">
+        <v>1.18</v>
+      </c>
+      <c r="AF56">
+        <v>1.53</v>
+      </c>
+      <c r="AG56">
+        <v>2.38</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>1.18</v>
+      </c>
+      <c r="AK56">
         <v>2.03</v>
-      </c>
-      <c r="AC56">
-        <v>2.74</v>
-      </c>
-      <c r="AD56">
-        <v>1.37</v>
-      </c>
-      <c r="AE56">
-        <v>1.11</v>
-      </c>
-      <c r="AF56">
-        <v>1.56</v>
-      </c>
-      <c r="AG56">
-        <v>2.28</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.46</v>
-      </c>
-      <c r="AK56">
-        <v>1.43</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.53</v>
+        <v>2.85</v>
       </c>
       <c r="O57">
-        <v>3.87</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q57">
-        <v>3.84</v>
+        <v>3.15</v>
       </c>
       <c r="R57">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="S57">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U57">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V57">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W57">
         <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>5.17</v>
+        <v>3.84</v>
       </c>
       <c r="AA57">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AB57">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="AC57">
-        <v>2.33</v>
+        <v>2.74</v>
       </c>
       <c r="AD57">
+        <v>1.37</v>
+      </c>
+      <c r="AE57">
+        <v>1.11</v>
+      </c>
+      <c r="AF57">
         <v>1.56</v>
       </c>
-      <c r="AE57">
-        <v>1.19</v>
-      </c>
-      <c r="AF57">
-        <v>1.48</v>
-      </c>
       <c r="AG57">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.46</v>
       </c>
       <c r="AK57">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-30 15:00:00</t>
+          <t>2026-10-30 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>11</v>
+        <v>3.53</v>
       </c>
       <c r="O58">
-        <v>7.11</v>
+        <v>3.87</v>
       </c>
       <c r="P58">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="Q58">
-        <v>9</v>
+        <v>3.84</v>
       </c>
       <c r="R58">
-        <v>2.98</v>
+        <v>2.34</v>
       </c>
       <c r="S58">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="T58">
-        <v>4.6</v>
+        <v>3.42</v>
       </c>
       <c r="U58">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="V58">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
+        <v>1.11</v>
+      </c>
+      <c r="X58">
+        <v>1.02</v>
+      </c>
+      <c r="Y58">
+        <v>1.13</v>
+      </c>
+      <c r="Z58">
+        <v>5.17</v>
+      </c>
+      <c r="AA58">
+        <v>1.52</v>
+      </c>
+      <c r="AB58">
+        <v>2.39</v>
+      </c>
+      <c r="AC58">
+        <v>2.33</v>
+      </c>
+      <c r="AD58">
+        <v>1.56</v>
+      </c>
+      <c r="AE58">
+        <v>1.19</v>
+      </c>
+      <c r="AF58">
+        <v>1.48</v>
+      </c>
+      <c r="AG58">
+        <v>2.45</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
         <v>1.22</v>
       </c>
-      <c r="X58">
-        <v>1</v>
-      </c>
-      <c r="Y58">
-        <v>1.07</v>
-      </c>
-      <c r="Z58">
-        <v>6.7</v>
-      </c>
-      <c r="AA58">
-        <v>1.33</v>
-      </c>
-      <c r="AB58">
-        <v>3.3</v>
-      </c>
-      <c r="AC58">
-        <v>1.82</v>
-      </c>
-      <c r="AD58">
-        <v>1.97</v>
-      </c>
-      <c r="AE58">
-        <v>1.41</v>
-      </c>
-      <c r="AF58">
-        <v>1.67</v>
-      </c>
-      <c r="AG58">
-        <v>2.15</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>4</v>
-      </c>
       <c r="AK58">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.74</v>
+        <v>11</v>
       </c>
       <c r="O59">
-        <v>2.53</v>
+        <v>7.11</v>
       </c>
       <c r="P59">
-        <v>2.79</v>
+        <v>1.28</v>
       </c>
       <c r="Q59">
-        <v>3.64</v>
+        <v>9</v>
       </c>
       <c r="R59">
-        <v>1.68</v>
+        <v>2.98</v>
       </c>
       <c r="S59">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="U59">
-        <v>3.9</v>
+        <v>1.93</v>
       </c>
       <c r="V59">
+        <v>1.91</v>
+      </c>
+      <c r="W59">
         <v>1.22</v>
       </c>
-      <c r="W59">
-        <v>1.01</v>
-      </c>
       <c r="X59">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>1.59</v>
+        <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>2.25</v>
+        <v>6.7</v>
       </c>
       <c r="AA59">
-        <v>2.83</v>
+        <v>1.33</v>
       </c>
       <c r="AB59">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="AC59">
-        <v>5.85</v>
+        <v>1.82</v>
       </c>
       <c r="AD59">
-        <v>1.07</v>
+        <v>1.97</v>
       </c>
       <c r="AE59">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AF59">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="AG59">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.28</v>
+        <v>4</v>
       </c>
       <c r="AK59">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="O60">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="P60">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="Q60">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="S60">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="T60">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U60">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="V60">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W60">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X60">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y60">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="Z60">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AA60">
-        <v>2.33</v>
+        <v>2.83</v>
       </c>
       <c r="AB60">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AC60">
-        <v>4.25</v>
+        <v>5.85</v>
       </c>
       <c r="AD60">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AG60">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
+        <v>1.28</v>
+      </c>
+      <c r="AK60">
         <v>1.36</v>
-      </c>
-      <c r="AK60">
-        <v>1.42</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10536,22 +10536,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Meppen</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,31 +10578,31 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="Q63">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R63">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="S63">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T63">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V63">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W63">
         <v>1.12</v>
@@ -10611,31 +10611,31 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
+        <v>1.15</v>
+      </c>
+      <c r="Z63">
+        <v>4.25</v>
+      </c>
+      <c r="AA63">
+        <v>1.64</v>
+      </c>
+      <c r="AB63">
+        <v>2.16</v>
+      </c>
+      <c r="AC63">
+        <v>2.52</v>
+      </c>
+      <c r="AD63">
+        <v>1.41</v>
+      </c>
+      <c r="AE63">
         <v>1.12</v>
       </c>
-      <c r="Z63">
-        <v>4.7</v>
-      </c>
-      <c r="AA63">
-        <v>1.48</v>
-      </c>
-      <c r="AB63">
-        <v>2.33</v>
-      </c>
-      <c r="AC63">
-        <v>2.37</v>
-      </c>
-      <c r="AD63">
-        <v>1.56</v>
-      </c>
-      <c r="AE63">
-        <v>1.19</v>
-      </c>
       <c r="AF63">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Meppen</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="R64">
-        <v>2.8</v>
+        <v>2.42</v>
       </c>
       <c r="S64">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="V64">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="W64">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="Z64">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="AA64">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AB64">
-        <v>3.39</v>
+        <v>2.33</v>
       </c>
       <c r="AC64">
-        <v>1.78</v>
+        <v>2.37</v>
       </c>
       <c r="AD64">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="AE64">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AF64">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>4.55</v>
       </c>
       <c r="P65">
-        <v>3.06</v>
+        <v>4.55</v>
       </c>
       <c r="Q65">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="S65">
+        <v>1.15</v>
+      </c>
+      <c r="T65">
+        <v>5.2</v>
+      </c>
+      <c r="U65">
+        <v>1.85</v>
+      </c>
+      <c r="V65">
+        <v>1.85</v>
+      </c>
+      <c r="W65">
         <v>1.25</v>
       </c>
-      <c r="T65">
-        <v>3.6</v>
-      </c>
-      <c r="U65">
-        <v>2.32</v>
-      </c>
-      <c r="V65">
-        <v>1.6</v>
-      </c>
-      <c r="W65">
-        <v>1.1</v>
-      </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="Z65">
-        <v>4.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA65">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AB65">
-        <v>2.25</v>
+        <v>3.39</v>
       </c>
       <c r="AC65">
-        <v>2.43</v>
+        <v>1.78</v>
       </c>
       <c r="AD65">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG65">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="O66">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>3.68</v>
+        <v>3.06</v>
       </c>
       <c r="Q66">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="R66">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.03</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.84</v>
+        <v>2.32</v>
       </c>
       <c r="V66">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z66">
-        <v>3.63</v>
+        <v>4.55</v>
       </c>
       <c r="AA66">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>3.26</v>
+        <v>2.43</v>
       </c>
       <c r="AD66">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF66">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG66">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-30 15:30:00</t>
+          <t>2026-10-30 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="O67">
-        <v>4.3</v>
+        <v>3.68</v>
       </c>
       <c r="P67">
-        <v>4.94</v>
+        <v>3.68</v>
       </c>
       <c r="Q67">
-        <v>1.97</v>
+        <v>2.74</v>
       </c>
       <c r="R67">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="S67">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>3.8</v>
+        <v>3.03</v>
       </c>
       <c r="U67">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="V67">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="W67">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>5.5</v>
+        <v>3.63</v>
       </c>
       <c r="AA67">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AB67">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="AC67">
-        <v>1.98</v>
+        <v>3.26</v>
       </c>
       <c r="AD67">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="AE67">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>1.49</v>
       </c>
       <c r="O68">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="P68">
-        <v>2.9</v>
+        <v>4.94</v>
       </c>
       <c r="Q68">
-        <v>2.63</v>
+        <v>1.97</v>
       </c>
       <c r="R68">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T68">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U68">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="W68">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X68">
         <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z68">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AB68">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AD68">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="AE68">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG68">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="O69">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="P69">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="Q69">
-        <v>1.62</v>
+        <v>2.63</v>
       </c>
       <c r="R69">
-        <v>2.85</v>
+        <v>2.28</v>
       </c>
       <c r="S69">
         <v>1.25</v>
       </c>
       <c r="T69">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U69">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V69">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W69">
         <v>1.14</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z69">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AA69">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AB69">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AC69">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD69">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AE69">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G70">
@@ -11715,68 +11715,68 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-10-30 16:00:00</t>
+          <t>2026-10-30 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G71">
@@ -11878,17 +11878,17 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N71">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.46</v>
+        <v>2.26</v>
       </c>
       <c r="O72">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="P72">
-        <v>6.57</v>
+        <v>3.22</v>
       </c>
       <c r="Q72">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z72">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD72">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG72">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK72">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.09</v>
+        <v>1.46</v>
       </c>
       <c r="O73">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="P73">
-        <v>2.24</v>
+        <v>6.57</v>
       </c>
       <c r="Q73">
-        <v>3.84</v>
+        <v>1.99</v>
       </c>
       <c r="R73">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="U73">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="V73">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z73">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA73">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AC73">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD73">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF73">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.33</v>
+        <v>2.62</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.99</v>
+        <v>3.09</v>
       </c>
       <c r="O74">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="P74">
-        <v>3.48</v>
+        <v>2.24</v>
       </c>
       <c r="Q74">
-        <v>2.65</v>
+        <v>3.84</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="U74">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V74">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z74">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB74">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AC74">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AD74">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF74">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="O75">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P75">
-        <v>3.06</v>
+        <v>3.48</v>
       </c>
       <c r="Q75">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="R75">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.7</v>
+        <v>3.23</v>
       </c>
       <c r="U75">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="V75">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z75">
-        <v>4.95</v>
+        <v>3.74</v>
       </c>
       <c r="AA75">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AB75">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="AC75">
-        <v>2.31</v>
+        <v>2.78</v>
       </c>
       <c r="AD75">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG75">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK75">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="O76">
-        <v>3.32</v>
+        <v>3.75</v>
       </c>
       <c r="P76">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q78">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R78">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S78">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T78">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U78">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V78">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W78">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y78">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z78">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB78">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AC78">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD78">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE78">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF78">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG78">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK78">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.68</v>
+        <v>2.12</v>
       </c>
       <c r="O79">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P79">
-        <v>4.09</v>
+        <v>2.87</v>
       </c>
       <c r="Q79">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="R79">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T79">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="U79">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="V79">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W79">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z79">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA79">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AB79">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC79">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AD79">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE79">
+        <v>1.28</v>
+      </c>
+      <c r="AF79">
+        <v>1.4</v>
+      </c>
+      <c r="AG79">
+        <v>2.8</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.25</v>
       </c>
-      <c r="AF79">
-        <v>1.43</v>
-      </c>
-      <c r="AG79">
-        <v>2.62</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.22</v>
-      </c>
       <c r="AK79">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="O80">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="P80">
-        <v>3.08</v>
+        <v>4.09</v>
       </c>
       <c r="Q80">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="R80">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T80">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="U80">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V80">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>4.3</v>
+        <v>5.55</v>
       </c>
       <c r="AA80">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB80">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AC80">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AD80">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AE80">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF80">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AG80">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK80">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O81">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="P81">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="Q81">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="R81">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="U81">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="V81">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="X81">
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AA81">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AB81">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AC81">
-        <v>1.72</v>
+        <v>2.38</v>
       </c>
       <c r="AD81">
-        <v>2.03</v>
+        <v>1.46</v>
       </c>
       <c r="AE81">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AF81">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AG81">
-        <v>3.34</v>
+        <v>2.39</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK81">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.67</v>
+        <v>2.02</v>
       </c>
       <c r="O82">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="P82">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="Q82">
-        <v>3.22</v>
+        <v>2.44</v>
       </c>
       <c r="R82">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T82">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="U82">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="V82">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Z82">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="AA82">
+        <v>1.25</v>
+      </c>
+      <c r="AB82">
+        <v>3.28</v>
+      </c>
+      <c r="AC82">
+        <v>1.72</v>
+      </c>
+      <c r="AD82">
+        <v>2.03</v>
+      </c>
+      <c r="AE82">
         <v>1.42</v>
       </c>
-      <c r="AB82">
-        <v>2.49</v>
-      </c>
-      <c r="AC82">
-        <v>2.15</v>
-      </c>
-      <c r="AD82">
-        <v>1.68</v>
-      </c>
-      <c r="AE82">
-        <v>1.21</v>
-      </c>
       <c r="AF82">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AG82">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P83">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q83">
-        <v>2.51</v>
+        <v>3.22</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U83">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V83">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W83">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z83">
-        <v>5.22</v>
+        <v>5.35</v>
       </c>
       <c r="AA83">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB83">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC83">
         <v>2.15</v>
       </c>
       <c r="AD83">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE83">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF83">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AG83">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>3.19</v>
+        <v>2.13</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="P86">
-        <v>2.17</v>
+        <v>3.04</v>
       </c>
       <c r="Q86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.3</v>
+        <v>3.19</v>
       </c>
       <c r="O87">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>2.89</v>
+        <v>2.17</v>
       </c>
       <c r="Q87">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T87">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="U87">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.47</v>
+        <v>3.08</v>
       </c>
       <c r="AA87">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB87">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC87">
-        <v>3.37</v>
+        <v>3.28</v>
       </c>
       <c r="AD87">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK87">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,81 +14979,81 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.76</v>
+        <v>3.34</v>
       </c>
       <c r="O90">
-        <v>3.8</v>
+        <v>4.07</v>
       </c>
       <c r="P90">
-        <v>3.98</v>
+        <v>2.13</v>
       </c>
       <c r="Q90">
-        <v>2.28</v>
+        <v>3.72</v>
       </c>
       <c r="R90">
+        <v>2.36</v>
+      </c>
+      <c r="S90">
+        <v>1.24</v>
+      </c>
+      <c r="T90">
+        <v>3.74</v>
+      </c>
+      <c r="U90">
         <v>2.23</v>
       </c>
-      <c r="S90">
+      <c r="V90">
+        <v>1.67</v>
+      </c>
+      <c r="W90">
+        <v>1.17</v>
+      </c>
+      <c r="X90">
+        <v>1</v>
+      </c>
+      <c r="Y90">
+        <v>1.13</v>
+      </c>
+      <c r="Z90">
+        <v>5.1</v>
+      </c>
+      <c r="AA90">
+        <v>1.5</v>
+      </c>
+      <c r="AB90">
+        <v>2.62</v>
+      </c>
+      <c r="AC90">
+        <v>2.2</v>
+      </c>
+      <c r="AD90">
+        <v>1.6</v>
+      </c>
+      <c r="AE90">
+        <v>1.29</v>
+      </c>
+      <c r="AF90">
+        <v>1.42</v>
+      </c>
+      <c r="AG90">
+        <v>2.69</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ90">
+        <v>1.75</v>
+      </c>
+      <c r="AK90">
         <v>1.3</v>
       </c>
-      <c r="T90">
-        <v>3.25</v>
-      </c>
-      <c r="U90">
-        <v>2.45</v>
-      </c>
-      <c r="V90">
-        <v>1.5</v>
-      </c>
-      <c r="W90">
-        <v>1.11</v>
-      </c>
-      <c r="X90">
-        <v>1.03</v>
-      </c>
-      <c r="Y90">
-        <v>1.18</v>
-      </c>
-      <c r="Z90">
-        <v>3.84</v>
-      </c>
-      <c r="AA90">
-        <v>1.69</v>
-      </c>
-      <c r="AB90">
-        <v>2.01</v>
-      </c>
-      <c r="AC90">
-        <v>2.7</v>
-      </c>
-      <c r="AD90">
-        <v>1.36</v>
-      </c>
-      <c r="AE90">
-        <v>1.11</v>
-      </c>
-      <c r="AF90">
-        <v>1.67</v>
-      </c>
-      <c r="AG90">
-        <v>2.1</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ90">
-        <v>1.19</v>
-      </c>
-      <c r="AK90">
-        <v>1.95</v>
-      </c>
       <c r="AL90">
         <v>0</v>
       </c>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S92">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="U92">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>4.02</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK92">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.87</v>
+        <v>4.84</v>
       </c>
       <c r="O93">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P93">
-        <v>3.57</v>
+        <v>1.63</v>
       </c>
       <c r="Q93">
-        <v>2.36</v>
+        <v>5.38</v>
       </c>
       <c r="R93">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="U93">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="V93">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="W93">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z93">
-        <v>5.07</v>
+        <v>4.02</v>
       </c>
       <c r="AA93">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AB93">
-        <v>2.49</v>
+        <v>2.09</v>
       </c>
       <c r="AC93">
-        <v>2.31</v>
+        <v>2.81</v>
       </c>
       <c r="AD93">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AF93">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AG93">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.25</v>
       </c>
       <c r="AK93">
-        <v>1.88</v>
+        <v>1.17</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="O94">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="P94">
-        <v>3.27</v>
+        <v>3.57</v>
       </c>
       <c r="Q94">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="R94">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="S94">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T94">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="V94">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="W94">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
+        <v>1.16</v>
+      </c>
+      <c r="Z94">
+        <v>5.07</v>
+      </c>
+      <c r="AA94">
+        <v>1.53</v>
+      </c>
+      <c r="AB94">
+        <v>2.49</v>
+      </c>
+      <c r="AC94">
+        <v>2.31</v>
+      </c>
+      <c r="AD94">
+        <v>1.61</v>
+      </c>
+      <c r="AE94">
         <v>1.25</v>
       </c>
-      <c r="Z94">
-        <v>3.88</v>
-      </c>
-      <c r="AA94">
-        <v>1.81</v>
-      </c>
-      <c r="AB94">
-        <v>1.93</v>
-      </c>
-      <c r="AC94">
-        <v>2.99</v>
-      </c>
-      <c r="AD94">
-        <v>1.38</v>
-      </c>
-      <c r="AE94">
-        <v>1.14</v>
-      </c>
       <c r="AF94">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AG94">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,31 +16120,31 @@
         </is>
       </c>
       <c r="N97">
-        <v>3.46</v>
+        <v>2.09</v>
       </c>
       <c r="O97">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>1.99</v>
+        <v>3.27</v>
       </c>
       <c r="Q97">
-        <v>3.48</v>
+        <v>2.65</v>
       </c>
       <c r="R97">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T97">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="U97">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="V97">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W97">
         <v>1.07</v>
@@ -16153,31 +16153,31 @@
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA97">
         <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC97">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD97">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AE97">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG97">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.97</v>
+        <v>3.46</v>
       </c>
       <c r="O98">
-        <v>4.25</v>
+        <v>3.48</v>
       </c>
       <c r="P98">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="Q98">
-        <v>5.25</v>
+        <v>3.48</v>
       </c>
       <c r="R98">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="S98">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="U98">
-        <v>2.02</v>
+        <v>2.47</v>
       </c>
       <c r="V98">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="W98">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z98">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="AA98">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="AB98">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF98">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Q100">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R100">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S100">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T100">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U100">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V100">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y100">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z100">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA100">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB100">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AC100">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AD100">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE100">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG100">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK100">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="O101">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="Q101">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="R101">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="S101">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="T101">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U101">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="V101">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z101">
-        <v>3.61</v>
+        <v>4.8</v>
       </c>
       <c r="AA101">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AB101">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="AC101">
-        <v>3.14</v>
+        <v>2.47</v>
       </c>
       <c r="AD101">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AE101">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK101">
-        <v>1.5</v>
+        <v>2.49</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17051,12 +17051,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q103">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R103">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S103">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T103">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U103">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V103">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W103">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y103">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z103">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA103">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB103">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC103">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AD103">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE103">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF103">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG103">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK103">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-30 17:05:00</t>
+          <t>2026-10-30 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-30 17:15:00</t>
+          <t>2026-10-30 17:05:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G105">
@@ -17433,55 +17433,55 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC105">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-30 19:00:00</t>
+          <t>2026-10-30 17:15:00</t>
         </is>
       </c>
     </row>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G106">
@@ -17596,55 +17596,55 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="R106">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="S106">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U106">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="V106">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
         <v>1.02</v>
       </c>
       <c r="Y106">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>5.68</v>
+        <v>3.2</v>
       </c>
       <c r="AA106">
-        <v>1.45</v>
+        <v>1.93</v>
       </c>
       <c r="AB106">
-        <v>2.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC106">
-        <v>2.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD106">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AF106">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG106">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK106">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="S108">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T108">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V108">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W108">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X108">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z108">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AG108">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK108">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-30 19:30:00</t>
+          <t>2026-10-30 19:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="O109">
-        <v>3.96</v>
+        <v>11.5</v>
       </c>
       <c r="P109">
-        <v>5.93</v>
+        <v>30</v>
       </c>
       <c r="Q109">
-        <v>2.28</v>
+        <v>1.29</v>
       </c>
       <c r="R109">
-        <v>2.28</v>
+        <v>3.58</v>
       </c>
       <c r="S109">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="T109">
-        <v>2.95</v>
+        <v>4.9</v>
       </c>
       <c r="U109">
-        <v>2.97</v>
+        <v>1.89</v>
       </c>
       <c r="V109">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="W109">
+        <v>1.22</v>
+      </c>
+      <c r="X109">
+        <v>1.01</v>
+      </c>
+      <c r="Y109">
         <v>1.05</v>
       </c>
-      <c r="X109">
-        <v>1.02</v>
-      </c>
-      <c r="Y109">
-        <v>1.32</v>
-      </c>
       <c r="Z109">
-        <v>3.41</v>
+        <v>6.55</v>
       </c>
       <c r="AA109">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AB109">
-        <v>1.75</v>
+        <v>3.16</v>
       </c>
       <c r="AC109">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD109">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AE109">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AF109">
-        <v>1.93</v>
+        <v>2.76</v>
       </c>
       <c r="AG109">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="AK109">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-30 20:00:00</t>
+          <t>2026-10-30 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,22 +21946,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G137">
@@ -22756,156 +22756,319 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Shkëndija Haraçinë</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tikveš</t>
+        </is>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>0</v>
+      </c>
+      <c r="R138">
+        <v>0</v>
+      </c>
+      <c r="S138">
+        <v>0</v>
+      </c>
+      <c r="T138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+      <c r="X138">
+        <v>0</v>
+      </c>
+      <c r="Y138">
+        <v>0</v>
+      </c>
+      <c r="Z138">
+        <v>0</v>
+      </c>
+      <c r="AA138">
+        <v>0</v>
+      </c>
+      <c r="AB138">
+        <v>0</v>
+      </c>
+      <c r="AC138">
+        <v>0</v>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138">
+        <v>0</v>
+      </c>
+      <c r="AF138">
+        <v>0</v>
+      </c>
+      <c r="AG138">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+      <c r="AK138">
+        <v>0</v>
+      </c>
+      <c r="AL138">
+        <v>0</v>
+      </c>
+      <c r="AM138">
+        <v>-1</v>
+      </c>
+      <c r="AN138">
+        <v>-1</v>
+      </c>
+      <c r="AO138">
+        <v>-1</v>
+      </c>
+      <c r="AP138">
+        <v>-1</v>
+      </c>
+      <c r="AQ138">
+        <v>0</v>
+      </c>
+      <c r="AR138">
+        <v>0</v>
+      </c>
+      <c r="AS138">
+        <v>0</v>
+      </c>
+      <c r="AT138">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>21:15</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>Curicó Unido</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Deportes Temuco</t>
         </is>
       </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-10-30 21:15:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G114">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G138">

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU139"/>
+  <dimension ref="A1:AU143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>2.9</v>
+      </c>
+      <c r="O4">
+        <v>3.3</v>
+      </c>
+      <c r="P4">
+        <v>2.35</v>
+      </c>
+      <c r="Q4">
         <v>3.4</v>
       </c>
-      <c r="O4">
-        <v>3.65</v>
-      </c>
-      <c r="P4">
-        <v>2.14</v>
-      </c>
-      <c r="Q4">
-        <v>3.58</v>
-      </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="U4">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
-        <v>3.44</v>
+        <v>3.14</v>
       </c>
       <c r="AD4">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
         <v>1.42</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W9">
         <v>0</v>
@@ -1809,16 +1809,16 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC9">
         <v>0</v>
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9.81</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W22">
         <v>0</v>
@@ -3928,16 +3928,16 @@
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3949,10 +3949,10 @@
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W29">
         <v>0</v>
@@ -5069,16 +5069,16 @@
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5090,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,22 +5208,22 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W30">
         <v>0</v>
@@ -5232,16 +5232,16 @@
         <v>0</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -5721,16 +5721,16 @@
         <v>0</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5742,10 +5742,10 @@
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,16 +5860,16 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5878,7 +5878,7 @@
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5887,22 +5887,22 @@
         <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.46</v>
+        <v>3.66</v>
       </c>
       <c r="AA34">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AC34">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE34">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.65</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="O35">
         <v>2.8</v>
       </c>
       <c r="P35">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="R35">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="S35">
         <v>1.55</v>
@@ -6035,7 +6035,7 @@
         <v>2.23</v>
       </c>
       <c r="U35">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="V35">
         <v>1.21</v>
@@ -6044,34 +6044,34 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Y35">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z35">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="AA35">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AB35">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC35">
-        <v>5.5</v>
+        <v>5.68</v>
       </c>
       <c r="AD35">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE35">
         <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O37">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>6.32</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="AA37">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC37">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD37">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
         <v>1.88</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G42">
@@ -7164,55 +7164,55 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7644,31 +7644,31 @@
         </is>
       </c>
       <c r="N45">
-        <v>4.84</v>
+        <v>4.94</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="P45">
         <v>1.62</v>
       </c>
       <c r="Q45">
-        <v>4.75</v>
+        <v>4.24</v>
       </c>
       <c r="R45">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T45">
         <v>3.4</v>
       </c>
       <c r="U45">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="V45">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="W45">
         <v>1.12</v>
@@ -7677,31 +7677,31 @@
         <v>1</v>
       </c>
       <c r="Y45">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="AA45">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB45">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AC45">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AD45">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE45">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF45">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG45">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK45">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O46">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="Q46">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
         <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="AA46">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AC46">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF46">
         <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q48">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="R48">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
         <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="V48">
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1</v>
       </c>
       <c r="Y48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
         <v>1.69</v>
       </c>
       <c r="AB48">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC48">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD48">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
         <v>2.2</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="O51">
-        <v>4.19</v>
+        <v>4.4</v>
       </c>
       <c r="P51">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Q51">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R51">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="S51">
         <v>1.32</v>
@@ -8661,16 +8661,16 @@
         <v>3.69</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AC51">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AD51">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
         <v>1.13</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>0</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,19 +9274,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P55">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q55">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="R55">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S55">
         <v>1.2</v>
@@ -9295,13 +9295,13 @@
         <v>4</v>
       </c>
       <c r="U55">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V55">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W55">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X55">
         <v>1.02</v>
@@ -9313,25 +9313,25 @@
         <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB55">
         <v>2.6</v>
       </c>
       <c r="AC55">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD55">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE55">
         <v>1.25</v>
       </c>
       <c r="AF55">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG55">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q56">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="R56">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S56">
         <v>1.22</v>
@@ -9458,16 +9458,16 @@
         <v>3.75</v>
       </c>
       <c r="U56">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="V56">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W56">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
         <v>1.18</v>
@@ -9476,22 +9476,22 @@
         <v>4.5</v>
       </c>
       <c r="AA56">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AB56">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC56">
         <v>2.38</v>
       </c>
       <c r="AD56">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE56">
         <v>1.18</v>
       </c>
       <c r="AF56">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG56">
         <v>2.38</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>2.03</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q57">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R57">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S57">
         <v>1.3</v>
@@ -9621,10 +9621,10 @@
         <v>3.25</v>
       </c>
       <c r="U57">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V57">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W57">
         <v>1.11</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>3.53</v>
+        <v>2.81</v>
       </c>
       <c r="O58">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="P58">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="Q58">
-        <v>3.84</v>
+        <v>3.59</v>
       </c>
       <c r="R58">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="S58">
         <v>1.23</v>
@@ -9793,34 +9793,34 @@
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
         <v>1.13</v>
       </c>
       <c r="Z58">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="AA58">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB58">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="AC58">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD58">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AE58">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF58">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,34 +9926,34 @@
         </is>
       </c>
       <c r="N59">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O59">
-        <v>7.11</v>
+        <v>6.8</v>
       </c>
       <c r="P59">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q59">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="R59">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="S59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T59">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U59">
         <v>1.93</v>
       </c>
       <c r="V59">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="W59">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X59">
         <v>1</v>
@@ -9962,22 +9962,22 @@
         <v>1.07</v>
       </c>
       <c r="Z59">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="AA59">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB59">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC59">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AD59">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AE59">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF59">
         <v>1.67</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="AK59">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,22 +10089,22 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="O60">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="P60">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="Q60">
         <v>3.64</v>
       </c>
       <c r="R60">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="S60">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="T60">
         <v>2.2</v>
@@ -10122,31 +10122,31 @@
         <v>1.1</v>
       </c>
       <c r="Y60">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z60">
         <v>2.25</v>
       </c>
       <c r="AA60">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AB60">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC60">
-        <v>5.85</v>
+        <v>6.25</v>
       </c>
       <c r="AD60">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE60">
         <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AG60">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10264,7 +10264,7 @@
         <v>3</v>
       </c>
       <c r="R61">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S61">
         <v>1.44</v>
@@ -10273,13 +10273,13 @@
         <v>2.32</v>
       </c>
       <c r="U61">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
       <c r="V61">
         <v>1.3</v>
       </c>
       <c r="W61">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X61">
         <v>1.06</v>
@@ -10288,10 +10288,10 @@
         <v>1.42</v>
       </c>
       <c r="Z61">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="AA61">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AB61">
         <v>1.51</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK61">
         <v>1.42</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10587,25 +10587,25 @@
         <v>4.44</v>
       </c>
       <c r="Q63">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R63">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T63">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U63">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V63">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X63">
         <v>1.02</v>
@@ -10635,7 +10635,7 @@
         <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,49 +10750,49 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="R64">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U64">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V64">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W64">
         <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z64">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AA64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB64">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC64">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AD64">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE64">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
         <v>1.5</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK64">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="O65">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P65">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="Q65">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R65">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="S65">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T65">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="U65">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V65">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="W65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X65">
         <v>1</v>
       </c>
       <c r="Y65">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>6.9</v>
+        <v>7.17</v>
       </c>
       <c r="AA65">
         <v>1.27</v>
       </c>
       <c r="AB65">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="AC65">
         <v>1.78</v>
       </c>
       <c r="AD65">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AE65">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF65">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG65">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,40 +11067,40 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="Q66">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U66">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W66">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
         <v>4.55</v>
@@ -11109,16 +11109,16 @@
         <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC66">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="AD66">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="AE66">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
         <v>1.5</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="O67">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P67">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="Q67">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="R67">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="S67">
         <v>1.36</v>
@@ -11251,7 +11251,7 @@
         <v>3.03</v>
       </c>
       <c r="U67">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
         <v>1.41</v>
@@ -11260,7 +11260,7 @@
         <v>1.07</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
         <v>1.28</v>
@@ -11269,10 +11269,10 @@
         <v>3.63</v>
       </c>
       <c r="AA67">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AB67">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC67">
         <v>3.26</v>
@@ -11287,7 +11287,7 @@
         <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK67">
         <v>1.72</v>
@@ -11405,7 +11405,7 @@
         <v>1.97</v>
       </c>
       <c r="R68">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="S68">
         <v>1.19</v>
@@ -11414,13 +11414,13 @@
         <v>3.8</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V68">
         <v>1.68</v>
       </c>
       <c r="W68">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11438,7 +11438,7 @@
         <v>2.66</v>
       </c>
       <c r="AC68">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD68">
         <v>1.71</v>
@@ -11447,10 +11447,10 @@
         <v>1.28</v>
       </c>
       <c r="AF68">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG68">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK68">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,40 +11565,40 @@
         <v>2.9</v>
       </c>
       <c r="Q69">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="R69">
         <v>2.28</v>
       </c>
       <c r="S69">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T69">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U69">
         <v>2.3</v>
       </c>
       <c r="V69">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W69">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z69">
-        <v>4.3</v>
+        <v>4.59</v>
       </c>
       <c r="AA69">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AB69">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AC69">
         <v>2.35</v>
@@ -11610,10 +11610,10 @@
         <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG69">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11719,55 +11719,55 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="O70">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="P70">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q70">
         <v>1.62</v>
       </c>
       <c r="R70">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="S70">
         <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="U70">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V70">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W70">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X70">
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z70">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA70">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AB70">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC70">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD70">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE70">
         <v>1.18</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK70">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N71">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="O72">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,37 +12208,37 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="O73">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P73">
-        <v>6.57</v>
+        <v>5.5</v>
       </c>
       <c r="Q73">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="R73">
         <v>2.3</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U73">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="V73">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
         <v>1.22</v>
@@ -12247,19 +12247,19 @@
         <v>3.5</v>
       </c>
       <c r="AA73">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB73">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AC73">
-        <v>2.88</v>
+        <v>3.01</v>
       </c>
       <c r="AD73">
         <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF73">
         <v>1.93</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P74">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q74">
         <v>3.84</v>
@@ -12389,22 +12389,22 @@
         <v>1.36</v>
       </c>
       <c r="T74">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U74">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V74">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z74">
         <v>3.08</v>
@@ -12416,10 +12416,10 @@
         <v>1.77</v>
       </c>
       <c r="AC74">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AD74">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE74">
         <v>1.05</v>
@@ -12444,7 +12444,7 @@
         <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O75">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="Q75">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R75">
         <v>2.2</v>
@@ -12570,28 +12570,28 @@
         <v>1.19</v>
       </c>
       <c r="Z75">
-        <v>3.74</v>
+        <v>3.98</v>
       </c>
       <c r="AA75">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AB75">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC75">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="AD75">
         <v>1.4</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF75">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG75">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK75">
         <v>1.73</v>
@@ -12697,19 +12697,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O76">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="Q76">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="R76">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="S76">
         <v>1.25</v>
@@ -12718,16 +12718,16 @@
         <v>3.7</v>
       </c>
       <c r="U76">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V76">
         <v>1.59</v>
       </c>
       <c r="W76">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
         <v>1.11</v>
@@ -12736,25 +12736,25 @@
         <v>4.95</v>
       </c>
       <c r="AA76">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AB76">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AC76">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
         <v>1.44</v>
       </c>
       <c r="AG76">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,55 +12869,55 @@
         <v>2.63</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P79">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q79">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R79">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S79">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T79">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V79">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="W79">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z79">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA79">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB79">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AC79">
         <v>2.01</v>
       </c>
       <c r="AD79">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE79">
         <v>1.28</v>
       </c>
       <c r="AF79">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG79">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.67</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O80">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>4.09</v>
+        <v>3.6</v>
       </c>
       <c r="Q80">
         <v>2.16</v>
@@ -13367,13 +13367,13 @@
         <v>1.16</v>
       </c>
       <c r="T80">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="U80">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V80">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="W80">
         <v>1.17</v>
@@ -13388,10 +13388,10 @@
         <v>5.55</v>
       </c>
       <c r="AA80">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB80">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC80">
         <v>2.06</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK80">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O81">
         <v>3.65</v>
@@ -13521,10 +13521,10 @@
         <v>3.08</v>
       </c>
       <c r="Q81">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R81">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
         <v>1.25</v>
@@ -13533,10 +13533,10 @@
         <v>3.5</v>
       </c>
       <c r="U81">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V81">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W81">
         <v>1.13</v>
@@ -13548,28 +13548,28 @@
         <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AA81">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AB81">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AC81">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AD81">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE81">
         <v>1.16</v>
       </c>
       <c r="AF81">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AK81">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,25 +13684,25 @@
         <v>2.94</v>
       </c>
       <c r="Q82">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R82">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="S82">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T82">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="U82">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V82">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="W82">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13714,19 +13714,19 @@
         <v>7</v>
       </c>
       <c r="AA82">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB82">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC82">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AD82">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AE82">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF82">
         <v>1.28</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
         <v>1.71</v>
@@ -13847,10 +13847,10 @@
         <v>2.2</v>
       </c>
       <c r="Q83">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R83">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S83">
         <v>1.2</v>
@@ -13859,7 +13859,7 @@
         <v>3.9</v>
       </c>
       <c r="U83">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
         <v>1.68</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK83">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14016,10 +14016,10 @@
         <v>2.38</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T84">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="U84">
         <v>2.2</v>
@@ -14028,7 +14028,7 @@
         <v>1.64</v>
       </c>
       <c r="W84">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
         <v>1.02</v>
@@ -14037,7 +14037,7 @@
         <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>5.22</v>
+        <v>5.15</v>
       </c>
       <c r="AA84">
         <v>1.43</v>
@@ -14052,7 +14052,7 @@
         <v>1.6</v>
       </c>
       <c r="AE84">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF84">
         <v>1.41</v>
@@ -14336,55 +14336,55 @@
         <v>3.04</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P87">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="Q87">
         <v>5</v>
@@ -14511,10 +14511,10 @@
         <v>2.68</v>
       </c>
       <c r="U87">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="V87">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W87">
         <v>1.04</v>
@@ -14526,7 +14526,7 @@
         <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA87">
         <v>2</v>
@@ -14544,7 +14544,7 @@
         <v>1.06</v>
       </c>
       <c r="AF87">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG87">
         <v>1.86</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK87">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,22 +14653,22 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O88">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="Q88">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R88">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S88">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
         <v>2.9</v>
@@ -14677,37 +14677,37 @@
         <v>2.7</v>
       </c>
       <c r="V88">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z88">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="AA88">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB88">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC88">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="AD88">
         <v>1.31</v>
       </c>
       <c r="AE88">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG88">
         <v>2</v>
@@ -14726,7 +14726,7 @@
         <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="O90">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="P90">
-        <v>2.13</v>
+        <v>2.01</v>
       </c>
       <c r="Q90">
-        <v>3.72</v>
+        <v>3.32</v>
       </c>
       <c r="R90">
         <v>2.36</v>
       </c>
       <c r="S90">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U90">
         <v>2.23</v>
       </c>
       <c r="V90">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="W90">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z90">
         <v>5.1</v>
       </c>
       <c r="AA90">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB90">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC90">
         <v>2.2</v>
       </c>
       <c r="AD90">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AE90">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF90">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG90">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AK90">
         <v>1.3</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="O91">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P91">
-        <v>3.98</v>
+        <v>4.6</v>
       </c>
       <c r="Q91">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="R91">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
         <v>1.3</v>
@@ -15163,13 +15163,13 @@
         <v>3.25</v>
       </c>
       <c r="U91">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V91">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15178,22 +15178,22 @@
         <v>1.18</v>
       </c>
       <c r="Z91">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AA91">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB91">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC91">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD91">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE91">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF91">
         <v>1.67</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK91">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>4.84</v>
+        <v>1.85</v>
       </c>
       <c r="O93">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P93">
-        <v>1.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q93">
-        <v>5.38</v>
+        <v>2.36</v>
       </c>
       <c r="R93">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="U93">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="V93">
+        <v>1.61</v>
+      </c>
+      <c r="W93">
+        <v>1.12</v>
+      </c>
+      <c r="X93">
+        <v>1.02</v>
+      </c>
+      <c r="Y93">
+        <v>1.11</v>
+      </c>
+      <c r="Z93">
+        <v>4.95</v>
+      </c>
+      <c r="AA93">
+        <v>1.46</v>
+      </c>
+      <c r="AB93">
+        <v>2.38</v>
+      </c>
+      <c r="AC93">
+        <v>2.25</v>
+      </c>
+      <c r="AD93">
+        <v>1.6</v>
+      </c>
+      <c r="AE93">
+        <v>1.25</v>
+      </c>
+      <c r="AF93">
         <v>1.47</v>
       </c>
-      <c r="W93">
-        <v>1.08</v>
-      </c>
-      <c r="X93">
-        <v>1</v>
-      </c>
-      <c r="Y93">
-        <v>1.23</v>
-      </c>
-      <c r="Z93">
-        <v>4.02</v>
-      </c>
-      <c r="AA93">
-        <v>1.72</v>
-      </c>
-      <c r="AB93">
-        <v>2.09</v>
-      </c>
-      <c r="AC93">
-        <v>2.81</v>
-      </c>
-      <c r="AD93">
-        <v>1.42</v>
-      </c>
-      <c r="AE93">
-        <v>1.12</v>
-      </c>
-      <c r="AF93">
-        <v>1.72</v>
-      </c>
       <c r="AG93">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="O94">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="P94">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="Q94">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="R94">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T94">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="U94">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="V94">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W94">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="Z94">
-        <v>5.07</v>
+        <v>3.97</v>
       </c>
       <c r="AA94">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB94">
-        <v>2.49</v>
+        <v>2.03</v>
       </c>
       <c r="AC94">
-        <v>2.31</v>
+        <v>2.83</v>
       </c>
       <c r="AD94">
+        <v>1.33</v>
+      </c>
+      <c r="AE94">
+        <v>1.09</v>
+      </c>
+      <c r="AF94">
         <v>1.61</v>
       </c>
-      <c r="AE94">
-        <v>1.25</v>
-      </c>
-      <c r="AF94">
-        <v>1.47</v>
-      </c>
       <c r="AG94">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK94">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.23</v>
+        <v>5</v>
       </c>
       <c r="O95">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="P95">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="Q95">
-        <v>3.91</v>
+        <v>5</v>
       </c>
       <c r="R95">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T95">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U95">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="AA95">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB95">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC95">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="AD95">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG95">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="O96">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="Q96">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R96">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S96">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V96">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
         <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>3.99</v>
+        <v>3.88</v>
       </c>
       <c r="AA96">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AB96">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AC96">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD96">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AE96">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG96">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.09</v>
+        <v>3.1</v>
       </c>
       <c r="O97">
         <v>3.5</v>
       </c>
       <c r="P97">
-        <v>3.27</v>
+        <v>2</v>
       </c>
       <c r="Q97">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="R97">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="S97">
         <v>1.3</v>
       </c>
       <c r="T97">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V97">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W97">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA97">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB97">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AC97">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AD97">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE97">
         <v>1.14</v>
       </c>
       <c r="AF97">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK97">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16283,34 +16283,34 @@
         </is>
       </c>
       <c r="N98">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="O98">
         <v>3.48</v>
       </c>
       <c r="P98">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q98">
         <v>3.48</v>
       </c>
       <c r="R98">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U98">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V98">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W98">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
         <v>1.01</v>
@@ -16322,10 +16322,10 @@
         <v>3.58</v>
       </c>
       <c r="AA98">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC98">
         <v>2.88</v>
@@ -16340,7 +16340,7 @@
         <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.2</v>
       </c>
       <c r="AK98">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,31 +16446,31 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.97</v>
+        <v>5.25</v>
       </c>
       <c r="O99">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="P99">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="Q99">
-        <v>5.25</v>
+        <v>3.98</v>
       </c>
       <c r="R99">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="S99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T99">
         <v>4</v>
       </c>
       <c r="U99">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="V99">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W99">
         <v>1.18</v>
@@ -16494,16 +16494,16 @@
         <v>2.03</v>
       </c>
       <c r="AD99">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE99">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF99">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG99">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.14</v>
+        <v>2.41</v>
       </c>
       <c r="AK99">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16772,31 +16772,31 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="O101">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P101">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q101">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R101">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="T101">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U101">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="V101">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W101">
         <v>1.13</v>
@@ -16805,28 +16805,28 @@
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AA101">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AB101">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AC101">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="AD101">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AE101">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF101">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG101">
         <v>2.12</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK101">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,22 +16935,22 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
         <v>2.7</v>
       </c>
       <c r="Q102">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R102">
         <v>2.06</v>
       </c>
       <c r="S102">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T102">
         <v>3</v>
@@ -16968,31 +16968,31 @@
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="AA102">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB102">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC102">
         <v>3.14</v>
       </c>
       <c r="AD102">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE102">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
         <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17261,16 +17261,16 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="P104">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q104">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="R104">
         <v>2.21</v>
@@ -17303,19 +17303,19 @@
         <v>1.75</v>
       </c>
       <c r="AB104">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC104">
-        <v>2.53</v>
+        <v>2.61</v>
       </c>
       <c r="AD104">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE104">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF104">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG104">
         <v>2.32</v>
@@ -17334,7 +17334,7 @@
         <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,25 +17587,25 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q106">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R106">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S106">
         <v>1.36</v>
       </c>
       <c r="T106">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="U106">
         <v>2.7</v>
@@ -17614,34 +17614,34 @@
         <v>1.4</v>
       </c>
       <c r="W106">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X106">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z106">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA106">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB106">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC106">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AD106">
         <v>1.33</v>
       </c>
       <c r="AE106">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF106">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG106">
         <v>1.85</v>
@@ -17750,22 +17750,22 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q107">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R107">
-        <v>2.97</v>
+        <v>2.69</v>
       </c>
       <c r="S107">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T107">
         <v>4</v>
@@ -17774,34 +17774,34 @@
         <v>2</v>
       </c>
       <c r="V107">
+        <v>1.75</v>
+      </c>
+      <c r="W107">
+        <v>1.2</v>
+      </c>
+      <c r="X107">
+        <v>1.01</v>
+      </c>
+      <c r="Y107">
+        <v>1.11</v>
+      </c>
+      <c r="Z107">
+        <v>5.81</v>
+      </c>
+      <c r="AA107">
+        <v>1.42</v>
+      </c>
+      <c r="AB107">
+        <v>2.65</v>
+      </c>
+      <c r="AC107">
+        <v>2.08</v>
+      </c>
+      <c r="AD107">
         <v>1.7</v>
       </c>
-      <c r="W107">
-        <v>1.18</v>
-      </c>
-      <c r="X107">
-        <v>1.02</v>
-      </c>
-      <c r="Y107">
-        <v>1.13</v>
-      </c>
-      <c r="Z107">
-        <v>5.68</v>
-      </c>
-      <c r="AA107">
-        <v>1.45</v>
-      </c>
-      <c r="AB107">
-        <v>2.55</v>
-      </c>
-      <c r="AC107">
-        <v>2.17</v>
-      </c>
-      <c r="AD107">
-        <v>1.67</v>
-      </c>
       <c r="AE107">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF107">
         <v>1.75</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK107">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="O109">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="P109">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="Q109">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="R109">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="S109">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T109">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="U109">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="V109">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="W109">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X109">
         <v>1.01</v>
       </c>
       <c r="Y109">
+        <v>1.26</v>
+      </c>
+      <c r="Z109">
+        <v>3.2</v>
+      </c>
+      <c r="AA109">
+        <v>1.89</v>
+      </c>
+      <c r="AB109">
+        <v>1.78</v>
+      </c>
+      <c r="AC109">
+        <v>3.28</v>
+      </c>
+      <c r="AD109">
+        <v>1.25</v>
+      </c>
+      <c r="AE109">
         <v>1.05</v>
       </c>
-      <c r="Z109">
-        <v>6.55</v>
-      </c>
-      <c r="AA109">
-        <v>1.33</v>
-      </c>
-      <c r="AB109">
-        <v>3.16</v>
-      </c>
-      <c r="AC109">
-        <v>1.9</v>
-      </c>
-      <c r="AD109">
-        <v>1.77</v>
-      </c>
-      <c r="AE109">
-        <v>1.31</v>
-      </c>
       <c r="AF109">
-        <v>2.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG109">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AK109">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="O110">
-        <v>3.96</v>
+        <v>11.5</v>
       </c>
       <c r="P110">
-        <v>5.93</v>
+        <v>30</v>
       </c>
       <c r="Q110">
-        <v>2.28</v>
+        <v>1.3</v>
       </c>
       <c r="R110">
-        <v>2.28</v>
+        <v>3.6</v>
       </c>
       <c r="S110">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="T110">
-        <v>2.95</v>
+        <v>4.8</v>
       </c>
       <c r="U110">
-        <v>2.97</v>
+        <v>1.91</v>
       </c>
       <c r="V110">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="W110">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="Z110">
-        <v>3.41</v>
+        <v>6.55</v>
       </c>
       <c r="AA110">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AB110">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC110">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="AD110">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AE110">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AF110">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="AG110">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AK110">
-        <v>2.18</v>
+        <v>10</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-30 20:00:00</t>
+          <t>2026-10-30 19:30:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 20:00:00</t>
         </is>
       </c>
     </row>
@@ -18681,27 +18681,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 20:30:00</t>
         </is>
       </c>
     </row>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,13 +20032,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q121">
         <v>0</v>
@@ -20071,10 +20071,10 @@
         <v>0</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC121">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -20358,64 +20358,64 @@
         </is>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P123">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R123">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S123">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T123">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U123">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V123">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W123">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X123">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z123">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA123">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB123">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC123">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AD123">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE123">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF123">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG123">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -20428,10 +20428,10 @@
         </is>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK123">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AL123">
         <v>0</v>
@@ -20521,64 +20521,64 @@
         </is>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P124">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q124">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R124">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S124">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T124">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U124">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V124">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W124">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X124">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y124">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD124">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE124">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF124">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG124">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK124">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21049,10 +21049,10 @@
         <v>0</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q128">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R128">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S128">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T128">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U128">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V128">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W128">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X128">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y128">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z128">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD128">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE128">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF128">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG128">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK128">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G129">
@@ -21345,55 +21345,55 @@
         <v>0</v>
       </c>
       <c r="Q129">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R129">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S129">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T129">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U129">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V129">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W129">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X129">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y129">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z129">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC129">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD129">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE129">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF129">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG129">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK129">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q130">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R130">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S130">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T130">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U130">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V130">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X130">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y130">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z130">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC130">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD130">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE130">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF130">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG130">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK130">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P131">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q131">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S131">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T131">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U131">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V131">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W131">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X131">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y131">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z131">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA131">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB131">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC131">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD131">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE131">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF131">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG131">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK131">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O132">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P132">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q132">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="AA132">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB132">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O133">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P133">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q133">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R133">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S133">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T133">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U133">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V133">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W133">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X133">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y133">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z133">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA133">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB133">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC133">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD133">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE133">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF133">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG133">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK133">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22109,22 +22109,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P134">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q134">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R134">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T134">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U134">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V134">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W134">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z134">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA134">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB134">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC134">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD134">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE134">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF134">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG134">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22272,22 +22272,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,64 +22314,64 @@
         </is>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O135">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P135">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q135">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R135">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S135">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T135">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U135">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V135">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W135">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X135">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y135">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z135">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA135">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB135">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC135">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD135">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE135">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF135">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG135">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK135">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22435,22 +22435,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q136">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R136">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S136">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U136">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V136">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W136">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X136">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z136">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA136">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD136">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE136">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF136">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG136">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK136">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G138">
@@ -22919,158 +22919,810 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>FK Bashkimi Kumanovo</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Aresimi</t>
+        </is>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>0</v>
+      </c>
+      <c r="R139">
+        <v>0</v>
+      </c>
+      <c r="S139">
+        <v>0</v>
+      </c>
+      <c r="T139">
+        <v>0</v>
+      </c>
+      <c r="U139">
+        <v>0</v>
+      </c>
+      <c r="V139">
+        <v>0</v>
+      </c>
+      <c r="W139">
+        <v>0</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+      <c r="AA139">
+        <v>0</v>
+      </c>
+      <c r="AB139">
+        <v>0</v>
+      </c>
+      <c r="AC139">
+        <v>0</v>
+      </c>
+      <c r="AD139">
+        <v>0</v>
+      </c>
+      <c r="AE139">
+        <v>0</v>
+      </c>
+      <c r="AF139">
+        <v>0</v>
+      </c>
+      <c r="AG139">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ139">
+        <v>0</v>
+      </c>
+      <c r="AK139">
+        <v>0</v>
+      </c>
+      <c r="AL139">
+        <v>0</v>
+      </c>
+      <c r="AM139">
+        <v>-1</v>
+      </c>
+      <c r="AN139">
+        <v>-1</v>
+      </c>
+      <c r="AO139">
+        <v>-1</v>
+      </c>
+      <c r="AP139">
+        <v>-1</v>
+      </c>
+      <c r="AQ139">
+        <v>0</v>
+      </c>
+      <c r="AR139">
+        <v>0</v>
+      </c>
+      <c r="AS139">
+        <v>0</v>
+      </c>
+      <c r="AT139">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Shkëndija Haraçinë</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Tikveš</t>
+        </is>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>0</v>
+      </c>
+      <c r="R140">
+        <v>0</v>
+      </c>
+      <c r="S140">
+        <v>0</v>
+      </c>
+      <c r="T140">
+        <v>0</v>
+      </c>
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140">
+        <v>0</v>
+      </c>
+      <c r="W140">
+        <v>0</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+      <c r="AA140">
+        <v>0</v>
+      </c>
+      <c r="AB140">
+        <v>0</v>
+      </c>
+      <c r="AC140">
+        <v>0</v>
+      </c>
+      <c r="AD140">
+        <v>0</v>
+      </c>
+      <c r="AE140">
+        <v>0</v>
+      </c>
+      <c r="AF140">
+        <v>0</v>
+      </c>
+      <c r="AG140">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ140">
+        <v>0</v>
+      </c>
+      <c r="AK140">
+        <v>0</v>
+      </c>
+      <c r="AL140">
+        <v>0</v>
+      </c>
+      <c r="AM140">
+        <v>-1</v>
+      </c>
+      <c r="AN140">
+        <v>-1</v>
+      </c>
+      <c r="AO140">
+        <v>-1</v>
+      </c>
+      <c r="AP140">
+        <v>-1</v>
+      </c>
+      <c r="AQ140">
+        <v>0</v>
+      </c>
+      <c r="AR140">
+        <v>0</v>
+      </c>
+      <c r="AS140">
+        <v>0</v>
+      </c>
+      <c r="AT140">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FYR Macedonia First Football League</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Bregalnica Štip</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Shkendija</t>
+        </is>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>0</v>
+      </c>
+      <c r="R141">
+        <v>0</v>
+      </c>
+      <c r="S141">
+        <v>0</v>
+      </c>
+      <c r="T141">
+        <v>0</v>
+      </c>
+      <c r="U141">
+        <v>0</v>
+      </c>
+      <c r="V141">
+        <v>0</v>
+      </c>
+      <c r="W141">
+        <v>0</v>
+      </c>
+      <c r="X141">
+        <v>0</v>
+      </c>
+      <c r="Y141">
+        <v>0</v>
+      </c>
+      <c r="Z141">
+        <v>0</v>
+      </c>
+      <c r="AA141">
+        <v>0</v>
+      </c>
+      <c r="AB141">
+        <v>0</v>
+      </c>
+      <c r="AC141">
+        <v>0</v>
+      </c>
+      <c r="AD141">
+        <v>0</v>
+      </c>
+      <c r="AE141">
+        <v>0</v>
+      </c>
+      <c r="AF141">
+        <v>0</v>
+      </c>
+      <c r="AG141">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ141">
+        <v>0</v>
+      </c>
+      <c r="AK141">
+        <v>0</v>
+      </c>
+      <c r="AL141">
+        <v>0</v>
+      </c>
+      <c r="AM141">
+        <v>-1</v>
+      </c>
+      <c r="AN141">
+        <v>-1</v>
+      </c>
+      <c r="AO141">
+        <v>-1</v>
+      </c>
+      <c r="AP141">
+        <v>-1</v>
+      </c>
+      <c r="AQ141">
+        <v>0</v>
+      </c>
+      <c r="AR141">
+        <v>0</v>
+      </c>
+      <c r="AS141">
+        <v>0</v>
+      </c>
+      <c r="AT141">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>2026-10-30 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>21:15</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Chile Primera B</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>Curicó Unido</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>Deportes Temuco</t>
         </is>
       </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>0</v>
+      </c>
+      <c r="R142">
+        <v>0</v>
+      </c>
+      <c r="S142">
+        <v>0</v>
+      </c>
+      <c r="T142">
+        <v>0</v>
+      </c>
+      <c r="U142">
+        <v>0</v>
+      </c>
+      <c r="V142">
+        <v>0</v>
+      </c>
+      <c r="W142">
+        <v>0</v>
+      </c>
+      <c r="X142">
+        <v>0</v>
+      </c>
+      <c r="Y142">
+        <v>0</v>
+      </c>
+      <c r="Z142">
+        <v>0</v>
+      </c>
+      <c r="AA142">
+        <v>0</v>
+      </c>
+      <c r="AB142">
+        <v>0</v>
+      </c>
+      <c r="AC142">
+        <v>0</v>
+      </c>
+      <c r="AD142">
+        <v>0</v>
+      </c>
+      <c r="AE142">
+        <v>0</v>
+      </c>
+      <c r="AF142">
+        <v>0</v>
+      </c>
+      <c r="AG142">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ142">
+        <v>0</v>
+      </c>
+      <c r="AK142">
+        <v>0</v>
+      </c>
+      <c r="AL142">
+        <v>0</v>
+      </c>
+      <c r="AM142">
+        <v>-1</v>
+      </c>
+      <c r="AN142">
+        <v>-1</v>
+      </c>
+      <c r="AO142">
+        <v>-1</v>
+      </c>
+      <c r="AP142">
+        <v>-1</v>
+      </c>
+      <c r="AQ142">
+        <v>0</v>
+      </c>
+      <c r="AR142">
+        <v>0</v>
+      </c>
+      <c r="AS142">
+        <v>0</v>
+      </c>
+      <c r="AT142">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
         <is>
           <t>2026-10-30 21:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N143">
+        <v>1.97</v>
+      </c>
+      <c r="O143">
+        <v>3.28</v>
+      </c>
+      <c r="P143">
+        <v>2.99</v>
+      </c>
+      <c r="Q143">
+        <v>2.7</v>
+      </c>
+      <c r="R143">
+        <v>2.2</v>
+      </c>
+      <c r="S143">
+        <v>1.35</v>
+      </c>
+      <c r="T143">
+        <v>3</v>
+      </c>
+      <c r="U143">
+        <v>2.62</v>
+      </c>
+      <c r="V143">
+        <v>1.4</v>
+      </c>
+      <c r="W143">
+        <v>1.1</v>
+      </c>
+      <c r="X143">
+        <v>1.01</v>
+      </c>
+      <c r="Y143">
+        <v>1.23</v>
+      </c>
+      <c r="Z143">
+        <v>3.42</v>
+      </c>
+      <c r="AA143">
+        <v>1.83</v>
+      </c>
+      <c r="AB143">
+        <v>1.84</v>
+      </c>
+      <c r="AC143">
+        <v>3.08</v>
+      </c>
+      <c r="AD143">
+        <v>1.28</v>
+      </c>
+      <c r="AE143">
+        <v>1.06</v>
+      </c>
+      <c r="AF143">
+        <v>1.7</v>
+      </c>
+      <c r="AG143">
+        <v>2.05</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ143">
+        <v>1.3</v>
+      </c>
+      <c r="AK143">
+        <v>1.62</v>
+      </c>
+      <c r="AL143">
+        <v>0</v>
+      </c>
+      <c r="AM143">
+        <v>-1</v>
+      </c>
+      <c r="AN143">
+        <v>-1</v>
+      </c>
+      <c r="AO143">
+        <v>-1</v>
+      </c>
+      <c r="AP143">
+        <v>-1</v>
+      </c>
+      <c r="AQ143">
+        <v>0</v>
+      </c>
+      <c r="AR143">
+        <v>0</v>
+      </c>
+      <c r="AS143">
+        <v>0</v>
+      </c>
+      <c r="AT143">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>2026-10-30 22:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AK11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="R31">
         <v>2.45</v>
@@ -5398,28 +5398,28 @@
         <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
       <c r="AA31">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB31">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AC31">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AD31">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
         <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
+        <v>1.19</v>
+      </c>
+      <c r="AK31">
         <v>1.25</v>
-      </c>
-      <c r="AK31">
-        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5878,7 +5878,7 @@
         <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -5924,7 +5924,7 @@
         <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O35">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R35">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="S35">
         <v>1.55</v>
@@ -6346,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q37">
         <v>1.89</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R42">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="S42">
         <v>1.17</v>
@@ -7209,7 +7209,7 @@
         <v>1.39</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG42">
         <v>2.77</v>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="N53">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="O53">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P53">
         <v>2.11</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q54">
         <v>2.1</v>
@@ -9150,10 +9150,10 @@
         <v>4.66</v>
       </c>
       <c r="AA54">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB54">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC54">
         <v>2.41</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="O58">
-        <v>3.71</v>
+        <v>3.9</v>
       </c>
       <c r="P58">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q58">
         <v>3.59</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O60">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P60">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q60">
         <v>3.64</v>
@@ -10252,28 +10252,28 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="P61">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R61">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="S61">
         <v>1.44</v>
       </c>
       <c r="T61">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="U61">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="V61">
         <v>1.3</v>
@@ -10282,31 +10282,31 @@
         <v>1.03</v>
       </c>
       <c r="X61">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y61">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z61">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="AA61">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="AB61">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC61">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AD61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE61">
         <v>1.01</v>
       </c>
       <c r="AF61">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG61">
         <v>1.73</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK61">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1.62</v>
       </c>
       <c r="R69">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="S69">
         <v>1.25</v>
@@ -11580,7 +11580,7 @@
         <v>2.2</v>
       </c>
       <c r="V69">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W69">
         <v>1.15</v>
@@ -11592,19 +11592,19 @@
         <v>1.12</v>
       </c>
       <c r="Z69">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA69">
         <v>1.52</v>
       </c>
       <c r="AB69">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC69">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AD69">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE69">
         <v>1.18</v>
@@ -11613,7 +11613,7 @@
         <v>2</v>
       </c>
       <c r="AG69">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.05</v>
       </c>
       <c r="AK69">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="O85">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="P85">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="Q85">
         <v>2.62</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK85">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14825,16 +14825,16 @@
         <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="R89">
         <v>2.62</v>
       </c>
       <c r="S89">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="U89">
         <v>2.23</v>
@@ -14855,19 +14855,19 @@
         <v>5.1</v>
       </c>
       <c r="AA89">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB89">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="AC89">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD89">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE89">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF89">
         <v>1.44</v>
@@ -14889,7 +14889,7 @@
         <v>1.75</v>
       </c>
       <c r="AK89">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T91">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U91">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V91">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W91">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y91">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z91">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD91">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE91">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AF91">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG91">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK91">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
+        <v>3.1</v>
+      </c>
+      <c r="O95">
+        <v>3.5</v>
+      </c>
+      <c r="P95">
         <v>2</v>
       </c>
-      <c r="O95">
-        <v>3.4</v>
-      </c>
-      <c r="P95">
-        <v>3.25</v>
-      </c>
       <c r="Q95">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="R95">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V95">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AB95">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="AC95">
-        <v>2.92</v>
+        <v>2.57</v>
       </c>
       <c r="AD95">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="AE95">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG95">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
+        <v>1.73</v>
+      </c>
+      <c r="AK95">
         <v>1.3</v>
-      </c>
-      <c r="AK95">
-        <v>1.7</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P96">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="Q96">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="R96">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V96">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z96">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="AA96">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB96">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AC96">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="AD96">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG96">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16289,7 +16289,7 @@
         <v>4.6</v>
       </c>
       <c r="P98">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Q98">
         <v>3.98</v>
@@ -16325,7 +16325,7 @@
         <v>1.4</v>
       </c>
       <c r="AB98">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC98">
         <v>2.03</v>
@@ -16334,7 +16334,7 @@
         <v>1.67</v>
       </c>
       <c r="AE98">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF98">
         <v>1.51</v>
@@ -18091,16 +18091,16 @@
         <v>3.6</v>
       </c>
       <c r="S109">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T109">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U109">
         <v>1.91</v>
       </c>
       <c r="V109">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="W109">
         <v>1.2</v>
@@ -18115,10 +18115,10 @@
         <v>6.55</v>
       </c>
       <c r="AA109">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AB109">
-        <v>2.6</v>
+        <v>3.13</v>
       </c>
       <c r="AC109">
         <v>1.9</v>
@@ -18130,10 +18130,10 @@
         <v>1.34</v>
       </c>
       <c r="AF109">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AG109">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,7 +976,7 @@
         <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
         <v>2.67</v>
@@ -991,28 +991,28 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB4">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC4">
         <v>3.14</v>
       </c>
       <c r="AD4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
         <v>1.73</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AK4">
         <v>1.42</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>5.07</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
@@ -6186,22 +6186,22 @@
         <v>2.51</v>
       </c>
       <c r="Q36">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="R36">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="S36">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T36">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="U36">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6222,19 +6222,19 @@
         <v>1.69</v>
       </c>
       <c r="AC36">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG36">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.32</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7647,10 +7647,10 @@
         <v>5</v>
       </c>
       <c r="O45">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q45">
         <v>4.24</v>
@@ -7683,10 +7683,10 @@
         <v>3.95</v>
       </c>
       <c r="AA45">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB45">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC45">
         <v>2.56</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O47">
         <v>3.6</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
         <v>1.62</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O48">
         <v>3.3</v>
       </c>
       <c r="P48">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
         <v>2.55</v>
@@ -8501,7 +8501,7 @@
         <v>1.75</v>
       </c>
       <c r="AB50">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
         <v>2.74</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="O51">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P51">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Q51">
         <v>1.87</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="O55">
         <v>3.7</v>
@@ -9313,7 +9313,7 @@
         <v>5.5</v>
       </c>
       <c r="AA55">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB55">
         <v>2.6</v>
@@ -9325,7 +9325,7 @@
         <v>1.68</v>
       </c>
       <c r="AE55">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF55">
         <v>1.4</v>
@@ -9446,52 +9446,52 @@
         <v>3.9</v>
       </c>
       <c r="Q56">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R56">
         <v>2.31</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T56">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U56">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="V56">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W56">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X56">
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z56">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA56">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB56">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC56">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD56">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE56">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG56">
         <v>2.38</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK56">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -10427,7 +10427,7 @@
         <v>2.2</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S62">
         <v>1.26</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>2.05</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P65">
         <v>3.02</v>
@@ -10943,7 +10943,7 @@
         <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB65">
         <v>2.33</v>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11254,10 +11254,10 @@
         <v>2</v>
       </c>
       <c r="V67">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W67">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X67">
         <v>1.01</v>
@@ -11284,7 +11284,7 @@
         <v>1.28</v>
       </c>
       <c r="AF67">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG67">
         <v>2.4</v>
@@ -11423,7 +11423,7 @@
         <v>1.13</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
         <v>1.18</v>
@@ -11450,7 +11450,7 @@
         <v>1.49</v>
       </c>
       <c r="AG68">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK71">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>3</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
         <v>2.15</v>
@@ -12072,7 +12072,7 @@
         <v>1.37</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
         <v>1.01</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
         <v>1.34</v>
@@ -12226,7 +12226,7 @@
         <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="U73">
         <v>2.5</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O74">
         <v>3.5</v>
       </c>
       <c r="P74">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q74">
         <v>2.6</v>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O75">
         <v>3.25</v>
@@ -12543,7 +12543,7 @@
         <v>2.95</v>
       </c>
       <c r="Q75">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="R75">
         <v>2.17</v>
@@ -12564,7 +12564,7 @@
         <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
         <v>1.33</v>
@@ -12576,10 +12576,10 @@
         <v>2.05</v>
       </c>
       <c r="AB75">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC75">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD75">
         <v>1.28</v>
@@ -12607,7 +12607,7 @@
         <v>1.33</v>
       </c>
       <c r="AK75">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13026,10 +13026,10 @@
         <v>2.15</v>
       </c>
       <c r="O78">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P78">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q78">
         <v>2.6</v>
@@ -13062,7 +13062,7 @@
         <v>6</v>
       </c>
       <c r="AA78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB78">
         <v>2.75</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P79">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q79">
-        <v>2.16</v>
+        <v>2.54</v>
       </c>
       <c r="R79">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U79">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="V79">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W79">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X79">
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z79">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA79">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB79">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC79">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AD79">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE79">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF79">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AG79">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AK79">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="O80">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P80">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q80">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T80">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U80">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="V80">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="AA80">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB80">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC80">
-        <v>2.44</v>
+        <v>2.06</v>
       </c>
       <c r="AD80">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE80">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF80">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AG80">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O81">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P81">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="Q81">
         <v>2.4</v>
@@ -13530,7 +13530,7 @@
         <v>1.13</v>
       </c>
       <c r="T81">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="U81">
         <v>1.85</v>
@@ -13539,7 +13539,7 @@
         <v>1.91</v>
       </c>
       <c r="W81">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X81">
         <v>1.01</v>
@@ -13551,10 +13551,10 @@
         <v>7</v>
       </c>
       <c r="AA81">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB81">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AC81">
         <v>1.74</v>
@@ -13729,10 +13729,10 @@
         <v>1.21</v>
       </c>
       <c r="AF82">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>2.38</v>
       </c>
       <c r="S83">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T83">
         <v>3.85</v>
@@ -13862,7 +13862,7 @@
         <v>2.2</v>
       </c>
       <c r="V83">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W83">
         <v>1.15</v>
@@ -13895,7 +13895,7 @@
         <v>1.41</v>
       </c>
       <c r="AG83">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.18</v>
       </c>
       <c r="AK83">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>3.1</v>
       </c>
       <c r="Q87">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R87">
         <v>2.1</v>
@@ -14563,7 +14563,7 @@
         <v>1.3</v>
       </c>
       <c r="AK87">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14834,7 +14834,7 @@
         <v>1.22</v>
       </c>
       <c r="T89">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U89">
         <v>2.23</v>
@@ -14858,7 +14858,7 @@
         <v>1.43</v>
       </c>
       <c r="AB89">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC89">
         <v>2.18</v>
@@ -14889,7 +14889,7 @@
         <v>1.75</v>
       </c>
       <c r="AK89">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15151,55 +15151,55 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P93">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="Q93">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="R93">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T93">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="U93">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V93">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X93">
         <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="Z93">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="AA93">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AB93">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AC93">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="AD93">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF93">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
-        <v>1.62</v>
+        <v>1.15</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,28 +15631,28 @@
         </is>
       </c>
       <c r="N94">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O94">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P94">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="Q94">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R94">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S94">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U94">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V94">
         <v>1.53</v>
@@ -15661,34 +15661,34 @@
         <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z94">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AA94">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB94">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="AC94">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="AD94">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AE94">
         <v>1.14</v>
       </c>
       <c r="AF94">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG94">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK94">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P95">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="Q95">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="R95">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W95">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z95">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="AA95">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AB95">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AC95">
-        <v>2.57</v>
+        <v>2.92</v>
       </c>
       <c r="AD95">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AG95">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,31 +15957,31 @@
         </is>
       </c>
       <c r="N96">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O96">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P96">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q96">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R96">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S96">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="U96">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V96">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W96">
         <v>1.11</v>
@@ -15990,31 +15990,31 @@
         <v>1.03</v>
       </c>
       <c r="Y96">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
-        <v>3.88</v>
+        <v>3.97</v>
       </c>
       <c r="AA96">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB96">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AC96">
-        <v>2.92</v>
+        <v>2.83</v>
       </c>
       <c r="AD96">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF96">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG96">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,7 +16123,7 @@
         <v>3.5</v>
       </c>
       <c r="O97">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
         <v>2</v>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="O100">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="P100">
         <v>6</v>
@@ -16630,10 +16630,10 @@
         <v>4</v>
       </c>
       <c r="U100">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V100">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W100">
         <v>1.13</v>
@@ -16651,7 +16651,7 @@
         <v>1.47</v>
       </c>
       <c r="AB100">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AC100">
         <v>2.38</v>
@@ -16663,7 +16663,7 @@
         <v>1.22</v>
       </c>
       <c r="AF100">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG100">
         <v>2.12</v>
@@ -16772,10 +16772,10 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P101">
         <v>2.5</v>
@@ -17264,7 +17264,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="O104">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="P104">
         <v>1.3</v>
@@ -17276,7 +17276,7 @@
         <v>2.51</v>
       </c>
       <c r="S104">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
         <v>3.32</v>
@@ -17433,7 +17433,7 @@
         <v>4.8</v>
       </c>
       <c r="Q105">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R105">
         <v>2.33</v>
@@ -17445,7 +17445,7 @@
         <v>3.01</v>
       </c>
       <c r="U105">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="V105">
         <v>1.4</v>
@@ -17481,7 +17481,7 @@
         <v>1.88</v>
       </c>
       <c r="AG105">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>8.5</v>
       </c>
       <c r="Q106">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R106">
         <v>2.69</v>
@@ -17605,10 +17605,10 @@
         <v>1.2</v>
       </c>
       <c r="T106">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U106">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V106">
         <v>1.75</v>
@@ -17620,25 +17620,25 @@
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z106">
-        <v>5.81</v>
+        <v>5.3</v>
       </c>
       <c r="AA106">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB106">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC106">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AD106">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AE106">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF106">
         <v>1.75</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="O109">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="P109">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Q109">
         <v>1.3</v>
@@ -18254,7 +18254,7 @@
         <v>2.13</v>
       </c>
       <c r="S110">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
         <v>2.66</v>
@@ -18263,10 +18263,10 @@
         <v>2.66</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W110">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X110">
         <v>1.03</v>
@@ -18293,10 +18293,10 @@
         <v>1.09</v>
       </c>
       <c r="AF110">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         <v>4.05</v>
       </c>
       <c r="Q117">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R117">
         <v>2.15</v>
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G119">
@@ -19715,55 +19715,55 @@
         <v>3.4</v>
       </c>
       <c r="Q119">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R119">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S119">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T119">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U119">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V119">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA119">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AB119">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="O120">
         <v>3</v>
       </c>
       <c r="P120">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P121">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q121">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R121">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S121">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T121">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U121">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V121">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W121">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X121">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y121">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z121">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA121">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB121">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC121">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD121">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE121">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF121">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG121">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK121">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G125">
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G126">
@@ -20951,7 +20951,7 @@
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 21:15:00</t>
         </is>
       </c>
     </row>
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q127">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R127">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S127">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T127">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U127">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V127">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W127">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X127">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z127">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC127">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD127">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE127">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF127">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK127">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21113,169 +21113,6 @@
         <v>0</v>
       </c>
       <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>1.97</v>
-      </c>
-      <c r="O128">
-        <v>3.28</v>
-      </c>
-      <c r="P128">
-        <v>2.99</v>
-      </c>
-      <c r="Q128">
-        <v>2.7</v>
-      </c>
-      <c r="R128">
-        <v>2.2</v>
-      </c>
-      <c r="S128">
-        <v>1.33</v>
-      </c>
-      <c r="T128">
-        <v>2.85</v>
-      </c>
-      <c r="U128">
-        <v>2.64</v>
-      </c>
-      <c r="V128">
-        <v>1.38</v>
-      </c>
-      <c r="W128">
-        <v>1.04</v>
-      </c>
-      <c r="X128">
-        <v>1.01</v>
-      </c>
-      <c r="Y128">
-        <v>1.23</v>
-      </c>
-      <c r="Z128">
-        <v>3.42</v>
-      </c>
-      <c r="AA128">
-        <v>1.83</v>
-      </c>
-      <c r="AB128">
-        <v>1.84</v>
-      </c>
-      <c r="AC128">
-        <v>3.08</v>
-      </c>
-      <c r="AD128">
-        <v>1.28</v>
-      </c>
-      <c r="AE128">
-        <v>1.06</v>
-      </c>
-      <c r="AF128">
-        <v>1.67</v>
-      </c>
-      <c r="AG128">
-        <v>2.06</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>1.24</v>
-      </c>
-      <c r="AK128">
-        <v>1.57</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-10-30 22:00:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.01</v>
+        <v>4.7</v>
       </c>
       <c r="O26">
-        <v>3.97</v>
+        <v>4.17</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Q26">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="R26">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="S26">
         <v>1.22</v>
@@ -4574,7 +4574,7 @@
         <v>1.6</v>
       </c>
       <c r="W26">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
         <v>1.01</v>
@@ -4583,28 +4583,28 @@
         <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>4.71</v>
+        <v>4.76</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB26">
         <v>2.35</v>
       </c>
       <c r="AC26">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AD26">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG26">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK26">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
         <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S34">
         <v>1.31</v>
@@ -5872,10 +5872,10 @@
         <v>2.95</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.08</v>
@@ -5890,10 +5890,10 @@
         <v>3.66</v>
       </c>
       <c r="AA34">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>3.07</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>2.51</v>
       </c>
       <c r="Q36">
-        <v>3.67</v>
+        <v>3.84</v>
       </c>
       <c r="R36">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
         <v>1.41</v>
@@ -6198,7 +6198,7 @@
         <v>2.78</v>
       </c>
       <c r="U36">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="V36">
         <v>1.34</v>
@@ -6222,7 +6222,7 @@
         <v>1.69</v>
       </c>
       <c r="AC36">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK36">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>5</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="P46">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q46">
         <v>4.24</v>
@@ -7846,10 +7846,10 @@
         <v>3.95</v>
       </c>
       <c r="AA46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB46">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC46">
         <v>2.56</v>
@@ -7861,10 +7861,10 @@
         <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG46">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7979,10 +7979,10 @@
         <v>3.14</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="S47">
         <v>1.28</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK47">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8172,10 +8172,10 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
         <v>2.31</v>
@@ -8299,10 +8299,10 @@
         <v>2</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P49">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q49">
         <v>2.55</v>
@@ -8369,7 +8369,7 @@
         <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P52">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q52">
         <v>1.87</v>
       </c>
       <c r="R52">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="S52">
         <v>1.32</v>
@@ -8830,7 +8830,7 @@
         <v>2.04</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="AD52">
         <v>1.35</v>
@@ -8842,7 +8842,7 @@
         <v>1.97</v>
       </c>
       <c r="AG52">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>3.1</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P54">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O55">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="P56">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
         <v>2.94</v>
@@ -9603,10 +9603,10 @@
         <v>1.62</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="P57">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q57">
         <v>2.2</v>
@@ -9621,10 +9621,10 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V57">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W57">
         <v>1.15</v>
@@ -9639,10 +9639,10 @@
         <v>4.33</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -9654,10 +9654,10 @@
         <v>1.16</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG57">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9802,10 +9802,10 @@
         <v>3.84</v>
       </c>
       <c r="AA58">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB58">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AC58">
         <v>2.74</v>
@@ -9929,19 +9929,19 @@
         <v>3.25</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="Q59">
-        <v>3.59</v>
+        <v>3.13</v>
       </c>
       <c r="R59">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S59">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
         <v>3.6</v>
@@ -9965,10 +9965,10 @@
         <v>5.08</v>
       </c>
       <c r="AA59">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB59">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC59">
         <v>2.27</v>
@@ -9980,7 +9980,7 @@
         <v>1.2</v>
       </c>
       <c r="AF59">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
         <v>2.5</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
+        <v>1.17</v>
+      </c>
+      <c r="AK59">
         <v>1.23</v>
-      </c>
-      <c r="AK59">
-        <v>1.31</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O60">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="P60">
-        <v>2.53</v>
+        <v>2.27</v>
       </c>
       <c r="Q60">
         <v>2.95</v>
@@ -10104,37 +10104,37 @@
         <v>2.35</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T60">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="U60">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="V60">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W60">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X60">
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
         <v>4.55</v>
       </c>
       <c r="AA60">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB60">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AD60">
         <v>1.61</v>
@@ -10143,10 +10143,10 @@
         <v>1.17</v>
       </c>
       <c r="AF60">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.23</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10741,34 +10741,34 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="O64">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="P64">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
       </c>
       <c r="R64">
+        <v>2.45</v>
+      </c>
+      <c r="S64">
+        <v>1.25</v>
+      </c>
+      <c r="T64">
+        <v>3.6</v>
+      </c>
+      <c r="U64">
         <v>2.3</v>
       </c>
-      <c r="S64">
-        <v>1.26</v>
-      </c>
-      <c r="T64">
-        <v>3.3</v>
-      </c>
-      <c r="U64">
-        <v>2.38</v>
-      </c>
       <c r="V64">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
         <v>1.02</v>
@@ -10777,28 +10777,28 @@
         <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
         <v>2.5</v>
       </c>
       <c r="AC64">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="AD64">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK64">
         <v>2.1</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
         <v>2.21</v>
@@ -10943,10 +10943,10 @@
         <v>4.6</v>
       </c>
       <c r="AA65">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AC65">
         <v>2.29</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>7.17</v>
       </c>
       <c r="AA66">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AB66">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC66">
         <v>1.78</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O71">
         <v>5.5</v>
@@ -11891,10 +11891,10 @@
         <v>8.5</v>
       </c>
       <c r="Q71">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R71">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="S71">
         <v>1.25</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK71">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O78">
         <v>3.4</v>
@@ -13062,10 +13062,10 @@
         <v>4.15</v>
       </c>
       <c r="AA78">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB78">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC78">
         <v>2.52</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.67</v>
+        <v>1.94</v>
       </c>
       <c r="O84">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P84">
+        <v>3.13</v>
+      </c>
+      <c r="Q84">
+        <v>2.51</v>
+      </c>
+      <c r="R84">
+        <v>2.38</v>
+      </c>
+      <c r="S84">
+        <v>1.22</v>
+      </c>
+      <c r="T84">
+        <v>3.85</v>
+      </c>
+      <c r="U84">
         <v>2.2</v>
       </c>
-      <c r="Q84">
-        <v>3.1</v>
-      </c>
-      <c r="R84">
-        <v>2.4</v>
-      </c>
-      <c r="S84">
-        <v>1.2</v>
-      </c>
-      <c r="T84">
-        <v>3.9</v>
-      </c>
-      <c r="U84">
-        <v>2.1</v>
-      </c>
       <c r="V84">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X84">
         <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z84">
-        <v>5.35</v>
+        <v>5.15</v>
       </c>
       <c r="AA84">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB84">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AC84">
         <v>2.15</v>
       </c>
       <c r="AD84">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE84">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG84">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.18</v>
       </c>
       <c r="AK84">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.94</v>
+        <v>2.67</v>
       </c>
       <c r="O85">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P85">
-        <v>3.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q85">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T85">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>5.35</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB85">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC85">
         <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE85">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AF85">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.18</v>
       </c>
       <c r="AK85">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14330,10 +14330,10 @@
         <v>1.53</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P86">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q86">
         <v>2.09</v>
@@ -14366,10 +14366,10 @@
         <v>3.28</v>
       </c>
       <c r="AA86">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB86">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC86">
         <v>3.2</v>
@@ -14499,10 +14499,10 @@
         <v>2.89</v>
       </c>
       <c r="Q87">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R87">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S87">
         <v>1.25</v>
@@ -14529,10 +14529,10 @@
         <v>4.75</v>
       </c>
       <c r="AA87">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB87">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC87">
         <v>2.37</v>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK87">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.4</v>
       </c>
       <c r="P88">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q88">
         <v>5</v>
@@ -14671,13 +14671,13 @@
         <v>1.37</v>
       </c>
       <c r="T88">
+        <v>2.76</v>
+      </c>
+      <c r="U88">
         <v>2.68</v>
       </c>
-      <c r="U88">
-        <v>2.76</v>
-      </c>
       <c r="V88">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W88">
         <v>1.04</v>
@@ -14686,7 +14686,7 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z88">
         <v>3.25</v>
@@ -14695,7 +14695,7 @@
         <v>2</v>
       </c>
       <c r="AB88">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AC88">
         <v>3.28</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK88">
         <v>1.2</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P89">
         <v>3.1</v>
@@ -14855,10 +14855,10 @@
         <v>3.49</v>
       </c>
       <c r="AA89">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB89">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC89">
         <v>3.3</v>
@@ -15018,10 +15018,10 @@
         <v>2.83</v>
       </c>
       <c r="AA90">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB90">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC90">
         <v>3.92</v>
@@ -15151,13 +15151,13 @@
         <v>2.05</v>
       </c>
       <c r="Q91">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R91">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T91">
         <v>3.8</v>
@@ -15175,10 +15175,10 @@
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z91">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA91">
         <v>1.43</v>
@@ -15187,19 +15187,19 @@
         <v>2.62</v>
       </c>
       <c r="AC91">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AD91">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE91">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF91">
         <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AK91">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15477,10 +15477,10 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R93">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="S93">
         <v>1.22</v>
@@ -15489,7 +15489,7 @@
         <v>3.8</v>
       </c>
       <c r="U93">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="V93">
         <v>1.61</v>
@@ -15519,13 +15519,13 @@
         <v>1.54</v>
       </c>
       <c r="AE93">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AG93">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK93">
         <v>3.44</v>
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="O99">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O100">
         <v>4.6</v>
       </c>
       <c r="P100">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Q100">
         <v>3.98</v>
@@ -17098,10 +17098,10 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P103">
         <v>2.7</v>
@@ -17140,7 +17140,7 @@
         <v>1.94</v>
       </c>
       <c r="AB103">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC103">
         <v>3.14</v>
@@ -17430,13 +17430,13 @@
         <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q105">
         <v>3.08</v>
       </c>
       <c r="R105">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S105">
         <v>1.32</v>
@@ -17445,7 +17445,7 @@
         <v>3.28</v>
       </c>
       <c r="U105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.53</v>
@@ -17481,7 +17481,7 @@
         <v>1.55</v>
       </c>
       <c r="AG105">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="O107">
         <v>3.75</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="Q107">
         <v>2.12</v>
@@ -17771,13 +17771,13 @@
         <v>3.01</v>
       </c>
       <c r="U107">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="V107">
         <v>1.4</v>
       </c>
       <c r="W107">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X107">
         <v>1.01</v>
@@ -17804,10 +17804,10 @@
         <v>1.06</v>
       </c>
       <c r="AF107">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG107">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="O108">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P108">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -18420,10 +18420,10 @@
         <v>1.18</v>
       </c>
       <c r="T111">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U111">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V111">
         <v>1.79</v>
@@ -18441,7 +18441,7 @@
         <v>6.55</v>
       </c>
       <c r="AA111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB111">
         <v>3.13</v>
@@ -18571,7 +18571,7 @@
         <v>3.68</v>
       </c>
       <c r="P112">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
         <v>2.26</v>
@@ -20195,7 +20195,7 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="O122">
         <v>3.4</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="Q4">
         <v>3.4</v>
@@ -988,7 +988,7 @@
         <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.04</v>
@@ -1018,7 +1018,7 @@
         <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         <v>5.2</v>
       </c>
       <c r="P11">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Q11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R11">
         <v>2.52</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -4553,7 +4553,7 @@
         <v>4.17</v>
       </c>
       <c r="P26">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q26">
         <v>3.84</v>
@@ -4577,19 +4577,19 @@
         <v>1.12</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>4.76</v>
+        <v>4.6</v>
       </c>
       <c r="AA26">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AB26">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC26">
         <v>2.31</v>
@@ -4598,7 +4598,7 @@
         <v>1.57</v>
       </c>
       <c r="AE26">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF26">
         <v>1.57</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="Q34">
         <v>2.9</v>
@@ -5893,7 +5893,7 @@
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC34">
         <v>3.07</v>
@@ -6017,7 +6017,7 @@
         <v>3.2</v>
       </c>
       <c r="O35">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P35">
         <v>2.2</v>
@@ -6026,7 +6026,7 @@
         <v>4</v>
       </c>
       <c r="R35">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="S35">
         <v>1.55</v>
@@ -6059,10 +6059,10 @@
         <v>1.4</v>
       </c>
       <c r="AC35">
-        <v>5.68</v>
+        <v>5.5</v>
       </c>
       <c r="AD35">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE35">
         <v>1.01</v>
@@ -6886,7 +6886,7 @@
         <v>1.45</v>
       </c>
       <c r="AG40">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="Q46">
         <v>4.24</v>
@@ -8299,7 +8299,7 @@
         <v>2</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>3</v>
@@ -8794,7 +8794,7 @@
         <v>5.3</v>
       </c>
       <c r="Q52">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R52">
         <v>2.33</v>
@@ -8818,16 +8818,16 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>3.69</v>
+        <v>3.79</v>
       </c>
       <c r="AA52">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB52">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
         <v>2.94</v>
@@ -8836,10 +8836,10 @@
         <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG52">
         <v>1.81</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK52">
-        <v>2.84</v>
+        <v>2.56</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>3.54</v>
       </c>
       <c r="P54">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>1.67</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
         <v>4.1</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
         <v>3.82</v>
@@ -9473,13 +9473,13 @@
         <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA56">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AB56">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC56">
         <v>2.21</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O59">
         <v>3.7</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O60">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
         <v>2.27</v>
@@ -10128,13 +10128,13 @@
         <v>4.55</v>
       </c>
       <c r="AA60">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB60">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AC60">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD60">
         <v>1.61</v>
@@ -10261,13 +10261,13 @@
         <v>1.25</v>
       </c>
       <c r="Q61">
-        <v>8.84</v>
+        <v>8.51</v>
       </c>
       <c r="R61">
         <v>2.98</v>
       </c>
       <c r="S61">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T61">
         <v>4.75</v>
@@ -10309,7 +10309,7 @@
         <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="O62">
         <v>2.62</v>
@@ -10454,7 +10454,7 @@
         <v>2.25</v>
       </c>
       <c r="AA62">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB62">
         <v>1.36</v>
@@ -10472,7 +10472,7 @@
         <v>2.3</v>
       </c>
       <c r="AG62">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O63">
         <v>2.8</v>
       </c>
       <c r="P63">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q63">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="R63">
         <v>1.78</v>
@@ -10617,7 +10617,7 @@
         <v>2.63</v>
       </c>
       <c r="AA63">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="AB63">
         <v>1.5</v>
@@ -10651,7 +10651,7 @@
         <v>1.35</v>
       </c>
       <c r="AK63">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O64">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
       </c>
       <c r="R64">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
         <v>1.25</v>
@@ -10765,7 +10765,7 @@
         <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10780,25 +10780,25 @@
         <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB64">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD64">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE64">
         <v>1.18</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
         <v>2.1</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q66">
         <v>2</v>
@@ -11230,10 +11230,10 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="O67">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
         <v>2.9</v>
@@ -11269,10 +11269,10 @@
         <v>4.55</v>
       </c>
       <c r="AA67">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC67">
         <v>2.34</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="O69">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P69">
-        <v>4.94</v>
+        <v>4.4</v>
       </c>
       <c r="Q69">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S69">
         <v>1.19</v>
       </c>
       <c r="T69">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U69">
         <v>2</v>
@@ -11583,22 +11583,22 @@
         <v>1.7</v>
       </c>
       <c r="W69">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z69">
         <v>5.5</v>
       </c>
       <c r="AA69">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB69">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AC69">
         <v>2.04</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,61 +11719,61 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="O70">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="P70">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q70">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="R70">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S70">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T70">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="U70">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V70">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="W70">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X70">
         <v>1.01</v>
       </c>
       <c r="Y70">
+        <v>1.21</v>
+      </c>
+      <c r="Z70">
+        <v>4.16</v>
+      </c>
+      <c r="AA70">
+        <v>1.57</v>
+      </c>
+      <c r="AB70">
+        <v>2.25</v>
+      </c>
+      <c r="AC70">
+        <v>2.56</v>
+      </c>
+      <c r="AD70">
+        <v>1.4</v>
+      </c>
+      <c r="AE70">
         <v>1.18</v>
       </c>
-      <c r="Z70">
-        <v>4.59</v>
-      </c>
-      <c r="AA70">
-        <v>1.6</v>
-      </c>
-      <c r="AB70">
-        <v>2.29</v>
-      </c>
-      <c r="AC70">
-        <v>2.35</v>
-      </c>
-      <c r="AD70">
-        <v>1.47</v>
-      </c>
-      <c r="AE70">
-        <v>1.16</v>
-      </c>
       <c r="AF70">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG70">
         <v>2.4</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>1.25</v>
       </c>
       <c r="O71">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P71">
-        <v>8.5</v>
+        <v>9.25</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -12214,7 +12214,7 @@
         <v>4.2</v>
       </c>
       <c r="P73">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="Q73">
         <v>1.97</v>
@@ -12410,10 +12410,10 @@
         <v>3.08</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC74">
         <v>3.34</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q75">
         <v>2.48</v>
@@ -12739,7 +12739,7 @@
         <v>1.53</v>
       </c>
       <c r="AB76">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC76">
         <v>2.23</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O78">
         <v>3.4</v>
@@ -13391,7 +13391,7 @@
         <v>1.44</v>
       </c>
       <c r="AB80">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC80">
         <v>2.01</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O81">
         <v>3.65</v>
@@ -13554,7 +13554,7 @@
         <v>1.57</v>
       </c>
       <c r="AB81">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC81">
         <v>2.44</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="O82">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P82">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="Q82">
         <v>2.1</v>
@@ -13708,7 +13708,7 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
         <v>5.55</v>
@@ -13717,22 +13717,22 @@
         <v>1.44</v>
       </c>
       <c r="AB82">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC82">
         <v>2.06</v>
       </c>
       <c r="AD82">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE82">
         <v>1.25</v>
       </c>
       <c r="AF82">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG82">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13841,10 +13841,10 @@
         <v>1.95</v>
       </c>
       <c r="O83">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q83">
         <v>2.4</v>
@@ -13880,7 +13880,7 @@
         <v>1.28</v>
       </c>
       <c r="AB83">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC83">
         <v>1.74</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK83">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="O84">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>3.13</v>
+        <v>2.83</v>
       </c>
       <c r="Q84">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S84">
         <v>1.22</v>
@@ -14055,10 +14055,10 @@
         <v>1.26</v>
       </c>
       <c r="AF84">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG84">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK84">
         <v>1.67</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="O85">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q85">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R85">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S85">
         <v>1.2</v>
@@ -14203,10 +14203,10 @@
         <v>5.35</v>
       </c>
       <c r="AA85">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC85">
         <v>2.15</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK85">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14369,7 +14369,7 @@
         <v>1.9</v>
       </c>
       <c r="AB86">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC86">
         <v>3.2</v>
@@ -14523,10 +14523,10 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA87">
         <v>1.57</v>
@@ -14544,7 +14544,7 @@
         <v>1.16</v>
       </c>
       <c r="AF87">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG87">
         <v>2.5</v>
@@ -14653,77 +14653,77 @@
         </is>
       </c>
       <c r="N88">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="O88">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q88">
-        <v>5</v>
+        <v>4.62</v>
       </c>
       <c r="R88">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S88">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>2.76</v>
+        <v>3.3</v>
       </c>
       <c r="U88">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="V88">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W88">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z88">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AA88">
+        <v>1.8</v>
+      </c>
+      <c r="AB88">
         <v>2</v>
       </c>
-      <c r="AB88">
-        <v>1.82</v>
-      </c>
       <c r="AC88">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AD88">
+        <v>1.35</v>
+      </c>
+      <c r="AE88">
+        <v>1.1</v>
+      </c>
+      <c r="AF88">
+        <v>1.67</v>
+      </c>
+      <c r="AG88">
+        <v>2.1</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.25</v>
-      </c>
-      <c r="AE88">
-        <v>1.06</v>
-      </c>
-      <c r="AF88">
-        <v>1.85</v>
-      </c>
-      <c r="AG88">
-        <v>1.86</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.21</v>
       </c>
       <c r="AK88">
         <v>1.2</v>
@@ -14819,7 +14819,7 @@
         <v>2.05</v>
       </c>
       <c r="O89">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P89">
         <v>3.1</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O90">
         <v>3.2</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="O91">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P91">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q91">
         <v>3.3</v>
@@ -15157,7 +15157,7 @@
         <v>2.64</v>
       </c>
       <c r="S91">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T91">
         <v>3.8</v>
@@ -15166,10 +15166,10 @@
         <v>2.23</v>
       </c>
       <c r="V91">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W91">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,80 +16120,80 @@
         </is>
       </c>
       <c r="N97">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O97">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>1.53</v>
+        <v>3.25</v>
       </c>
       <c r="Q97">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="R97">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S97">
         <v>1.3</v>
       </c>
       <c r="T97">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="U97">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V97">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>4.05</v>
+        <v>3.58</v>
       </c>
       <c r="AA97">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AB97">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AC97">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="AD97">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AE97">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
+        <v>1.66</v>
+      </c>
+      <c r="AG97">
+        <v>2.06</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ97">
+        <v>1.3</v>
+      </c>
+      <c r="AK97">
         <v>1.7</v>
-      </c>
-      <c r="AG97">
-        <v>2.04</v>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ97">
-        <v>1.22</v>
-      </c>
-      <c r="AK97">
-        <v>1.15</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P98">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q98">
-        <v>2.66</v>
+        <v>5</v>
       </c>
       <c r="R98">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S98">
         <v>1.3</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U98">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="V98">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W98">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y98">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z98">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA98">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="AB98">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AC98">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="AD98">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG98">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16452,7 +16452,7 @@
         <v>3.4</v>
       </c>
       <c r="P99">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q99">
         <v>3.75</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="O100">
         <v>4.6</v>
       </c>
       <c r="P100">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Q100">
         <v>3.98</v>
@@ -16648,10 +16648,10 @@
         <v>6</v>
       </c>
       <c r="AA100">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB100">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC100">
         <v>2.03</v>
@@ -16944,10 +16944,10 @@
         <v>5.8</v>
       </c>
       <c r="Q102">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R102">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="S102">
         <v>1.25</v>
@@ -17104,7 +17104,7 @@
         <v>3.41</v>
       </c>
       <c r="P103">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -17128,7 +17128,7 @@
         <v>1.06</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
         <v>1.25</v>
@@ -17140,7 +17140,7 @@
         <v>1.94</v>
       </c>
       <c r="AB103">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC103">
         <v>3.14</v>
@@ -17454,7 +17454,7 @@
         <v>1.12</v>
       </c>
       <c r="X105">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
         <v>1.2</v>
@@ -17466,7 +17466,7 @@
         <v>1.77</v>
       </c>
       <c r="AB105">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC105">
         <v>2.64</v>
@@ -17590,10 +17590,10 @@
         <v>9.6</v>
       </c>
       <c r="O106">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q106">
         <v>6.18</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="O107">
         <v>3.75</v>
       </c>
       <c r="P107">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
         <v>2.12</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="O108">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="P108">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -17946,7 +17946,7 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z108">
         <v>5.3</v>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18604,7 +18604,7 @@
         <v>3.38</v>
       </c>
       <c r="AA112">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB112">
         <v>1.78</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q118">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3907,52 +3907,52 @@
         <v>3.42</v>
       </c>
       <c r="R22">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S22">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T22">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="U22">
-        <v>3.91</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Z22">
-        <v>2.28</v>
+        <v>2.17</v>
       </c>
       <c r="AA22">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AB22">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AG22">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
         <v>1.38</v>
@@ -4553,7 +4553,7 @@
         <v>4.17</v>
       </c>
       <c r="P26">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q26">
         <v>3.84</v>
@@ -4580,10 +4580,10 @@
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z26">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="AA26">
         <v>1.51</v>
@@ -4598,7 +4598,7 @@
         <v>1.57</v>
       </c>
       <c r="AE26">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF26">
         <v>1.57</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -6346,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="P37">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>1.89</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q43">
         <v>1.8</v>
@@ -7357,10 +7357,10 @@
         <v>7.6</v>
       </c>
       <c r="AA43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB43">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC43">
         <v>1.73</v>
@@ -9117,7 +9117,7 @@
         <v>3.54</v>
       </c>
       <c r="P54">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O55">
         <v>3.75</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.72</v>
+        <v>10</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="P60">
-        <v>2.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q60">
-        <v>2.95</v>
+        <v>8.51</v>
       </c>
       <c r="R60">
-        <v>2.35</v>
+        <v>2.98</v>
       </c>
       <c r="S60">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T60">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="U60">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="V60">
-        <v>1.61</v>
+        <v>1.88</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X60">
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>4.55</v>
+        <v>6.9</v>
       </c>
       <c r="AA60">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AB60">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="AC60">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="AD60">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AE60">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG60">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK60">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>10</v>
+        <v>2.72</v>
       </c>
       <c r="O61">
-        <v>6.8</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>1.25</v>
+        <v>2.27</v>
       </c>
       <c r="Q61">
-        <v>8.51</v>
+        <v>2.95</v>
       </c>
       <c r="R61">
-        <v>2.98</v>
+        <v>2.35</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="T61">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="V61">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="W61">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>6.9</v>
+        <v>4.55</v>
       </c>
       <c r="AA61">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AB61">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC61">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="AD61">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AE61">
+        <v>1.17</v>
+      </c>
+      <c r="AF61">
         <v>1.44</v>
       </c>
-      <c r="AF61">
-        <v>1.67</v>
-      </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK61">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O64">
         <v>3.7</v>
       </c>
       <c r="P64">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -11124,7 +11124,7 @@
         <v>1.33</v>
       </c>
       <c r="AG66">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11885,10 +11885,10 @@
         <v>1.25</v>
       </c>
       <c r="O71">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P71">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11918,19 +11918,19 @@
         <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA71">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AC71">
         <v>2.37</v>
       </c>
       <c r="AD71">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE71">
         <v>1.18</v>
@@ -15199,7 +15199,7 @@
         <v>1.44</v>
       </c>
       <c r="AG91">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15477,55 +15477,55 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15637,7 +15637,7 @@
         <v>3.6</v>
       </c>
       <c r="P94">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q94">
         <v>2.36</v>
@@ -15658,7 +15658,7 @@
         <v>1.61</v>
       </c>
       <c r="W94">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X94">
         <v>1.02</v>
@@ -15670,10 +15670,10 @@
         <v>4.95</v>
       </c>
       <c r="AA94">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB94">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC94">
         <v>2.25</v>
@@ -15797,16 +15797,16 @@
         <v>3</v>
       </c>
       <c r="O95">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P95">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q95">
         <v>3.5</v>
       </c>
       <c r="R95">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S95">
         <v>1.3</v>
@@ -15818,7 +15818,7 @@
         <v>2.4</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W95">
         <v>1.12</v>
@@ -15836,13 +15836,13 @@
         <v>1.62</v>
       </c>
       <c r="AB95">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AC95">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AD95">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE95">
         <v>1.14</v>
@@ -15960,10 +15960,10 @@
         <v>2.1</v>
       </c>
       <c r="O96">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q96">
         <v>2.74</v>
@@ -15972,43 +15972,43 @@
         <v>2.18</v>
       </c>
       <c r="S96">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T96">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="U96">
         <v>2.5</v>
       </c>
       <c r="V96">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W96">
         <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z96">
-        <v>3.97</v>
+        <v>4.03</v>
       </c>
       <c r="AA96">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB96">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC96">
         <v>2.83</v>
       </c>
       <c r="AD96">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE96">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF96">
         <v>1.61</v>
@@ -16126,25 +16126,25 @@
         <v>3.4</v>
       </c>
       <c r="P97">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="R97">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S97">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T97">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U97">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V97">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W97">
         <v>1.11</v>
@@ -16153,31 +16153,31 @@
         <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AA97">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB97">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AC97">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD97">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE97">
         <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG97">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,7 +16286,7 @@
         <v>4.8</v>
       </c>
       <c r="O98">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P98">
         <v>1.53</v>
@@ -16328,7 +16328,7 @@
         <v>2.17</v>
       </c>
       <c r="AC98">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD98">
         <v>1.42</v>
@@ -16648,10 +16648,10 @@
         <v>6</v>
       </c>
       <c r="AA100">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB100">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC100">
         <v>2.03</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="O107">
         <v>3.75</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="Q107">
         <v>2.12</v>
@@ -17952,7 +17952,7 @@
         <v>5.3</v>
       </c>
       <c r="AA108">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB108">
         <v>2.7</v>
@@ -18293,10 +18293,10 @@
         <v>1.05</v>
       </c>
       <c r="AF110">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG110">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>1.21</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
-        <v>6.3</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>8.710000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-30 09:55:00</t>
+          <t>2026-10-30 09:30:00</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubai United</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="O14">
-        <v>3.77</v>
+        <v>6.3</v>
       </c>
       <c r="P14">
-        <v>3.62</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Dubai United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G15">
@@ -2750,17 +2750,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N15">
-        <v>4.93</v>
+        <v>1.85</v>
       </c>
       <c r="O15">
-        <v>3.9</v>
+        <v>3.77</v>
       </c>
       <c r="P15">
-        <v>1.58</v>
+        <v>3.62</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:00:00</t>
+          <t>2026-10-30 09:55:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Halaba Ketema</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Halaba Ketema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:15:00</t>
+          <t>2026-10-30 10:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:30:00</t>
+          <t>2026-10-30 10:15:00</t>
         </is>
       </c>
     </row>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:45:00</t>
+          <t>2026-10-30 10:30:00</t>
         </is>
       </c>
     </row>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="O27">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.61</v>
+        <v>2.78</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
         <v>2.9</v>
@@ -5866,7 +5866,7 @@
         <v>2.08</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
         <v>2.95</v>
@@ -5887,7 +5887,7 @@
         <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="AA34">
         <v>1.83</v>
@@ -5896,7 +5896,7 @@
         <v>1.93</v>
       </c>
       <c r="AC34">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="AD34">
         <v>1.35</v>
@@ -6186,7 +6186,7 @@
         <v>2.51</v>
       </c>
       <c r="Q36">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="R36">
         <v>1.95</v>
@@ -6198,7 +6198,7 @@
         <v>2.78</v>
       </c>
       <c r="U36">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="V36">
         <v>1.34</v>
@@ -6213,16 +6213,16 @@
         <v>1.33</v>
       </c>
       <c r="Z36">
-        <v>3.01</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AB36">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC36">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6231,10 +6231,10 @@
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O41">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P41">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="P46">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q46">
         <v>4.24</v>
@@ -7822,19 +7822,19 @@
         <v>2.25</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1</v>
@@ -8024,7 +8024,7 @@
         <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG47">
         <v>2.28</v>
@@ -8163,7 +8163,7 @@
         <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.12</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O52">
         <v>4.1</v>
       </c>
       <c r="P52">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -8818,10 +8818,10 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -8830,7 +8830,7 @@
         <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AD52">
         <v>1.35</v>
@@ -9479,7 +9479,7 @@
         <v>1.51</v>
       </c>
       <c r="AB56">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
         <v>2.21</v>
@@ -9621,7 +9621,7 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.45</v>
+        <v>2.23</v>
       </c>
       <c r="V57">
         <v>1.56</v>
@@ -10110,10 +10110,10 @@
         <v>4.75</v>
       </c>
       <c r="U60">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W60">
         <v>1.25</v>
@@ -10128,13 +10128,13 @@
         <v>6.9</v>
       </c>
       <c r="AA60">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
         <v>3.4</v>
       </c>
       <c r="AC60">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AD60">
         <v>2</v>
@@ -10255,7 +10255,7 @@
         <v>2.72</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="P61">
         <v>2.27</v>
@@ -10267,19 +10267,19 @@
         <v>2.35</v>
       </c>
       <c r="S61">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
         <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="V61">
         <v>1.61</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
         <v>1</v>
@@ -10291,10 +10291,10 @@
         <v>4.55</v>
       </c>
       <c r="AA61">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB61">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
         <v>2.24</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O68">
         <v>3.4</v>
@@ -11432,7 +11432,7 @@
         <v>3.63</v>
       </c>
       <c r="AA68">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB68">
         <v>1.91</v>
@@ -12211,7 +12211,7 @@
         <v>1.44</v>
       </c>
       <c r="O73">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P73">
         <v>6</v>
@@ -12235,7 +12235,7 @@
         <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
         <v>1.02</v>
@@ -12540,7 +12540,7 @@
         <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q75">
         <v>2.48</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12917,7 +12917,7 @@
         <v>1.75</v>
       </c>
       <c r="AG77">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q78">
         <v>2.88</v>
@@ -13053,7 +13053,7 @@
         <v>1.11</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
         <v>1.16</v>
@@ -14330,10 +14330,10 @@
         <v>1.53</v>
       </c>
       <c r="O86">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q86">
         <v>2.09</v>
@@ -14668,10 +14668,10 @@
         <v>2.2</v>
       </c>
       <c r="S88">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T88">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U88">
         <v>2.6</v>
@@ -14707,10 +14707,10 @@
         <v>1.1</v>
       </c>
       <c r="AF88">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG88">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14825,19 +14825,19 @@
         <v>3.1</v>
       </c>
       <c r="Q89">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R89">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S89">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="U89">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V89">
         <v>1.41</v>
@@ -14849,10 +14849,10 @@
         <v>1.03</v>
       </c>
       <c r="Y89">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z89">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="AA89">
         <v>1.9</v>
@@ -14861,7 +14861,7 @@
         <v>1.87</v>
       </c>
       <c r="AC89">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="AD89">
         <v>1.31</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O90">
         <v>3.2</v>
@@ -15344,10 +15344,10 @@
         <v>3.92</v>
       </c>
       <c r="AA92">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC92">
         <v>2.62</v>
@@ -16485,10 +16485,10 @@
         <v>3.58</v>
       </c>
       <c r="AA99">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB99">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC99">
         <v>2.88</v>
@@ -16503,7 +16503,7 @@
         <v>1.67</v>
       </c>
       <c r="AG99">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="O102">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P102">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q102">
         <v>1.92</v>
@@ -16974,10 +16974,10 @@
         <v>4.95</v>
       </c>
       <c r="AA102">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB102">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AC102">
         <v>2.38</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="O103">
         <v>3.41</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17300,10 +17300,10 @@
         <v>0</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC104">
         <v>0</v>
@@ -17439,10 +17439,10 @@
         <v>2.2</v>
       </c>
       <c r="S105">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U105">
         <v>2.55</v>
@@ -17463,7 +17463,7 @@
         <v>4.2</v>
       </c>
       <c r="AA105">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB105">
         <v>2.1</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU122"/>
+  <dimension ref="A1:AU121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,55 +1785,55 @@
         <v>2.75</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="R9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S9">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="T9">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U9">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="V9">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y9">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Z9">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="AA9">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AB9">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AG9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
         <v>1.42</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="O20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.8</v>
+        <v>2.26</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="O21">
+        <v>3.15</v>
+      </c>
+      <c r="P21">
+        <v>2.8</v>
+      </c>
+      <c r="Q21">
         <v>3.2</v>
       </c>
-      <c r="P21">
-        <v>2.26</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
+        <v>1.8</v>
+      </c>
+      <c r="AC27">
+        <v>3.28</v>
+      </c>
+      <c r="AD27">
+        <v>1.25</v>
+      </c>
+      <c r="AE27">
+        <v>1.05</v>
+      </c>
+      <c r="AF27">
         <v>1.7</v>
       </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>3.5</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>1.99</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P37">
         <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R37">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
         <v>2.45</v>
@@ -6394,7 +6394,7 @@
         <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
         <v>1.85</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK37">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>4.2</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6995,10 +6995,10 @@
         <v>1.33</v>
       </c>
       <c r="O41">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="P41">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
+        <v>1.95</v>
+      </c>
+      <c r="AB41">
         <v>1.85</v>
-      </c>
-      <c r="AB41">
-        <v>1.95</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>7.6</v>
       </c>
       <c r="AA43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AB43">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AC43">
         <v>1.73</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="O46">
         <v>4.12</v>
       </c>
       <c r="P46">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="Q46">
         <v>4.24</v>
@@ -7985,13 +7985,13 @@
         <v>2.17</v>
       </c>
       <c r="S47">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
         <v>3.3</v>
       </c>
       <c r="U47">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
         <v>1.51</v>
@@ -8163,7 +8163,7 @@
         <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.12</v>
@@ -8172,10 +8172,10 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
         <v>2.31</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O49">
         <v>3.4</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q49">
         <v>2.55</v>
@@ -8317,10 +8317,10 @@
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
         <v>1.08</v>
@@ -9114,10 +9114,10 @@
         <v>3.1</v>
       </c>
       <c r="O54">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>1.7</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
         <v>4.1</v>
@@ -9440,7 +9440,7 @@
         <v>2.6</v>
       </c>
       <c r="O56">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="P56">
         <v>2.2</v>
@@ -9461,7 +9461,7 @@
         <v>2.1</v>
       </c>
       <c r="V56">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
         <v>1.18</v>
@@ -9473,28 +9473,28 @@
         <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AB56">
         <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AD56">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG56">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="O57">
-        <v>4.05</v>
+        <v>3.67</v>
       </c>
       <c r="P57">
         <v>3.75</v>
@@ -9766,10 +9766,10 @@
         <v>2.6</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
         <v>3.2</v>
@@ -10747,7 +10747,7 @@
         <v>3.7</v>
       </c>
       <c r="P64">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -10756,49 +10756,49 @@
         <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U64">
         <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA64">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AB64">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC64">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AD64">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE64">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
         <v>2.1</v>
@@ -10931,7 +10931,7 @@
         <v>1.58</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10946,7 +10946,7 @@
         <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC65">
         <v>2.29</v>
@@ -11088,7 +11088,7 @@
         <v>4.65</v>
       </c>
       <c r="U66">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V66">
         <v>1.98</v>
@@ -11103,7 +11103,7 @@
         <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>7.17</v>
+        <v>7.2</v>
       </c>
       <c r="AA66">
         <v>1.3</v>
@@ -11124,7 +11124,7 @@
         <v>1.33</v>
       </c>
       <c r="AG66">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O68">
         <v>3.4</v>
@@ -11411,13 +11411,13 @@
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="U68">
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
         <v>1.07</v>
@@ -11432,13 +11432,13 @@
         <v>3.63</v>
       </c>
       <c r="AA68">
+        <v>1.93</v>
+      </c>
+      <c r="AB68">
         <v>1.9</v>
       </c>
-      <c r="AB68">
-        <v>1.91</v>
-      </c>
       <c r="AC68">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -11466,7 +11466,7 @@
         <v>1.28</v>
       </c>
       <c r="AK68">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>1.25</v>
       </c>
       <c r="O71">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P71">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11900,10 +11900,10 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="U71">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
         <v>1.62</v>
@@ -11912,34 +11912,34 @@
         <v>1.15</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
         <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB71">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC71">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AD71">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE71">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG71">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12211,10 +12211,10 @@
         <v>1.44</v>
       </c>
       <c r="O73">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P73">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q73">
         <v>1.97</v>
@@ -12377,7 +12377,7 @@
         <v>3.2</v>
       </c>
       <c r="P74">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q74">
         <v>3.84</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="O75">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P75">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q75">
         <v>2.48</v>
@@ -12552,7 +12552,7 @@
         <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U75">
         <v>2.5</v>
@@ -12567,10 +12567,10 @@
         <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z75">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AA75">
         <v>1.73</v>
@@ -12579,10 +12579,10 @@
         <v>2.1</v>
       </c>
       <c r="AC75">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AD75">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE75">
         <v>1.1</v>
@@ -12607,7 +12607,7 @@
         <v>1.26</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>2.45</v>
       </c>
       <c r="AC76">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AD76">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE76">
         <v>1.2</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12878,7 +12878,7 @@
         <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="U77">
         <v>2.98</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="P78">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="Q78">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R78">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T78">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="U78">
+        <v>3.3</v>
+      </c>
+      <c r="V78">
+        <v>1.25</v>
+      </c>
+      <c r="W78">
+        <v>1.05</v>
+      </c>
+      <c r="X78">
+        <v>1.06</v>
+      </c>
+      <c r="Y78">
+        <v>1.49</v>
+      </c>
+      <c r="Z78">
         <v>2.38</v>
       </c>
-      <c r="V78">
+      <c r="AA78">
+        <v>2.5</v>
+      </c>
+      <c r="AB78">
         <v>1.5</v>
       </c>
-      <c r="W78">
+      <c r="AC78">
+        <v>4.9</v>
+      </c>
+      <c r="AD78">
         <v>1.11</v>
       </c>
-      <c r="X78">
-        <v>1.04</v>
-      </c>
-      <c r="Y78">
-        <v>1.16</v>
-      </c>
-      <c r="Z78">
-        <v>4.15</v>
-      </c>
-      <c r="AA78">
-        <v>1.67</v>
-      </c>
-      <c r="AB78">
-        <v>2.15</v>
-      </c>
-      <c r="AC78">
-        <v>2.52</v>
-      </c>
-      <c r="AD78">
-        <v>1.45</v>
-      </c>
       <c r="AE78">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AF78">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK78">
         <v>1.5</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="O81">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Q81">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U81">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="V81">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W81">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z81">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA81">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB81">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AC81">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="AD81">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AE81">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF81">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AG81">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="O82">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="P82">
-        <v>4.09</v>
+        <v>2.9</v>
       </c>
       <c r="Q82">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="R82">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="V82">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W82">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA82">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC82">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AD82">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AE82">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF82">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AK82">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P83">
-        <v>3.09</v>
+        <v>4.09</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="R83">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S83">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T83">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U83">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="V83">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="W83">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="AA83">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB83">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC83">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AD83">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AE83">
+        <v>1.25</v>
+      </c>
+      <c r="AF83">
         <v>1.44</v>
       </c>
-      <c r="AF83">
-        <v>1.28</v>
-      </c>
       <c r="AG83">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="Q84">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="T84">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="U84">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="V84">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="W84">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z84">
-        <v>5.15</v>
+        <v>7</v>
       </c>
       <c r="AA84">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AB84">
-        <v>2.46</v>
+        <v>3.4</v>
       </c>
       <c r="AC84">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AD84">
-        <v>1.6</v>
+        <v>2.07</v>
       </c>
       <c r="AE84">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AF84">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AG84">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK84">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-10-30 16:15:00</t>
+          <t>2026-10-30 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="O85">
         <v>3.5</v>
       </c>
       <c r="P85">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="Q85">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="R85">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V85">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X85">
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z85">
-        <v>5.35</v>
+        <v>5.15</v>
       </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB85">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC85">
         <v>2.15</v>
       </c>
       <c r="AD85">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AF85">
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.19</v>
       </c>
       <c r="AK85">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>5.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q86">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="R86">
+        <v>2.36</v>
+      </c>
+      <c r="S86">
+        <v>1.2</v>
+      </c>
+      <c r="T86">
+        <v>3.9</v>
+      </c>
+      <c r="U86">
         <v>2.1</v>
       </c>
-      <c r="S86">
-        <v>1.35</v>
-      </c>
-      <c r="T86">
-        <v>2.77</v>
-      </c>
-      <c r="U86">
-        <v>2.69</v>
-      </c>
       <c r="V86">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z86">
-        <v>3.28</v>
+        <v>5.35</v>
       </c>
       <c r="AA86">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="AC86">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD86">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AE86">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-10-30 16:30:00</t>
+          <t>2026-10-30 16:15:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="O87">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P87">
-        <v>2.89</v>
+        <v>5.5</v>
       </c>
       <c r="Q87">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="R87">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S87">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T87">
-        <v>3.6</v>
+        <v>2.77</v>
       </c>
       <c r="U87">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="V87">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="W87">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z87">
-        <v>4.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA87">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AB87">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC87">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="AD87">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="AE87">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF87">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AG87">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK87">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.93</v>
+        <v>1.98</v>
       </c>
       <c r="O88">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
-        <v>1.74</v>
+        <v>2.89</v>
       </c>
       <c r="Q88">
-        <v>4.62</v>
+        <v>2.62</v>
       </c>
       <c r="R88">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S88">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="V88">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="Z88">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA88">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC88">
-        <v>2.74</v>
+        <v>2.37</v>
       </c>
       <c r="AD88">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AE88">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF88">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AG88">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK88">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.05</v>
+        <v>3.93</v>
       </c>
       <c r="O89">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>3.1</v>
+        <v>1.74</v>
       </c>
       <c r="Q89">
-        <v>2.68</v>
+        <v>4.62</v>
       </c>
       <c r="R89">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T89">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="U89">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V89">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="AA89">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB89">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC89">
-        <v>3.36</v>
+        <v>2.74</v>
       </c>
       <c r="AD89">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE89">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,65 +14979,65 @@
         </is>
       </c>
       <c r="N90">
+        <v>2.05</v>
+      </c>
+      <c r="O90">
+        <v>3.44</v>
+      </c>
+      <c r="P90">
+        <v>3.1</v>
+      </c>
+      <c r="Q90">
+        <v>2.68</v>
+      </c>
+      <c r="R90">
+        <v>2.23</v>
+      </c>
+      <c r="S90">
+        <v>1.39</v>
+      </c>
+      <c r="T90">
+        <v>2.96</v>
+      </c>
+      <c r="U90">
+        <v>2.88</v>
+      </c>
+      <c r="V90">
+        <v>1.41</v>
+      </c>
+      <c r="W90">
+        <v>1.05</v>
+      </c>
+      <c r="X90">
+        <v>1.03</v>
+      </c>
+      <c r="Y90">
+        <v>1.3</v>
+      </c>
+      <c r="Z90">
+        <v>3.48</v>
+      </c>
+      <c r="AA90">
+        <v>1.9</v>
+      </c>
+      <c r="AB90">
+        <v>1.87</v>
+      </c>
+      <c r="AC90">
+        <v>3.36</v>
+      </c>
+      <c r="AD90">
+        <v>1.31</v>
+      </c>
+      <c r="AE90">
+        <v>1.07</v>
+      </c>
+      <c r="AF90">
+        <v>1.7</v>
+      </c>
+      <c r="AG90">
         <v>2</v>
       </c>
-      <c r="O90">
-        <v>3.2</v>
-      </c>
-      <c r="P90">
-        <v>3.4</v>
-      </c>
-      <c r="Q90">
-        <v>2.65</v>
-      </c>
-      <c r="R90">
-        <v>1.98</v>
-      </c>
-      <c r="S90">
-        <v>1.38</v>
-      </c>
-      <c r="T90">
-        <v>2.65</v>
-      </c>
-      <c r="U90">
-        <v>2.95</v>
-      </c>
-      <c r="V90">
-        <v>1.31</v>
-      </c>
-      <c r="W90">
-        <v>1.03</v>
-      </c>
-      <c r="X90">
-        <v>1.01</v>
-      </c>
-      <c r="Y90">
-        <v>1.33</v>
-      </c>
-      <c r="Z90">
-        <v>2.83</v>
-      </c>
-      <c r="AA90">
-        <v>2.15</v>
-      </c>
-      <c r="AB90">
-        <v>1.67</v>
-      </c>
-      <c r="AC90">
-        <v>3.92</v>
-      </c>
-      <c r="AD90">
-        <v>1.18</v>
-      </c>
-      <c r="AE90">
-        <v>1.02</v>
-      </c>
-      <c r="AF90">
-        <v>1.87</v>
-      </c>
-      <c r="AG90">
-        <v>1.8</v>
-      </c>
       <c r="AH90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK90">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.89</v>
+        <v>2</v>
       </c>
       <c r="O91">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P91">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="R91">
-        <v>2.64</v>
+        <v>1.98</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="T91">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="U91">
-        <v>2.23</v>
+        <v>2.95</v>
       </c>
       <c r="V91">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="W91">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
         <v>1.01</v>
       </c>
       <c r="Y91">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="Z91">
-        <v>6</v>
+        <v>2.83</v>
       </c>
       <c r="AA91">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AB91">
-        <v>2.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC91">
-        <v>2.15</v>
+        <v>3.92</v>
       </c>
       <c r="AD91">
-        <v>1.67</v>
+        <v>1.18</v>
       </c>
       <c r="AE91">
-        <v>1.29</v>
+        <v>1.02</v>
       </c>
       <c r="AF91">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AG91">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AK91">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,80 +15305,80 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.59</v>
+        <v>3.2</v>
       </c>
       <c r="O92">
+        <v>3.85</v>
+      </c>
+      <c r="P92">
+        <v>2.03</v>
+      </c>
+      <c r="Q92">
+        <v>3.3</v>
+      </c>
+      <c r="R92">
+        <v>2.64</v>
+      </c>
+      <c r="S92">
+        <v>1.22</v>
+      </c>
+      <c r="T92">
         <v>3.8</v>
       </c>
-      <c r="P92">
-        <v>4.4</v>
-      </c>
-      <c r="Q92">
-        <v>2.1</v>
-      </c>
-      <c r="R92">
-        <v>2.3</v>
-      </c>
-      <c r="S92">
-        <v>1.3</v>
-      </c>
-      <c r="T92">
-        <v>3.25</v>
-      </c>
       <c r="U92">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X92">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y92">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z92">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="AB92">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AC92">
+        <v>2.15</v>
+      </c>
+      <c r="AD92">
+        <v>1.67</v>
+      </c>
+      <c r="AE92">
+        <v>1.29</v>
+      </c>
+      <c r="AF92">
+        <v>1.4</v>
+      </c>
+      <c r="AG92">
         <v>2.62</v>
       </c>
-      <c r="AD92">
-        <v>1.42</v>
-      </c>
-      <c r="AE92">
-        <v>1.16</v>
-      </c>
-      <c r="AF92">
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.67</v>
       </c>
-      <c r="AG92">
-        <v>2.1</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.17</v>
-      </c>
       <c r="AK92">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-30 16:45:00</t>
+          <t>2026-10-30 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q93">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="R93">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U93">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V93">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W93">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z93">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA93">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB93">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC93">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="AD93">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AE93">
         <v>1.16</v>
       </c>
       <c r="AF93">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>3.62</v>
+        <v>2.15</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q94">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="R94">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="S94">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T94">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="U94">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V94">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W94">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z94">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA94">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC94">
-        <v>2.25</v>
+        <v>2.53</v>
       </c>
       <c r="AD94">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AE94">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF94">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK94">
-        <v>1.85</v>
+        <v>3.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="O95">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Q95">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="R95">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="S95">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T95">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="U95">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="V95">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="W95">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z95">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA95">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AB95">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AC95">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD95">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG95">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK95">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O96">
         <v>3.5</v>
       </c>
       <c r="P96">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="Q96">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="R96">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="S96">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U96">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V96">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="W96">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB96">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AC96">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AD96">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AE96">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF96">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK96">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q97">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="R97">
         <v>2.18</v>
       </c>
       <c r="S97">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T97">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U97">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V97">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z97">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AA97">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AB97">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC97">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD97">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE97">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF97">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG97">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O98">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="Q98">
-        <v>5</v>
+        <v>2.57</v>
       </c>
       <c r="R98">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U98">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V98">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W98">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="AA98">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AB98">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK98">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="O99">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P99">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="Q99">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="R99">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S99">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U99">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V99">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z99">
-        <v>3.58</v>
+        <v>4.05</v>
       </c>
       <c r="AA99">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AB99">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AC99">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD99">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AE99">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF99">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG99">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>1.22</v>
       </c>
       <c r="AK99">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>5.55</v>
+        <v>3.5</v>
       </c>
       <c r="O100">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="Q100">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="R100">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="S100">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T100">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="V100">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="W100">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z100">
-        <v>6</v>
+        <v>3.58</v>
       </c>
       <c r="AA100">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AB100">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD100">
+        <v>1.32</v>
+      </c>
+      <c r="AE100">
+        <v>1.09</v>
+      </c>
+      <c r="AF100">
         <v>1.67</v>
       </c>
-      <c r="AE100">
-        <v>1.29</v>
-      </c>
-      <c r="AF100">
-        <v>1.51</v>
-      </c>
       <c r="AG100">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>2.41</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-30 17:00:00</t>
+          <t>2026-10-30 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="Q102">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AC102">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.32</v>
+        <v>1.35</v>
       </c>
       <c r="O103">
-        <v>3.41</v>
+        <v>4.8</v>
       </c>
       <c r="P103">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q103">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="R103">
-        <v>2.06</v>
+        <v>2.67</v>
       </c>
       <c r="S103">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z103">
-        <v>3.28</v>
+        <v>4.95</v>
       </c>
       <c r="AA103">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AC103">
-        <v>3.14</v>
+        <v>2.38</v>
       </c>
       <c r="AD103">
-        <v>1.27</v>
+        <v>1.63</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AF103">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK103">
-        <v>1.44</v>
+        <v>2.79</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O104">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA104">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="AB104">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O106">
         <v>5.5</v>
       </c>
       <c r="P106">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q106">
         <v>6.18</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="O107">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P107">
-        <v>5.05</v>
+        <v>5.17</v>
       </c>
       <c r="Q107">
         <v>2.12</v>
@@ -17952,7 +17952,7 @@
         <v>5.3</v>
       </c>
       <c r="AA108">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB108">
         <v>2.7</v>
@@ -18278,10 +18278,10 @@
         <v>3.2</v>
       </c>
       <c r="AA110">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB110">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC110">
         <v>3.28</v>
@@ -18571,7 +18571,7 @@
         <v>3.68</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q112">
         <v>2.26</v>
@@ -18583,7 +18583,7 @@
         <v>1.36</v>
       </c>
       <c r="T112">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
         <v>2.7</v>
@@ -18746,7 +18746,7 @@
         <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U113">
         <v>2.44</v>
@@ -18767,10 +18767,10 @@
         <v>3.48</v>
       </c>
       <c r="AA113">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB113">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC113">
         <v>2.88</v>
@@ -18801,7 +18801,7 @@
         <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18912,10 +18912,10 @@
         <v>4.15</v>
       </c>
       <c r="U114">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="V114">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W114">
         <v>1.17</v>
@@ -18930,10 +18930,10 @@
         <v>5.35</v>
       </c>
       <c r="AA114">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB114">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC114">
         <v>2.08</v>
@@ -18945,10 +18945,10 @@
         <v>1.23</v>
       </c>
       <c r="AF114">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG114">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>2.31</v>
+        <v>4.64</v>
       </c>
       <c r="O116">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P116">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>4.64</v>
+        <v>6.14</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="P117">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>6.14</v>
+        <v>1.71</v>
       </c>
       <c r="O118">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>1.49</v>
+        <v>4.05</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P119">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q119">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R119">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S119">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T119">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U119">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V119">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W119">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y119">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z119">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AA119">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB119">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC119">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD119">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE119">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF119">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG119">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK119">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19822,12 +19822,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 21:15:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O121">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P121">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20135,169 +20135,6 @@
         <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>2.09</v>
-      </c>
-      <c r="O122">
-        <v>3.4</v>
-      </c>
-      <c r="P122">
-        <v>2.99</v>
-      </c>
-      <c r="Q122">
-        <v>2.7</v>
-      </c>
-      <c r="R122">
-        <v>2.2</v>
-      </c>
-      <c r="S122">
-        <v>1.35</v>
-      </c>
-      <c r="T122">
-        <v>3</v>
-      </c>
-      <c r="U122">
-        <v>2.64</v>
-      </c>
-      <c r="V122">
-        <v>1.38</v>
-      </c>
-      <c r="W122">
-        <v>1.04</v>
-      </c>
-      <c r="X122">
-        <v>1.01</v>
-      </c>
-      <c r="Y122">
-        <v>1.23</v>
-      </c>
-      <c r="Z122">
-        <v>3.42</v>
-      </c>
-      <c r="AA122">
-        <v>1.83</v>
-      </c>
-      <c r="AB122">
-        <v>1.84</v>
-      </c>
-      <c r="AC122">
-        <v>3.08</v>
-      </c>
-      <c r="AD122">
-        <v>1.28</v>
-      </c>
-      <c r="AE122">
-        <v>1.06</v>
-      </c>
-      <c r="AF122">
-        <v>1.67</v>
-      </c>
-      <c r="AG122">
-        <v>2.06</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.24</v>
-      </c>
-      <c r="AK122">
-        <v>1.57</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
         <is>
           <t>2026-10-30 22:00:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>3.4</v>
       </c>
       <c r="R4">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="U4">
         <v>2.74</v>
@@ -991,13 +991,13 @@
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
         <v>1.97</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AK4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>4.45</v>
       </c>
       <c r="AA11">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
         <v>2.42</v>
@@ -2434,19 +2434,19 @@
         <v>4.05</v>
       </c>
       <c r="P13">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q13">
-        <v>3.84</v>
+        <v>4.05</v>
       </c>
       <c r="R13">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S13">
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U13">
         <v>2.15</v>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
         <v>3.28</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
         <v>1.25</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="R34">
         <v>2.08</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T34">
         <v>2.95</v>
       </c>
       <c r="U34">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
         <v>1.08</v>
@@ -5908,7 +5908,7 @@
         <v>1.64</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O35">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q35">
         <v>4</v>
@@ -6032,10 +6032,10 @@
         <v>1.55</v>
       </c>
       <c r="T35">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U35">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="V35">
         <v>1.21</v>
@@ -6068,10 +6068,10 @@
         <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AG35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O38">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="P38">
         <v>6</v>
@@ -6705,7 +6705,7 @@
         <v>3.08</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
         <v>1.73</v>
@@ -6838,22 +6838,22 @@
         <v>0</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="R40">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T40">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="U40">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V40">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W40">
         <v>1.14</v>
@@ -6862,31 +6862,31 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA40">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB40">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AC40">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AD40">
         <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF40">
         <v>1.45</v>
       </c>
       <c r="AG40">
-        <v>2.59</v>
+        <v>2.44</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O41">
         <v>4.33</v>
       </c>
       <c r="P41">
-        <v>8.5</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7339,13 +7339,13 @@
         <v>4.6</v>
       </c>
       <c r="U43">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V43">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W43">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7357,10 +7357,10 @@
         <v>7.6</v>
       </c>
       <c r="AA43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB43">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC43">
         <v>1.73</v>
@@ -7372,10 +7372,10 @@
         <v>1.39</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
         <v>2.48</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="O46">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="Q46">
-        <v>4.24</v>
+        <v>4.03</v>
       </c>
       <c r="R46">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AK46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O47">
         <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="Q47">
         <v>2.47</v>
@@ -7994,7 +7994,7 @@
         <v>2.4</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
         <v>1.12</v>
@@ -8003,10 +8003,10 @@
         <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA47">
         <v>1.66</v>
@@ -8027,7 +8027,7 @@
         <v>1.57</v>
       </c>
       <c r="AG47">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O48">
         <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q48">
         <v>2.59</v>
@@ -8172,10 +8172,10 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
         <v>2.31</v>
@@ -8296,19 +8296,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="P49">
         <v>3.2</v>
       </c>
       <c r="Q49">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8323,13 +8323,13 @@
         <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z49">
         <v>4.1</v>
@@ -8347,7 +8347,7 @@
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8788,7 +8788,7 @@
         <v>1.43</v>
       </c>
       <c r="O52">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P52">
         <v>5.4</v>
@@ -8821,7 +8821,7 @@
         <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>3.97</v>
+        <v>4.07</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="O54">
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O55">
         <v>3.7</v>
       </c>
       <c r="P55">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q55">
         <v>2.1</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="O56">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="R56">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
         <v>1.22</v>
@@ -9479,7 +9479,7 @@
         <v>1.48</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC56">
         <v>2.15</v>
@@ -9491,7 +9491,7 @@
         <v>1.25</v>
       </c>
       <c r="AF56">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
         <v>2.8</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="AK56">
         <v>1.39</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O57">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q57">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9621,13 +9621,13 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
         <v>1.56</v>
       </c>
       <c r="W57">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
         <v>1.03</v>
@@ -9642,7 +9642,7 @@
         <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>2.6</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
         <v>2.37</v>
@@ -9784,7 +9784,7 @@
         <v>3.25</v>
       </c>
       <c r="U58">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V58">
         <v>1.44</v>
@@ -9817,7 +9817,7 @@
         <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG58">
         <v>2.25</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="O59">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="P59">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q59">
         <v>3.13</v>
@@ -10098,7 +10098,7 @@
         <v>1.25</v>
       </c>
       <c r="Q60">
-        <v>8.51</v>
+        <v>6.86</v>
       </c>
       <c r="R60">
         <v>2.98</v>
@@ -10107,13 +10107,13 @@
         <v>1.17</v>
       </c>
       <c r="T60">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="V60">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="W60">
         <v>1.25</v>
@@ -10128,13 +10128,13 @@
         <v>6.9</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AB60">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="AC60">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AD60">
         <v>2</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O61">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="Q61">
         <v>2.95</v>
@@ -10325,7 +10325,7 @@
         <v>1.23</v>
       </c>
       <c r="AK61">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
         <v>2.62</v>
@@ -10424,7 +10424,7 @@
         <v>2.9</v>
       </c>
       <c r="Q62">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
         <v>1.84</v>
@@ -10442,13 +10442,13 @@
         <v>1.22</v>
       </c>
       <c r="W62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X62">
         <v>1.1</v>
       </c>
       <c r="Y62">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z62">
         <v>2.25</v>
@@ -10466,7 +10466,7 @@
         <v>1.11</v>
       </c>
       <c r="AE62">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF62">
         <v>2.3</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="O63">
         <v>2.8</v>
@@ -10587,16 +10587,16 @@
         <v>2.62</v>
       </c>
       <c r="Q63">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="R63">
         <v>1.78</v>
       </c>
       <c r="S63">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="T63">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="U63">
         <v>3.6</v>
@@ -10605,7 +10605,7 @@
         <v>1.3</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X63">
         <v>1.08</v>
@@ -10614,7 +10614,7 @@
         <v>1.44</v>
       </c>
       <c r="Z63">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="AA63">
         <v>2.55</v>
@@ -10629,7 +10629,7 @@
         <v>1.14</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
         <v>2</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -10783,10 +10783,10 @@
         <v>1.59</v>
       </c>
       <c r="AB64">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AD64">
         <v>1.49</v>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
         <v>3.55</v>
       </c>
       <c r="P65">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
         <v>2.21</v>
@@ -10925,10 +10925,10 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="V65">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W65">
         <v>1.15</v>
@@ -10937,25 +10937,25 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA65">
         <v>1.53</v>
       </c>
       <c r="AB65">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC65">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD65">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF65">
         <v>1.5</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P66">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="Q66">
         <v>2</v>
@@ -11088,10 +11088,10 @@
         <v>4.65</v>
       </c>
       <c r="U66">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="V66">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="W66">
         <v>1.24</v>
@@ -11112,10 +11112,10 @@
         <v>3.4</v>
       </c>
       <c r="AC66">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD66">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="AE66">
         <v>1.41</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="Q67">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R67">
         <v>2.38</v>
@@ -11257,13 +11257,13 @@
         <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
         <v>4.55</v>
@@ -11278,7 +11278,7 @@
         <v>2.34</v>
       </c>
       <c r="AD67">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AE67">
         <v>1.17</v>
@@ -11393,25 +11393,25 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O68">
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q68">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="R68">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="U68">
         <v>2.62</v>
@@ -11420,7 +11420,7 @@
         <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.03</v>
@@ -11432,7 +11432,7 @@
         <v>3.63</v>
       </c>
       <c r="AA68">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB68">
         <v>1.9</v>
@@ -11450,7 +11450,7 @@
         <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,19 +11556,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O69">
         <v>4.15</v>
       </c>
       <c r="P69">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q69">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="R69">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S69">
         <v>1.19</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>4.16</v>
       </c>
       <c r="AA70">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB70">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC70">
         <v>2.56</v>
@@ -11885,10 +11885,10 @@
         <v>1.25</v>
       </c>
       <c r="O71">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="P71">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11900,7 +11900,7 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="U71">
         <v>2.25</v>
@@ -11921,7 +11921,7 @@
         <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB71">
         <v>2.28</v>
@@ -12211,16 +12211,16 @@
         <v>1.44</v>
       </c>
       <c r="O73">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="P73">
-        <v>6.5</v>
+        <v>6.57</v>
       </c>
       <c r="Q73">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="R73">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
         <v>1.29</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK73">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,16 +12371,16 @@
         </is>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P74">
         <v>2.2</v>
       </c>
       <c r="Q74">
-        <v>3.84</v>
+        <v>3.47</v>
       </c>
       <c r="R74">
         <v>2.02</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
+        <v>1.27</v>
+      </c>
+      <c r="AK74">
         <v>1.3</v>
-      </c>
-      <c r="AK74">
-        <v>1.34</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P75">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q75">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R75">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S75">
         <v>1.29</v>
@@ -12573,10 +12573,10 @@
         <v>4.05</v>
       </c>
       <c r="AA75">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC75">
         <v>2.87</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
         <v>1.77</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O76">
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q76">
         <v>2.41</v>
@@ -12742,10 +12742,10 @@
         <v>2.45</v>
       </c>
       <c r="AC76">
-        <v>2.24</v>
+        <v>2.35</v>
       </c>
       <c r="AD76">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE76">
         <v>1.2</v>
@@ -13062,10 +13062,10 @@
         <v>2.38</v>
       </c>
       <c r="AA78">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AB78">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AC78">
         <v>4.9</v>
@@ -13077,10 +13077,10 @@
         <v>1.01</v>
       </c>
       <c r="AF78">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AG78">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O79">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R79">
         <v>2.3</v>
@@ -13210,10 +13210,10 @@
         <v>2.38</v>
       </c>
       <c r="V79">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
         <v>1.04</v>
@@ -13225,7 +13225,7 @@
         <v>4.15</v>
       </c>
       <c r="AA79">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB79">
         <v>2.15</v>
@@ -13240,7 +13240,7 @@
         <v>1.17</v>
       </c>
       <c r="AF79">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG79">
         <v>2.3</v>
@@ -13533,7 +13533,7 @@
         <v>4</v>
       </c>
       <c r="U81">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V81">
         <v>1.65</v>
@@ -13678,31 +13678,31 @@
         <v>2.08</v>
       </c>
       <c r="O82">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q82">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R82">
         <v>2.3</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U82">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="V82">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W82">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O83">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P83">
-        <v>4.09</v>
+        <v>3.7</v>
       </c>
       <c r="Q83">
         <v>2.1</v>
@@ -13865,7 +13865,7 @@
         <v>1.65</v>
       </c>
       <c r="W83">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>1.01</v>
@@ -14016,7 +14016,7 @@
         <v>2.75</v>
       </c>
       <c r="S84">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
         <v>4.8</v>
@@ -14034,7 +14034,7 @@
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
         <v>7</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
         <v>1.77</v>
@@ -14173,10 +14173,10 @@
         <v>2.83</v>
       </c>
       <c r="Q85">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="R85">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
         <v>1.22</v>
@@ -14185,7 +14185,7 @@
         <v>3.85</v>
       </c>
       <c r="U85">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V85">
         <v>1.65</v>
@@ -14221,7 +14221,7 @@
         <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK85">
         <v>1.67</v>
@@ -14336,10 +14336,10 @@
         <v>2.16</v>
       </c>
       <c r="Q86">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R86">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S86">
         <v>1.2</v>
@@ -14372,7 +14372,7 @@
         <v>2.6</v>
       </c>
       <c r="AC86">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD86">
         <v>1.68</v>
@@ -14381,10 +14381,10 @@
         <v>1.21</v>
       </c>
       <c r="AF86">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG86">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14532,7 +14532,7 @@
         <v>1.9</v>
       </c>
       <c r="AB87">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC87">
         <v>3.2</v>
@@ -14680,7 +14680,7 @@
         <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14692,10 +14692,10 @@
         <v>4.8</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB88">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AC88">
         <v>2.37</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
         <v>1.67</v>
@@ -14822,7 +14822,7 @@
         <v>3.5</v>
       </c>
       <c r="P89">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
@@ -14831,19 +14831,19 @@
         <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="U89">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="V89">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
         <v>1.01</v>
@@ -14855,10 +14855,10 @@
         <v>3.9</v>
       </c>
       <c r="AA89">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB89">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
         <v>2.74</v>
@@ -14889,7 +14889,7 @@
         <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O90">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q90">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="R90">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="S90">
         <v>1.39</v>
@@ -15000,13 +15000,13 @@
         <v>2.96</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="V90">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.03</v>
@@ -15015,16 +15015,16 @@
         <v>1.3</v>
       </c>
       <c r="Z90">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="AA90">
         <v>1.9</v>
       </c>
       <c r="AB90">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC90">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="AD90">
         <v>1.31</v>
@@ -15033,10 +15033,10 @@
         <v>1.07</v>
       </c>
       <c r="AF90">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK90">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,7 +15148,7 @@
         <v>3.2</v>
       </c>
       <c r="P91">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
         <v>2.65</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O92">
         <v>3.85</v>
@@ -15314,7 +15314,7 @@
         <v>2.03</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
         <v>2.64</v>
@@ -15347,7 +15347,7 @@
         <v>1.43</v>
       </c>
       <c r="AB92">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC92">
         <v>2.15</v>
@@ -15510,7 +15510,7 @@
         <v>1.66</v>
       </c>
       <c r="AB93">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC93">
         <v>2.62</v>
@@ -16612,16 +16612,16 @@
         <v>3.5</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="Q100">
-        <v>3.75</v>
+        <v>4.13</v>
       </c>
       <c r="R100">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S100">
         <v>1.29</v>
@@ -16630,7 +16630,7 @@
         <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V100">
         <v>1.47</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="O101">
         <v>4.6</v>
       </c>
       <c r="P101">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Q101">
         <v>4.22</v>
@@ -16811,10 +16811,10 @@
         <v>6</v>
       </c>
       <c r="AA101">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB101">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC101">
         <v>2.03</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="O103">
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="Q103">
         <v>1.93</v>
@@ -17137,7 +17137,7 @@
         <v>4.95</v>
       </c>
       <c r="AA103">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB103">
         <v>2.46</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O104">
         <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -17288,7 +17288,7 @@
         <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X104">
         <v>1.04</v>
@@ -17303,7 +17303,7 @@
         <v>1.94</v>
       </c>
       <c r="AB104">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC104">
         <v>3.14</v>
@@ -17430,10 +17430,10 @@
         <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="Q105">
-        <v>3.08</v>
+        <v>2.76</v>
       </c>
       <c r="R105">
         <v>2.2</v>
@@ -17442,7 +17442,7 @@
         <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="U105">
         <v>2.55</v>
@@ -17472,7 +17472,7 @@
         <v>2.64</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE105">
         <v>1.16</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK105">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,10 +17590,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="O106">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P106">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q106">
         <v>6.18</v>
@@ -17756,31 +17756,31 @@
         <v>3.8</v>
       </c>
       <c r="P107">
-        <v>5.17</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R107">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T107">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="U107">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="V107">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W107">
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y107">
         <v>1.29</v>
@@ -17789,25 +17789,25 @@
         <v>3.4</v>
       </c>
       <c r="AA107">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AB107">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AC107">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE107">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF107">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG107">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17922,10 +17922,10 @@
         <v>7.5</v>
       </c>
       <c r="Q108">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R108">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="S108">
         <v>1.2</v>
@@ -17934,10 +17934,10 @@
         <v>4.2</v>
       </c>
       <c r="U108">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V108">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W108">
         <v>1.2</v>
@@ -17949,22 +17949,22 @@
         <v>1.1</v>
       </c>
       <c r="Z108">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA108">
         <v>1.4</v>
       </c>
       <c r="AB108">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC108">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AD108">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="AE108">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF108">
         <v>1.75</v>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK108">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18242,10 +18242,10 @@
         <v>1.61</v>
       </c>
       <c r="O110">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q110">
         <v>2.15</v>
@@ -18278,10 +18278,10 @@
         <v>3.2</v>
       </c>
       <c r="AA110">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AB110">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC110">
         <v>3.28</v>
@@ -18402,19 +18402,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="O111">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P111">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q111">
         <v>1.3</v>
       </c>
       <c r="R111">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S111">
         <v>1.18</v>
@@ -18426,16 +18426,16 @@
         <v>1.83</v>
       </c>
       <c r="V111">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="W111">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X111">
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z111">
         <v>6.55</v>
@@ -18444,16 +18444,16 @@
         <v>1.36</v>
       </c>
       <c r="AB111">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="AC111">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AD111">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE111">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF111">
         <v>2.75</v>
@@ -18571,7 +18571,7 @@
         <v>3.68</v>
       </c>
       <c r="P112">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="Q112">
         <v>2.26</v>
@@ -18607,7 +18607,7 @@
         <v>1.9</v>
       </c>
       <c r="AB112">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC112">
         <v>3.5</v>
@@ -18616,7 +18616,7 @@
         <v>1.25</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF112">
         <v>1.91</v>
@@ -18731,7 +18731,7 @@
         <v>1.97</v>
       </c>
       <c r="O113">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P113">
         <v>3.15</v>
@@ -18767,10 +18767,10 @@
         <v>3.48</v>
       </c>
       <c r="AA113">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB113">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC113">
         <v>2.88</v>
@@ -18782,10 +18782,10 @@
         <v>1.09</v>
       </c>
       <c r="AF113">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG113">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.3</v>
       </c>
       <c r="AK113">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19549,7 +19549,7 @@
         <v>3.45</v>
       </c>
       <c r="P118">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="Q118">
         <v>2.25</v>
@@ -19582,10 +19582,10 @@
         <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB118">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC118">
         <v>3.28</v>
@@ -20035,7 +20035,7 @@
         <v>2.09</v>
       </c>
       <c r="O121">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="P121">
         <v>2.99</v>
@@ -20074,7 +20074,7 @@
         <v>1.83</v>
       </c>
       <c r="AB121">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC121">
         <v>3.08</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
         <v>3.24</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
         <v>1.61</v>
@@ -2458,22 +2458,22 @@
         <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC13">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
         <v>1.57</v>
@@ -2482,10 +2482,10 @@
         <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AD20">
         <v>1.19</v>
@@ -3623,10 +3623,10 @@
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
         <v>1.35</v>
@@ -3771,16 +3771,16 @@
         <v>2.74</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB21">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
         <v>1.03</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -4115,7 +4115,7 @@
         <v>2.25</v>
       </c>
       <c r="AG23">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         <v>3</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -5395,16 +5395,16 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB31">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AC31">
         <v>2.2</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O34">
         <v>3.42</v>
@@ -5881,13 +5881,13 @@
         <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
         <v>1.83</v>
@@ -5896,10 +5896,10 @@
         <v>1.93</v>
       </c>
       <c r="AC34">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
         <v>1.13</v>
@@ -6346,7 +6346,7 @@
         <v>4.2</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q37">
         <v>1.91</v>
@@ -6370,13 +6370,13 @@
         <v>1.11</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>3.96</v>
+        <v>4.33</v>
       </c>
       <c r="AA37">
         <v>1.7</v>
@@ -6385,19 +6385,19 @@
         <v>2.06</v>
       </c>
       <c r="AC37">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AD37">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -7327,13 +7327,13 @@
         <v>4.75</v>
       </c>
       <c r="Q43">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R43">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T43">
         <v>4.6</v>
@@ -7372,10 +7372,10 @@
         <v>1.39</v>
       </c>
       <c r="AF43">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK43">
         <v>2.48</v>
@@ -8471,52 +8471,52 @@
         <v>1.73</v>
       </c>
       <c r="R50">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S50">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T50">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="U50">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V50">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W50">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>5.95</v>
+        <v>5.7</v>
       </c>
       <c r="AA50">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB50">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AC50">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AD50">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE50">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK50">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8679,7 +8679,7 @@
         <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -9929,19 +9929,19 @@
         <v>3.22</v>
       </c>
       <c r="O59">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
         <v>2.01</v>
       </c>
       <c r="Q59">
-        <v>3.13</v>
+        <v>3.64</v>
       </c>
       <c r="R59">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T59">
         <v>3.6</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AK59">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10744,16 +10744,16 @@
         <v>1.73</v>
       </c>
       <c r="O64">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q64">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S64">
         <v>1.29</v>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11073,7 +11073,7 @@
         <v>4.5</v>
       </c>
       <c r="P66">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="Q66">
         <v>2</v>
@@ -11094,7 +11094,7 @@
         <v>1.94</v>
       </c>
       <c r="W66">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X66">
         <v>1</v>
@@ -11106,7 +11106,7 @@
         <v>7.2</v>
       </c>
       <c r="AA66">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB66">
         <v>3.4</v>
@@ -11118,7 +11118,7 @@
         <v>1.99</v>
       </c>
       <c r="AE66">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF66">
         <v>1.33</v>
@@ -11924,7 +11924,7 @@
         <v>1.55</v>
       </c>
       <c r="AB71">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC71">
         <v>2.39</v>
@@ -14662,10 +14662,10 @@
         <v>2.89</v>
       </c>
       <c r="Q88">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="R88">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="S88">
         <v>1.25</v>
@@ -14686,7 +14686,7 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
         <v>4.8</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK88">
         <v>1.67</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.93</v>
+        <v>3.6</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P89">
         <v>1.75</v>
@@ -14828,7 +14828,7 @@
         <v>4.62</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
         <v>1.35</v>
@@ -15148,13 +15148,13 @@
         <v>3.2</v>
       </c>
       <c r="P91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S91">
         <v>1.38</v>
@@ -15163,13 +15163,13 @@
         <v>2.65</v>
       </c>
       <c r="U91">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V91">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
         <v>1.01</v>
@@ -15199,7 +15199,7 @@
         <v>1.87</v>
       </c>
       <c r="AG91">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O92">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>2.03</v>
+        <v>2.16</v>
       </c>
       <c r="Q92">
         <v>3.4</v>
@@ -15344,19 +15344,19 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB92">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC92">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD92">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE92">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
         <v>1.4</v>
@@ -15640,55 +15640,55 @@
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T94">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U94">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AD94">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE94">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK94">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O95">
         <v>3.6</v>
@@ -15803,7 +15803,7 @@
         <v>3.2</v>
       </c>
       <c r="Q95">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="R95">
         <v>2.39</v>
@@ -15833,25 +15833,25 @@
         <v>4.95</v>
       </c>
       <c r="AA95">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB95">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC95">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD95">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE95">
         <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AG95">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15966,7 +15966,7 @@
         <v>2</v>
       </c>
       <c r="Q96">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="R96">
         <v>2.44</v>
@@ -15996,10 +15996,10 @@
         <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB96">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC96">
         <v>2.55</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
         <v>1.3</v>
@@ -16144,7 +16144,7 @@
         <v>2.5</v>
       </c>
       <c r="V97">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W97">
         <v>1.11</v>
@@ -16159,25 +16159,25 @@
         <v>4.03</v>
       </c>
       <c r="AA97">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB97">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC97">
         <v>2.83</v>
       </c>
       <c r="AD97">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE97">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF97">
         <v>1.61</v>
       </c>
       <c r="AG97">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16446,22 +16446,22 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P99">
         <v>1.53</v>
       </c>
       <c r="Q99">
-        <v>5</v>
+        <v>5.29</v>
       </c>
       <c r="R99">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T99">
         <v>3.22</v>
@@ -16470,10 +16470,10 @@
         <v>2.38</v>
       </c>
       <c r="V99">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X99">
         <v>1.03</v>
@@ -16503,7 +16503,7 @@
         <v>1.7</v>
       </c>
       <c r="AG99">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.22</v>
+        <v>2.36</v>
       </c>
       <c r="AK99">
         <v>1.15</v>
@@ -16778,13 +16778,13 @@
         <v>4.6</v>
       </c>
       <c r="P101">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Q101">
         <v>4.22</v>
       </c>
       <c r="R101">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="S101">
         <v>1.2</v>
@@ -16814,16 +16814,16 @@
         <v>1.38</v>
       </c>
       <c r="AB101">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC101">
         <v>2.03</v>
       </c>
       <c r="AD101">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE101">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF101">
         <v>1.51</v>
@@ -17792,7 +17792,7 @@
         <v>1.87</v>
       </c>
       <c r="AB107">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
         <v>3.4</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O108">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P108">
         <v>7.5</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="O110">
         <v>3.63</v>
       </c>
       <c r="P110">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q110">
         <v>2.15</v>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O112">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P112">
-        <v>4.78</v>
+        <v>4.25</v>
       </c>
       <c r="Q112">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="R112">
         <v>2.13</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O113">
         <v>3.18</v>
       </c>
       <c r="P113">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="Q113">
         <v>2.5</v>
@@ -19552,7 +19552,7 @@
         <v>4.3</v>
       </c>
       <c r="Q118">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R118">
         <v>2.15</v>
@@ -19582,10 +19582,10 @@
         <v>3.14</v>
       </c>
       <c r="AA118">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB118">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC118">
         <v>3.28</v>
@@ -20038,7 +20038,7 @@
         <v>3.21</v>
       </c>
       <c r="P121">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q121">
         <v>2.7</v>
@@ -20074,7 +20074,7 @@
         <v>1.83</v>
       </c>
       <c r="AB121">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC121">
         <v>3.08</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU121"/>
+  <dimension ref="A1:AU118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1782,7 +1782,7 @@
         <v>2.87</v>
       </c>
       <c r="P9">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q9">
         <v>3.24</v>
@@ -3753,7 +3753,7 @@
         <v>2.55</v>
       </c>
       <c r="U21">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V21">
         <v>1.3</v>
@@ -3762,16 +3762,16 @@
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z21">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA21">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
         <v>1.61</v>
@@ -3789,7 +3789,7 @@
         <v>1.86</v>
       </c>
       <c r="AG21">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
         <v>2.8</v>
@@ -4740,28 +4740,28 @@
         <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
         <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC27">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD27">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
         <v>1.7</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="O28">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="P28">
         <v>2.46</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA28">
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>3.1</v>
       </c>
       <c r="O35">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P35">
         <v>2.25</v>
@@ -6032,7 +6032,7 @@
         <v>1.55</v>
       </c>
       <c r="T35">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="U35">
         <v>3.7</v>
@@ -6044,34 +6044,34 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y35">
         <v>1.57</v>
       </c>
       <c r="Z35">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AA35">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="AB35">
         <v>1.4</v>
       </c>
       <c r="AC35">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD35">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>3.62</v>
       </c>
       <c r="R36">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="S36">
         <v>1.41</v>
@@ -6207,7 +6207,7 @@
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
         <v>1.33</v>
@@ -6696,31 +6696,31 @@
         <v>1.05</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
         <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD39">
         <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
         <v>1.85</v>
@@ -6995,7 +6995,7 @@
         <v>1.35</v>
       </c>
       <c r="O41">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P41">
         <v>8.949999999999999</v>
@@ -7813,13 +7813,13 @@
         <v>4.15</v>
       </c>
       <c r="P46">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>4.03</v>
+        <v>5.12</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7840,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
         <v>3.95</v>
@@ -7880,7 +7880,7 @@
         <v>2.15</v>
       </c>
       <c r="AK46">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="Q47">
         <v>2.47</v>
@@ -8009,10 +8009,10 @@
         <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB47">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AC47">
         <v>2.56</v>
@@ -8021,7 +8021,7 @@
         <v>1.4</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF47">
         <v>1.57</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8160,7 +8160,7 @@
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8172,10 +8172,10 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
         <v>2.31</v>
@@ -8299,7 +8299,7 @@
         <v>1.95</v>
       </c>
       <c r="O49">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>3.2</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK52">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="O54">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="P54">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB54">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9280,13 +9280,13 @@
         <v>3.7</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q55">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="R55">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9295,13 +9295,13 @@
         <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="V55">
         <v>1.57</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,13 +9313,13 @@
         <v>4.66</v>
       </c>
       <c r="AA55">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC55">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="AD55">
         <v>1.49</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK55">
         <v>2.05</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
         <v>2.86</v>
@@ -9479,7 +9479,7 @@
         <v>1.48</v>
       </c>
       <c r="AB56">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC56">
         <v>2.15</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="O57">
         <v>3.6</v>
       </c>
       <c r="P57">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q57">
         <v>2.12</v>
@@ -9621,7 +9621,7 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="V57">
         <v>1.56</v>
@@ -9642,7 +9642,7 @@
         <v>1.61</v>
       </c>
       <c r="AB57">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -10092,7 +10092,7 @@
         <v>10</v>
       </c>
       <c r="O60">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="P60">
         <v>1.25</v>
@@ -10125,13 +10125,13 @@
         <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>6.9</v>
+        <v>7.07</v>
       </c>
       <c r="AA60">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="AC60">
         <v>1.84</v>
@@ -10162,7 +10162,7 @@
         <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P61">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="Q61">
         <v>2.95</v>
@@ -10306,7 +10306,7 @@
         <v>1.17</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG61">
         <v>2.7</v>
@@ -10418,7 +10418,7 @@
         <v>2.5</v>
       </c>
       <c r="O62">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="P62">
         <v>2.9</v>
@@ -10433,7 +10433,7 @@
         <v>1.6</v>
       </c>
       <c r="T62">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="U62">
         <v>3.9</v>
@@ -10454,7 +10454,7 @@
         <v>2.25</v>
       </c>
       <c r="AA62">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB62">
         <v>1.36</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK62">
         <v>1.45</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="O63">
         <v>2.8</v>
@@ -10623,13 +10623,13 @@
         <v>1.5</v>
       </c>
       <c r="AC63">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD63">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF63">
         <v>2</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O65">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q65">
         <v>2.21</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q68">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11420,7 +11420,7 @@
         <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
         <v>1.03</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
         <v>1.65</v>
@@ -12211,10 +12211,10 @@
         <v>1.44</v>
       </c>
       <c r="O73">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P73">
-        <v>6.57</v>
+        <v>6</v>
       </c>
       <c r="Q73">
         <v>1.9</v>
@@ -12226,7 +12226,7 @@
         <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="U73">
         <v>2.6</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q74">
         <v>3.47</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="O75">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P75">
         <v>3.35</v>
@@ -12573,10 +12573,10 @@
         <v>4.05</v>
       </c>
       <c r="AA75">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB75">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC75">
         <v>2.87</v>
@@ -12607,7 +12607,7 @@
         <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="O76">
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q76">
         <v>2.41</v>
@@ -12748,13 +12748,13 @@
         <v>1.56</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF76">
         <v>1.44</v>
       </c>
       <c r="AG76">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK76">
         <v>1.79</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -13044,7 +13044,7 @@
         <v>2.45</v>
       </c>
       <c r="U78">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V78">
         <v>1.25</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q79">
         <v>2.56</v>
@@ -13213,10 +13213,10 @@
         <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
         <v>1.16</v>
@@ -13234,10 +13234,10 @@
         <v>2.52</v>
       </c>
       <c r="AD79">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE79">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
         <v>1.55</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.5</v>
@@ -14532,7 +14532,7 @@
         <v>1.9</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC87">
         <v>3.2</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O89">
         <v>3.6</v>
@@ -14831,10 +14831,10 @@
         <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T89">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="U89">
         <v>2.44</v>
@@ -14852,7 +14852,7 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK89">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,22 +14979,22 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P90">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="Q90">
         <v>2.71</v>
       </c>
       <c r="R90">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S90">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
         <v>2.96</v>
@@ -15021,13 +15021,13 @@
         <v>1.9</v>
       </c>
       <c r="AB90">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC90">
         <v>3.37</v>
       </c>
       <c r="AD90">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE90">
         <v>1.07</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK90">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15308,13 +15308,13 @@
         <v>3.2</v>
       </c>
       <c r="O92">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P92">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q92">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R92">
         <v>2.64</v>
@@ -15326,7 +15326,7 @@
         <v>3.8</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="V92">
         <v>1.66</v>
@@ -15344,10 +15344,10 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB92">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AC92">
         <v>2.2</v>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.67</v>
+        <v>1.21</v>
       </c>
       <c r="AK92">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.91</v>
+        <v>4.6</v>
       </c>
       <c r="O95">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P95">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="Q95">
-        <v>2.25</v>
+        <v>5.29</v>
       </c>
       <c r="R95">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S95">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T95">
-        <v>3.55</v>
+        <v>3.22</v>
       </c>
       <c r="U95">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z95">
-        <v>4.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB95">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="AC95">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF95">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AG95">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>2.36</v>
       </c>
       <c r="AK95">
-        <v>1.8</v>
+        <v>1.15</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Q96">
-        <v>3.84</v>
+        <v>2.25</v>
       </c>
       <c r="R96">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="S96">
+        <v>1.22</v>
+      </c>
+      <c r="T96">
+        <v>3.55</v>
+      </c>
+      <c r="U96">
+        <v>2.24</v>
+      </c>
+      <c r="V96">
+        <v>1.61</v>
+      </c>
+      <c r="W96">
+        <v>1.17</v>
+      </c>
+      <c r="X96">
+        <v>1.02</v>
+      </c>
+      <c r="Y96">
+        <v>1.11</v>
+      </c>
+      <c r="Z96">
+        <v>4.95</v>
+      </c>
+      <c r="AA96">
+        <v>1.53</v>
+      </c>
+      <c r="AB96">
+        <v>2.38</v>
+      </c>
+      <c r="AC96">
+        <v>2.27</v>
+      </c>
+      <c r="AD96">
+        <v>1.59</v>
+      </c>
+      <c r="AE96">
+        <v>1.25</v>
+      </c>
+      <c r="AF96">
+        <v>1.46</v>
+      </c>
+      <c r="AG96">
+        <v>2.53</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.3</v>
       </c>
-      <c r="T96">
-        <v>3.4</v>
-      </c>
-      <c r="U96">
-        <v>2.4</v>
-      </c>
-      <c r="V96">
-        <v>1.54</v>
-      </c>
-      <c r="W96">
-        <v>1.12</v>
-      </c>
-      <c r="X96">
-        <v>1.01</v>
-      </c>
-      <c r="Y96">
-        <v>1.15</v>
-      </c>
-      <c r="Z96">
-        <v>4.25</v>
-      </c>
-      <c r="AA96">
-        <v>1.61</v>
-      </c>
-      <c r="AB96">
-        <v>2.25</v>
-      </c>
-      <c r="AC96">
-        <v>2.55</v>
-      </c>
-      <c r="AD96">
-        <v>1.51</v>
-      </c>
-      <c r="AE96">
-        <v>1.14</v>
-      </c>
-      <c r="AF96">
-        <v>1.53</v>
-      </c>
-      <c r="AG96">
-        <v>2.4</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.29</v>
-      </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O97">
         <v>3.5</v>
       </c>
       <c r="P97">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="Q97">
-        <v>2.74</v>
+        <v>3.84</v>
       </c>
       <c r="R97">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="S97">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T97">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U97">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V97">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W97">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X97">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y97">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z97">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="AA97">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB97">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC97">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AD97">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AE97">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF97">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG97">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK97">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P98">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q98">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="R98">
         <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T98">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U98">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V98">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W98">
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z98">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AA98">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC98">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG98">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK98">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>1.53</v>
+        <v>3.2</v>
       </c>
       <c r="Q99">
-        <v>5.29</v>
+        <v>2.57</v>
       </c>
       <c r="R99">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="S99">
+        <v>1.29</v>
+      </c>
+      <c r="T99">
+        <v>3.3</v>
+      </c>
+      <c r="U99">
+        <v>2.6</v>
+      </c>
+      <c r="V99">
+        <v>1.42</v>
+      </c>
+      <c r="W99">
+        <v>1.11</v>
+      </c>
+      <c r="X99">
+        <v>1.01</v>
+      </c>
+      <c r="Y99">
+        <v>1.2</v>
+      </c>
+      <c r="Z99">
+        <v>3.72</v>
+      </c>
+      <c r="AA99">
+        <v>1.85</v>
+      </c>
+      <c r="AB99">
+        <v>1.95</v>
+      </c>
+      <c r="AC99">
+        <v>2.88</v>
+      </c>
+      <c r="AD99">
+        <v>1.32</v>
+      </c>
+      <c r="AE99">
+        <v>1.08</v>
+      </c>
+      <c r="AF99">
+        <v>1.67</v>
+      </c>
+      <c r="AG99">
+        <v>2.11</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
         <v>1.28</v>
       </c>
-      <c r="T99">
-        <v>3.22</v>
-      </c>
-      <c r="U99">
-        <v>2.38</v>
-      </c>
-      <c r="V99">
-        <v>1.5</v>
-      </c>
-      <c r="W99">
-        <v>1.09</v>
-      </c>
-      <c r="X99">
-        <v>1.03</v>
-      </c>
-      <c r="Y99">
-        <v>1.16</v>
-      </c>
-      <c r="Z99">
-        <v>4.05</v>
-      </c>
-      <c r="AA99">
-        <v>1.64</v>
-      </c>
-      <c r="AB99">
-        <v>2.17</v>
-      </c>
-      <c r="AC99">
-        <v>2.62</v>
-      </c>
-      <c r="AD99">
-        <v>1.42</v>
-      </c>
-      <c r="AE99">
-        <v>1.14</v>
-      </c>
-      <c r="AF99">
-        <v>1.7</v>
-      </c>
-      <c r="AG99">
-        <v>2</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>2.36</v>
-      </c>
       <c r="AK99">
-        <v>1.15</v>
+        <v>1.75</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,28 +16609,28 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O100">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Q100">
-        <v>4.13</v>
+        <v>3.75</v>
       </c>
       <c r="R100">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="S100">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
         <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V100">
         <v>1.47</v>
@@ -16639,7 +16639,7 @@
         <v>1.08</v>
       </c>
       <c r="X100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
         <v>1.21</v>
@@ -16654,13 +16654,13 @@
         <v>1.93</v>
       </c>
       <c r="AC100">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD100">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17104,7 +17104,7 @@
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q103">
         <v>1.93</v>
@@ -17113,7 +17113,7 @@
         <v>2.67</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T103">
         <v>4</v>
@@ -17140,7 +17140,7 @@
         <v>1.47</v>
       </c>
       <c r="AB103">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AC103">
         <v>2.38</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK103">
         <v>2.79</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="O104">
         <v>3.5</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="Q105">
         <v>2.76</v>
@@ -17472,7 +17472,7 @@
         <v>2.64</v>
       </c>
       <c r="AD105">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE105">
         <v>1.16</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK105">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O106">
         <v>5.8</v>
@@ -17638,7 +17638,7 @@
         <v>1.53</v>
       </c>
       <c r="AE106">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF106">
         <v>2</v>
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>6.14</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-30 21:00:00</t>
+          <t>2026-10-30 21:15:00</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="O118">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="P118">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S118">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T118">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U118">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="Z118">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AA118">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB118">
         <v>1.85</v>
       </c>
       <c r="AC118">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD118">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE118">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF118">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG118">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK118">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19646,495 +19646,6 @@
         <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Aurora</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-      <c r="X119">
-        <v>0</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119">
-        <v>0</v>
-      </c>
-      <c r="AB119">
-        <v>0</v>
-      </c>
-      <c r="AC119">
-        <v>0</v>
-      </c>
-      <c r="AD119">
-        <v>0</v>
-      </c>
-      <c r="AE119">
-        <v>0</v>
-      </c>
-      <c r="AF119">
-        <v>0</v>
-      </c>
-      <c r="AG119">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-      <c r="AK119">
-        <v>0</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Deportes Temuco</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
-      <c r="U120">
-        <v>0</v>
-      </c>
-      <c r="V120">
-        <v>0</v>
-      </c>
-      <c r="W120">
-        <v>0</v>
-      </c>
-      <c r="X120">
-        <v>0</v>
-      </c>
-      <c r="Y120">
-        <v>0</v>
-      </c>
-      <c r="Z120">
-        <v>0</v>
-      </c>
-      <c r="AA120">
-        <v>0</v>
-      </c>
-      <c r="AB120">
-        <v>0</v>
-      </c>
-      <c r="AC120">
-        <v>0</v>
-      </c>
-      <c r="AD120">
-        <v>0</v>
-      </c>
-      <c r="AE120">
-        <v>0</v>
-      </c>
-      <c r="AF120">
-        <v>0</v>
-      </c>
-      <c r="AG120">
-        <v>0</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>0</v>
-      </c>
-      <c r="AK120">
-        <v>0</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>2026-10-30 21:15:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N121">
-        <v>2.09</v>
-      </c>
-      <c r="O121">
-        <v>3.21</v>
-      </c>
-      <c r="P121">
-        <v>3.25</v>
-      </c>
-      <c r="Q121">
-        <v>2.7</v>
-      </c>
-      <c r="R121">
-        <v>2.2</v>
-      </c>
-      <c r="S121">
-        <v>1.35</v>
-      </c>
-      <c r="T121">
-        <v>3</v>
-      </c>
-      <c r="U121">
-        <v>2.64</v>
-      </c>
-      <c r="V121">
-        <v>1.38</v>
-      </c>
-      <c r="W121">
-        <v>1.04</v>
-      </c>
-      <c r="X121">
-        <v>1.01</v>
-      </c>
-      <c r="Y121">
-        <v>1.23</v>
-      </c>
-      <c r="Z121">
-        <v>3.42</v>
-      </c>
-      <c r="AA121">
-        <v>1.83</v>
-      </c>
-      <c r="AB121">
-        <v>1.85</v>
-      </c>
-      <c r="AC121">
-        <v>3.08</v>
-      </c>
-      <c r="AD121">
-        <v>1.28</v>
-      </c>
-      <c r="AE121">
-        <v>1.06</v>
-      </c>
-      <c r="AF121">
-        <v>1.67</v>
-      </c>
-      <c r="AG121">
-        <v>2.06</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.24</v>
-      </c>
-      <c r="AK121">
-        <v>1.57</v>
-      </c>
-      <c r="AL121">
-        <v>0</v>
-      </c>
-      <c r="AM121">
-        <v>-1</v>
-      </c>
-      <c r="AN121">
-        <v>-1</v>
-      </c>
-      <c r="AO121">
-        <v>-1</v>
-      </c>
-      <c r="AP121">
-        <v>-1</v>
-      </c>
-      <c r="AQ121">
-        <v>0</v>
-      </c>
-      <c r="AR121">
-        <v>0</v>
-      </c>
-      <c r="AS121">
-        <v>0</v>
-      </c>
-      <c r="AT121">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
         <is>
           <t>2026-10-30 22:00:00</t>
         </is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2434,13 +2434,13 @@
         <v>4.1</v>
       </c>
       <c r="P13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q13">
         <v>4.05</v>
       </c>
       <c r="R13">
-        <v>2.32</v>
+        <v>2.57</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2458,7 +2458,7 @@
         <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2467,19 +2467,19 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB13">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AD13">
         <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF13">
         <v>1.6</v>
@@ -2501,7 +2501,7 @@
         <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -4731,13 +4731,13 @@
         <v>2.77</v>
       </c>
       <c r="U27">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="V27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
         <v>1.05</v>
@@ -4746,13 +4746,13 @@
         <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA27">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
         <v>3.4</v>
@@ -4761,7 +4761,7 @@
         <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>1.7</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="Q28">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="S28">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="T28">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC28">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF28">
         <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5377,19 +5377,19 @@
         <v>2.45</v>
       </c>
       <c r="S31">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V31">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5401,25 +5401,25 @@
         <v>6</v>
       </c>
       <c r="AA31">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB31">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AC31">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AD31">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE31">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
         <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>2.35</v>
@@ -5866,16 +5866,16 @@
         <v>2.08</v>
       </c>
       <c r="S34">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
         <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.08</v>
@@ -6189,7 +6189,7 @@
         <v>3.62</v>
       </c>
       <c r="R36">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
         <v>1.41</v>
@@ -6207,7 +6207,7 @@
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
         <v>1.33</v>
@@ -6250,7 +6250,7 @@
         <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,16 +6349,16 @@
         <v>5.75</v>
       </c>
       <c r="Q37">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
         <v>2.45</v>
@@ -6391,13 +6391,13 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="V40">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
         <v>1.14</v>
@@ -6862,47 +6862,47 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="AA40">
+        <v>1.58</v>
+      </c>
+      <c r="AB40">
+        <v>2.27</v>
+      </c>
+      <c r="AC40">
+        <v>2.45</v>
+      </c>
+      <c r="AD40">
         <v>1.5</v>
       </c>
-      <c r="AB40">
-        <v>2.28</v>
-      </c>
-      <c r="AC40">
-        <v>2.29</v>
-      </c>
-      <c r="AD40">
+      <c r="AE40">
+        <v>1.17</v>
+      </c>
+      <c r="AF40">
+        <v>1.47</v>
+      </c>
+      <c r="AG40">
+        <v>2.39</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.4</v>
+      </c>
+      <c r="AK40">
         <v>1.53</v>
-      </c>
-      <c r="AE40">
-        <v>1.19</v>
-      </c>
-      <c r="AF40">
-        <v>1.45</v>
-      </c>
-      <c r="AG40">
-        <v>2.44</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.2</v>
-      </c>
-      <c r="AK40">
-        <v>1.57</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O41">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="P41">
-        <v>8.949999999999999</v>
+        <v>8</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O43">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q43">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R43">
         <v>2.72</v>
       </c>
       <c r="S43">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T43">
         <v>4.6</v>
@@ -7351,25 +7351,25 @@
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z43">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD43">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AE43">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF43">
         <v>1.38</v>
@@ -7819,7 +7819,7 @@
         <v>5.12</v>
       </c>
       <c r="R46">
-        <v>2.51</v>
+        <v>2.32</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7840,7 +7840,7 @@
         <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
         <v>3.95</v>
@@ -7852,19 +7852,19 @@
         <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AD46">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE46">
         <v>1.13</v>
       </c>
       <c r="AF46">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AK46">
         <v>1.18</v>
@@ -7976,7 +7976,7 @@
         <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="Q47">
         <v>2.47</v>
@@ -8009,10 +8009,10 @@
         <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB47">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AC47">
         <v>2.56</v>
@@ -8163,7 +8163,7 @@
         <v>1.15</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.12</v>
@@ -8175,16 +8175,16 @@
         <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="AD48">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AE48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK48">
         <v>1.62</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P49">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q49">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8317,10 +8317,10 @@
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
         <v>1.11</v>
@@ -8335,25 +8335,25 @@
         <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC49">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD49">
         <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q50">
+        <v>1.92</v>
+      </c>
+      <c r="R50">
+        <v>2.47</v>
+      </c>
+      <c r="S50">
+        <v>1.17</v>
+      </c>
+      <c r="T50">
+        <v>3.95</v>
+      </c>
+      <c r="U50">
+        <v>2</v>
+      </c>
+      <c r="V50">
         <v>1.73</v>
       </c>
-      <c r="R50">
-        <v>2.75</v>
-      </c>
-      <c r="S50">
-        <v>1.19</v>
-      </c>
-      <c r="T50">
-        <v>4.15</v>
-      </c>
-      <c r="U50">
-        <v>1.91</v>
-      </c>
-      <c r="V50">
-        <v>1.8</v>
-      </c>
       <c r="W50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z50">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AA50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB50">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AC50">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="O51">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q51">
-        <v>3.3</v>
+        <v>4.12</v>
       </c>
       <c r="R51">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T51">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U51">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AA51">
         <v>1.75</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD51">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="O52">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P52">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -8818,10 +8818,10 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -8842,7 +8842,7 @@
         <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9114,10 +9114,10 @@
         <v>2.98</v>
       </c>
       <c r="O54">
-        <v>3.31</v>
+        <v>3.54</v>
       </c>
       <c r="P54">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O55">
         <v>3.7</v>
@@ -9283,10 +9283,10 @@
         <v>4.1</v>
       </c>
       <c r="Q55">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="R55">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9301,19 +9301,19 @@
         <v>1.57</v>
       </c>
       <c r="W55">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z55">
         <v>4.66</v>
       </c>
       <c r="AA55">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB55">
         <v>2.33</v>
@@ -9322,10 +9322,10 @@
         <v>2.3</v>
       </c>
       <c r="AD55">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AE55">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF55">
         <v>1.57</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK55">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O56">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
         <v>2.86</v>
@@ -9467,7 +9467,7 @@
         <v>1.18</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
         <v>1.11</v>
@@ -9479,13 +9479,13 @@
         <v>1.48</v>
       </c>
       <c r="AB56">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD56">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE56">
         <v>1.25</v>
@@ -9633,13 +9633,13 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z57">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
         <v>2.25</v>
@@ -9769,7 +9769,7 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.37</v>
+        <v>2.18</v>
       </c>
       <c r="Q58">
         <v>3.2</v>
@@ -9793,10 +9793,10 @@
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z58">
         <v>3.84</v>
@@ -9929,16 +9929,16 @@
         <v>3.22</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P59">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="Q59">
-        <v>3.64</v>
+        <v>3.69</v>
       </c>
       <c r="R59">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S59">
         <v>1.23</v>
@@ -9965,7 +9965,7 @@
         <v>5.08</v>
       </c>
       <c r="AA59">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB59">
         <v>2.55</v>
@@ -10095,7 +10095,7 @@
         <v>6.5</v>
       </c>
       <c r="P60">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Q60">
         <v>6.86</v>
@@ -10131,7 +10131,7 @@
         <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC60">
         <v>1.84</v>
@@ -10146,7 +10146,7 @@
         <v>1.67</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -10762,7 +10762,7 @@
         <v>3.4</v>
       </c>
       <c r="U64">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V64">
         <v>1.55</v>
@@ -10786,13 +10786,13 @@
         <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AD64">
         <v>1.49</v>
       </c>
       <c r="AE64">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
@@ -10910,10 +10910,10 @@
         <v>3.7</v>
       </c>
       <c r="P65">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R65">
         <v>2.29</v>
@@ -10937,10 +10937,10 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="AA65">
         <v>1.53</v>
@@ -10955,7 +10955,7 @@
         <v>1.52</v>
       </c>
       <c r="AE65">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF65">
         <v>1.5</v>
@@ -11073,7 +11073,7 @@
         <v>4.5</v>
       </c>
       <c r="P66">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="Q66">
         <v>2</v>
@@ -11106,10 +11106,10 @@
         <v>7.2</v>
       </c>
       <c r="AA66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB66">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC66">
         <v>1.83</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O68">
         <v>3.4</v>
@@ -11405,7 +11405,7 @@
         <v>2.73</v>
       </c>
       <c r="R68">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11417,16 +11417,16 @@
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z68">
         <v>3.63</v>
@@ -11435,7 +11435,7 @@
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC68">
         <v>3.27</v>
@@ -11450,7 +11450,7 @@
         <v>1.67</v>
       </c>
       <c r="AG68">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O71">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P71">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11900,7 +11900,7 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="U71">
         <v>2.25</v>
@@ -11927,7 +11927,7 @@
         <v>2.35</v>
       </c>
       <c r="AC71">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AD71">
         <v>1.54</v>
@@ -11936,10 +11936,10 @@
         <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG71">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12214,10 +12214,10 @@
         <v>4.3</v>
       </c>
       <c r="P73">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q73">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R73">
         <v>2.3</v>
@@ -12226,7 +12226,7 @@
         <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="U73">
         <v>2.6</v>
@@ -12259,13 +12259,13 @@
         <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12374,10 +12374,10 @@
         <v>3</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q74">
         <v>3.47</v>
@@ -12386,7 +12386,7 @@
         <v>2.02</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T74">
         <v>2.82</v>
@@ -12395,7 +12395,7 @@
         <v>2.7</v>
       </c>
       <c r="V74">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W74">
         <v>1.08</v>
@@ -12407,13 +12407,13 @@
         <v>1.3</v>
       </c>
       <c r="Z74">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA74">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
         <v>3.34</v>
@@ -12422,10 +12422,10 @@
         <v>1.24</v>
       </c>
       <c r="AE74">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF74">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG74">
         <v>2</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK74">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12537,7 +12537,7 @@
         <v>1.99</v>
       </c>
       <c r="O75">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P75">
         <v>3.35</v>
@@ -12552,7 +12552,7 @@
         <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U75">
         <v>2.5</v>
@@ -12564,13 +12564,13 @@
         <v>1.11</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA75">
         <v>1.73</v>
@@ -12721,13 +12721,13 @@
         <v>2.17</v>
       </c>
       <c r="V76">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W76">
         <v>1.15</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
         <v>1.11</v>
@@ -12745,16 +12745,16 @@
         <v>2.35</v>
       </c>
       <c r="AD76">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE76">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
         <v>1.44</v>
       </c>
       <c r="AG76">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
         <v>1.79</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12872,7 +12872,7 @@
         <v>2.76</v>
       </c>
       <c r="R77">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12881,7 +12881,7 @@
         <v>2.87</v>
       </c>
       <c r="U77">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="V77">
         <v>1.36</v>
@@ -12896,7 +12896,7 @@
         <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="AA77">
         <v>2.1</v>
@@ -12911,7 +12911,7 @@
         <v>1.28</v>
       </c>
       <c r="AE77">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
         <v>1.75</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK77">
         <v>1.53</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O78">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P78">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="Q78">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R78">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S78">
         <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="U78">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="V78">
         <v>1.25</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
         <v>1.06</v>
       </c>
       <c r="Y78">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Z78">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AA78">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AC78">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD78">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE78">
         <v>1.01</v>
       </c>
       <c r="AF78">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AG78">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.4</v>
       </c>
       <c r="AK78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14499,34 +14499,34 @@
         <v>5.5</v>
       </c>
       <c r="Q87">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="R87">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="S87">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T87">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U87">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="V87">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z87">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AA87">
         <v>1.9</v>
@@ -14535,19 +14535,19 @@
         <v>1.87</v>
       </c>
       <c r="AC87">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="AD87">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG87">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14662,10 +14662,10 @@
         <v>2.89</v>
       </c>
       <c r="Q88">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R88">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="S88">
         <v>1.25</v>
@@ -14689,7 +14689,7 @@
         <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA88">
         <v>1.56</v>
@@ -14726,7 +14726,7 @@
         <v>1.29</v>
       </c>
       <c r="AK88">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15027,16 +15027,16 @@
         <v>3.37</v>
       </c>
       <c r="AD90">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE90">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
         <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y91">
         <v>1.33</v>
@@ -15184,16 +15184,16 @@
         <v>2.15</v>
       </c>
       <c r="AB91">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC91">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AD91">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF91">
         <v>1.87</v>
@@ -15495,7 +15495,7 @@
         <v>1.5</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
         <v>1.03</v>
@@ -15513,7 +15513,7 @@
         <v>2.05</v>
       </c>
       <c r="AC93">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD93">
         <v>1.42</v>
@@ -15541,7 +15541,7 @@
         <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>4.6</v>
+        <v>1.91</v>
       </c>
       <c r="O95">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
+        <v>3.2</v>
+      </c>
+      <c r="Q95">
+        <v>2.25</v>
+      </c>
+      <c r="R95">
+        <v>2.39</v>
+      </c>
+      <c r="S95">
+        <v>1.22</v>
+      </c>
+      <c r="T95">
+        <v>3.55</v>
+      </c>
+      <c r="U95">
+        <v>2.24</v>
+      </c>
+      <c r="V95">
+        <v>1.61</v>
+      </c>
+      <c r="W95">
+        <v>1.17</v>
+      </c>
+      <c r="X95">
+        <v>1.02</v>
+      </c>
+      <c r="Y95">
+        <v>1.11</v>
+      </c>
+      <c r="Z95">
+        <v>4.95</v>
+      </c>
+      <c r="AA95">
         <v>1.53</v>
       </c>
-      <c r="Q95">
-        <v>5.29</v>
-      </c>
-      <c r="R95">
-        <v>2.36</v>
-      </c>
-      <c r="S95">
-        <v>1.28</v>
-      </c>
-      <c r="T95">
-        <v>3.22</v>
-      </c>
-      <c r="U95">
+      <c r="AB95">
         <v>2.38</v>
       </c>
-      <c r="V95">
-        <v>1.5</v>
-      </c>
-      <c r="W95">
-        <v>1.09</v>
-      </c>
-      <c r="X95">
-        <v>1.03</v>
-      </c>
-      <c r="Y95">
-        <v>1.16</v>
-      </c>
-      <c r="Z95">
-        <v>4.05</v>
-      </c>
-      <c r="AA95">
-        <v>1.64</v>
-      </c>
-      <c r="AB95">
-        <v>2.17</v>
-      </c>
       <c r="AC95">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AD95">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF95">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AG95">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>2.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Q96">
+        <v>3.84</v>
+      </c>
+      <c r="R96">
+        <v>2.44</v>
+      </c>
+      <c r="S96">
+        <v>1.3</v>
+      </c>
+      <c r="T96">
+        <v>3.4</v>
+      </c>
+      <c r="U96">
+        <v>2.4</v>
+      </c>
+      <c r="V96">
+        <v>1.54</v>
+      </c>
+      <c r="W96">
+        <v>1.12</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.15</v>
+      </c>
+      <c r="Z96">
+        <v>4.25</v>
+      </c>
+      <c r="AA96">
+        <v>1.61</v>
+      </c>
+      <c r="AB96">
         <v>2.25</v>
       </c>
-      <c r="R96">
-        <v>2.39</v>
-      </c>
-      <c r="S96">
-        <v>1.22</v>
-      </c>
-      <c r="T96">
-        <v>3.55</v>
-      </c>
-      <c r="U96">
-        <v>2.24</v>
-      </c>
-      <c r="V96">
-        <v>1.61</v>
-      </c>
-      <c r="W96">
-        <v>1.17</v>
-      </c>
-      <c r="X96">
-        <v>1.02</v>
-      </c>
-      <c r="Y96">
-        <v>1.11</v>
-      </c>
-      <c r="Z96">
-        <v>4.95</v>
-      </c>
-      <c r="AA96">
+      <c r="AC96">
+        <v>2.55</v>
+      </c>
+      <c r="AD96">
+        <v>1.51</v>
+      </c>
+      <c r="AE96">
+        <v>1.14</v>
+      </c>
+      <c r="AF96">
         <v>1.53</v>
       </c>
-      <c r="AB96">
-        <v>2.38</v>
-      </c>
-      <c r="AC96">
-        <v>2.27</v>
-      </c>
-      <c r="AD96">
-        <v>1.59</v>
-      </c>
-      <c r="AE96">
-        <v>1.25</v>
-      </c>
-      <c r="AF96">
-        <v>1.46</v>
-      </c>
       <c r="AG96">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
+        <v>1.29</v>
+      </c>
+      <c r="AK96">
         <v>1.3</v>
-      </c>
-      <c r="AK96">
-        <v>1.8</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,65 +16120,65 @@
         </is>
       </c>
       <c r="N97">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O97">
         <v>3.5</v>
       </c>
       <c r="P97">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="Q97">
-        <v>3.84</v>
+        <v>2.74</v>
       </c>
       <c r="R97">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="S97">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T97">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U97">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V97">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W97">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z97">
-        <v>4.25</v>
+        <v>4.03</v>
       </c>
       <c r="AA97">
+        <v>1.75</v>
+      </c>
+      <c r="AB97">
+        <v>2.07</v>
+      </c>
+      <c r="AC97">
+        <v>2.83</v>
+      </c>
+      <c r="AD97">
+        <v>1.33</v>
+      </c>
+      <c r="AE97">
+        <v>1.09</v>
+      </c>
+      <c r="AF97">
         <v>1.61</v>
       </c>
-      <c r="AB97">
+      <c r="AG97">
         <v>2.25</v>
       </c>
-      <c r="AC97">
-        <v>2.55</v>
-      </c>
-      <c r="AD97">
-        <v>1.51</v>
-      </c>
-      <c r="AE97">
-        <v>1.14</v>
-      </c>
-      <c r="AF97">
-        <v>1.53</v>
-      </c>
-      <c r="AG97">
-        <v>2.4</v>
-      </c>
       <c r="AH97" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O98">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q98">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="R98">
         <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U98">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V98">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W98">
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4.03</v>
+        <v>3.72</v>
       </c>
       <c r="AA98">
+        <v>1.85</v>
+      </c>
+      <c r="AB98">
+        <v>1.95</v>
+      </c>
+      <c r="AC98">
+        <v>2.88</v>
+      </c>
+      <c r="AD98">
+        <v>1.32</v>
+      </c>
+      <c r="AE98">
+        <v>1.08</v>
+      </c>
+      <c r="AF98">
+        <v>1.67</v>
+      </c>
+      <c r="AG98">
+        <v>2.11</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <v>1.28</v>
+      </c>
+      <c r="AK98">
         <v>1.75</v>
-      </c>
-      <c r="AB98">
-        <v>2.07</v>
-      </c>
-      <c r="AC98">
-        <v>2.83</v>
-      </c>
-      <c r="AD98">
-        <v>1.33</v>
-      </c>
-      <c r="AE98">
-        <v>1.09</v>
-      </c>
-      <c r="AF98">
-        <v>1.61</v>
-      </c>
-      <c r="AG98">
-        <v>2.25</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.27</v>
-      </c>
-      <c r="AK98">
-        <v>1.62</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,65 +16446,65 @@
         </is>
       </c>
       <c r="N99">
+        <v>4.6</v>
+      </c>
+      <c r="O99">
+        <v>4.1</v>
+      </c>
+      <c r="P99">
+        <v>1.53</v>
+      </c>
+      <c r="Q99">
+        <v>5.29</v>
+      </c>
+      <c r="R99">
+        <v>2.36</v>
+      </c>
+      <c r="S99">
+        <v>1.28</v>
+      </c>
+      <c r="T99">
+        <v>3.22</v>
+      </c>
+      <c r="U99">
+        <v>2.38</v>
+      </c>
+      <c r="V99">
+        <v>1.5</v>
+      </c>
+      <c r="W99">
+        <v>1.09</v>
+      </c>
+      <c r="X99">
+        <v>1.03</v>
+      </c>
+      <c r="Y99">
+        <v>1.16</v>
+      </c>
+      <c r="Z99">
+        <v>4.05</v>
+      </c>
+      <c r="AA99">
+        <v>1.64</v>
+      </c>
+      <c r="AB99">
+        <v>2.17</v>
+      </c>
+      <c r="AC99">
+        <v>2.62</v>
+      </c>
+      <c r="AD99">
+        <v>1.42</v>
+      </c>
+      <c r="AE99">
+        <v>1.14</v>
+      </c>
+      <c r="AF99">
+        <v>1.7</v>
+      </c>
+      <c r="AG99">
         <v>2</v>
       </c>
-      <c r="O99">
-        <v>3.4</v>
-      </c>
-      <c r="P99">
-        <v>3.2</v>
-      </c>
-      <c r="Q99">
-        <v>2.57</v>
-      </c>
-      <c r="R99">
-        <v>2.18</v>
-      </c>
-      <c r="S99">
-        <v>1.29</v>
-      </c>
-      <c r="T99">
-        <v>3.3</v>
-      </c>
-      <c r="U99">
-        <v>2.6</v>
-      </c>
-      <c r="V99">
-        <v>1.42</v>
-      </c>
-      <c r="W99">
-        <v>1.11</v>
-      </c>
-      <c r="X99">
-        <v>1.01</v>
-      </c>
-      <c r="Y99">
-        <v>1.2</v>
-      </c>
-      <c r="Z99">
-        <v>3.72</v>
-      </c>
-      <c r="AA99">
-        <v>1.85</v>
-      </c>
-      <c r="AB99">
-        <v>1.95</v>
-      </c>
-      <c r="AC99">
-        <v>2.88</v>
-      </c>
-      <c r="AD99">
-        <v>1.32</v>
-      </c>
-      <c r="AE99">
-        <v>1.08</v>
-      </c>
-      <c r="AF99">
-        <v>1.67</v>
-      </c>
-      <c r="AG99">
-        <v>2.11</v>
-      </c>
       <c r="AH99" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.28</v>
+        <v>2.36</v>
       </c>
       <c r="AK99">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16814,22 +16814,22 @@
         <v>1.38</v>
       </c>
       <c r="AB101">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC101">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="AD101">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE101">
         <v>1.25</v>
       </c>
       <c r="AF101">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG101">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -17104,16 +17104,16 @@
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="Q103">
         <v>1.93</v>
       </c>
       <c r="R103">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="S103">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
         <v>4</v>
@@ -17131,10 +17131,10 @@
         <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z103">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AA103">
         <v>1.47</v>
@@ -17146,7 +17146,7 @@
         <v>2.38</v>
       </c>
       <c r="AD103">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE103">
         <v>1.22</v>
@@ -17276,13 +17276,13 @@
         <v>2.06</v>
       </c>
       <c r="S104">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T104">
         <v>3</v>
       </c>
       <c r="U104">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V104">
         <v>1.4</v>
@@ -17306,19 +17306,19 @@
         <v>1.88</v>
       </c>
       <c r="AC104">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD104">
         <v>1.27</v>
       </c>
       <c r="AE104">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF104">
         <v>1.73</v>
       </c>
       <c r="AG104">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17427,16 +17427,16 @@
         <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="P105">
         <v>2.51</v>
       </c>
       <c r="Q105">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R105">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S105">
         <v>1.29</v>
@@ -17448,7 +17448,7 @@
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W105">
         <v>1.12</v>
@@ -17472,7 +17472,7 @@
         <v>2.64</v>
       </c>
       <c r="AD105">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE105">
         <v>1.16</v>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="O106">
         <v>5.8</v>
@@ -17599,19 +17599,19 @@
         <v>6.18</v>
       </c>
       <c r="R106">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T106">
         <v>3.32</v>
       </c>
       <c r="U106">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V106">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
         <v>1.11</v>
@@ -17623,16 +17623,16 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA106">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AB106">
         <v>2.4</v>
       </c>
       <c r="AC106">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD106">
         <v>1.53</v>
@@ -17641,7 +17641,7 @@
         <v>1.21</v>
       </c>
       <c r="AF106">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG106">
         <v>1.75</v>
@@ -17756,7 +17756,7 @@
         <v>3.8</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -17765,16 +17765,16 @@
         <v>2.2</v>
       </c>
       <c r="S107">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.73</v>
+        <v>3.01</v>
       </c>
       <c r="U107">
-        <v>2.59</v>
+        <v>2.84</v>
       </c>
       <c r="V107">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W107">
         <v>1.08</v>
@@ -17789,19 +17789,19 @@
         <v>3.4</v>
       </c>
       <c r="AA107">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB107">
         <v>1.85</v>
       </c>
       <c r="AC107">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD107">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE107">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
         <v>1.87</v>
@@ -17922,7 +17922,7 @@
         <v>7.5</v>
       </c>
       <c r="Q108">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="R108">
         <v>2.85</v>
@@ -17934,10 +17934,10 @@
         <v>4.2</v>
       </c>
       <c r="U108">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V108">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W108">
         <v>1.2</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18275,19 +18275,19 @@
         <v>1.26</v>
       </c>
       <c r="Z110">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AA110">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AB110">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC110">
-        <v>3.28</v>
+        <v>3.37</v>
       </c>
       <c r="AD110">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE110">
         <v>1.05</v>
@@ -18296,7 +18296,7 @@
         <v>1.87</v>
       </c>
       <c r="AG110">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18414,7 +18414,7 @@
         <v>1.3</v>
       </c>
       <c r="R111">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S111">
         <v>1.18</v>
@@ -18435,10 +18435,10 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z111">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA111">
         <v>1.36</v>
@@ -18447,19 +18447,19 @@
         <v>3.1</v>
       </c>
       <c r="AC111">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AD111">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE111">
+        <v>1.36</v>
+      </c>
+      <c r="AF111">
+        <v>3.25</v>
+      </c>
+      <c r="AG111">
         <v>1.33</v>
-      </c>
-      <c r="AF111">
-        <v>2.75</v>
-      </c>
-      <c r="AG111">
-        <v>1.4</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18601,13 +18601,13 @@
         <v>1.32</v>
       </c>
       <c r="Z112">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA112">
         <v>1.9</v>
       </c>
       <c r="AB112">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC112">
         <v>3.5</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O113">
         <v>3.18</v>
       </c>
       <c r="P113">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Q113">
         <v>2.5</v>
@@ -18752,7 +18752,7 @@
         <v>2.44</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W113">
         <v>1.1</v>
@@ -18767,7 +18767,7 @@
         <v>3.48</v>
       </c>
       <c r="AA113">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB113">
         <v>1.89</v>
@@ -18933,7 +18933,7 @@
         <v>1.5</v>
       </c>
       <c r="AB114">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AC114">
         <v>2.08</v>
@@ -18948,7 +18948,7 @@
         <v>1.69</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>4.3</v>
       </c>
       <c r="Q115">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R115">
         <v>2.15</v>
@@ -19096,13 +19096,13 @@
         <v>1.95</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC115">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD115">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE115">
         <v>1.05</v>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AK115">
         <v>2</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19546,13 +19546,13 @@
         <v>2.09</v>
       </c>
       <c r="O118">
-        <v>3.21</v>
+        <v>3.5</v>
       </c>
       <c r="P118">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="R118">
         <v>2.2</v>
@@ -19564,59 +19564,59 @@
         <v>3</v>
       </c>
       <c r="U118">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W118">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
         <v>1.01</v>
       </c>
       <c r="Y118">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z118">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="AA118">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB118">
         <v>1.85</v>
       </c>
       <c r="AC118">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD118">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE118">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF118">
+        <v>1.7</v>
+      </c>
+      <c r="AG118">
+        <v>2.05</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>1.25</v>
+      </c>
+      <c r="AK118">
         <v>1.67</v>
-      </c>
-      <c r="AG118">
-        <v>2.06</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.24</v>
-      </c>
-      <c r="AK118">
-        <v>1.57</v>
       </c>
       <c r="AL118">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -970,22 +970,22 @@
         <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
         <v>1.08</v>
@@ -994,10 +994,10 @@
         <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA4">
         <v>1.97</v>
@@ -1006,7 +1006,7 @@
         <v>1.87</v>
       </c>
       <c r="AC4">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1015,7 +1015,7 @@
         <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
         <v>2.05</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AK4">
         <v>1.4</v>
@@ -1450,61 +1450,61 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.72</v>
+        <v>5.25</v>
       </c>
       <c r="O7">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="P7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
-        <v>5.49</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="S7">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T7">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="V7">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC7">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AD7">
         <v>1.65</v>
       </c>
       <c r="AE7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
         <v>2.2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.12</v>
+        <v>2.62</v>
       </c>
       <c r="AK7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>1.67</v>
       </c>
       <c r="R11">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="S11">
         <v>1.23</v>
@@ -2123,13 +2123,13 @@
         <v>3.4</v>
       </c>
       <c r="U11">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2144,13 +2144,13 @@
         <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC11">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE11">
         <v>1.14</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
         <v>3.6</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="O13">
         <v>4.1</v>
@@ -2446,7 +2446,7 @@
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
         <v>2.15</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>2.07</v>
       </c>
       <c r="AK13">
         <v>1.17</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="O16">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
         <v>3.8</v>
@@ -3774,7 +3774,7 @@
         <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
         <v>4.5</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -5368,7 +5368,7 @@
         <v>3.6</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -5383,10 +5383,10 @@
         <v>3.9</v>
       </c>
       <c r="U31">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V31">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W31">
         <v>1.15</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
         <v>2.35</v>
       </c>
       <c r="Q34">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
         <v>1.33</v>
@@ -5893,7 +5893,7 @@
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P35">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q35">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="R35">
         <v>1.85</v>
@@ -6032,19 +6032,19 @@
         <v>1.55</v>
       </c>
       <c r="T35">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="U35">
         <v>3.7</v>
       </c>
       <c r="V35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W35">
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y35">
         <v>1.57</v>
@@ -6056,19 +6056,19 @@
         <v>2.88</v>
       </c>
       <c r="AB35">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AD35">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF35">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AG35">
         <v>1.6</v>
@@ -6087,7 +6087,7 @@
         <v>1.4</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6346,13 +6346,13 @@
         <v>4.2</v>
       </c>
       <c r="P37">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="Q37">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R37">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>1.3</v>
@@ -6379,10 +6379,10 @@
         <v>4.33</v>
       </c>
       <c r="AA37">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AC37">
         <v>2.7</v>
@@ -6391,7 +6391,7 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK37">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>5.5</v>
       </c>
       <c r="P38">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB39">
         <v>1.73</v>
@@ -6995,10 +6995,10 @@
         <v>1.37</v>
       </c>
       <c r="O41">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="P41">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P43">
         <v>4.8</v>
@@ -7372,7 +7372,7 @@
         <v>1.44</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG43">
         <v>2.77</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7813,10 +7813,10 @@
         <v>4.15</v>
       </c>
       <c r="P46">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q46">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
       <c r="R46">
         <v>2.32</v>
@@ -7855,7 +7855,7 @@
         <v>2.57</v>
       </c>
       <c r="AD46">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE46">
         <v>1.13</v>
@@ -8000,7 +8000,7 @@
         <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
         <v>1.2</v>
@@ -8009,10 +8009,10 @@
         <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB47">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
         <v>2.56</v>
@@ -8474,10 +8474,10 @@
         <v>2.47</v>
       </c>
       <c r="S50">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
         <v>2</v>
@@ -8532,7 +8532,7 @@
         <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q51">
-        <v>4.12</v>
+        <v>3.96</v>
       </c>
       <c r="R51">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S51">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AA51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
+        <v>2.88</v>
+      </c>
+      <c r="AD51">
+        <v>1.32</v>
+      </c>
+      <c r="AE51">
+        <v>1.09</v>
+      </c>
+      <c r="AF51">
+        <v>1.67</v>
+      </c>
+      <c r="AG51">
         <v>2.1</v>
-      </c>
-      <c r="AC51">
-        <v>2.69</v>
-      </c>
-      <c r="AD51">
-        <v>1.36</v>
-      </c>
-      <c r="AE51">
-        <v>1.14</v>
-      </c>
-      <c r="AF51">
-        <v>1.61</v>
-      </c>
-      <c r="AG51">
-        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9114,10 +9114,10 @@
         <v>2.98</v>
       </c>
       <c r="O54">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
       <c r="P54">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9277,7 +9277,7 @@
         <v>1.72</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
         <v>4.1</v>
@@ -9304,7 +9304,7 @@
         <v>1.15</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y55">
         <v>1.15</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
         <v>2.86</v>
@@ -9603,16 +9603,16 @@
         <v>1.76</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="P57">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="Q57">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R57">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9642,7 +9642,7 @@
         <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -9769,13 +9769,13 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
         <v>3.2</v>
       </c>
       <c r="R58">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
         <v>1.3</v>
@@ -9799,22 +9799,22 @@
         <v>1.2</v>
       </c>
       <c r="Z58">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA58">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB58">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC58">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD58">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
         <v>1.57</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="O59">
         <v>3.7</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="O60">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P60">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q60">
         <v>6.86</v>
@@ -10255,7 +10255,7 @@
         <v>2.72</v>
       </c>
       <c r="O61">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
         <v>2.27</v>
@@ -10288,25 +10288,25 @@
         <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>4.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AC61">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AD61">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
         <v>2.7</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Olympic El Qanah</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="O62">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="P62">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R62">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="S62">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="T62">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="U62">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="V62">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W62">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y62">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="Z62">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA62">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AB62">
+        <v>1.5</v>
+      </c>
+      <c r="AC62">
+        <v>4.4</v>
+      </c>
+      <c r="AD62">
+        <v>1.14</v>
+      </c>
+      <c r="AE62">
+        <v>1.01</v>
+      </c>
+      <c r="AF62">
+        <v>2</v>
+      </c>
+      <c r="AG62">
+        <v>1.7</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.35</v>
+      </c>
+      <c r="AK62">
         <v>1.36</v>
-      </c>
-      <c r="AC62">
-        <v>6.25</v>
-      </c>
-      <c r="AD62">
-        <v>1.11</v>
-      </c>
-      <c r="AE62">
-        <v>1.02</v>
-      </c>
-      <c r="AF62">
-        <v>2.3</v>
-      </c>
-      <c r="AG62">
-        <v>1.55</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.33</v>
-      </c>
-      <c r="AK62">
-        <v>1.45</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olympic El Qanah</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O63">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P63">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Q63">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R63">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="S63">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="T63">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="U63">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="V63">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W63">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X63">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y63">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Z63">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AA63">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AB63">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC63">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="AD63">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG63">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK63">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10747,7 +10747,7 @@
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="Q64">
         <v>2.3</v>
@@ -10771,7 +10771,7 @@
         <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
         <v>1.17</v>
@@ -10783,7 +10783,7 @@
         <v>1.59</v>
       </c>
       <c r="AB64">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC64">
         <v>2.4</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
         <v>3.7</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O66">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R66">
         <v>2.57</v>
@@ -11088,7 +11088,7 @@
         <v>4.65</v>
       </c>
       <c r="U66">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V66">
         <v>1.94</v>
@@ -11112,10 +11112,10 @@
         <v>3.2</v>
       </c>
       <c r="AC66">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AD66">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AE66">
         <v>1.43</v>
@@ -11230,28 +11230,28 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
         <v>3.7</v>
       </c>
       <c r="P67">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="Q67">
         <v>2.45</v>
       </c>
       <c r="R67">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="V67">
         <v>1.57</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O68">
         <v>3.4</v>
@@ -11420,7 +11420,7 @@
         <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11559,10 +11559,10 @@
         <v>1.53</v>
       </c>
       <c r="O69">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q69">
         <v>1.9</v>
@@ -11586,7 +11586,7 @@
         <v>1.18</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
         <v>1.1</v>
@@ -11601,13 +11601,13 @@
         <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AD69">
         <v>1.71</v>
       </c>
       <c r="AE69">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF69">
         <v>1.44</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK69">
         <v>2.28</v>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O70">
         <v>3.35</v>
@@ -11758,10 +11758,10 @@
         <v>4.16</v>
       </c>
       <c r="AA70">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AB70">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC70">
         <v>2.56</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O71">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="P71">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11900,7 +11900,7 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="U71">
         <v>2.25</v>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,16 +12208,16 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="O73">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>6.57</v>
       </c>
       <c r="Q73">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R73">
         <v>2.3</v>
@@ -12262,7 +12262,7 @@
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG73">
         <v>1.78</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O74">
         <v>3.25</v>
       </c>
       <c r="P74">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q74">
         <v>3.47</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P75">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q75">
         <v>2.42</v>
       </c>
       <c r="R75">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S75">
         <v>1.29</v>
@@ -12579,10 +12579,10 @@
         <v>2.1</v>
       </c>
       <c r="AC75">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AD75">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
         <v>1.1</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="O76">
         <v>3.5</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -12872,7 +12872,7 @@
         <v>2.76</v>
       </c>
       <c r="R77">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12933,7 +12933,7 @@
         <v>1.36</v>
       </c>
       <c r="AK77">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O80">
         <v>3.4</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q81">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R81">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
         <v>1.2</v>
@@ -13551,10 +13551,10 @@
         <v>6</v>
       </c>
       <c r="AA81">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB81">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC81">
         <v>2.01</v>
@@ -13566,7 +13566,7 @@
         <v>1.28</v>
       </c>
       <c r="AF81">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG81">
         <v>2.88</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,34 +13675,34 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O82">
         <v>3.4</v>
       </c>
       <c r="P82">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="Q82">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R82">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V82">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
         <v>1.01</v>
@@ -13720,13 +13720,13 @@
         <v>2.38</v>
       </c>
       <c r="AC82">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="AD82">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE82">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
         <v>1.47</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
         <v>1.65</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="O83">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="Q83">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S83">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U83">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V83">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="W83">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z83">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA83">
+        <v>1.28</v>
+      </c>
+      <c r="AB83">
+        <v>3.4</v>
+      </c>
+      <c r="AC83">
+        <v>1.74</v>
+      </c>
+      <c r="AD83">
+        <v>2.07</v>
+      </c>
+      <c r="AE83">
         <v>1.44</v>
       </c>
-      <c r="AB83">
-        <v>2.7</v>
-      </c>
-      <c r="AC83">
-        <v>2.06</v>
-      </c>
-      <c r="AD83">
-        <v>1.66</v>
-      </c>
-      <c r="AE83">
-        <v>1.25</v>
-      </c>
       <c r="AF83">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AG83">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK83">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O84">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="P84">
-        <v>3.09</v>
+        <v>4.09</v>
       </c>
       <c r="Q84">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="R84">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="S84">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T84">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U84">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="V84">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="W84">
+        <v>1.2</v>
+      </c>
+      <c r="X84">
+        <v>1.02</v>
+      </c>
+      <c r="Y84">
+        <v>1.13</v>
+      </c>
+      <c r="Z84">
+        <v>6</v>
+      </c>
+      <c r="AA84">
+        <v>1.44</v>
+      </c>
+      <c r="AB84">
+        <v>2.7</v>
+      </c>
+      <c r="AC84">
+        <v>2.13</v>
+      </c>
+      <c r="AD84">
+        <v>1.67</v>
+      </c>
+      <c r="AE84">
         <v>1.29</v>
       </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.05</v>
-      </c>
-      <c r="Z84">
-        <v>7</v>
-      </c>
-      <c r="AA84">
-        <v>1.28</v>
-      </c>
-      <c r="AB84">
-        <v>3.4</v>
-      </c>
-      <c r="AC84">
-        <v>1.74</v>
-      </c>
-      <c r="AD84">
-        <v>2.07</v>
-      </c>
-      <c r="AE84">
-        <v>1.44</v>
-      </c>
       <c r="AF84">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AG84">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,16 +14164,16 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="Q85">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="R85">
         <v>2.38</v>
@@ -14182,7 +14182,7 @@
         <v>1.22</v>
       </c>
       <c r="T85">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="U85">
         <v>2.1</v>
@@ -14191,31 +14191,31 @@
         <v>1.65</v>
       </c>
       <c r="W85">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z85">
-        <v>5.15</v>
+        <v>5.4</v>
       </c>
       <c r="AA85">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB85">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AD85">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE85">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF85">
         <v>1.4</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK85">
         <v>1.67</v>
@@ -14327,22 +14327,22 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Q86">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R86">
         <v>2.4</v>
       </c>
       <c r="S86">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T86">
         <v>3.9</v>
@@ -14351,19 +14351,19 @@
         <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>5.35</v>
+        <v>5.55</v>
       </c>
       <c r="AA86">
         <v>1.44</v>
@@ -14372,35 +14372,35 @@
         <v>2.6</v>
       </c>
       <c r="AC86">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD86">
         <v>1.68</v>
       </c>
       <c r="AE86">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF86">
+        <v>1.4</v>
+      </c>
+      <c r="AG86">
+        <v>2.7</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>1.19</v>
+      </c>
+      <c r="AK86">
         <v>1.36</v>
-      </c>
-      <c r="AG86">
-        <v>2.8</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.18</v>
-      </c>
-      <c r="AK86">
-        <v>1.37</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14496,28 +14496,28 @@
         <v>3.6</v>
       </c>
       <c r="P87">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q87">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R87">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S87">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T87">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V87">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X87">
         <v>1.03</v>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.45</v>
       </c>
       <c r="P88">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="Q88">
         <v>2.62</v>
@@ -14677,13 +14677,13 @@
         <v>2.3</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W88">
         <v>1.14</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
         <v>1.12</v>
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.75</v>
+        <v>3.93</v>
       </c>
       <c r="O89">
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
       </c>
       <c r="R89">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T89">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="U89">
         <v>2.44</v>
@@ -14852,13 +14852,13 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
       </c>
       <c r="AB89">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC89">
         <v>2.74</v>
@@ -15006,10 +15006,10 @@
         <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
         <v>1.3</v>
@@ -15030,7 +15030,7 @@
         <v>1.31</v>
       </c>
       <c r="AE90">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF90">
         <v>1.75</v>
@@ -15052,7 +15052,7 @@
         <v>1.24</v>
       </c>
       <c r="AK90">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O91">
         <v>3.2</v>
@@ -15184,7 +15184,7 @@
         <v>2.15</v>
       </c>
       <c r="AB91">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC91">
         <v>4.1</v>
@@ -15311,7 +15311,7 @@
         <v>3.8</v>
       </c>
       <c r="P92">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q92">
         <v>3.28</v>
@@ -15326,7 +15326,7 @@
         <v>3.8</v>
       </c>
       <c r="U92">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V92">
         <v>1.66</v>
@@ -15350,13 +15350,13 @@
         <v>2.66</v>
       </c>
       <c r="AC92">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD92">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE92">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF92">
         <v>1.4</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O93">
         <v>3.8</v>
@@ -15495,16 +15495,16 @@
         <v>1.5</v>
       </c>
       <c r="W93">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y93">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z93">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="AA93">
         <v>1.66</v>
@@ -15513,7 +15513,7 @@
         <v>2.05</v>
       </c>
       <c r="AC93">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD93">
         <v>1.42</v>
@@ -15525,7 +15525,7 @@
         <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>1.17</v>
       </c>
       <c r="AK93">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,16 +15631,16 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O94">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="P94">
-        <v>8.300000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="Q94">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="R94">
         <v>2.66</v>
@@ -15658,31 +15658,31 @@
         <v>1.55</v>
       </c>
       <c r="W94">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y94">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="Z94">
-        <v>4.31</v>
+        <v>3.3</v>
       </c>
       <c r="AA94">
         <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AC94">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="AD94">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE94">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF94">
         <v>2.05</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O100">
         <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q100">
         <v>3.75</v>
@@ -16648,7 +16648,7 @@
         <v>3.58</v>
       </c>
       <c r="AA100">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB100">
         <v>1.93</v>
@@ -16781,7 +16781,7 @@
         <v>1.53</v>
       </c>
       <c r="Q101">
-        <v>4.22</v>
+        <v>5.52</v>
       </c>
       <c r="R101">
         <v>2.6</v>
@@ -16808,7 +16808,7 @@
         <v>1.1</v>
       </c>
       <c r="Z101">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA101">
         <v>1.38</v>
@@ -16817,7 +16817,7 @@
         <v>2.62</v>
       </c>
       <c r="AC101">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD101">
         <v>1.67</v>
@@ -17107,10 +17107,10 @@
         <v>6.6</v>
       </c>
       <c r="Q103">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R103">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="S103">
         <v>1.25</v>
@@ -17140,7 +17140,7 @@
         <v>1.47</v>
       </c>
       <c r="AB103">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="AC103">
         <v>2.38</v>
@@ -17261,10 +17261,10 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="P104">
         <v>2.71</v>
@@ -17427,7 +17427,7 @@
         <v>2.25</v>
       </c>
       <c r="O105">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="P105">
         <v>2.51</v>
@@ -17445,13 +17445,13 @@
         <v>3.28</v>
       </c>
       <c r="U105">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V105">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W105">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1.02</v>
@@ -17478,10 +17478,10 @@
         <v>1.16</v>
       </c>
       <c r="AF105">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="O106">
         <v>5.8</v>
@@ -17617,7 +17617,7 @@
         <v>1.11</v>
       </c>
       <c r="X106">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y106">
         <v>1.14</v>
@@ -17660,7 +17660,7 @@
         <v>1.12</v>
       </c>
       <c r="AK106">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17771,7 +17771,7 @@
         <v>3.01</v>
       </c>
       <c r="U107">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
         <v>1.4</v>
@@ -17780,7 +17780,7 @@
         <v>1.08</v>
       </c>
       <c r="X107">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y107">
         <v>1.29</v>
@@ -17789,19 +17789,19 @@
         <v>3.4</v>
       </c>
       <c r="AA107">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC107">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE107">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF107">
         <v>1.87</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O108">
         <v>5.5</v>
       </c>
       <c r="P108">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -17946,10 +17946,10 @@
         <v>1.01</v>
       </c>
       <c r="Y108">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z108">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA108">
         <v>1.4</v>
@@ -17958,13 +17958,13 @@
         <v>2.75</v>
       </c>
       <c r="AC108">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AD108">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE108">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF108">
         <v>1.75</v>
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O109">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P109">
-        <v>6.8</v>
+        <v>6.25</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="O110">
-        <v>3.63</v>
+        <v>3.45</v>
       </c>
       <c r="P110">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q110">
         <v>2.15</v>
@@ -18254,49 +18254,49 @@
         <v>2.2</v>
       </c>
       <c r="S110">
+        <v>1.4</v>
+      </c>
+      <c r="T110">
+        <v>2.75</v>
+      </c>
+      <c r="U110">
+        <v>2.9</v>
+      </c>
+      <c r="V110">
         <v>1.36</v>
       </c>
-      <c r="T110">
-        <v>2.9</v>
-      </c>
-      <c r="U110">
-        <v>2.75</v>
-      </c>
-      <c r="V110">
-        <v>1.4</v>
-      </c>
       <c r="W110">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y110">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z110">
-        <v>3.31</v>
+        <v>3.05</v>
       </c>
       <c r="AA110">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AB110">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC110">
-        <v>3.37</v>
+        <v>3.71</v>
       </c>
       <c r="AD110">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE110">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG110">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O112">
         <v>3.7</v>
       </c>
       <c r="P112">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q112">
         <v>2.15</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="O113">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="P113">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="Q113">
         <v>2.5</v>
@@ -18749,10 +18749,10 @@
         <v>3.2</v>
       </c>
       <c r="U113">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W113">
         <v>1.1</v>
@@ -18764,22 +18764,22 @@
         <v>1.22</v>
       </c>
       <c r="Z113">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AA113">
         <v>1.8</v>
       </c>
       <c r="AB113">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC113">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD113">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE113">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF113">
         <v>1.67</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="O114">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="P114">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -18906,10 +18906,10 @@
         <v>2.62</v>
       </c>
       <c r="S114">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T114">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="U114">
         <v>2.1</v>
@@ -18918,37 +18918,37 @@
         <v>1.67</v>
       </c>
       <c r="W114">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X114">
         <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z114">
-        <v>5.35</v>
+        <v>4.95</v>
       </c>
       <c r="AA114">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB114">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC114">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="AD114">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE114">
         <v>1.23</v>
       </c>
       <c r="AF114">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AG114">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK114">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="O115">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P115">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="Q115">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R115">
         <v>2.15</v>
@@ -19081,37 +19081,37 @@
         <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z115">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA115">
         <v>1.95</v>
       </c>
       <c r="AB115">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC115">
-        <v>3.42</v>
+        <v>3.71</v>
       </c>
       <c r="AD115">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE115">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG115">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O116">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="P116">
-        <v>4.1</v>
+        <v>4.02</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="O118">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="P118">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q118">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="R118">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S118">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T118">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U118">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V118">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W118">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z118">
-        <v>3.44</v>
+        <v>3.19</v>
       </c>
       <c r="AA118">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AB118">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC118">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="AD118">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE118">
         <v>1.11</v>
       </c>
       <c r="AF118">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG118">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK118">
         <v>1.67</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -1779,7 +1779,7 @@
         <v>2.45</v>
       </c>
       <c r="O9">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
         <v>2.75</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="O13">
         <v>4.1</v>
       </c>
       <c r="P13">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q13">
         <v>4.05</v>
       </c>
       <c r="R13">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2479,7 +2479,7 @@
         <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
         <v>1.6</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.07</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="O16">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P19">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3753,16 +3753,16 @@
         <v>2.55</v>
       </c>
       <c r="U21">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V21">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W21">
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
         <v>1.36</v>
@@ -3774,7 +3774,7 @@
         <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC21">
         <v>4.5</v>
@@ -3783,13 +3783,13 @@
         <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG21">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -4719,55 +4719,55 @@
         <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="U27">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
         <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK27">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O28">
         <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q28">
         <v>2.95</v>
@@ -4894,7 +4894,7 @@
         <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -4912,10 +4912,10 @@
         <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB28">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
         <v>2.92</v>
@@ -5389,7 +5389,7 @@
         <v>1.67</v>
       </c>
       <c r="W31">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5854,61 +5854,61 @@
         <v>2.43</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P34">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
         <v>1.08</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA34">
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6192,16 +6192,16 @@
         <v>1.95</v>
       </c>
       <c r="S36">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T36">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="U36">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="V36">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6210,19 +6210,19 @@
         <v>1.04</v>
       </c>
       <c r="Y36">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="AA36">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AB36">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC36">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="O37">
         <v>4.2</v>
@@ -6397,7 +6397,7 @@
         <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6681,16 +6681,16 @@
         <v>2.03</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U39">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6705,10 +6705,10 @@
         <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>3.8</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="O41">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="P41">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O43">
         <v>4.35</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.38</v>
+        <v>1.4</v>
       </c>
       <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>6</v>
+      </c>
+      <c r="Q44">
+        <v>1.98</v>
+      </c>
+      <c r="R44">
+        <v>2.17</v>
+      </c>
+      <c r="S44">
+        <v>1.34</v>
+      </c>
+      <c r="T44">
         <v>2.81</v>
       </c>
-      <c r="P44">
-        <v>2.93</v>
-      </c>
-      <c r="Q44">
-        <v>3.45</v>
-      </c>
-      <c r="R44">
-        <v>1.9</v>
-      </c>
-      <c r="S44">
-        <v>1.6</v>
-      </c>
-      <c r="T44">
-        <v>2.27</v>
-      </c>
       <c r="U44">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="V44">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="W44">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1.54</v>
+        <v>1.26</v>
       </c>
       <c r="Z44">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="AA44">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="AB44">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="AC44">
-        <v>6</v>
+        <v>3.14</v>
       </c>
       <c r="AD44">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF44">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AG44">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>2.52</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>2.81</v>
       </c>
       <c r="P45">
+        <v>2.93</v>
+      </c>
+      <c r="Q45">
+        <v>3.45</v>
+      </c>
+      <c r="R45">
+        <v>1.9</v>
+      </c>
+      <c r="S45">
+        <v>1.6</v>
+      </c>
+      <c r="T45">
+        <v>2.27</v>
+      </c>
+      <c r="U45">
+        <v>3.75</v>
+      </c>
+      <c r="V45">
+        <v>1.22</v>
+      </c>
+      <c r="W45">
+        <v>1.02</v>
+      </c>
+      <c r="X45">
+        <v>1.1</v>
+      </c>
+      <c r="Y45">
+        <v>1.54</v>
+      </c>
+      <c r="Z45">
+        <v>2.37</v>
+      </c>
+      <c r="AA45">
+        <v>2.75</v>
+      </c>
+      <c r="AB45">
+        <v>1.41</v>
+      </c>
+      <c r="AC45">
         <v>6</v>
       </c>
-      <c r="Q45">
-        <v>1.98</v>
-      </c>
-      <c r="R45">
-        <v>2.17</v>
-      </c>
-      <c r="S45">
-        <v>1.34</v>
-      </c>
-      <c r="T45">
-        <v>2.81</v>
-      </c>
-      <c r="U45">
-        <v>2.65</v>
-      </c>
-      <c r="V45">
-        <v>1.38</v>
-      </c>
-      <c r="W45">
-        <v>1.08</v>
-      </c>
-      <c r="X45">
-        <v>1</v>
-      </c>
-      <c r="Y45">
-        <v>1.26</v>
-      </c>
-      <c r="Z45">
-        <v>3.2</v>
-      </c>
-      <c r="AA45">
-        <v>1.88</v>
-      </c>
-      <c r="AB45">
-        <v>1.79</v>
-      </c>
-      <c r="AC45">
-        <v>3.14</v>
-      </c>
       <c r="AD45">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AG45">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,22 +7810,22 @@
         <v>4.6</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="P46">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q46">
-        <v>5.16</v>
+        <v>5.2</v>
       </c>
       <c r="R46">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S46">
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
         <v>2.3</v>
@@ -7852,7 +7852,7 @@
         <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="AD46">
         <v>1.51</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O47">
         <v>3.4</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8142,16 +8142,16 @@
         <v>2.87</v>
       </c>
       <c r="Q48">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="R48">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U48">
         <v>2.3</v>
@@ -8160,13 +8160,13 @@
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
         <v>4.65</v>
@@ -8178,19 +8178,19 @@
         <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AD48">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.4</v>
       </c>
       <c r="AK48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O50">
         <v>4.4</v>
       </c>
       <c r="P50">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="Q50">
         <v>1.92</v>
@@ -8498,7 +8498,7 @@
         <v>5.55</v>
       </c>
       <c r="AA50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
         <v>2.62</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O54">
         <v>3.31</v>
       </c>
       <c r="P54">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O55">
         <v>3.75</v>
@@ -9443,10 +9443,10 @@
         <v>3.85</v>
       </c>
       <c r="P56">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
         <v>2.4</v>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.54</v>
+        <v>1.22</v>
       </c>
       <c r="AK56">
         <v>1.39</v>
@@ -9603,13 +9603,13 @@
         <v>1.76</v>
       </c>
       <c r="O57">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="P57">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="Q57">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R57">
         <v>2.45</v>
@@ -9621,7 +9621,7 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
         <v>1.56</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="O58">
         <v>3.3</v>
@@ -9929,55 +9929,55 @@
         <v>3.25</v>
       </c>
       <c r="O59">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P59">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q59">
-        <v>3.69</v>
+        <v>3.84</v>
       </c>
       <c r="R59">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S59">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T59">
         <v>3.6</v>
       </c>
       <c r="U59">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V59">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z59">
-        <v>5.08</v>
+        <v>5.39</v>
       </c>
       <c r="AA59">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AB59">
         <v>2.55</v>
       </c>
       <c r="AC59">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AD59">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE59">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF59">
         <v>1.44</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AK59">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>7</v>
       </c>
       <c r="P60">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q60">
         <v>6.86</v>
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
         <v>2.27</v>
@@ -10270,10 +10270,10 @@
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="U61">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V61">
         <v>1.61</v>
@@ -10291,7 +10291,7 @@
         <v>5.5</v>
       </c>
       <c r="AA61">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB61">
         <v>2.31</v>
@@ -10309,7 +10309,7 @@
         <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10744,31 +10744,31 @@
         <v>1.73</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="R64">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="Q65">
         <v>2.15</v>
       </c>
       <c r="R65">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10958,7 +10958,7 @@
         <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
         <v>2.4</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK65">
         <v>1.82</v>
@@ -11070,7 +11070,7 @@
         <v>1.7</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P66">
         <v>3.8</v>
@@ -11124,7 +11124,7 @@
         <v>1.33</v>
       </c>
       <c r="AG66">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q68">
         <v>2.73</v>
@@ -11411,16 +11411,16 @@
         <v>1.36</v>
       </c>
       <c r="T68">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="U68">
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11435,7 +11435,7 @@
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC68">
         <v>3.27</v>
@@ -11888,7 +11888,7 @@
         <v>5.6</v>
       </c>
       <c r="P71">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O73">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="P73">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="Q73">
         <v>1.93</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="P74">
         <v>2.25</v>
@@ -12428,7 +12428,7 @@
         <v>1.76</v>
       </c>
       <c r="AG74">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.28</v>
       </c>
       <c r="AK74">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O75">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P75">
         <v>3.1</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O76">
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
         <v>2.41</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O77">
         <v>3.3</v>
@@ -13023,7 +13023,7 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O78">
         <v>2.75</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O88">
         <v>3.45</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q88">
         <v>2.62</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.93</v>
+        <v>3.75</v>
       </c>
       <c r="O89">
         <v>3.6</v>
       </c>
       <c r="P89">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
@@ -14834,10 +14834,10 @@
         <v>1.35</v>
       </c>
       <c r="T89">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="U89">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V89">
         <v>1.47</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O90">
         <v>3.44</v>
@@ -14988,7 +14988,7 @@
         <v>3.45</v>
       </c>
       <c r="Q90">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="R90">
         <v>2.05</v>
@@ -15000,7 +15000,7 @@
         <v>2.96</v>
       </c>
       <c r="U90">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V90">
         <v>1.4</v>
@@ -15012,10 +15012,10 @@
         <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="AA90">
         <v>1.9</v>
@@ -15024,7 +15024,7 @@
         <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="AD90">
         <v>1.31</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="O92">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P92">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q92">
         <v>3.28</v>
@@ -15359,7 +15359,7 @@
         <v>1.29</v>
       </c>
       <c r="AF92">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG92">
         <v>2.62</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="O93">
         <v>3.8</v>
@@ -15483,16 +15483,16 @@
         <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T93">
         <v>3.25</v>
       </c>
       <c r="U93">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V93">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W93">
         <v>1.11</v>
@@ -15794,7 +15794,7 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O95">
         <v>3.6</v>
@@ -15806,13 +15806,13 @@
         <v>2.25</v>
       </c>
       <c r="R95">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="S95">
         <v>1.22</v>
       </c>
       <c r="T95">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U95">
         <v>2.24</v>
@@ -15824,7 +15824,7 @@
         <v>1.17</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
         <v>1.11</v>
@@ -15833,25 +15833,25 @@
         <v>4.95</v>
       </c>
       <c r="AA95">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB95">
         <v>2.38</v>
       </c>
       <c r="AC95">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AD95">
         <v>1.59</v>
       </c>
       <c r="AE95">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF95">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG95">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,65 +15957,65 @@
         </is>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O96">
         <v>3.5</v>
       </c>
       <c r="P96">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="Q96">
-        <v>3.84</v>
+        <v>2.74</v>
       </c>
       <c r="R96">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="S96">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T96">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="U96">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V96">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="W96">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y96">
+        <v>1.23</v>
+      </c>
+      <c r="Z96">
+        <v>4.03</v>
+      </c>
+      <c r="AA96">
+        <v>1.72</v>
+      </c>
+      <c r="AB96">
+        <v>2.05</v>
+      </c>
+      <c r="AC96">
+        <v>2.83</v>
+      </c>
+      <c r="AD96">
+        <v>1.33</v>
+      </c>
+      <c r="AE96">
         <v>1.15</v>
       </c>
-      <c r="Z96">
-        <v>4.25</v>
-      </c>
-      <c r="AA96">
+      <c r="AF96">
         <v>1.61</v>
       </c>
-      <c r="AB96">
+      <c r="AG96">
         <v>2.25</v>
       </c>
-      <c r="AC96">
-        <v>2.55</v>
-      </c>
-      <c r="AD96">
-        <v>1.51</v>
-      </c>
-      <c r="AE96">
-        <v>1.14</v>
-      </c>
-      <c r="AF96">
-        <v>1.53</v>
-      </c>
-      <c r="AG96">
-        <v>2.4</v>
-      </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P97">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="Q97">
-        <v>2.74</v>
+        <v>2.57</v>
       </c>
       <c r="R97">
         <v>2.18</v>
       </c>
       <c r="S97">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T97">
-        <v>3.26</v>
+        <v>2.82</v>
       </c>
       <c r="U97">
         <v>2.5</v>
       </c>
       <c r="V97">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W97">
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z97">
-        <v>4.03</v>
+        <v>3.72</v>
       </c>
       <c r="AA97">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB97">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AC97">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD97">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE97">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK97">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P98">
+        <v>1.55</v>
+      </c>
+      <c r="Q98">
+        <v>5.75</v>
+      </c>
+      <c r="R98">
+        <v>2.52</v>
+      </c>
+      <c r="S98">
+        <v>1.3</v>
+      </c>
+      <c r="T98">
         <v>3.2</v>
       </c>
-      <c r="Q98">
-        <v>2.57</v>
-      </c>
-      <c r="R98">
-        <v>2.18</v>
-      </c>
-      <c r="S98">
-        <v>1.29</v>
-      </c>
-      <c r="T98">
-        <v>3.3</v>
-      </c>
       <c r="U98">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V98">
+        <v>1.53</v>
+      </c>
+      <c r="W98">
+        <v>1.12</v>
+      </c>
+      <c r="X98">
+        <v>1.03</v>
+      </c>
+      <c r="Y98">
+        <v>1.18</v>
+      </c>
+      <c r="Z98">
+        <v>4.33</v>
+      </c>
+      <c r="AA98">
+        <v>1.64</v>
+      </c>
+      <c r="AB98">
+        <v>2.17</v>
+      </c>
+      <c r="AC98">
+        <v>2.62</v>
+      </c>
+      <c r="AD98">
         <v>1.42</v>
       </c>
-      <c r="W98">
-        <v>1.11</v>
-      </c>
-      <c r="X98">
-        <v>1.01</v>
-      </c>
-      <c r="Y98">
-        <v>1.2</v>
-      </c>
-      <c r="Z98">
-        <v>3.72</v>
-      </c>
-      <c r="AA98">
-        <v>1.85</v>
-      </c>
-      <c r="AB98">
-        <v>1.95</v>
-      </c>
-      <c r="AC98">
-        <v>2.88</v>
-      </c>
-      <c r="AD98">
-        <v>1.32</v>
-      </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG98">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK98">
-        <v>1.75</v>
+        <v>1.15</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,65 +16446,65 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="O99">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="P99">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="Q99">
-        <v>5.29</v>
+        <v>3.84</v>
       </c>
       <c r="R99">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S99">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U99">
+        <v>2.4</v>
+      </c>
+      <c r="V99">
+        <v>1.54</v>
+      </c>
+      <c r="W99">
+        <v>1.12</v>
+      </c>
+      <c r="X99">
+        <v>1.01</v>
+      </c>
+      <c r="Y99">
+        <v>1.15</v>
+      </c>
+      <c r="Z99">
+        <v>4.25</v>
+      </c>
+      <c r="AA99">
+        <v>1.61</v>
+      </c>
+      <c r="AB99">
+        <v>2.15</v>
+      </c>
+      <c r="AC99">
+        <v>2.55</v>
+      </c>
+      <c r="AD99">
+        <v>1.45</v>
+      </c>
+      <c r="AE99">
+        <v>1.15</v>
+      </c>
+      <c r="AF99">
+        <v>1.5</v>
+      </c>
+      <c r="AG99">
         <v>2.38</v>
       </c>
-      <c r="V99">
-        <v>1.5</v>
-      </c>
-      <c r="W99">
-        <v>1.09</v>
-      </c>
-      <c r="X99">
-        <v>1.03</v>
-      </c>
-      <c r="Y99">
-        <v>1.16</v>
-      </c>
-      <c r="Z99">
-        <v>4.05</v>
-      </c>
-      <c r="AA99">
-        <v>1.64</v>
-      </c>
-      <c r="AB99">
-        <v>2.17</v>
-      </c>
-      <c r="AC99">
-        <v>2.62</v>
-      </c>
-      <c r="AD99">
-        <v>1.42</v>
-      </c>
-      <c r="AE99">
-        <v>1.14</v>
-      </c>
-      <c r="AF99">
-        <v>1.7</v>
-      </c>
-      <c r="AG99">
-        <v>2</v>
-      </c>
       <c r="AH99" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>2.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK99">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P100">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q100">
         <v>3.75</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O101">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P101">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="Q101">
         <v>5.52</v>
@@ -17104,7 +17104,7 @@
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.6</v>
+        <v>6.25</v>
       </c>
       <c r="Q103">
         <v>1.9</v>
@@ -17261,19 +17261,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O104">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="Q104">
         <v>3</v>
       </c>
       <c r="R104">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S104">
         <v>1.39</v>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK104">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="O105">
         <v>3.55</v>
       </c>
       <c r="P105">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="Q105">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="R105">
         <v>2.25</v>
@@ -17463,10 +17463,10 @@
         <v>4.2</v>
       </c>
       <c r="AA105">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AB105">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC105">
         <v>2.64</v>
@@ -17497,7 +17497,7 @@
         <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="O106">
         <v>5.8</v>
@@ -17916,10 +17916,10 @@
         <v>1.3</v>
       </c>
       <c r="O108">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="P108">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -18115,10 +18115,10 @@
         <v>4.9</v>
       </c>
       <c r="AA109">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB109">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC109">
         <v>2.17</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O110">
         <v>3.45</v>
       </c>
       <c r="P110">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q110">
         <v>2.15</v>
@@ -18293,10 +18293,10 @@
         <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O112">
         <v>3.7</v>
@@ -18604,10 +18604,10 @@
         <v>3.4</v>
       </c>
       <c r="AA112">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB112">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC112">
         <v>3.5</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O113">
         <v>3.21</v>
       </c>
       <c r="P113">
-        <v>3.02</v>
+        <v>3.35</v>
       </c>
       <c r="Q113">
         <v>2.5</v>
@@ -18767,7 +18767,7 @@
         <v>3.5</v>
       </c>
       <c r="AA113">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB113">
         <v>1.93</v>
@@ -18897,7 +18897,7 @@
         <v>4.55</v>
       </c>
       <c r="P114">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -19093,10 +19093,10 @@
         <v>2.97</v>
       </c>
       <c r="AA115">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB115">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC115">
         <v>3.71</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="O116">
         <v>3.82</v>
       </c>
       <c r="P116">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="Q116">
         <v>2.21</v>
@@ -19259,7 +19259,7 @@
         <v>1.5</v>
       </c>
       <c r="AB116">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AC116">
         <v>2.13</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O118">
         <v>3.13</v>
       </c>
       <c r="P118">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q118">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
         <v>2.1</v>
@@ -19564,13 +19564,13 @@
         <v>2.88</v>
       </c>
       <c r="U118">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="V118">
         <v>1.36</v>
       </c>
       <c r="W118">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
         <v>1.02</v>
@@ -19616,7 +19616,7 @@
         <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL118">
         <v>0</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O11">
         <v>5.2</v>
       </c>
       <c r="P11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -2138,19 +2138,19 @@
         <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.45</v>
+        <v>4.63</v>
       </c>
       <c r="AA11">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE11">
         <v>1.14</v>
@@ -2434,13 +2434,13 @@
         <v>4.1</v>
       </c>
       <c r="P13">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q13">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="R13">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3578,10 +3578,10 @@
         <v>2.26</v>
       </c>
       <c r="Q20">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
         <v>1.36</v>
@@ -3753,16 +3753,16 @@
         <v>2.55</v>
       </c>
       <c r="U21">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
         <v>1.36</v>
@@ -3783,13 +3783,13 @@
         <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG21">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
         <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O31">
         <v>3.6</v>
       </c>
       <c r="P31">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="O34">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q34">
         <v>3.25</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
         <v>4.2</v>
       </c>
       <c r="P37">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q37">
         <v>1.9</v>
@@ -6681,16 +6681,16 @@
         <v>2.03</v>
       </c>
       <c r="S39">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T39">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="U39">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V39">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
         <v>1.05</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O44">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P44">
         <v>6</v>
       </c>
       <c r="Q44">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R44">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="S44">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U44">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="V44">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AA44">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AB44">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AC44">
-        <v>3.14</v>
+        <v>3.42</v>
       </c>
       <c r="AD44">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AE44">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF44">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AG44">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK44">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="O45">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="P45">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Q45">
         <v>3.45</v>
@@ -7659,16 +7659,16 @@
         <v>1.9</v>
       </c>
       <c r="S45">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="T45">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U45">
         <v>3.75</v>
       </c>
       <c r="V45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W45">
         <v>1.02</v>
@@ -7686,7 +7686,7 @@
         <v>2.75</v>
       </c>
       <c r="AB45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC45">
         <v>6</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
         <v>1.44</v>
@@ -8462,7 +8462,7 @@
         <v>1.43</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="P50">
         <v>5.25</v>
@@ -8492,16 +8492,16 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="AA50">
         <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC50">
         <v>1.99</v>
@@ -8510,7 +8510,7 @@
         <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
@@ -8664,7 +8664,7 @@
         <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC51">
         <v>2.88</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="O54">
         <v>3.31</v>
@@ -9304,19 +9304,19 @@
         <v>1.15</v>
       </c>
       <c r="X55">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
         <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>4.66</v>
+        <v>4.71</v>
       </c>
       <c r="AA55">
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC55">
         <v>2.3</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.43</v>
+        <v>1.76</v>
       </c>
       <c r="O56">
-        <v>3.85</v>
+        <v>3.71</v>
       </c>
       <c r="P56">
+        <v>3.45</v>
+      </c>
+      <c r="Q56">
+        <v>2.12</v>
+      </c>
+      <c r="R56">
+        <v>2.45</v>
+      </c>
+      <c r="S56">
+        <v>1.25</v>
+      </c>
+      <c r="T56">
+        <v>3.5</v>
+      </c>
+      <c r="U56">
         <v>2.25</v>
       </c>
-      <c r="Q56">
-        <v>3.1</v>
-      </c>
-      <c r="R56">
-        <v>2.4</v>
-      </c>
-      <c r="S56">
-        <v>1.22</v>
-      </c>
-      <c r="T56">
-        <v>4</v>
-      </c>
-      <c r="U56">
-        <v>2.1</v>
-      </c>
       <c r="V56">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="W56">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA56">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC56">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AD56">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AE56">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG56">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK56">
-        <v>1.39</v>
+        <v>2.06</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.76</v>
+        <v>2.43</v>
       </c>
       <c r="O57">
-        <v>3.71</v>
+        <v>3.85</v>
       </c>
       <c r="P57">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q57">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="R57">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
+        <v>1.22</v>
+      </c>
+      <c r="T57">
+        <v>4</v>
+      </c>
+      <c r="U57">
+        <v>2.1</v>
+      </c>
+      <c r="V57">
+        <v>1.67</v>
+      </c>
+      <c r="W57">
+        <v>1.18</v>
+      </c>
+      <c r="X57">
+        <v>1.01</v>
+      </c>
+      <c r="Y57">
+        <v>1.11</v>
+      </c>
+      <c r="Z57">
+        <v>5.5</v>
+      </c>
+      <c r="AA57">
+        <v>1.48</v>
+      </c>
+      <c r="AB57">
+        <v>2.5</v>
+      </c>
+      <c r="AC57">
+        <v>2.08</v>
+      </c>
+      <c r="AD57">
+        <v>1.64</v>
+      </c>
+      <c r="AE57">
         <v>1.25</v>
       </c>
-      <c r="T57">
-        <v>3.5</v>
-      </c>
-      <c r="U57">
-        <v>2.25</v>
-      </c>
-      <c r="V57">
-        <v>1.56</v>
-      </c>
-      <c r="W57">
-        <v>1.12</v>
-      </c>
-      <c r="X57">
-        <v>1.03</v>
-      </c>
-      <c r="Y57">
-        <v>1.17</v>
-      </c>
-      <c r="Z57">
-        <v>5</v>
-      </c>
-      <c r="AA57">
-        <v>1.6</v>
-      </c>
-      <c r="AB57">
-        <v>2.3</v>
-      </c>
-      <c r="AC57">
-        <v>2.45</v>
-      </c>
-      <c r="AD57">
-        <v>1.51</v>
-      </c>
-      <c r="AE57">
-        <v>1.16</v>
-      </c>
       <c r="AF57">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG57">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>2.06</v>
+        <v>1.39</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="O58">
         <v>3.3</v>
@@ -9790,7 +9790,7 @@
         <v>1.44</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
         <v>1.02</v>
@@ -9929,16 +9929,16 @@
         <v>3.25</v>
       </c>
       <c r="O59">
+        <v>3.8</v>
+      </c>
+      <c r="P59">
+        <v>1.94</v>
+      </c>
+      <c r="Q59">
         <v>3.75</v>
       </c>
-      <c r="P59">
-        <v>1.93</v>
-      </c>
-      <c r="Q59">
-        <v>3.84</v>
-      </c>
       <c r="R59">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="S59">
         <v>1.21</v>
@@ -9950,7 +9950,7 @@
         <v>2.15</v>
       </c>
       <c r="V59">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W59">
         <v>1.12</v>
@@ -9959,7 +9959,7 @@
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z59">
         <v>5.39</v>
@@ -9974,10 +9974,10 @@
         <v>2.17</v>
       </c>
       <c r="AD59">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AE59">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF59">
         <v>1.44</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AK59">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>3.8</v>
       </c>
       <c r="Q66">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>2.57</v>
@@ -11085,7 +11085,7 @@
         <v>1.13</v>
       </c>
       <c r="T66">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="U66">
         <v>1.85</v>
@@ -11103,7 +11103,7 @@
         <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>7.2</v>
+        <v>7.36</v>
       </c>
       <c r="AA66">
         <v>1.3</v>
@@ -11112,13 +11112,13 @@
         <v>3.2</v>
       </c>
       <c r="AC66">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AD66">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AE66">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF66">
         <v>1.33</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O71">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="P71">
         <v>9.9</v>
@@ -11900,7 +11900,7 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="U71">
         <v>2.25</v>
@@ -11921,10 +11921,10 @@
         <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC71">
         <v>2.45</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O72">
         <v>2.9</v>
       </c>
       <c r="P72">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q72">
         <v>2.69</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q79">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC79">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14674,16 +14674,16 @@
         <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V88">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W88">
         <v>1.14</v>
       </c>
       <c r="X88">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
         <v>1.12</v>
@@ -14692,13 +14692,13 @@
         <v>4.75</v>
       </c>
       <c r="AA88">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AC88">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD88">
         <v>1.56</v>
@@ -15172,7 +15172,7 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y91">
         <v>1.33</v>
@@ -15190,10 +15190,10 @@
         <v>4.1</v>
       </c>
       <c r="AD91">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE91">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF91">
         <v>1.87</v>
@@ -15308,10 +15308,10 @@
         <v>2.77</v>
       </c>
       <c r="O92">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q92">
         <v>3.28</v>
@@ -15329,7 +15329,7 @@
         <v>2.15</v>
       </c>
       <c r="V92">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W92">
         <v>1.18</v>
@@ -15344,7 +15344,7 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
         <v>2.66</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.25</v>
+        <v>5.55</v>
       </c>
       <c r="O101">
         <v>4.5</v>
       </c>
       <c r="P101">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q101">
-        <v>5.52</v>
+        <v>5.48</v>
       </c>
       <c r="R101">
         <v>2.6</v>
@@ -16796,7 +16796,7 @@
         <v>2</v>
       </c>
       <c r="V101">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W101">
         <v>1.18</v>
@@ -16805,19 +16805,19 @@
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z101">
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD101">
         <v>1.67</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -1453,10 +1453,10 @@
         <v>5.25</v>
       </c>
       <c r="O7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -1465,19 +1465,19 @@
         <v>2.63</v>
       </c>
       <c r="S7">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T7">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="U7">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1492,22 +1492,22 @@
         <v>1.44</v>
       </c>
       <c r="AB7">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC7">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD7">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         <v>2.45</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P9">
         <v>2.75</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,10 +2105,10 @@
         <v>1.23</v>
       </c>
       <c r="O11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="P11">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -4719,10 +4719,10 @@
         <v>2.78</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4749,10 +4749,10 @@
         <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AC27">
         <v>3.6</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>2.6</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
         <v>2.45</v>
@@ -4891,7 +4891,7 @@
         <v>1.31</v>
       </c>
       <c r="T28">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U28">
         <v>2.72</v>
@@ -4946,7 +4946,7 @@
         <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O41">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P41">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="O45">
         <v>2.7</v>
       </c>
       <c r="P45">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q45">
-        <v>3.45</v>
+        <v>3.67</v>
       </c>
       <c r="R45">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S45">
         <v>1.53</v>
@@ -7677,13 +7677,13 @@
         <v>1.1</v>
       </c>
       <c r="Y45">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="Z45">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AA45">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AB45">
         <v>1.4</v>
@@ -7695,13 +7695,13 @@
         <v>1.13</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG45">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
+        <v>1.44</v>
+      </c>
+      <c r="AK45">
         <v>1.4</v>
-      </c>
-      <c r="AK45">
-        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>4.6</v>
       </c>
       <c r="O46">
-        <v>3.88</v>
+        <v>3.91</v>
       </c>
       <c r="P46">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="Q46">
         <v>5.2</v>
@@ -7852,10 +7852,10 @@
         <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AD46">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE46">
         <v>1.13</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
         <v>3</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8160,7 +8160,7 @@
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,13 +8172,13 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
         <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD48">
         <v>1.52</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q51">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="R51">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S51">
         <v>1.32</v>
@@ -8664,7 +8664,7 @@
         <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC51">
         <v>2.88</v>
@@ -8673,7 +8673,7 @@
         <v>1.32</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
         <v>1.67</v>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8791,7 +8791,7 @@
         <v>4.2</v>
       </c>
       <c r="P52">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -8821,7 +8821,7 @@
         <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O56">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="Q56">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R56">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9479,7 +9479,7 @@
         <v>1.6</v>
       </c>
       <c r="AB56">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC56">
         <v>2.45</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.43</v>
+        <v>2.86</v>
       </c>
       <c r="O57">
-        <v>3.85</v>
+        <v>3.52</v>
       </c>
       <c r="P57">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q57">
         <v>3.1</v>
@@ -9639,10 +9639,10 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB57">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC57">
         <v>2.08</v>
@@ -10098,16 +10098,16 @@
         <v>1.26</v>
       </c>
       <c r="Q60">
-        <v>6.86</v>
+        <v>6.57</v>
       </c>
       <c r="R60">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="S60">
         <v>1.17</v>
       </c>
       <c r="T60">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U60">
         <v>1.93</v>
@@ -10116,7 +10116,7 @@
         <v>1.91</v>
       </c>
       <c r="W60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
         <v>1</v>
@@ -10125,7 +10125,7 @@
         <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>7.07</v>
+        <v>7.09</v>
       </c>
       <c r="AA60">
         <v>1.33</v>
@@ -10134,13 +10134,13 @@
         <v>3.4</v>
       </c>
       <c r="AC60">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AD60">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE60">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AF60">
         <v>1.67</v>
@@ -10162,7 +10162,7 @@
         <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
         <v>2.27</v>
       </c>
       <c r="Q61">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R61">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10276,7 +10276,7 @@
         <v>2.15</v>
       </c>
       <c r="V61">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W61">
         <v>1.16</v>
@@ -10285,13 +10285,13 @@
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB61">
         <v>2.31</v>
@@ -10303,7 +10303,7 @@
         <v>1.57</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
         <v>1.44</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
         <v>1.39</v>
@@ -10747,7 +10747,7 @@
         <v>3.85</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -10771,7 +10771,7 @@
         <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
         <v>1.17</v>
@@ -10792,7 +10792,7 @@
         <v>1.49</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
         <v>3.5</v>
@@ -10916,7 +10916,7 @@
         <v>2.15</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10925,7 +10925,7 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="V65">
         <v>1.56</v>
@@ -10958,7 +10958,7 @@
         <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
         <v>2.4</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK65">
         <v>1.82</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q68">
         <v>2.73</v>
@@ -11408,7 +11408,7 @@
         <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
         <v>3</v>
@@ -11417,7 +11417,7 @@
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W68">
         <v>1.06</v>
@@ -11429,16 +11429,16 @@
         <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="AA68">
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC68">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -12054,7 +12054,7 @@
         <v>3.8</v>
       </c>
       <c r="Q72">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R72">
         <v>1.85</v>
@@ -12099,10 +12099,10 @@
         <v>1.03</v>
       </c>
       <c r="AF72">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AG72">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK72">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O73">
         <v>4.1</v>
       </c>
       <c r="P73">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q73">
         <v>1.93</v>
@@ -12226,7 +12226,7 @@
         <v>1.29</v>
       </c>
       <c r="T73">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U73">
         <v>2.6</v>
@@ -12250,16 +12250,16 @@
         <v>1.8</v>
       </c>
       <c r="AB73">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC73">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="AD73">
         <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
         <v>1.91</v>
@@ -12371,10 +12371,10 @@
         </is>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="O74">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
         <v>2.25</v>
@@ -12537,7 +12537,7 @@
         <v>1.9</v>
       </c>
       <c r="O75">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
         <v>3.1</v>
@@ -12552,13 +12552,13 @@
         <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U75">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W75">
         <v>1.11</v>
@@ -12579,10 +12579,10 @@
         <v>2.1</v>
       </c>
       <c r="AC75">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="AD75">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE75">
         <v>1.1</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12703,7 +12703,7 @@
         <v>3.5</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q76">
         <v>2.41</v>
@@ -12742,7 +12742,7 @@
         <v>2.45</v>
       </c>
       <c r="AC76">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD76">
         <v>1.55</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12878,37 +12878,37 @@
         <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W77">
         <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y77">
         <v>1.32</v>
       </c>
       <c r="Z77">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="AA77">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB77">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC77">
         <v>3.6</v>
       </c>
       <c r="AD77">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE77">
         <v>1.07</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="O78">
+        <v>2.8</v>
+      </c>
+      <c r="P78">
         <v>2.75</v>
-      </c>
-      <c r="P78">
-        <v>2.95</v>
       </c>
       <c r="Q78">
         <v>3.2</v>
@@ -13041,7 +13041,7 @@
         <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="U78">
         <v>3.4</v>
@@ -13062,10 +13062,10 @@
         <v>2.41</v>
       </c>
       <c r="AA78">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB78">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC78">
         <v>4.8</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R80">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S80">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U80">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V80">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X80">
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z80">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA80">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB80">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AC80">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD80">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE80">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF80">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AG80">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,22 +13512,22 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P81">
-        <v>2.66</v>
+        <v>4.09</v>
       </c>
       <c r="Q81">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S81">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T81">
         <v>4</v>
@@ -13536,40 +13536,40 @@
         <v>2.05</v>
       </c>
       <c r="V81">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W81">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z81">
         <v>6</v>
       </c>
       <c r="AA81">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB81">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC81">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AD81">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AE81">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF81">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82">
@@ -13678,61 +13678,61 @@
         <v>2.05</v>
       </c>
       <c r="O82">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="Q82">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V82">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AC82">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AD82">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="AE82">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O83">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="R83">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
+        <v>1.25</v>
+      </c>
+      <c r="T83">
+        <v>3.5</v>
+      </c>
+      <c r="U83">
+        <v>2.25</v>
+      </c>
+      <c r="V83">
+        <v>1.6</v>
+      </c>
+      <c r="W83">
         <v>1.15</v>
-      </c>
-      <c r="T83">
-        <v>4.8</v>
-      </c>
-      <c r="U83">
-        <v>1.8</v>
-      </c>
-      <c r="V83">
-        <v>1.91</v>
-      </c>
-      <c r="W83">
-        <v>1.25</v>
       </c>
       <c r="X83">
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AA83">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AB83">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC83">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="AD83">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="AE83">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="AG83">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O84">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P84">
-        <v>4.09</v>
+        <v>3.09</v>
       </c>
       <c r="Q84">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="S84">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="T84">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U84">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="V84">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="W84">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Z84">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA84">
+        <v>1.28</v>
+      </c>
+      <c r="AB84">
+        <v>3.4</v>
+      </c>
+      <c r="AC84">
+        <v>1.74</v>
+      </c>
+      <c r="AD84">
+        <v>2.07</v>
+      </c>
+      <c r="AE84">
         <v>1.44</v>
       </c>
-      <c r="AB84">
-        <v>2.7</v>
-      </c>
-      <c r="AC84">
-        <v>2.13</v>
-      </c>
-      <c r="AD84">
-        <v>1.67</v>
-      </c>
-      <c r="AE84">
-        <v>1.29</v>
-      </c>
       <c r="AF84">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AG84">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK84">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14505,19 +14505,19 @@
         <v>2.31</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
         <v>3</v>
       </c>
       <c r="U87">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V87">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X87">
         <v>1.03</v>
@@ -14852,13 +14852,13 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
       </c>
       <c r="AB89">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
         <v>2.74</v>
@@ -14889,7 +14889,7 @@
         <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O90">
         <v>3.44</v>
@@ -14997,10 +14997,10 @@
         <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V90">
         <v>1.4</v>
@@ -15012,10 +15012,10 @@
         <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z90">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AA90">
         <v>1.9</v>
@@ -15024,10 +15024,10 @@
         <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="AD90">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE90">
         <v>1.1</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK90">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O91">
         <v>3.2</v>
@@ -15317,7 +15317,7 @@
         <v>3.28</v>
       </c>
       <c r="R92">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="S92">
         <v>1.22</v>
@@ -15344,7 +15344,7 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB92">
         <v>2.66</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="O93">
         <v>3.8</v>
@@ -15483,7 +15483,7 @@
         <v>2.3</v>
       </c>
       <c r="S93">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
         <v>3.25</v>
@@ -15498,7 +15498,7 @@
         <v>1.11</v>
       </c>
       <c r="X93">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
         <v>1.15</v>
@@ -15507,7 +15507,7 @@
         <v>3</v>
       </c>
       <c r="AA93">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB93">
         <v>2.05</v>
@@ -15516,7 +15516,7 @@
         <v>2.25</v>
       </c>
       <c r="AD93">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE93">
         <v>1.16</v>
@@ -15634,7 +15634,7 @@
         <v>1.26</v>
       </c>
       <c r="O94">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="P94">
         <v>9.25</v>
@@ -15661,7 +15661,7 @@
         <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y94">
         <v>1.11</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,65 +15794,65 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="O95">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P95">
-        <v>3.2</v>
+        <v>2.03</v>
       </c>
       <c r="Q95">
-        <v>2.25</v>
+        <v>3.84</v>
       </c>
       <c r="R95">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="S95">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="V95">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="W95">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>4.95</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AB95">
+        <v>2.15</v>
+      </c>
+      <c r="AC95">
+        <v>2.55</v>
+      </c>
+      <c r="AD95">
+        <v>1.45</v>
+      </c>
+      <c r="AE95">
+        <v>1.15</v>
+      </c>
+      <c r="AF95">
+        <v>1.5</v>
+      </c>
+      <c r="AG95">
         <v>2.38</v>
       </c>
-      <c r="AC95">
-        <v>2.19</v>
-      </c>
-      <c r="AD95">
-        <v>1.59</v>
-      </c>
-      <c r="AE95">
-        <v>1.2</v>
-      </c>
-      <c r="AF95">
-        <v>1.44</v>
-      </c>
-      <c r="AG95">
-        <v>2.55</v>
-      </c>
       <c r="AH95" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
+        <v>1.29</v>
+      </c>
+      <c r="AK95">
         <v>1.3</v>
-      </c>
-      <c r="AK95">
-        <v>1.83</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q96">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="R96">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="S96">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="T96">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="U96">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="V96">
+        <v>1.61</v>
+      </c>
+      <c r="W96">
+        <v>1.17</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.11</v>
+      </c>
+      <c r="Z96">
+        <v>4.95</v>
+      </c>
+      <c r="AA96">
         <v>1.46</v>
       </c>
-      <c r="W96">
-        <v>1.11</v>
-      </c>
-      <c r="X96">
-        <v>1.04</v>
-      </c>
-      <c r="Y96">
-        <v>1.23</v>
-      </c>
-      <c r="Z96">
-        <v>4.03</v>
-      </c>
-      <c r="AA96">
-        <v>1.72</v>
-      </c>
       <c r="AB96">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AC96">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD96">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AE96">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF96">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG96">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O97">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q97">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="R97">
         <v>2.18</v>
       </c>
       <c r="S97">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T97">
-        <v>2.82</v>
+        <v>3.26</v>
       </c>
       <c r="U97">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V97">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W97">
         <v>1.11</v>
       </c>
       <c r="X97">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y97">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z97">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AA97">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB97">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC97">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD97">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE97">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF97">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG97">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK97">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,80 +16283,80 @@
         </is>
       </c>
       <c r="N98">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O98">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q98">
-        <v>5.75</v>
+        <v>2.57</v>
       </c>
       <c r="R98">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U98">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V98">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W98">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AA98">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AB98">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AC98">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD98">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF98">
+        <v>1.65</v>
+      </c>
+      <c r="AG98">
+        <v>2.11</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ98">
+        <v>1.28</v>
+      </c>
+      <c r="AK98">
         <v>1.7</v>
-      </c>
-      <c r="AG98">
-        <v>2.04</v>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ98">
-        <v>1.22</v>
-      </c>
-      <c r="AK98">
-        <v>1.15</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="O99">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P99">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="Q99">
-        <v>3.84</v>
+        <v>5.75</v>
       </c>
       <c r="R99">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="S99">
         <v>1.3</v>
       </c>
       <c r="T99">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V99">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W99">
         <v>1.12</v>
       </c>
       <c r="X99">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y99">
+        <v>1.18</v>
+      </c>
+      <c r="Z99">
+        <v>4.33</v>
+      </c>
+      <c r="AA99">
+        <v>1.64</v>
+      </c>
+      <c r="AB99">
+        <v>2.17</v>
+      </c>
+      <c r="AC99">
+        <v>2.62</v>
+      </c>
+      <c r="AD99">
+        <v>1.42</v>
+      </c>
+      <c r="AE99">
+        <v>1.14</v>
+      </c>
+      <c r="AF99">
+        <v>1.7</v>
+      </c>
+      <c r="AG99">
+        <v>2.04</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.22</v>
+      </c>
+      <c r="AK99">
         <v>1.15</v>
-      </c>
-      <c r="Z99">
-        <v>4.25</v>
-      </c>
-      <c r="AA99">
-        <v>1.61</v>
-      </c>
-      <c r="AB99">
-        <v>2.15</v>
-      </c>
-      <c r="AC99">
-        <v>2.55</v>
-      </c>
-      <c r="AD99">
-        <v>1.45</v>
-      </c>
-      <c r="AE99">
-        <v>1.15</v>
-      </c>
-      <c r="AF99">
-        <v>1.5</v>
-      </c>
-      <c r="AG99">
-        <v>2.38</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.29</v>
-      </c>
-      <c r="AK99">
-        <v>1.3</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.46</v>
+        <v>3.08</v>
       </c>
       <c r="O100">
         <v>3.6</v>
       </c>
       <c r="P100">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q100">
         <v>3.75</v>
@@ -16682,7 +16682,7 @@
         <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="O103">
         <v>4.8</v>
@@ -17137,19 +17137,19 @@
         <v>6</v>
       </c>
       <c r="AA103">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB103">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AC103">
         <v>2.38</v>
       </c>
       <c r="AD103">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE103">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
@@ -17171,7 +17171,7 @@
         <v>1.14</v>
       </c>
       <c r="AK103">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17267,7 +17267,7 @@
         <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="Q104">
         <v>3</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O105">
         <v>3.55</v>
       </c>
       <c r="P105">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q105">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="R105">
         <v>2.25</v>
@@ -17442,10 +17442,10 @@
         <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V105">
         <v>1.53</v>
@@ -17460,7 +17460,7 @@
         <v>1.2</v>
       </c>
       <c r="Z105">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA105">
         <v>1.77</v>
@@ -17469,19 +17469,19 @@
         <v>2.15</v>
       </c>
       <c r="AC105">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="AD105">
         <v>1.44</v>
       </c>
       <c r="AE105">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF105">
         <v>1.57</v>
       </c>
       <c r="AG105">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17602,7 +17602,7 @@
         <v>2.6</v>
       </c>
       <c r="S106">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T106">
         <v>3.32</v>
@@ -17614,7 +17614,7 @@
         <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17623,22 +17623,22 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA106">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AB106">
         <v>2.4</v>
       </c>
       <c r="AC106">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AD106">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE106">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF106">
         <v>1.95</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AK106">
         <v>1.02</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O107">
         <v>3.8</v>
       </c>
       <c r="P107">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -17792,7 +17792,7 @@
         <v>1.96</v>
       </c>
       <c r="AB107">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
         <v>3.4</v>
@@ -18079,22 +18079,22 @@
         <v>1.36</v>
       </c>
       <c r="O109">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="P109">
         <v>6.25</v>
       </c>
       <c r="Q109">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="R109">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S109">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T109">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U109">
         <v>2.05</v>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O110">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="P110">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q110">
         <v>2.15</v>
@@ -18296,7 +18296,7 @@
         <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18574,10 +18574,10 @@
         <v>4.6</v>
       </c>
       <c r="Q112">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S112">
         <v>1.36</v>
@@ -18592,16 +18592,16 @@
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X112">
         <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA112">
         <v>2</v>
@@ -18610,7 +18610,7 @@
         <v>1.82</v>
       </c>
       <c r="AC112">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD112">
         <v>1.25</v>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18897,7 +18897,7 @@
         <v>4.55</v>
       </c>
       <c r="P114">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -19054,16 +19054,16 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
         <v>3.25</v>
       </c>
       <c r="P115">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="Q115">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R115">
         <v>2.15</v>
@@ -19217,19 +19217,19 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="O116">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q116">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R116">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S116">
         <v>1.22</v>
@@ -19244,7 +19244,7 @@
         <v>1.65</v>
       </c>
       <c r="W116">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X116">
         <v>1.02</v>
@@ -19271,10 +19271,10 @@
         <v>1.23</v>
       </c>
       <c r="AF116">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG116">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19546,7 +19546,7 @@
         <v>2.07</v>
       </c>
       <c r="O118">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P118">
         <v>3.3</v>
@@ -19597,10 +19597,10 @@
         <v>1.11</v>
       </c>
       <c r="AF118">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG118">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -964,25 +964,25 @@
         <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P4">
         <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="V4">
         <v>1.41</v>
@@ -1006,7 +1006,7 @@
         <v>1.87</v>
       </c>
       <c r="AC4">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>5.15</v>
       </c>
       <c r="O13">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="R13">
         <v>2.45</v>
@@ -2455,7 +2455,7 @@
         <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2470,22 +2470,22 @@
         <v>1.51</v>
       </c>
       <c r="AB13">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AC13">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE13">
         <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK13">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2920,61 +2920,61 @@
         <v>1.83</v>
       </c>
       <c r="O16">
+        <v>3.3</v>
+      </c>
+      <c r="P16">
+        <v>3.6</v>
+      </c>
+      <c r="Q16">
+        <v>2.39</v>
+      </c>
+      <c r="R16">
+        <v>2.08</v>
+      </c>
+      <c r="S16">
+        <v>1.33</v>
+      </c>
+      <c r="T16">
+        <v>3</v>
+      </c>
+      <c r="U16">
+        <v>2.55</v>
+      </c>
+      <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.09</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.22</v>
+      </c>
+      <c r="Z16">
         <v>3.5</v>
       </c>
-      <c r="P16">
-        <v>3.5</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>2.2</v>
+      </c>
+      <c r="O17">
+        <v>3.3</v>
+      </c>
+      <c r="P17">
+        <v>2.7</v>
+      </c>
+      <c r="Q17">
+        <v>2.72</v>
+      </c>
+      <c r="R17">
+        <v>2.19</v>
+      </c>
+      <c r="S17">
+        <v>1.3</v>
+      </c>
+      <c r="T17">
+        <v>3.1</v>
+      </c>
+      <c r="U17">
+        <v>2.5</v>
+      </c>
+      <c r="V17">
+        <v>1.44</v>
+      </c>
+      <c r="W17">
+        <v>1.1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1.21</v>
+      </c>
+      <c r="Z17">
+        <v>3.58</v>
+      </c>
+      <c r="AA17">
+        <v>1.8</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
-      <c r="O17">
-        <v>3.4</v>
-      </c>
-      <c r="P17">
-        <v>3.1</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P18">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P19">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Q19">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R19">
         <v>2.4</v>
@@ -3427,43 +3427,43 @@
         <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
         <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z19">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
+        <v>1.56</v>
+      </c>
+      <c r="AB19">
+        <v>2.22</v>
+      </c>
+      <c r="AC19">
+        <v>2.38</v>
+      </c>
+      <c r="AD19">
+        <v>1.46</v>
+      </c>
+      <c r="AE19">
+        <v>1.15</v>
+      </c>
+      <c r="AF19">
         <v>1.67</v>
       </c>
-      <c r="AB19">
-        <v>2.04</v>
-      </c>
-      <c r="AC19">
-        <v>2.69</v>
-      </c>
-      <c r="AD19">
-        <v>1.36</v>
-      </c>
-      <c r="AE19">
-        <v>1.1</v>
-      </c>
-      <c r="AF19">
-        <v>1.74</v>
-      </c>
       <c r="AG19">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
+        <v>3.2</v>
+      </c>
+      <c r="O32">
         <v>3.1</v>
       </c>
-      <c r="O32">
-        <v>3.15</v>
-      </c>
       <c r="P32">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5872,7 +5872,7 @@
         <v>2.77</v>
       </c>
       <c r="U34">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V34">
         <v>1.44</v>
@@ -6020,7 +6020,7 @@
         <v>2.87</v>
       </c>
       <c r="P35">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="Q35">
         <v>3.8</v>
@@ -6035,7 +6035,7 @@
         <v>2.19</v>
       </c>
       <c r="U35">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="V35">
         <v>1.22</v>
@@ -6053,7 +6053,7 @@
         <v>2.38</v>
       </c>
       <c r="AA35">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AB35">
         <v>1.37</v>
@@ -6071,7 +6071,7 @@
         <v>2.17</v>
       </c>
       <c r="AG35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.73</v>
+      </c>
+      <c r="O36">
+        <v>3.2</v>
+      </c>
+      <c r="P36">
+        <v>2.26</v>
+      </c>
+      <c r="Q36">
+        <v>3.5</v>
+      </c>
+      <c r="R36">
+        <v>2.17</v>
+      </c>
+      <c r="S36">
+        <v>1.39</v>
+      </c>
+      <c r="T36">
+        <v>2.91</v>
+      </c>
+      <c r="U36">
         <v>2.98</v>
       </c>
-      <c r="O36">
-        <v>3.19</v>
-      </c>
-      <c r="P36">
-        <v>2.51</v>
-      </c>
-      <c r="Q36">
-        <v>3.62</v>
-      </c>
-      <c r="R36">
-        <v>1.95</v>
-      </c>
-      <c r="S36">
-        <v>1.42</v>
-      </c>
-      <c r="T36">
-        <v>2.79</v>
-      </c>
-      <c r="U36">
-        <v>3.12</v>
-      </c>
       <c r="V36">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6346,7 +6346,7 @@
         <v>4.2</v>
       </c>
       <c r="P37">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="Q37">
         <v>1.9</v>
@@ -6995,10 +6995,10 @@
         <v>1.34</v>
       </c>
       <c r="O41">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="P41">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O43">
         <v>4.35</v>
@@ -7372,7 +7372,7 @@
         <v>1.44</v>
       </c>
       <c r="AF43">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
         <v>2.77</v>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="P46">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="Q46">
-        <v>5.2</v>
+        <v>5.38</v>
       </c>
       <c r="R46">
         <v>2.33</v>
@@ -7825,40 +7825,40 @@
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
         <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="AD46">
         <v>1.52</v>
       </c>
       <c r="AE46">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF46">
         <v>1.62</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="AK46">
         <v>1.18</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O47">
         <v>3.6</v>
@@ -7979,10 +7979,10 @@
         <v>3</v>
       </c>
       <c r="Q47">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
         <v>1.3</v>
@@ -8021,7 +8021,7 @@
         <v>1.4</v>
       </c>
       <c r="AE47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF47">
         <v>1.57</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8299,7 +8299,7 @@
         <v>1.85</v>
       </c>
       <c r="O49">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="P49">
         <v>3.3</v>
@@ -8465,7 +8465,7 @@
         <v>4.33</v>
       </c>
       <c r="P50">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="Q50">
         <v>1.92</v>
@@ -8532,7 +8532,7 @@
         <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="P53">
         <v>2.5</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,19 +9437,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.92</v>
+        <v>3.35</v>
       </c>
       <c r="Q56">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="R56">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S56">
         <v>1.25</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="Q57">
         <v>3.1</v>
@@ -9639,10 +9639,10 @@
         <v>5.5</v>
       </c>
       <c r="AA57">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB57">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AC57">
         <v>2.08</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q58">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R58">
         <v>2.25</v>
@@ -9793,7 +9793,7 @@
         <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
         <v>1.2</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,19 +9926,19 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O59">
+        <v>3.85</v>
+      </c>
+      <c r="P59">
+        <v>1.8</v>
+      </c>
+      <c r="Q59">
         <v>3.8</v>
       </c>
-      <c r="P59">
-        <v>1.94</v>
-      </c>
-      <c r="Q59">
-        <v>3.75</v>
-      </c>
       <c r="R59">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S59">
         <v>1.21</v>
@@ -9962,7 +9962,7 @@
         <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
       <c r="AA59">
         <v>1.48</v>
@@ -9983,7 +9983,7 @@
         <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AK59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10137,7 +10137,7 @@
         <v>1.87</v>
       </c>
       <c r="AD60">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE60">
         <v>1.43</v>
@@ -10255,7 +10255,7 @@
         <v>2.56</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
         <v>2.27</v>
@@ -10325,7 +10325,7 @@
         <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O62">
         <v>2.8</v>
       </c>
       <c r="P62">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q62">
         <v>3.42</v>
@@ -10451,7 +10451,7 @@
         <v>1.44</v>
       </c>
       <c r="Z62">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA62">
         <v>2.55</v>
@@ -10463,7 +10463,7 @@
         <v>4.4</v>
       </c>
       <c r="AD62">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE62">
         <v>1.01</v>
@@ -10472,7 +10472,7 @@
         <v>2</v>
       </c>
       <c r="AG62">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10581,10 +10581,10 @@
         <v>2.45</v>
       </c>
       <c r="O63">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P63">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q63">
         <v>3.3</v>
@@ -10596,7 +10596,7 @@
         <v>1.6</v>
       </c>
       <c r="T63">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="U63">
         <v>3.9</v>
@@ -10605,7 +10605,7 @@
         <v>1.22</v>
       </c>
       <c r="W63">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X63">
         <v>1.13</v>
@@ -10623,13 +10623,13 @@
         <v>1.36</v>
       </c>
       <c r="AC63">
-        <v>6.25</v>
+        <v>6.34</v>
       </c>
       <c r="AD63">
         <v>1.11</v>
       </c>
       <c r="AE63">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF63">
         <v>2.3</v>
@@ -10747,7 +10747,7 @@
         <v>3.85</v>
       </c>
       <c r="P64">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
         <v>2.2</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
         <v>3.5</v>
@@ -10958,7 +10958,7 @@
         <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
         <v>2.4</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="O66">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R66">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="S66">
         <v>1.13</v>
@@ -11088,10 +11088,10 @@
         <v>4.55</v>
       </c>
       <c r="U66">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V66">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="W66">
         <v>1.22</v>
@@ -11103,7 +11103,7 @@
         <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>7.36</v>
+        <v>7.28</v>
       </c>
       <c r="AA66">
         <v>1.3</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK66">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,16 +11230,16 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P67">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="Q67">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="R67">
         <v>2.4</v>
@@ -11251,7 +11251,7 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V67">
         <v>1.57</v>
@@ -11275,7 +11275,7 @@
         <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="AD67">
         <v>1.51</v>
@@ -11303,7 +11303,7 @@
         <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O68">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="P68">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="Q68">
         <v>2.73</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S68">
         <v>1.37</v>
@@ -11420,7 +11420,7 @@
         <v>1.41</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11556,22 +11556,22 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O69">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P69">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Q69">
         <v>1.9</v>
       </c>
       <c r="R69">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="S69">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T69">
         <v>4</v>
@@ -11589,10 +11589,10 @@
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z69">
-        <v>5.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA69">
         <v>1.36</v>
@@ -11601,19 +11601,19 @@
         <v>2.88</v>
       </c>
       <c r="AC69">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD69">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE69">
         <v>1.29</v>
       </c>
       <c r="AF69">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK69">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,22 +11719,22 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="O70">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="R70">
         <v>2.22</v>
       </c>
       <c r="S70">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T70">
         <v>3.4</v>
@@ -11749,19 +11749,19 @@
         <v>1.12</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z70">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="AA70">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB70">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC70">
         <v>2.56</v>
@@ -11773,10 +11773,10 @@
         <v>1.18</v>
       </c>
       <c r="AF70">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.21</v>
       </c>
       <c r="AK70">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11888,7 +11888,7 @@
         <v>5.5</v>
       </c>
       <c r="P71">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11912,7 +11912,7 @@
         <v>1.15</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.12</v>
@@ -11921,16 +11921,16 @@
         <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB71">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC71">
         <v>2.45</v>
       </c>
       <c r="AD71">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE71">
         <v>1.17</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="O73">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>6.2</v>
+        <v>2.87</v>
       </c>
       <c r="Q73">
-        <v>1.93</v>
+        <v>2.76</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="S73">
+        <v>1.36</v>
+      </c>
+      <c r="T73">
+        <v>2.88</v>
+      </c>
+      <c r="U73">
+        <v>3.01</v>
+      </c>
+      <c r="V73">
+        <v>1.39</v>
+      </c>
+      <c r="W73">
+        <v>1.08</v>
+      </c>
+      <c r="X73">
+        <v>1.05</v>
+      </c>
+      <c r="Y73">
+        <v>1.32</v>
+      </c>
+      <c r="Z73">
+        <v>3.34</v>
+      </c>
+      <c r="AA73">
+        <v>2.05</v>
+      </c>
+      <c r="AB73">
+        <v>1.75</v>
+      </c>
+      <c r="AC73">
+        <v>3.6</v>
+      </c>
+      <c r="AD73">
         <v>1.29</v>
       </c>
-      <c r="T73">
-        <v>3.17</v>
-      </c>
-      <c r="U73">
-        <v>2.6</v>
-      </c>
-      <c r="V73">
-        <v>1.44</v>
-      </c>
-      <c r="W73">
-        <v>1.11</v>
-      </c>
-      <c r="X73">
-        <v>1.02</v>
-      </c>
-      <c r="Y73">
-        <v>1.22</v>
-      </c>
-      <c r="Z73">
-        <v>3.5</v>
-      </c>
-      <c r="AA73">
-        <v>1.8</v>
-      </c>
-      <c r="AB73">
-        <v>1.99</v>
-      </c>
-      <c r="AC73">
-        <v>3.07</v>
-      </c>
-      <c r="AD73">
-        <v>1.32</v>
-      </c>
       <c r="AE73">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF73">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK73">
-        <v>2.7</v>
+        <v>1.51</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.58</v>
+        <v>1.48</v>
       </c>
       <c r="O74">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="P74">
-        <v>2.25</v>
+        <v>6.17</v>
       </c>
       <c r="Q74">
-        <v>3.47</v>
+        <v>1.95</v>
       </c>
       <c r="R74">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="U74">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="V74">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z74">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB74">
+        <v>1.9</v>
+      </c>
+      <c r="AC74">
+        <v>3.12</v>
+      </c>
+      <c r="AD74">
+        <v>1.32</v>
+      </c>
+      <c r="AE74">
+        <v>1.13</v>
+      </c>
+      <c r="AF74">
+        <v>1.9</v>
+      </c>
+      <c r="AG74">
         <v>1.8</v>
       </c>
-      <c r="AC74">
-        <v>3.34</v>
-      </c>
-      <c r="AD74">
-        <v>1.24</v>
-      </c>
-      <c r="AE74">
-        <v>1.06</v>
-      </c>
-      <c r="AF74">
-        <v>1.76</v>
-      </c>
-      <c r="AG74">
-        <v>1.96</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.9</v>
+        <v>2.97</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P75">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q75">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="R75">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T75">
-        <v>3.27</v>
+        <v>2.82</v>
       </c>
       <c r="U75">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V75">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z75">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA75">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC75">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="AD75">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE75">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF75">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG75">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK75">
-        <v>1.66</v>
+        <v>1.34</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P76">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q76">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R76">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="U76">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="V76">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="W76">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA76">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB76">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC76">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="AD76">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AE76">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG76">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
+        <v>1.97</v>
+      </c>
+      <c r="O77">
+        <v>3.5</v>
+      </c>
+      <c r="P77">
+        <v>3.2</v>
+      </c>
+      <c r="Q77">
+        <v>2.41</v>
+      </c>
+      <c r="R77">
+        <v>2.28</v>
+      </c>
+      <c r="S77">
+        <v>1.25</v>
+      </c>
+      <c r="T77">
+        <v>3.7</v>
+      </c>
+      <c r="U77">
         <v>2.17</v>
       </c>
-      <c r="O77">
-        <v>3.3</v>
-      </c>
-      <c r="P77">
-        <v>2.9</v>
-      </c>
-      <c r="Q77">
-        <v>2.76</v>
-      </c>
-      <c r="R77">
-        <v>2.01</v>
-      </c>
-      <c r="S77">
-        <v>1.36</v>
-      </c>
-      <c r="T77">
-        <v>2.88</v>
-      </c>
-      <c r="U77">
-        <v>3.01</v>
-      </c>
       <c r="V77">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="W77">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z77">
-        <v>3.34</v>
+        <v>4.95</v>
       </c>
       <c r="AA77">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AB77">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AC77">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="AD77">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AE77">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AF77">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AG77">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O79">
         <v>3.4</v>
       </c>
       <c r="P79">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q79">
         <v>2.56</v>
@@ -13259,7 +13259,7 @@
         <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q80">
         <v>2.8</v>
@@ -13382,31 +13382,31 @@
         <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z80">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="AA80">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB80">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC80">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD80">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE80">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF80">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AG80">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK80">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O81">
         <v>4.3</v>
       </c>
       <c r="P81">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="Q81">
         <v>2.16</v>
@@ -13542,7 +13542,7 @@
         <v>1.2</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.13</v>
@@ -13557,7 +13557,7 @@
         <v>2.7</v>
       </c>
       <c r="AC81">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AD81">
         <v>1.67</v>
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="Q82">
         <v>2.55</v>
@@ -13841,10 +13841,10 @@
         <v>2.05</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Q83">
         <v>2.6</v>
@@ -13883,10 +13883,10 @@
         <v>2.38</v>
       </c>
       <c r="AC83">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD83">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE83">
         <v>1.18</v>
@@ -14004,13 +14004,13 @@
         <v>1.95</v>
       </c>
       <c r="O84">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P84">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="Q84">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R84">
         <v>2.62</v>
@@ -14043,13 +14043,13 @@
         <v>1.28</v>
       </c>
       <c r="AB84">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC84">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD84">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AE84">
         <v>1.44</v>
@@ -14058,7 +14058,7 @@
         <v>1.28</v>
       </c>
       <c r="AG84">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>2.37</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
         <v>1.22</v>
@@ -14209,7 +14209,7 @@
         <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AD85">
         <v>1.64</v>
@@ -14327,19 +14327,19 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O86">
         <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q86">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R86">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S86">
         <v>1.19</v>
@@ -14360,7 +14360,7 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z86">
         <v>5.55</v>
@@ -14381,10 +14381,10 @@
         <v>1.22</v>
       </c>
       <c r="AF86">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG86">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O87">
         <v>3.6</v>
@@ -14656,7 +14656,7 @@
         <v>2.1</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
         <v>2.95</v>
@@ -14837,10 +14837,10 @@
         <v>2.86</v>
       </c>
       <c r="U89">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V89">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W89">
         <v>1.08</v>
@@ -14852,7 +14852,7 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
@@ -14979,28 +14979,28 @@
         </is>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="O90">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P90">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q90">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="R90">
         <v>2.05</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T90">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U90">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="V90">
         <v>1.4</v>
@@ -15012,10 +15012,10 @@
         <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z90">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="AA90">
         <v>1.9</v>
@@ -15024,7 +15024,7 @@
         <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="AD90">
         <v>1.32</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O93">
         <v>3.8</v>
       </c>
       <c r="P93">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q93">
         <v>2.1</v>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O94">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="P94">
         <v>9.25</v>
       </c>
       <c r="Q94">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R94">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="S94">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="T94">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="U94">
         <v>2.3</v>
@@ -15658,37 +15658,37 @@
         <v>1.55</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X94">
         <v>1.01</v>
       </c>
       <c r="Y94">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA94">
         <v>1.57</v>
       </c>
       <c r="AB94">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC94">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AD94">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AE94">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF94">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AG94">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P96">
+        <v>1.55</v>
+      </c>
+      <c r="Q96">
+        <v>5.75</v>
+      </c>
+      <c r="R96">
+        <v>2.52</v>
+      </c>
+      <c r="S96">
+        <v>1.3</v>
+      </c>
+      <c r="T96">
         <v>3.2</v>
       </c>
-      <c r="Q96">
-        <v>2.25</v>
-      </c>
-      <c r="R96">
-        <v>2.53</v>
-      </c>
-      <c r="S96">
+      <c r="U96">
+        <v>2.38</v>
+      </c>
+      <c r="V96">
+        <v>1.53</v>
+      </c>
+      <c r="W96">
+        <v>1.12</v>
+      </c>
+      <c r="X96">
+        <v>1.03</v>
+      </c>
+      <c r="Y96">
+        <v>1.18</v>
+      </c>
+      <c r="Z96">
+        <v>4.33</v>
+      </c>
+      <c r="AA96">
+        <v>1.64</v>
+      </c>
+      <c r="AB96">
+        <v>2.17</v>
+      </c>
+      <c r="AC96">
+        <v>2.62</v>
+      </c>
+      <c r="AD96">
+        <v>1.42</v>
+      </c>
+      <c r="AE96">
+        <v>1.14</v>
+      </c>
+      <c r="AF96">
+        <v>1.7</v>
+      </c>
+      <c r="AG96">
+        <v>2.04</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
         <v>1.22</v>
       </c>
-      <c r="T96">
-        <v>3.8</v>
-      </c>
-      <c r="U96">
-        <v>2.24</v>
-      </c>
-      <c r="V96">
-        <v>1.61</v>
-      </c>
-      <c r="W96">
-        <v>1.17</v>
-      </c>
-      <c r="X96">
-        <v>1.01</v>
-      </c>
-      <c r="Y96">
-        <v>1.11</v>
-      </c>
-      <c r="Z96">
-        <v>4.95</v>
-      </c>
-      <c r="AA96">
-        <v>1.46</v>
-      </c>
-      <c r="AB96">
-        <v>2.38</v>
-      </c>
-      <c r="AC96">
-        <v>2.19</v>
-      </c>
-      <c r="AD96">
-        <v>1.59</v>
-      </c>
-      <c r="AE96">
-        <v>1.2</v>
-      </c>
-      <c r="AF96">
-        <v>1.44</v>
-      </c>
-      <c r="AG96">
-        <v>2.55</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.3</v>
-      </c>
       <c r="AK96">
-        <v>1.83</v>
+        <v>1.15</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P97">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="R97">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="S97">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="T97">
-        <v>3.26</v>
+        <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="V97">
+        <v>1.61</v>
+      </c>
+      <c r="W97">
+        <v>1.17</v>
+      </c>
+      <c r="X97">
+        <v>1.01</v>
+      </c>
+      <c r="Y97">
+        <v>1.11</v>
+      </c>
+      <c r="Z97">
+        <v>4.95</v>
+      </c>
+      <c r="AA97">
         <v>1.46</v>
       </c>
-      <c r="W97">
-        <v>1.11</v>
-      </c>
-      <c r="X97">
-        <v>1.04</v>
-      </c>
-      <c r="Y97">
-        <v>1.23</v>
-      </c>
-      <c r="Z97">
-        <v>4.03</v>
-      </c>
-      <c r="AA97">
-        <v>1.72</v>
-      </c>
       <c r="AB97">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AC97">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD97">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AE97">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF97">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG97">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK97">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P98">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q98">
-        <v>2.57</v>
+        <v>2.74</v>
       </c>
       <c r="R98">
         <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T98">
-        <v>2.82</v>
+        <v>3.26</v>
       </c>
       <c r="U98">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V98">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W98">
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z98">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AA98">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB98">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC98">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF98">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AG98">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK98">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,80 +16446,80 @@
         </is>
       </c>
       <c r="N99">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O99">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P99">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q99">
-        <v>5.75</v>
+        <v>2.57</v>
       </c>
       <c r="R99">
-        <v>2.52</v>
+        <v>2.18</v>
       </c>
       <c r="S99">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U99">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V99">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W99">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="AA99">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AB99">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="AC99">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD99">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AE99">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF99">
+        <v>1.65</v>
+      </c>
+      <c r="AG99">
+        <v>2.11</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ99">
+        <v>1.28</v>
+      </c>
+      <c r="AK99">
         <v>1.7</v>
-      </c>
-      <c r="AG99">
-        <v>2.04</v>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ99">
-        <v>1.22</v>
-      </c>
-      <c r="AK99">
-        <v>1.15</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="O100">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P100">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q100">
         <v>3.75</v>
@@ -16682,7 +16682,7 @@
         <v>1.22</v>
       </c>
       <c r="AK100">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,19 +16772,19 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="O101">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P101">
         <v>1.53</v>
       </c>
       <c r="Q101">
-        <v>5.48</v>
+        <v>5.6</v>
       </c>
       <c r="R101">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S101">
         <v>1.2</v>
@@ -16805,22 +16805,22 @@
         <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z101">
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AB101">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC101">
         <v>2.1</v>
       </c>
       <c r="AD101">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE101">
         <v>1.25</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>2.41</v>
+        <v>2.46</v>
       </c>
       <c r="AK101">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
+        <v>1.83</v>
+      </c>
+      <c r="O102">
+        <v>3.3</v>
+      </c>
+      <c r="P102">
+        <v>3.84</v>
+      </c>
+      <c r="Q102">
+        <v>2.47</v>
+      </c>
+      <c r="R102">
+        <v>2</v>
+      </c>
+      <c r="S102">
+        <v>1.4</v>
+      </c>
+      <c r="T102">
+        <v>2.75</v>
+      </c>
+      <c r="U102">
+        <v>2.9</v>
+      </c>
+      <c r="V102">
+        <v>1.36</v>
+      </c>
+      <c r="W102">
+        <v>1.07</v>
+      </c>
+      <c r="X102">
+        <v>1.03</v>
+      </c>
+      <c r="Y102">
+        <v>1.29</v>
+      </c>
+      <c r="Z102">
+        <v>3.04</v>
+      </c>
+      <c r="AA102">
+        <v>2.02</v>
+      </c>
+      <c r="AB102">
+        <v>1.68</v>
+      </c>
+      <c r="AC102">
+        <v>3.58</v>
+      </c>
+      <c r="AD102">
+        <v>1.21</v>
+      </c>
+      <c r="AE102">
+        <v>1.08</v>
+      </c>
+      <c r="AF102">
+        <v>1.8</v>
+      </c>
+      <c r="AG102">
+        <v>1.91</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.23</v>
+      </c>
+      <c r="AK102">
         <v>1.78</v>
-      </c>
-      <c r="O102">
-        <v>3.5</v>
-      </c>
-      <c r="P102">
-        <v>4.3</v>
-      </c>
-      <c r="Q102">
-        <v>0</v>
-      </c>
-      <c r="R102">
-        <v>0</v>
-      </c>
-      <c r="S102">
-        <v>0</v>
-      </c>
-      <c r="T102">
-        <v>0</v>
-      </c>
-      <c r="U102">
-        <v>0</v>
-      </c>
-      <c r="V102">
-        <v>0</v>
-      </c>
-      <c r="W102">
-        <v>0</v>
-      </c>
-      <c r="X102">
-        <v>0</v>
-      </c>
-      <c r="Y102">
-        <v>0</v>
-      </c>
-      <c r="Z102">
-        <v>0</v>
-      </c>
-      <c r="AA102">
-        <v>0</v>
-      </c>
-      <c r="AB102">
-        <v>0</v>
-      </c>
-      <c r="AC102">
-        <v>0</v>
-      </c>
-      <c r="AD102">
-        <v>0</v>
-      </c>
-      <c r="AE102">
-        <v>0</v>
-      </c>
-      <c r="AF102">
-        <v>0</v>
-      </c>
-      <c r="AG102">
-        <v>0</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>0</v>
-      </c>
-      <c r="AK102">
-        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,16 +17098,16 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O103">
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q103">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R103">
         <v>2.73</v>
@@ -17140,13 +17140,13 @@
         <v>1.49</v>
       </c>
       <c r="AB103">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="AC103">
         <v>2.38</v>
       </c>
       <c r="AD103">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE103">
         <v>1.23</v>
@@ -17155,7 +17155,7 @@
         <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>2.39</v>
       </c>
       <c r="O104">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P104">
         <v>2.7</v>
@@ -17273,7 +17273,7 @@
         <v>3</v>
       </c>
       <c r="R104">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S104">
         <v>1.39</v>
@@ -17300,10 +17300,10 @@
         <v>3.28</v>
       </c>
       <c r="AA104">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC104">
         <v>3.25</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O105">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P105">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="Q105">
         <v>3</v>
@@ -17478,7 +17478,7 @@
         <v>1.15</v>
       </c>
       <c r="AF105">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG105">
         <v>2.38</v>
@@ -17623,16 +17623,16 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA106">
         <v>1.56</v>
       </c>
       <c r="AB106">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD106">
         <v>1.51</v>
@@ -17660,7 +17660,7 @@
         <v>1.06</v>
       </c>
       <c r="AK106">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17768,7 +17768,7 @@
         <v>1.36</v>
       </c>
       <c r="T107">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="U107">
         <v>2.75</v>
@@ -17792,10 +17792,10 @@
         <v>1.96</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AC107">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AD107">
         <v>1.3</v>
@@ -17952,25 +17952,25 @@
         <v>6.5</v>
       </c>
       <c r="AA108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB108">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC108">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AD108">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE108">
         <v>1.29</v>
       </c>
       <c r="AF108">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O110">
         <v>3.43</v>
@@ -18248,10 +18248,10 @@
         <v>4.5</v>
       </c>
       <c r="Q110">
+        <v>2.25</v>
+      </c>
+      <c r="R110">
         <v>2.15</v>
-      </c>
-      <c r="R110">
-        <v>2.2</v>
       </c>
       <c r="S110">
         <v>1.4</v>
@@ -18260,34 +18260,34 @@
         <v>2.75</v>
       </c>
       <c r="U110">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V110">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W110">
         <v>1.07</v>
       </c>
       <c r="X110">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="AA110">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB110">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC110">
-        <v>3.71</v>
+        <v>3.99</v>
       </c>
       <c r="AD110">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
@@ -18296,7 +18296,7 @@
         <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18414,19 +18414,19 @@
         <v>1.3</v>
       </c>
       <c r="R111">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="S111">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T111">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="U111">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V111">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W111">
         <v>1.25</v>
@@ -18435,25 +18435,25 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z111">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA111">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB111">
         <v>3.1</v>
       </c>
       <c r="AC111">
+        <v>1.87</v>
+      </c>
+      <c r="AD111">
         <v>1.9</v>
       </c>
-      <c r="AD111">
-        <v>1.87</v>
-      </c>
       <c r="AE111">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF111">
         <v>3.25</v>
@@ -18475,7 +18475,7 @@
         <v>1.04</v>
       </c>
       <c r="AK111">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O112">
         <v>3.7</v>
       </c>
       <c r="P112">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q112">
         <v>2.3</v>
@@ -18604,7 +18604,7 @@
         <v>3.25</v>
       </c>
       <c r="AA112">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
         <v>1.82</v>
@@ -18728,19 +18728,19 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="O113">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="P113">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q113">
         <v>2.5</v>
       </c>
       <c r="R113">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S113">
         <v>1.3</v>
@@ -18752,7 +18752,7 @@
         <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W113">
         <v>1.1</v>
@@ -18782,10 +18782,10 @@
         <v>1.1</v>
       </c>
       <c r="AF113">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG113">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK113">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O114">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="P114">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -18930,16 +18930,16 @@
         <v>4.95</v>
       </c>
       <c r="AA114">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AB114">
         <v>2.38</v>
       </c>
       <c r="AC114">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="AD114">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE114">
         <v>1.23</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O115">
         <v>3.25</v>
@@ -19078,10 +19078,10 @@
         <v>2.8</v>
       </c>
       <c r="V115">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19099,7 +19099,7 @@
         <v>1.7</v>
       </c>
       <c r="AC115">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="AD115">
         <v>1.25</v>
@@ -19223,7 +19223,7 @@
         <v>3.8</v>
       </c>
       <c r="P116">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -19259,7 +19259,7 @@
         <v>1.5</v>
       </c>
       <c r="AB116">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AC116">
         <v>2.13</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O118">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P118">
-        <v>3.3</v>
+        <v>2.73</v>
       </c>
       <c r="Q118">
         <v>2.7</v>
@@ -19561,7 +19561,7 @@
         <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U118">
         <v>2.8</v>
@@ -19576,22 +19576,22 @@
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z118">
-        <v>3.19</v>
+        <v>3.3</v>
       </c>
       <c r="AA118">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AB118">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AC118">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="AD118">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE118">
         <v>1.11</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
         <v>4.5</v>
       </c>
       <c r="P13">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Q13">
-        <v>4.05</v>
+        <v>4.44</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
         <v>3.6</v>
@@ -2467,16 +2467,16 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AC13">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AD13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE13">
         <v>1.2</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.26</v>
       </c>
       <c r="Q20">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD20">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG20">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK20">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>2.8</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R21">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T21">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="U21">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="V21">
+        <v>1.34</v>
+      </c>
+      <c r="W21">
+        <v>1.05</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
         <v>1.3</v>
       </c>
-      <c r="W21">
-        <v>1.03</v>
-      </c>
-      <c r="X21">
-        <v>1.04</v>
-      </c>
-      <c r="Y21">
-        <v>1.36</v>
-      </c>
       <c r="Z21">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="AA21">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB21">
         <v>1.61</v>
       </c>
       <c r="AC21">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD21">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF21">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG21">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
         <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G24">
@@ -4224,61 +4224,61 @@
         <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q24">
-        <v>2.23</v>
+        <v>2.42</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T24">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="V24">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.4</v>
+      </c>
+      <c r="Z24">
+        <v>2.65</v>
+      </c>
+      <c r="AA24">
+        <v>2.26</v>
+      </c>
+      <c r="AB24">
+        <v>1.59</v>
+      </c>
+      <c r="AC24">
+        <v>4.14</v>
+      </c>
+      <c r="AD24">
+        <v>1.17</v>
+      </c>
+      <c r="AE24">
         <v>1.02</v>
       </c>
-      <c r="Y24">
-        <v>1.19</v>
-      </c>
-      <c r="Z24">
-        <v>3.74</v>
-      </c>
-      <c r="AA24">
-        <v>1.83</v>
-      </c>
-      <c r="AB24">
-        <v>1.97</v>
-      </c>
-      <c r="AC24">
-        <v>2.79</v>
-      </c>
-      <c r="AD24">
-        <v>1.38</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>1.69</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK24">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G25">
@@ -4387,61 +4387,61 @@
         <v>1.95</v>
       </c>
       <c r="O25">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q25">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="R25">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="T25">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="V25">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>2.65</v>
+        <v>3.74</v>
       </c>
       <c r="AA25">
-        <v>2.26</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>1.59</v>
+        <v>1.97</v>
       </c>
       <c r="AC25">
-        <v>4.14</v>
+        <v>2.79</v>
       </c>
       <c r="AD25">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
         <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="Q27">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="R27">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4743,31 +4743,31 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB27">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AD27">
         <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF27">
         <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
         <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="U28">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O31">
         <v>3.6</v>
       </c>
       <c r="P31">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -5380,7 +5380,7 @@
         <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U31">
         <v>2.04</v>
@@ -5398,7 +5398,7 @@
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>6.01</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5413,7 +5413,7 @@
         <v>1.64</v>
       </c>
       <c r="AE31">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF31">
         <v>1.44</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
+        <v>3.25</v>
+      </c>
+      <c r="O32">
         <v>3.2</v>
       </c>
-      <c r="O32">
-        <v>3.1</v>
-      </c>
       <c r="P32">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>2.38</v>
       </c>
       <c r="AA35">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AB35">
         <v>1.37</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="O36">
         <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="Q36">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R36">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S36">
         <v>1.39</v>
       </c>
       <c r="T36">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="U36">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V36">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6213,16 +6213,16 @@
         <v>1.31</v>
       </c>
       <c r="Z36">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AA36">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB36">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC36">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="AD36">
         <v>1.26</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="O37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="Q37">
         <v>1.9</v>
@@ -6705,10 +6705,10 @@
         <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC39">
         <v>3.8</v>
@@ -6856,7 +6856,7 @@
         <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X40">
         <v>1.01</v>
@@ -6995,7 +6995,7 @@
         <v>1.34</v>
       </c>
       <c r="O41">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="P41">
         <v>7.5</v>
@@ -7164,25 +7164,25 @@
         <v>3.1</v>
       </c>
       <c r="Q42">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S42">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T42">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U42">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V42">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X42">
         <v>1.01</v>
@@ -7191,22 +7191,22 @@
         <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>5.95</v>
+        <v>6.05</v>
       </c>
       <c r="AA42">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB42">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC42">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AD42">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF42">
         <v>1.32</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,7 +7321,7 @@
         <v>1.47</v>
       </c>
       <c r="O43">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
         <v>4.8</v>
@@ -7816,10 +7816,10 @@
         <v>1.48</v>
       </c>
       <c r="Q46">
-        <v>5.38</v>
+        <v>4.21</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7846,16 +7846,16 @@
         <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AD46">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE46">
         <v>1.15</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AK46">
         <v>1.18</v>
@@ -8000,7 +8000,7 @@
         <v>1.12</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.2</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8178,7 +8178,7 @@
         <v>2.38</v>
       </c>
       <c r="AC48">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
         <v>1.52</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O49">
         <v>3.31</v>
       </c>
       <c r="P49">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q49">
         <v>2.4</v>
@@ -8350,7 +8350,7 @@
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG49">
         <v>2.12</v>
@@ -8637,7 +8637,7 @@
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
         <v>3.02</v>
@@ -8652,31 +8652,31 @@
         <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB51">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE51">
         <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
         <v>2.1</v>
@@ -9117,7 +9117,7 @@
         <v>3.31</v>
       </c>
       <c r="P54">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>3.35</v>
+        <v>2.29</v>
       </c>
       <c r="Q56">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R56">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="S56">
+        <v>1.22</v>
+      </c>
+      <c r="T56">
+        <v>4</v>
+      </c>
+      <c r="U56">
+        <v>2.1</v>
+      </c>
+      <c r="V56">
+        <v>1.67</v>
+      </c>
+      <c r="W56">
+        <v>1.18</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
+        <v>1.11</v>
+      </c>
+      <c r="Z56">
+        <v>5.5</v>
+      </c>
+      <c r="AA56">
+        <v>1.48</v>
+      </c>
+      <c r="AB56">
+        <v>2.49</v>
+      </c>
+      <c r="AC56">
+        <v>2.08</v>
+      </c>
+      <c r="AD56">
+        <v>1.64</v>
+      </c>
+      <c r="AE56">
         <v>1.25</v>
       </c>
-      <c r="T56">
-        <v>3.5</v>
-      </c>
-      <c r="U56">
-        <v>2.25</v>
-      </c>
-      <c r="V56">
-        <v>1.56</v>
-      </c>
-      <c r="W56">
-        <v>1.12</v>
-      </c>
-      <c r="X56">
-        <v>1.03</v>
-      </c>
-      <c r="Y56">
-        <v>1.17</v>
-      </c>
-      <c r="Z56">
-        <v>5</v>
-      </c>
-      <c r="AA56">
-        <v>1.6</v>
-      </c>
-      <c r="AB56">
-        <v>2.25</v>
-      </c>
-      <c r="AC56">
-        <v>2.45</v>
-      </c>
-      <c r="AD56">
-        <v>1.51</v>
-      </c>
-      <c r="AE56">
-        <v>1.16</v>
-      </c>
       <c r="AF56">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.19</v>
       </c>
       <c r="AK56">
-        <v>1.97</v>
+        <v>1.37</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O57">
+        <v>3.68</v>
+      </c>
+      <c r="P57">
         <v>3.75</v>
       </c>
-      <c r="P57">
-        <v>2.29</v>
-      </c>
       <c r="Q57">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S57">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W57">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z57">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="AD57">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF57">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG57">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.37</v>
+        <v>1.97</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="O58">
         <v>3.4</v>
@@ -9929,13 +9929,13 @@
         <v>3.7</v>
       </c>
       <c r="O59">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P59">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q59">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="R59">
         <v>2.4</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AK59">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,13 +10095,13 @@
         <v>7</v>
       </c>
       <c r="P60">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Q60">
         <v>6.57</v>
       </c>
       <c r="R60">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="S60">
         <v>1.17</v>
@@ -10131,7 +10131,7 @@
         <v>1.33</v>
       </c>
       <c r="AB60">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AC60">
         <v>1.87</v>
@@ -10255,7 +10255,7 @@
         <v>2.56</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
         <v>2.27</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O62">
         <v>2.8</v>
@@ -10750,7 +10750,7 @@
         <v>3.9</v>
       </c>
       <c r="Q64">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R64">
         <v>2.4</v>
@@ -10814,7 +10814,7 @@
         <v>1.22</v>
       </c>
       <c r="AK64">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
         <v>3.5</v>
@@ -10958,7 +10958,7 @@
         <v>1.18</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
         <v>2.4</v>
@@ -10977,7 +10977,7 @@
         <v>1.17</v>
       </c>
       <c r="AK65">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="O66">
         <v>4</v>
@@ -11076,10 +11076,10 @@
         <v>4</v>
       </c>
       <c r="Q66">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R66">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S66">
         <v>1.13</v>
@@ -11103,7 +11103,7 @@
         <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>7.28</v>
+        <v>7.38</v>
       </c>
       <c r="AA66">
         <v>1.3</v>
@@ -11112,10 +11112,10 @@
         <v>3.2</v>
       </c>
       <c r="AC66">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD66">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AE66">
         <v>1.41</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="O68">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="P68">
-        <v>3.32</v>
+        <v>2.95</v>
       </c>
       <c r="Q68">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="R68">
         <v>2.08</v>
@@ -11420,7 +11420,7 @@
         <v>1.41</v>
       </c>
       <c r="W68">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11429,16 +11429,16 @@
         <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="AA68">
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC68">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -11466,7 +11466,7 @@
         <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O71">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P71">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11924,7 +11924,7 @@
         <v>1.55</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC71">
         <v>2.45</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.19</v>
+        <v>2.37</v>
       </c>
       <c r="O73">
         <v>3.3</v>
@@ -12265,7 +12265,7 @@
         <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="O74">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>6.17</v>
+        <v>3.32</v>
       </c>
       <c r="Q74">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="R74">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="U74">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="V74">
+        <v>1.59</v>
+      </c>
+      <c r="W74">
+        <v>1.15</v>
+      </c>
+      <c r="X74">
+        <v>1.01</v>
+      </c>
+      <c r="Y74">
+        <v>1.11</v>
+      </c>
+      <c r="Z74">
+        <v>4.95</v>
+      </c>
+      <c r="AA74">
+        <v>1.53</v>
+      </c>
+      <c r="AB74">
+        <v>2.45</v>
+      </c>
+      <c r="AC74">
+        <v>2.35</v>
+      </c>
+      <c r="AD74">
+        <v>1.56</v>
+      </c>
+      <c r="AE74">
+        <v>1.22</v>
+      </c>
+      <c r="AF74">
         <v>1.44</v>
       </c>
-      <c r="W74">
-        <v>1.1</v>
-      </c>
-      <c r="X74">
-        <v>1.02</v>
-      </c>
-      <c r="Y74">
-        <v>1.23</v>
-      </c>
-      <c r="Z74">
-        <v>3.42</v>
-      </c>
-      <c r="AA74">
-        <v>1.87</v>
-      </c>
-      <c r="AB74">
-        <v>1.9</v>
-      </c>
-      <c r="AC74">
-        <v>3.12</v>
-      </c>
-      <c r="AD74">
-        <v>1.32</v>
-      </c>
-      <c r="AE74">
-        <v>1.13</v>
-      </c>
-      <c r="AF74">
-        <v>1.9</v>
-      </c>
       <c r="AG74">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,65 +12534,65 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.97</v>
+        <v>1.48</v>
       </c>
       <c r="O75">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="P75">
-        <v>2.2</v>
+        <v>5.7</v>
       </c>
       <c r="Q75">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="R75">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="U75">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="V75">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z75">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="AA75">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
+        <v>1.9</v>
+      </c>
+      <c r="AC75">
+        <v>3.12</v>
+      </c>
+      <c r="AD75">
+        <v>1.32</v>
+      </c>
+      <c r="AE75">
+        <v>1.13</v>
+      </c>
+      <c r="AF75">
+        <v>1.9</v>
+      </c>
+      <c r="AG75">
         <v>1.8</v>
       </c>
-      <c r="AC75">
-        <v>3.34</v>
-      </c>
-      <c r="AD75">
-        <v>1.24</v>
-      </c>
-      <c r="AE75">
-        <v>1.06</v>
-      </c>
-      <c r="AF75">
-        <v>1.76</v>
-      </c>
-      <c r="AG75">
-        <v>1.96</v>
-      </c>
       <c r="AH75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.9</v>
+        <v>2.97</v>
       </c>
       <c r="O76">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q76">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="R76">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S76">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T76">
-        <v>3.27</v>
+        <v>2.82</v>
       </c>
       <c r="U76">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="V76">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="W76">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA76">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AC76">
-        <v>2.91</v>
+        <v>3.34</v>
       </c>
       <c r="AD76">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG76">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P77">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q77">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="R77">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="S77">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="U77">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="V77">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="W77">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>4.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA77">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AB77">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC77">
-        <v>2.35</v>
+        <v>2.91</v>
       </c>
       <c r="AD77">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="AE77">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AG77">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13065,7 +13065,7 @@
         <v>2.6</v>
       </c>
       <c r="AB78">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AC78">
         <v>4.8</v>
@@ -13195,10 +13195,10 @@
         <v>2.65</v>
       </c>
       <c r="Q79">
-        <v>2.56</v>
+        <v>2.95</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S79">
         <v>1.29</v>
@@ -13222,7 +13222,7 @@
         <v>1.2</v>
       </c>
       <c r="Z79">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="AA79">
         <v>1.67</v>
@@ -13231,13 +13231,13 @@
         <v>2.15</v>
       </c>
       <c r="AC79">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AD79">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE79">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
         <v>1.55</v>
@@ -13388,10 +13388,10 @@
         <v>3.92</v>
       </c>
       <c r="AA80">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB80">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC80">
         <v>2.62</v>
@@ -14677,7 +14677,7 @@
         <v>2.31</v>
       </c>
       <c r="V88">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W88">
         <v>1.14</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
         <v>1.75</v>
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="O92">
         <v>3.8</v>
@@ -15344,7 +15344,7 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
         <v>2.66</v>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK92">
         <v>1.36</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="O93">
         <v>3.8</v>
@@ -15510,7 +15510,7 @@
         <v>1.7</v>
       </c>
       <c r="AB93">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC93">
         <v>2.25</v>
@@ -15634,7 +15634,7 @@
         <v>1.25</v>
       </c>
       <c r="O94">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="P94">
         <v>9.25</v>
@@ -15670,7 +15670,7 @@
         <v>3.4</v>
       </c>
       <c r="AA94">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB94">
         <v>2.02</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="O95">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P95">
-        <v>2.03</v>
+        <v>1.54</v>
       </c>
       <c r="Q95">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="R95">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
+        <v>1.18</v>
+      </c>
+      <c r="Z95">
+        <v>4.33</v>
+      </c>
+      <c r="AA95">
+        <v>1.64</v>
+      </c>
+      <c r="AB95">
+        <v>2.17</v>
+      </c>
+      <c r="AC95">
+        <v>2.63</v>
+      </c>
+      <c r="AD95">
+        <v>1.42</v>
+      </c>
+      <c r="AE95">
+        <v>1.14</v>
+      </c>
+      <c r="AF95">
+        <v>1.7</v>
+      </c>
+      <c r="AG95">
+        <v>2.04</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.22</v>
+      </c>
+      <c r="AK95">
         <v>1.15</v>
-      </c>
-      <c r="Z95">
-        <v>4.25</v>
-      </c>
-      <c r="AA95">
-        <v>1.61</v>
-      </c>
-      <c r="AB95">
-        <v>2.15</v>
-      </c>
-      <c r="AC95">
-        <v>2.55</v>
-      </c>
-      <c r="AD95">
-        <v>1.45</v>
-      </c>
-      <c r="AE95">
-        <v>1.15</v>
-      </c>
-      <c r="AF95">
-        <v>1.5</v>
-      </c>
-      <c r="AG95">
-        <v>2.38</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.29</v>
-      </c>
-      <c r="AK95">
-        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="O96">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P96">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q96">
-        <v>5.75</v>
+        <v>3.84</v>
       </c>
       <c r="R96">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U96">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="V96">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W96">
         <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB96">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC96">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD96">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF96">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG96">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16123,10 +16123,10 @@
         <v>1.93</v>
       </c>
       <c r="O97">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P97">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q97">
         <v>2.25</v>
@@ -16141,10 +16141,10 @@
         <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V97">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W97">
         <v>1.17</v>
@@ -16162,7 +16162,7 @@
         <v>1.46</v>
       </c>
       <c r="AB97">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC97">
         <v>2.19</v>
@@ -16286,7 +16286,7 @@
         <v>2.1</v>
       </c>
       <c r="O98">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
         <v>2.87</v>
@@ -16301,13 +16301,13 @@
         <v>1.34</v>
       </c>
       <c r="T98">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="U98">
         <v>2.41</v>
       </c>
       <c r="V98">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W98">
         <v>1.11</v>
@@ -16316,16 +16316,16 @@
         <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z98">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="AA98">
         <v>1.72</v>
       </c>
       <c r="AB98">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC98">
         <v>2.83</v>
@@ -16334,7 +16334,7 @@
         <v>1.33</v>
       </c>
       <c r="AE98">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF98">
         <v>1.61</v>
@@ -16452,7 +16452,7 @@
         <v>3.4</v>
       </c>
       <c r="P99">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q99">
         <v>2.57</v>
@@ -16461,16 +16461,16 @@
         <v>2.18</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T99">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="U99">
         <v>2.5</v>
       </c>
       <c r="V99">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W99">
         <v>1.11</v>
@@ -16651,7 +16651,7 @@
         <v>1.85</v>
       </c>
       <c r="AB100">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC100">
         <v>3</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
         <v>1.2</v>
@@ -16811,10 +16811,10 @@
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB101">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
         <v>2.1</v>
@@ -16829,7 +16829,7 @@
         <v>1.5</v>
       </c>
       <c r="AG101">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16944,22 +16944,22 @@
         <v>3.84</v>
       </c>
       <c r="Q102">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S102">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T102">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U102">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="V102">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W102">
         <v>1.07</v>
@@ -16974,10 +16974,10 @@
         <v>3.04</v>
       </c>
       <c r="AA102">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AB102">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC102">
         <v>3.58</v>
@@ -16986,13 +16986,13 @@
         <v>1.21</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG102">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O103">
         <v>4.8</v>
@@ -17107,7 +17107,7 @@
         <v>6.5</v>
       </c>
       <c r="Q103">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R103">
         <v>2.73</v>
@@ -17119,13 +17119,13 @@
         <v>4</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W103">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -17137,10 +17137,10 @@
         <v>6</v>
       </c>
       <c r="AA103">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="AC103">
         <v>2.38</v>
@@ -17303,7 +17303,7 @@
         <v>1.9</v>
       </c>
       <c r="AB104">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC104">
         <v>3.25</v>
@@ -17442,7 +17442,7 @@
         <v>1.29</v>
       </c>
       <c r="T105">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U105">
         <v>2.55</v>
@@ -17596,7 +17596,7 @@
         <v>1.28</v>
       </c>
       <c r="Q106">
-        <v>6.18</v>
+        <v>6.09</v>
       </c>
       <c r="R106">
         <v>2.6</v>
@@ -17623,7 +17623,7 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA106">
         <v>1.56</v>
@@ -17632,7 +17632,7 @@
         <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD106">
         <v>1.51</v>
@@ -17641,7 +17641,7 @@
         <v>1.19</v>
       </c>
       <c r="AF106">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG106">
         <v>1.75</v>
@@ -17756,7 +17756,7 @@
         <v>3.8</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -17792,7 +17792,7 @@
         <v>1.96</v>
       </c>
       <c r="AB107">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC107">
         <v>3.28</v>
@@ -17823,7 +17823,7 @@
         <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17931,10 +17931,10 @@
         <v>1.2</v>
       </c>
       <c r="T108">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U108">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V108">
         <v>1.75</v>
@@ -17970,7 +17970,7 @@
         <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18091,10 +18091,10 @@
         <v>2.62</v>
       </c>
       <c r="S109">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T109">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U109">
         <v>2.05</v>
@@ -18278,7 +18278,7 @@
         <v>2.91</v>
       </c>
       <c r="AA110">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AB110">
         <v>1.66</v>
@@ -18601,10 +18601,10 @@
         <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA112">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB112">
         <v>1.82</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="O114">
         <v>4.6</v>
       </c>
       <c r="P114">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -19223,7 +19223,7 @@
         <v>3.8</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK116">
         <v>2</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
+        <v>2.5</v>
+      </c>
+      <c r="O117">
+        <v>3.25</v>
+      </c>
+      <c r="P117">
         <v>2.45</v>
-      </c>
-      <c r="O117">
-        <v>3.4</v>
-      </c>
-      <c r="P117">
-        <v>2.6</v>
       </c>
       <c r="Q117">
         <v>3.13</v>
@@ -19410,7 +19410,7 @@
         <v>1.12</v>
       </c>
       <c r="X117">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
         <v>1.2</v>
@@ -19419,10 +19419,10 @@
         <v>4.1</v>
       </c>
       <c r="AA117">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AB117">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AC117">
         <v>2.73</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O118">
         <v>3.15</v>
       </c>
       <c r="P118">
-        <v>2.73</v>
+        <v>3.2</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
         <v>2.1</v>
@@ -19561,40 +19561,40 @@
         <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="U118">
         <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W118">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X118">
         <v>1.02</v>
       </c>
       <c r="Y118">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z118">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA118">
         <v>1.92</v>
       </c>
       <c r="AB118">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC118">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD118">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE118">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF118">
         <v>1.75</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="O13">
         <v>4.5</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK13">
         <v>1.08</v>
@@ -3614,19 +3614,19 @@
         <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD20">
         <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK20">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>1.98</v>
       </c>
       <c r="AB21">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC21">
         <v>3.8</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.61</v>
+        <v>4.4</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q29">
-        <v>5.66</v>
+        <v>5.6</v>
       </c>
       <c r="R29">
         <v>1.86</v>
@@ -5054,7 +5054,7 @@
         <v>1.5</v>
       </c>
       <c r="T29">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="U29">
         <v>3.86</v>
@@ -5066,13 +5066,13 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z29">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AA29">
         <v>2.76</v>
@@ -5081,19 +5081,19 @@
         <v>1.37</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE29">
         <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AG29">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK29">
         <v>1.11</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P33">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="Q33">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="R33">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="S33">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="T33">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W33">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y33">
         <v>1.67</v>
       </c>
       <c r="Z33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AA33">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="AB33">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AG33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
         <v>1.63</v>
@@ -5854,7 +5854,7 @@
         <v>2.59</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>2.55</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="O37">
         <v>4.4</v>
       </c>
       <c r="P37">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q37">
         <v>1.9</v>
@@ -6358,13 +6358,13 @@
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
         <v>1.11</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK37">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>4.2</v>
       </c>
       <c r="Q39">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R39">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="S39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U39">
-        <v>2.77</v>
+        <v>2.59</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.25</v>
+      </c>
+      <c r="Z39">
+        <v>3.6</v>
+      </c>
+      <c r="AA39">
+        <v>1.83</v>
+      </c>
+      <c r="AB39">
+        <v>1.84</v>
+      </c>
+      <c r="AC39">
+        <v>3.2</v>
+      </c>
+      <c r="AD39">
         <v>1.3</v>
       </c>
-      <c r="Z39">
-        <v>3.2</v>
-      </c>
-      <c r="AA39">
-        <v>2</v>
-      </c>
-      <c r="AB39">
-        <v>1.73</v>
-      </c>
-      <c r="AC39">
-        <v>3.8</v>
-      </c>
-      <c r="AD39">
-        <v>1.22</v>
-      </c>
       <c r="AE39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6877,16 +6877,16 @@
         <v>2.45</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG40">
-        <v>2.39</v>
+        <v>2.63</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
         <v>2.55</v>
@@ -7191,13 +7191,13 @@
         <v>1.11</v>
       </c>
       <c r="Z42">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="AA42">
         <v>1.38</v>
       </c>
       <c r="AB42">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC42">
         <v>1.81</v>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,13 +7321,13 @@
         <v>1.47</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P43">
         <v>4.8</v>
       </c>
       <c r="Q43">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R43">
         <v>2.72</v>
@@ -7360,7 +7360,7 @@
         <v>1.29</v>
       </c>
       <c r="AB43">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC43">
         <v>1.75</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P44">
         <v>6</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O45">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P45">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q45">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="R45">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S45">
         <v>1.53</v>
@@ -7674,19 +7674,19 @@
         <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y45">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="Z45">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AA45">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC45">
         <v>6</v>
@@ -7698,10 +7698,10 @@
         <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7810,10 +7810,10 @@
         <v>5</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q46">
         <v>4.21</v>
@@ -7825,7 +7825,7 @@
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
         <v>2.3</v>
@@ -7843,22 +7843,22 @@
         <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AD46">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE46">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
         <v>1.62</v>
@@ -8136,7 +8136,7 @@
         <v>2.15</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
         <v>2.87</v>
@@ -8151,7 +8151,7 @@
         <v>1.19</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U48">
         <v>2.3</v>
@@ -8175,7 +8175,7 @@
         <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
         <v>2.31</v>
@@ -8350,7 +8350,7 @@
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
         <v>2.12</v>
@@ -8462,10 +8462,10 @@
         <v>1.43</v>
       </c>
       <c r="O50">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="Q50">
         <v>1.92</v>
@@ -8498,7 +8498,7 @@
         <v>6</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
         <v>2.75</v>
@@ -8637,10 +8637,10 @@
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U51">
         <v>2.63</v>
@@ -9117,7 +9117,7 @@
         <v>3.31</v>
       </c>
       <c r="P54">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>1.7</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P55">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q55">
         <v>2.17</v>
@@ -9310,13 +9310,13 @@
         <v>1.15</v>
       </c>
       <c r="Z55">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="AA55">
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC55">
         <v>2.3</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P56">
         <v>2.29</v>
@@ -9455,7 +9455,7 @@
         <v>1.22</v>
       </c>
       <c r="T56">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U56">
         <v>2.1</v>
@@ -9476,7 +9476,7 @@
         <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB56">
         <v>2.49</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="O57">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="P57">
-        <v>3.75</v>
+        <v>4.35</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9624,7 +9624,7 @@
         <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W57">
         <v>1.12</v>
@@ -9642,7 +9642,7 @@
         <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -9775,16 +9775,16 @@
         <v>3.4</v>
       </c>
       <c r="R58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S58">
         <v>1.3</v>
       </c>
       <c r="T58">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U58">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V58">
         <v>1.44</v>
@@ -9796,25 +9796,25 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA58">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AB58">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC58">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE58">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
         <v>1.57</v>
@@ -9929,13 +9929,13 @@
         <v>3.7</v>
       </c>
       <c r="O59">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="P59">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q59">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R59">
         <v>2.4</v>
@@ -9950,7 +9950,7 @@
         <v>2.15</v>
       </c>
       <c r="V59">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W59">
         <v>1.12</v>
@@ -9968,7 +9968,7 @@
         <v>1.48</v>
       </c>
       <c r="AB59">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AC59">
         <v>2.17</v>
@@ -9980,7 +9980,7 @@
         <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG59">
         <v>2.55</v>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AK59">
         <v>1.25</v>
@@ -11067,25 +11067,25 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P66">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R66">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="S66">
         <v>1.13</v>
       </c>
       <c r="T66">
-        <v>4.55</v>
+        <v>4.65</v>
       </c>
       <c r="U66">
         <v>1.91</v>
@@ -11106,19 +11106,19 @@
         <v>7.38</v>
       </c>
       <c r="AA66">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC66">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AD66">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AE66">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF66">
         <v>1.33</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="O69">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>1.9</v>
+        <v>2.53</v>
       </c>
       <c r="R69">
-        <v>2.61</v>
+        <v>2.22</v>
       </c>
       <c r="S69">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="T69">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="U69">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V69">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="W69">
+        <v>1.12</v>
+      </c>
+      <c r="X69">
+        <v>1.03</v>
+      </c>
+      <c r="Y69">
+        <v>1.22</v>
+      </c>
+      <c r="Z69">
+        <v>4.15</v>
+      </c>
+      <c r="AA69">
+        <v>1.66</v>
+      </c>
+      <c r="AB69">
+        <v>2.05</v>
+      </c>
+      <c r="AC69">
+        <v>2.56</v>
+      </c>
+      <c r="AD69">
+        <v>1.4</v>
+      </c>
+      <c r="AE69">
         <v>1.18</v>
       </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.08</v>
-      </c>
-      <c r="Z69">
-        <v>6.15</v>
-      </c>
-      <c r="AA69">
-        <v>1.36</v>
-      </c>
-      <c r="AB69">
-        <v>2.88</v>
-      </c>
-      <c r="AC69">
-        <v>1.95</v>
-      </c>
-      <c r="AD69">
-        <v>1.74</v>
-      </c>
-      <c r="AE69">
-        <v>1.29</v>
-      </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG69">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,80 +11719,80 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="P70">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="Q70">
-        <v>2.53</v>
+        <v>1.9</v>
       </c>
       <c r="R70">
-        <v>2.22</v>
+        <v>2.61</v>
       </c>
       <c r="S70">
+        <v>1.17</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70">
+        <v>2</v>
+      </c>
+      <c r="V70">
+        <v>1.7</v>
+      </c>
+      <c r="W70">
+        <v>1.18</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
+        <v>1.08</v>
+      </c>
+      <c r="Z70">
+        <v>6.15</v>
+      </c>
+      <c r="AA70">
+        <v>1.36</v>
+      </c>
+      <c r="AB70">
+        <v>2.88</v>
+      </c>
+      <c r="AC70">
+        <v>1.95</v>
+      </c>
+      <c r="AD70">
+        <v>1.74</v>
+      </c>
+      <c r="AE70">
         <v>1.29</v>
       </c>
-      <c r="T70">
-        <v>3.4</v>
-      </c>
-      <c r="U70">
-        <v>2.4</v>
-      </c>
-      <c r="V70">
-        <v>1.51</v>
-      </c>
-      <c r="W70">
+      <c r="AF70">
+        <v>1.5</v>
+      </c>
+      <c r="AG70">
+        <v>2.34</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
         <v>1.12</v>
       </c>
-      <c r="X70">
-        <v>1.03</v>
-      </c>
-      <c r="Y70">
-        <v>1.22</v>
-      </c>
-      <c r="Z70">
-        <v>4.15</v>
-      </c>
-      <c r="AA70">
-        <v>1.66</v>
-      </c>
-      <c r="AB70">
-        <v>2.05</v>
-      </c>
-      <c r="AC70">
-        <v>2.56</v>
-      </c>
-      <c r="AD70">
-        <v>1.4</v>
-      </c>
-      <c r="AE70">
-        <v>1.18</v>
-      </c>
-      <c r="AF70">
-        <v>1.55</v>
-      </c>
-      <c r="AG70">
-        <v>2.3</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>1.21</v>
-      </c>
       <c r="AK70">
-        <v>1.49</v>
+        <v>2.45</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O71">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P71">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11915,16 +11915,16 @@
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z71">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA71">
         <v>1.55</v>
       </c>
       <c r="AB71">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC71">
         <v>2.45</v>
@@ -12045,58 +12045,58 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="O72">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q72">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R72">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S72">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T72">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="U72">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="V72">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X72">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y72">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z72">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AA72">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="AB72">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AC72">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD72">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AE72">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF72">
         <v>2.2</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="P73">
-        <v>2.87</v>
+        <v>5.7</v>
       </c>
       <c r="Q73">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="R73">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="U73">
-        <v>3.01</v>
+        <v>2.6</v>
       </c>
       <c r="V73">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
+        <v>1.23</v>
+      </c>
+      <c r="Z73">
+        <v>3.42</v>
+      </c>
+      <c r="AA73">
+        <v>1.87</v>
+      </c>
+      <c r="AB73">
+        <v>1.9</v>
+      </c>
+      <c r="AC73">
+        <v>3.12</v>
+      </c>
+      <c r="AD73">
         <v>1.32</v>
       </c>
-      <c r="Z73">
-        <v>3.34</v>
-      </c>
-      <c r="AA73">
-        <v>2.05</v>
-      </c>
-      <c r="AB73">
-        <v>1.75</v>
-      </c>
-      <c r="AC73">
-        <v>3.6</v>
-      </c>
-      <c r="AD73">
-        <v>1.29</v>
-      </c>
       <c r="AE73">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.48</v>
+        <v>2.37</v>
       </c>
       <c r="O75">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>5.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q75">
-        <v>1.95</v>
+        <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>3.13</v>
+        <v>2.88</v>
       </c>
       <c r="U75">
-        <v>2.6</v>
+        <v>3.01</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z75">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA75">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB75">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC75">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AD75">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG75">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK75">
-        <v>2.45</v>
+        <v>1.51</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13029,7 +13029,7 @@
         <v>2.8</v>
       </c>
       <c r="P78">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
         <v>3.2</v>
@@ -14656,7 +14656,7 @@
         <v>2.1</v>
       </c>
       <c r="O88">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
         <v>2.95</v>
@@ -14674,7 +14674,7 @@
         <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V88">
         <v>1.57</v>
@@ -14686,31 +14686,31 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB88">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC88">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD88">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE88">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF88">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG88">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -15142,10 +15142,10 @@
         </is>
       </c>
       <c r="N91">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O91">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P91">
         <v>3.4</v>
@@ -15181,10 +15181,10 @@
         <v>2.83</v>
       </c>
       <c r="AA91">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB91">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC91">
         <v>4.1</v>
@@ -15308,13 +15308,13 @@
         <v>2.72</v>
       </c>
       <c r="O92">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P92">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q92">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="R92">
         <v>2.63</v>
@@ -16775,13 +16775,13 @@
         <v>5.25</v>
       </c>
       <c r="O101">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="P101">
         <v>1.53</v>
       </c>
       <c r="Q101">
-        <v>5.6</v>
+        <v>5.78</v>
       </c>
       <c r="R101">
         <v>2.63</v>
@@ -16796,7 +16796,7 @@
         <v>2</v>
       </c>
       <c r="V101">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W101">
         <v>1.18</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB3">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="O7">
         <v>4.6</v>
@@ -1462,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="S7">
         <v>1.16</v>
@@ -1471,34 +1471,34 @@
         <v>4.1</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V7">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA7">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB7">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC7">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD7">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE7">
         <v>1.29</v>
@@ -1523,7 +1523,7 @@
         <v>2.62</v>
       </c>
       <c r="AK7">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>2.45</v>
       </c>
       <c r="O9">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P9">
         <v>2.75</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="O10">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="P10">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q10">
         <v>4.1</v>
@@ -1957,7 +1957,7 @@
         <v>1.6</v>
       </c>
       <c r="T10">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
         <v>4.4</v>
@@ -1978,7 +1978,7 @@
         <v>2.02</v>
       </c>
       <c r="AA10">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="AB10">
         <v>1.3</v>
@@ -1990,7 +1990,7 @@
         <v>1.06</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
         <v>2.4</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="O11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="P11">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Q11">
         <v>1.67</v>
@@ -2138,19 +2138,19 @@
         <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.63</v>
+        <v>4.45</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC11">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD11">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE11">
         <v>1.14</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
         <v>2.7</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q28">
         <v>2.95</v>
@@ -4891,10 +4891,10 @@
         <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="U28">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -5051,16 +5051,16 @@
         <v>1.86</v>
       </c>
       <c r="S29">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T29">
         <v>2.29</v>
       </c>
       <c r="U29">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="V29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>2.29</v>
       </c>
       <c r="AA29">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AB29">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AC29">
         <v>5.3</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="O41">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
+        <v>2.45</v>
+      </c>
+      <c r="O45">
         <v>2.7</v>
       </c>
-      <c r="O45">
-        <v>2.75</v>
-      </c>
       <c r="P45">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="Q45">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R45">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="S45">
         <v>1.53</v>
@@ -7671,7 +7671,7 @@
         <v>1.25</v>
       </c>
       <c r="W45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
         <v>1.07</v>
@@ -7680,13 +7680,13 @@
         <v>1.48</v>
       </c>
       <c r="Z45">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AA45">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC45">
         <v>6</v>
@@ -7701,7 +7701,7 @@
         <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.44</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q47">
         <v>2.5</v>
@@ -8015,16 +8015,16 @@
         <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD47">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE47">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
         <v>2.25</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8637,10 +8637,10 @@
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U51">
         <v>2.63</v>
@@ -8788,10 +8788,10 @@
         <v>1.42</v>
       </c>
       <c r="O52">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P52">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -8818,10 +8818,10 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z52">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
+        <v>2.65</v>
+      </c>
+      <c r="O53">
         <v>2.8</v>
       </c>
-      <c r="O53">
-        <v>3</v>
-      </c>
       <c r="P53">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q53">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="R53">
         <v>1.95</v>
       </c>
       <c r="S53">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T53">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U53">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="V53">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W53">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X53">
         <v>1.07</v>
       </c>
       <c r="Y53">
+        <v>1.54</v>
+      </c>
+      <c r="Z53">
+        <v>2.28</v>
+      </c>
+      <c r="AA53">
+        <v>2.83</v>
+      </c>
+      <c r="AB53">
+        <v>1.39</v>
+      </c>
+      <c r="AC53">
+        <v>5.35</v>
+      </c>
+      <c r="AD53">
+        <v>1.11</v>
+      </c>
+      <c r="AE53">
+        <v>1.01</v>
+      </c>
+      <c r="AF53">
+        <v>2.15</v>
+      </c>
+      <c r="AG53">
+        <v>1.62</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.33</v>
+      </c>
+      <c r="AK53">
         <v>1.44</v>
-      </c>
-      <c r="Z53">
-        <v>2.38</v>
-      </c>
-      <c r="AA53">
-        <v>2.56</v>
-      </c>
-      <c r="AB53">
-        <v>1.47</v>
-      </c>
-      <c r="AC53">
-        <v>5</v>
-      </c>
-      <c r="AD53">
-        <v>1.13</v>
-      </c>
-      <c r="AE53">
-        <v>1.05</v>
-      </c>
-      <c r="AF53">
-        <v>2</v>
-      </c>
-      <c r="AG53">
-        <v>1.73</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>1.36</v>
-      </c>
-      <c r="AK53">
-        <v>1.4</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
         <v>2.29</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O57">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>4.35</v>
+        <v>3.35</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9624,7 +9624,7 @@
         <v>2.25</v>
       </c>
       <c r="V57">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W57">
         <v>1.12</v>
@@ -9642,7 +9642,7 @@
         <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC57">
         <v>2.45</v>
@@ -10089,19 +10089,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="O60">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P60">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Q60">
         <v>6.57</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="S60">
         <v>1.17</v>
@@ -10125,19 +10125,19 @@
         <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>7.09</v>
+        <v>6.71</v>
       </c>
       <c r="AA60">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AB60">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="AC60">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD60">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE60">
         <v>1.43</v>
@@ -10162,7 +10162,7 @@
         <v>1.12</v>
       </c>
       <c r="AK60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10261,10 +10261,10 @@
         <v>2.27</v>
       </c>
       <c r="Q61">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R61">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10276,7 +10276,7 @@
         <v>2.15</v>
       </c>
       <c r="V61">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W61">
         <v>1.16</v>
@@ -10285,10 +10285,10 @@
         <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA61">
         <v>1.57</v>
@@ -10303,13 +10303,13 @@
         <v>1.57</v>
       </c>
       <c r="AE61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF61">
         <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10741,10 +10741,10 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O64">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="P64">
         <v>3.9</v>
@@ -10759,13 +10759,13 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U64">
         <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10774,25 +10774,25 @@
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA64">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB64">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC64">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AD64">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AE64">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF64">
         <v>1.57</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10916,7 +10916,7 @@
         <v>2.15</v>
       </c>
       <c r="R65">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10925,7 +10925,7 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="V65">
         <v>1.56</v>
@@ -10943,10 +10943,10 @@
         <v>4.55</v>
       </c>
       <c r="AA65">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC65">
         <v>2.31</v>
@@ -11399,7 +11399,7 @@
         <v>3.4</v>
       </c>
       <c r="P68">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q68">
         <v>2.59</v>
@@ -11408,7 +11408,7 @@
         <v>2.08</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T68">
         <v>3</v>
@@ -11429,16 +11429,16 @@
         <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="AA68">
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC68">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O72">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P72">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R72">
         <v>1.91</v>
@@ -12078,10 +12078,10 @@
         <v>1.07</v>
       </c>
       <c r="Y72">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Z72">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA72">
         <v>2.38</v>
@@ -12118,7 +12118,7 @@
         <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="O73">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="Q73">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.13</v>
+        <v>3.7</v>
       </c>
       <c r="U73">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="V73">
+        <v>1.59</v>
+      </c>
+      <c r="W73">
+        <v>1.15</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>1.11</v>
+      </c>
+      <c r="Z73">
+        <v>4.95</v>
+      </c>
+      <c r="AA73">
+        <v>1.53</v>
+      </c>
+      <c r="AB73">
+        <v>2.45</v>
+      </c>
+      <c r="AC73">
+        <v>2.37</v>
+      </c>
+      <c r="AD73">
+        <v>1.55</v>
+      </c>
+      <c r="AE73">
+        <v>1.22</v>
+      </c>
+      <c r="AF73">
         <v>1.44</v>
       </c>
-      <c r="W73">
-        <v>1.1</v>
-      </c>
-      <c r="X73">
-        <v>1.02</v>
-      </c>
-      <c r="Y73">
-        <v>1.23</v>
-      </c>
-      <c r="Z73">
-        <v>3.42</v>
-      </c>
-      <c r="AA73">
-        <v>1.87</v>
-      </c>
-      <c r="AB73">
-        <v>1.9</v>
-      </c>
-      <c r="AC73">
-        <v>3.12</v>
-      </c>
-      <c r="AD73">
-        <v>1.32</v>
-      </c>
-      <c r="AE73">
-        <v>1.13</v>
-      </c>
-      <c r="AF73">
-        <v>1.9</v>
-      </c>
       <c r="AG73">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.97</v>
+        <v>1.47</v>
       </c>
       <c r="O74">
+        <v>4.1</v>
+      </c>
+      <c r="P74">
+        <v>6.5</v>
+      </c>
+      <c r="Q74">
+        <v>1.93</v>
+      </c>
+      <c r="R74">
+        <v>2.3</v>
+      </c>
+      <c r="S74">
+        <v>1.3</v>
+      </c>
+      <c r="T74">
+        <v>3.21</v>
+      </c>
+      <c r="U74">
+        <v>2.6</v>
+      </c>
+      <c r="V74">
+        <v>1.44</v>
+      </c>
+      <c r="W74">
+        <v>1.1</v>
+      </c>
+      <c r="X74">
+        <v>1.02</v>
+      </c>
+      <c r="Y74">
+        <v>1.22</v>
+      </c>
+      <c r="Z74">
         <v>3.5</v>
       </c>
-      <c r="P74">
-        <v>3.32</v>
-      </c>
-      <c r="Q74">
-        <v>2.41</v>
-      </c>
-      <c r="R74">
-        <v>2.28</v>
-      </c>
-      <c r="S74">
-        <v>1.25</v>
-      </c>
-      <c r="T74">
-        <v>3.7</v>
-      </c>
-      <c r="U74">
-        <v>2.17</v>
-      </c>
-      <c r="V74">
-        <v>1.59</v>
-      </c>
-      <c r="W74">
-        <v>1.15</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>1.11</v>
-      </c>
-      <c r="Z74">
-        <v>4.95</v>
-      </c>
       <c r="AA74">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB74">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC74">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AD74">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AE74">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF74">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="AG74">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>1.22</v>
       </c>
       <c r="AK74">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,55 +12534,55 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q75">
         <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
+        <v>1.4</v>
+      </c>
+      <c r="T75">
+        <v>2.78</v>
+      </c>
+      <c r="U75">
+        <v>3.17</v>
+      </c>
+      <c r="V75">
+        <v>1.34</v>
+      </c>
+      <c r="W75">
+        <v>1.07</v>
+      </c>
+      <c r="X75">
+        <v>1.06</v>
+      </c>
+      <c r="Y75">
         <v>1.36</v>
       </c>
-      <c r="T75">
-        <v>2.88</v>
-      </c>
-      <c r="U75">
-        <v>3.01</v>
-      </c>
-      <c r="V75">
-        <v>1.39</v>
-      </c>
-      <c r="W75">
-        <v>1.08</v>
-      </c>
-      <c r="X75">
-        <v>1.05</v>
-      </c>
-      <c r="Y75">
-        <v>1.32</v>
-      </c>
       <c r="Z75">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="AA75">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB75">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC75">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD75">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK75">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="O76">
         <v>3.1</v>
@@ -12709,7 +12709,7 @@
         <v>3.6</v>
       </c>
       <c r="R76">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S76">
         <v>1.41</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK76">
         <v>1.34</v>
@@ -12860,16 +12860,16 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
         <v>3.1</v>
       </c>
       <c r="Q77">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="R77">
         <v>2.21</v>
@@ -12881,7 +12881,7 @@
         <v>3.27</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V77">
         <v>1.47</v>
@@ -12905,7 +12905,7 @@
         <v>2.1</v>
       </c>
       <c r="AC77">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="AD77">
         <v>1.41</v>
@@ -13059,13 +13059,13 @@
         <v>1.48</v>
       </c>
       <c r="Z78">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AA78">
         <v>2.6</v>
       </c>
       <c r="AB78">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AC78">
         <v>4.8</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
         <v>3.4</v>
@@ -13195,10 +13195,10 @@
         <v>2.65</v>
       </c>
       <c r="Q79">
-        <v>2.95</v>
+        <v>2.56</v>
       </c>
       <c r="R79">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S79">
         <v>1.29</v>
@@ -13216,7 +13216,7 @@
         <v>1.11</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
         <v>1.2</v>
@@ -13225,16 +13225,16 @@
         <v>4.32</v>
       </c>
       <c r="AA79">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB79">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC79">
         <v>2.68</v>
       </c>
       <c r="AD79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE79">
         <v>1.14</v>
@@ -14499,13 +14499,13 @@
         <v>5.25</v>
       </c>
       <c r="Q87">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="R87">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="S87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
         <v>3</v>
@@ -14517,10 +14517,10 @@
         <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
         <v>1.23</v>
@@ -14529,10 +14529,10 @@
         <v>3.42</v>
       </c>
       <c r="AA87">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB87">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC87">
         <v>3.05</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O89">
         <v>3.5</v>
       </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
@@ -14834,7 +14834,7 @@
         <v>1.35</v>
       </c>
       <c r="T89">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U89">
         <v>2.46</v>
@@ -14852,7 +14852,7 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
@@ -14979,16 +14979,16 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="O90">
         <v>3.25</v>
       </c>
       <c r="P90">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q90">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R90">
         <v>2.05</v>
@@ -14997,10 +14997,10 @@
         <v>1.39</v>
       </c>
       <c r="T90">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U90">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="V90">
         <v>1.4</v>
@@ -15012,10 +15012,10 @@
         <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z90">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA90">
         <v>1.9</v>
@@ -15024,10 +15024,10 @@
         <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="AD90">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE90">
         <v>1.1</v>
@@ -15148,28 +15148,28 @@
         <v>3</v>
       </c>
       <c r="P91">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R91">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S91">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T91">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U91">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V91">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X91">
         <v>1.06</v>
@@ -15178,22 +15178,22 @@
         <v>1.33</v>
       </c>
       <c r="Z91">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA91">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB91">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AD91">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
         <v>1.87</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK91">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>2.15</v>
       </c>
       <c r="Q92">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="R92">
         <v>2.63</v>
@@ -15344,10 +15344,10 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB92">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AC92">
         <v>2.15</v>
@@ -15362,7 +15362,7 @@
         <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="O93">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="P93">
-        <v>4.33</v>
+        <v>9.25</v>
       </c>
       <c r="Q93">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="R93">
+        <v>2.71</v>
+      </c>
+      <c r="S93">
+        <v>1.18</v>
+      </c>
+      <c r="T93">
+        <v>2.8</v>
+      </c>
+      <c r="U93">
         <v>2.3</v>
       </c>
-      <c r="S93">
-        <v>1.3</v>
-      </c>
-      <c r="T93">
-        <v>3.25</v>
-      </c>
-      <c r="U93">
-        <v>2.34</v>
-      </c>
       <c r="V93">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W93">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y93">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z93">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AB93">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AC93">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AD93">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="AE93">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF93">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG93">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK93">
-        <v>2</v>
+        <v>3.62</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="O94">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="P94">
-        <v>9.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q94">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="R94">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="S94">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="U94">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V94">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W94">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z94">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA94">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AB94">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC94">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AD94">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AE94">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF94">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG94">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>3.62</v>
+        <v>2</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16651,7 +16651,7 @@
         <v>1.85</v>
       </c>
       <c r="AB100">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC100">
         <v>3</v>
@@ -16989,7 +16989,7 @@
         <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
         <v>1.83</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="O103">
         <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Q103">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R103">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="S103">
         <v>1.25</v>
@@ -17140,22 +17140,22 @@
         <v>1.5</v>
       </c>
       <c r="AB103">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AC103">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD103">
         <v>1.65</v>
       </c>
       <c r="AE103">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF103">
         <v>1.67</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.14</v>
       </c>
       <c r="AK103">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="O104">
         <v>3.38</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O105">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P105">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q105">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R105">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S105">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T105">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U105">
         <v>2.55</v>
       </c>
       <c r="V105">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W105">
         <v>1.08</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z105">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AA105">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AB105">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AC105">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="AD105">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE105">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF105">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG105">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK105">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O106">
         <v>5.8</v>
@@ -17614,7 +17614,7 @@
         <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X106">
         <v>1.01</v>
@@ -17756,7 +17756,7 @@
         <v>3.8</v>
       </c>
       <c r="P107">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -17919,7 +17919,7 @@
         <v>5.4</v>
       </c>
       <c r="P108">
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -18239,7 +18239,7 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="O110">
         <v>3.43</v>
@@ -18278,7 +18278,7 @@
         <v>2.91</v>
       </c>
       <c r="AA110">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AB110">
         <v>1.66</v>
@@ -18619,10 +18619,10 @@
         <v>1.06</v>
       </c>
       <c r="AF112">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG112">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>3.5</v>
       </c>
       <c r="AA113">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB113">
         <v>1.93</v>
@@ -19057,10 +19057,10 @@
         <v>1.79</v>
       </c>
       <c r="O115">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P115">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q115">
         <v>2.25</v>
@@ -19069,46 +19069,46 @@
         <v>2.15</v>
       </c>
       <c r="S115">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T115">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V115">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AA115">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB115">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC115">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AD115">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE115">
         <v>1.04</v>
       </c>
       <c r="AF115">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG115">
         <v>1.75</v>
@@ -19127,7 +19127,7 @@
         <v>1.14</v>
       </c>
       <c r="AK115">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19223,7 +19223,7 @@
         <v>3.8</v>
       </c>
       <c r="P116">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="Q116">
         <v>2.15</v>
@@ -19256,7 +19256,7 @@
         <v>4.95</v>
       </c>
       <c r="AA116">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB116">
         <v>2.5</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK116">
         <v>2</v>
@@ -19380,65 +19380,65 @@
         </is>
       </c>
       <c r="N117">
+        <v>2.45</v>
+      </c>
+      <c r="O117">
+        <v>3.4</v>
+      </c>
+      <c r="P117">
+        <v>2.37</v>
+      </c>
+      <c r="Q117">
+        <v>3</v>
+      </c>
+      <c r="R117">
+        <v>2.3</v>
+      </c>
+      <c r="S117">
+        <v>1.26</v>
+      </c>
+      <c r="T117">
+        <v>3.24</v>
+      </c>
+      <c r="U117">
+        <v>2.25</v>
+      </c>
+      <c r="V117">
+        <v>1.57</v>
+      </c>
+      <c r="W117">
+        <v>1.15</v>
+      </c>
+      <c r="X117">
+        <v>1.01</v>
+      </c>
+      <c r="Y117">
+        <v>1.17</v>
+      </c>
+      <c r="Z117">
+        <v>4.6</v>
+      </c>
+      <c r="AA117">
+        <v>1.52</v>
+      </c>
+      <c r="AB117">
+        <v>2.37</v>
+      </c>
+      <c r="AC117">
+        <v>2.36</v>
+      </c>
+      <c r="AD117">
+        <v>1.44</v>
+      </c>
+      <c r="AE117">
+        <v>1.14</v>
+      </c>
+      <c r="AF117">
+        <v>1.44</v>
+      </c>
+      <c r="AG117">
         <v>2.5</v>
       </c>
-      <c r="O117">
-        <v>3.25</v>
-      </c>
-      <c r="P117">
-        <v>2.45</v>
-      </c>
-      <c r="Q117">
-        <v>3.13</v>
-      </c>
-      <c r="R117">
-        <v>2.2</v>
-      </c>
-      <c r="S117">
-        <v>1.3</v>
-      </c>
-      <c r="T117">
-        <v>3.2</v>
-      </c>
-      <c r="U117">
-        <v>2.49</v>
-      </c>
-      <c r="V117">
-        <v>1.5</v>
-      </c>
-      <c r="W117">
-        <v>1.12</v>
-      </c>
-      <c r="X117">
-        <v>1.04</v>
-      </c>
-      <c r="Y117">
-        <v>1.2</v>
-      </c>
-      <c r="Z117">
-        <v>4.1</v>
-      </c>
-      <c r="AA117">
-        <v>1.69</v>
-      </c>
-      <c r="AB117">
-        <v>2.12</v>
-      </c>
-      <c r="AC117">
-        <v>2.73</v>
-      </c>
-      <c r="AD117">
-        <v>1.41</v>
-      </c>
-      <c r="AE117">
-        <v>1.13</v>
-      </c>
-      <c r="AF117">
-        <v>1.55</v>
-      </c>
-      <c r="AG117">
-        <v>2.25</v>
-      </c>
       <c r="AH117" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK117">
         <v>1.44</v>
@@ -19543,16 +19543,16 @@
         </is>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="O118">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="P118">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R118">
         <v>2.1</v>
@@ -19561,40 +19561,40 @@
         <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="U118">
         <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W118">
         <v>1.05</v>
       </c>
       <c r="X118">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y118">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z118">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AB118">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC118">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD118">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE118">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF118">
         <v>1.75</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -644,10 +644,10 @@
         <v>2.95</v>
       </c>
       <c r="Q2">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="R2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="S2">
         <v>1.23</v>
@@ -656,43 +656,43 @@
         <v>3.46</v>
       </c>
       <c r="U2">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="V2">
         <v>1.53</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA2">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AB2">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="AD2">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AG2">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -964,49 +964,49 @@
         <v>2.8</v>
       </c>
       <c r="O4">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
         <v>2.4</v>
       </c>
       <c r="Q4">
-        <v>3.16</v>
+        <v>3.4</v>
       </c>
       <c r="R4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S4">
         <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AA4">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AB4">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
@@ -1015,7 +1015,7 @@
         <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
         <v>2.05</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
         <v>1.4</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q5">
         <v>3.12</v>
@@ -1142,22 +1142,22 @@
         <v>1.4</v>
       </c>
       <c r="T5">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
         <v>2.92</v>
@@ -1169,19 +1169,19 @@
         <v>1.65</v>
       </c>
       <c r="AC5">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
         <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="AD6">
+        <v>1.22</v>
+      </c>
+      <c r="AE6">
+        <v>1.04</v>
+      </c>
+      <c r="AF6">
+        <v>1.83</v>
+      </c>
+      <c r="AG6">
+        <v>1.91</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.24</v>
       </c>
-      <c r="AE6">
-        <v>1.05</v>
-      </c>
-      <c r="AF6">
-        <v>1.82</v>
-      </c>
-      <c r="AG6">
-        <v>1.85</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.17</v>
-      </c>
       <c r="AK6">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="Q8">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="R8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
         <v>1.1</v>
@@ -1646,25 +1646,25 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AA8">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
         <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O12">
+        <v>3.66</v>
+      </c>
+      <c r="P12">
+        <v>2.71</v>
+      </c>
+      <c r="Q12">
+        <v>2.72</v>
+      </c>
+      <c r="R12">
+        <v>2.27</v>
+      </c>
+      <c r="S12">
+        <v>1.22</v>
+      </c>
+      <c r="T12">
         <v>3.52</v>
       </c>
-      <c r="P12">
-        <v>2.64</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>5.3</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="P13">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="Q13">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="R13">
         <v>2.5</v>
@@ -2482,10 +2482,10 @@
         <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>2.5</v>
       </c>
       <c r="AK13">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
         <v>3.6</v>
       </c>
       <c r="Q16">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="R16">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
+        <v>1.36</v>
+      </c>
+      <c r="T16">
+        <v>2.88</v>
+      </c>
+      <c r="U16">
+        <v>2.86</v>
+      </c>
+      <c r="V16">
         <v>1.33</v>
       </c>
-      <c r="T16">
-        <v>3</v>
-      </c>
-      <c r="U16">
-        <v>2.55</v>
-      </c>
-      <c r="V16">
-        <v>1.4</v>
-      </c>
       <c r="W16">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y16">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AC16">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
         <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AG16">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q17">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U17">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
         <v>1.1</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
         <v>2</v>
       </c>
       <c r="AC17">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
         <v>2.15</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK17">
         <v>1.53</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q18">
         <v>3.25</v>
@@ -3258,43 +3258,43 @@
         <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
         <v>1.73</v>
       </c>
       <c r="AB18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC18">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AD18">
         <v>1.4</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="O19">
         <v>4.1</v>
       </c>
       <c r="P19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q19">
         <v>5.5</v>
@@ -3460,7 +3460,7 @@
         <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
         <v>2.05</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
         <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R20">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T20">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <v>1.07</v>
@@ -3602,10 +3602,10 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA20">
         <v>2.06</v>
@@ -3614,19 +3614,19 @@
         <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE20">
         <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q21">
         <v>2.9</v>
@@ -3789,7 +3789,7 @@
         <v>1.75</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q24">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>1.44</v>
       </c>
       <c r="T24">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
+        <v>4.2</v>
+      </c>
+      <c r="Q25">
+        <v>2.15</v>
+      </c>
+      <c r="R25">
+        <v>2.28</v>
+      </c>
+      <c r="S25">
+        <v>1.25</v>
+      </c>
+      <c r="T25">
         <v>3.3</v>
       </c>
-      <c r="Q25">
-        <v>2.23</v>
-      </c>
-      <c r="R25">
-        <v>2.3</v>
-      </c>
-      <c r="S25">
-        <v>1.32</v>
-      </c>
-      <c r="T25">
-        <v>3.08</v>
-      </c>
       <c r="U25">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AB25">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="AD25">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,37 +4547,37 @@
         </is>
       </c>
       <c r="N26">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P26">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q26">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>2.87</v>
+        <v>2.96</v>
       </c>
       <c r="U26">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
         <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.25</v>
@@ -4586,10 +4586,10 @@
         <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
@@ -4601,11 +4601,11 @@
         <v>1.1</v>
       </c>
       <c r="AF26">
+        <v>1.83</v>
+      </c>
+      <c r="AG26">
         <v>1.87</v>
       </c>
-      <c r="AG26">
-        <v>1.85</v>
-      </c>
       <c r="AH26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,10 +4713,10 @@
         <v>2.3</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
         <v>2.8</v>
@@ -4894,7 +4894,7 @@
         <v>2.79</v>
       </c>
       <c r="U28">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -5398,7 +5398,7 @@
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5528,10 +5528,10 @@
         <v>3.25</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5866,16 +5866,16 @@
         <v>2.15</v>
       </c>
       <c r="S34">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T34">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
         <v>2.45</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
         <v>1.08</v>
@@ -5893,7 +5893,7 @@
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
@@ -5905,10 +5905,10 @@
         <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>2.9</v>
       </c>
       <c r="O35">
-        <v>2.87</v>
+        <v>2.72</v>
       </c>
       <c r="P35">
         <v>2.35</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="O36">
         <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
         <v>3.54</v>
@@ -6340,31 +6340,31 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="O37">
         <v>4.4</v>
       </c>
       <c r="P37">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
         <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
         <v>1.11</v>
@@ -6379,10 +6379,10 @@
         <v>4.33</v>
       </c>
       <c r="AA37">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC37">
         <v>2.7</v>
@@ -6394,10 +6394,10 @@
         <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG37">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK37">
         <v>2.74</v>
@@ -6509,7 +6509,7 @@
         <v>5.5</v>
       </c>
       <c r="P38">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="O39">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q39">
         <v>2.46</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O40">
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6995,7 +6995,7 @@
         <v>1.41</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="P41">
         <v>6.5</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.47</v>
+      </c>
+      <c r="O42">
+        <v>4.5</v>
+      </c>
+      <c r="P42">
+        <v>4.65</v>
+      </c>
+      <c r="Q42">
         <v>1.87</v>
       </c>
-      <c r="O42">
-        <v>3.75</v>
-      </c>
-      <c r="P42">
-        <v>3</v>
-      </c>
-      <c r="Q42">
-        <v>2.38</v>
-      </c>
       <c r="R42">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="S42">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T42">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="U42">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="W42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>6.03</v>
+        <v>8</v>
       </c>
       <c r="AA42">
+        <v>1.29</v>
+      </c>
+      <c r="AB42">
+        <v>3.3</v>
+      </c>
+      <c r="AC42">
+        <v>1.75</v>
+      </c>
+      <c r="AD42">
+        <v>2.05</v>
+      </c>
+      <c r="AE42">
+        <v>1.44</v>
+      </c>
+      <c r="AF42">
         <v>1.38</v>
       </c>
-      <c r="AB42">
-        <v>2.92</v>
-      </c>
-      <c r="AC42">
-        <v>1.81</v>
-      </c>
-      <c r="AD42">
-        <v>1.86</v>
-      </c>
-      <c r="AE42">
-        <v>1.36</v>
-      </c>
-      <c r="AF42">
-        <v>1.32</v>
-      </c>
       <c r="AG42">
-        <v>2.98</v>
+        <v>2.77</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK42">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O43">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q43">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="R43">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="U43">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="V43">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="W43">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AA43">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AB43">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="AC43">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AD43">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AE43">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AG43">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O46">
         <v>4.25</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AK46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P47">
         <v>2.8</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R47">
         <v>2.25</v>
@@ -8012,7 +8012,7 @@
         <v>1.7</v>
       </c>
       <c r="AB47">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC47">
         <v>2.59</v>
@@ -8024,7 +8024,7 @@
         <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG47">
         <v>2.25</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
         <v>2.87</v>
       </c>
       <c r="Q48">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S48">
         <v>1.19</v>
@@ -8172,7 +8172,7 @@
         <v>4.65</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
@@ -8184,7 +8184,7 @@
         <v>1.52</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
         <v>1.53</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AK48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8308,7 +8308,7 @@
         <v>2.4</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8369,7 +8369,7 @@
         <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O50">
         <v>4.4</v>
@@ -8652,7 +8652,7 @@
         <v>1.1</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.25</v>
@@ -8791,7 +8791,7 @@
         <v>4.25</v>
       </c>
       <c r="P52">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O54">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB54">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -9277,16 +9277,16 @@
         <v>1.7</v>
       </c>
       <c r="O55">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P55">
         <v>4</v>
       </c>
       <c r="Q55">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="R55">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
         <v>1.25</v>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O56">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
         <v>2.29</v>
@@ -9476,10 +9476,10 @@
         <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB56">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="AC56">
         <v>2.08</v>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.19</v>
+        <v>1.55</v>
       </c>
       <c r="AK56">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,31 +9600,31 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="P57">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
       </c>
       <c r="R57">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V57">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W57">
         <v>1.12</v>
@@ -9633,25 +9633,25 @@
         <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z57">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA57">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB57">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC57">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="AD57">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AE57">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
         <v>1.57</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O58">
         <v>3.4</v>
@@ -9790,7 +9790,7 @@
         <v>1.44</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X58">
         <v>1.03</v>
@@ -9808,10 +9808,10 @@
         <v>2</v>
       </c>
       <c r="AC58">
-        <v>2.76</v>
+        <v>2.93</v>
       </c>
       <c r="AD58">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE58">
         <v>1.11</v>
@@ -9820,7 +9820,7 @@
         <v>1.57</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,16 +9926,16 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O59">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P59">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q59">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R59">
         <v>2.4</v>
@@ -9956,13 +9956,13 @@
         <v>1.12</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
         <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>5.41</v>
+        <v>5.68</v>
       </c>
       <c r="AA59">
         <v>1.48</v>
@@ -9974,7 +9974,7 @@
         <v>2.17</v>
       </c>
       <c r="AD59">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE59">
         <v>1.22</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AK59">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10140,13 +10140,13 @@
         <v>1.9</v>
       </c>
       <c r="AE60">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AF60">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O61">
         <v>3.75</v>
@@ -10325,7 +10325,7 @@
         <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="O62">
         <v>2.8</v>
       </c>
       <c r="P62">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q62">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R62">
         <v>1.78</v>
@@ -10581,7 +10581,7 @@
         <v>2.45</v>
       </c>
       <c r="O63">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P63">
         <v>3</v>
@@ -10590,13 +10590,13 @@
         <v>3.3</v>
       </c>
       <c r="R63">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S63">
         <v>1.6</v>
       </c>
       <c r="T63">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U63">
         <v>3.9</v>
@@ -10608,22 +10608,22 @@
         <v>1.01</v>
       </c>
       <c r="X63">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y63">
         <v>1.61</v>
       </c>
       <c r="Z63">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AA63">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB63">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC63">
-        <v>6.34</v>
+        <v>6.44</v>
       </c>
       <c r="AD63">
         <v>1.11</v>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O64">
-        <v>3.91</v>
+        <v>3.93</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q64">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="R64">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
         <v>1.25</v>
@@ -10762,7 +10762,7 @@
         <v>3.6</v>
       </c>
       <c r="U64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V64">
         <v>1.57</v>
@@ -10771,31 +10771,31 @@
         <v>1.13</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
         <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA64">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC64">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AD64">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE64">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG64">
         <v>2.25</v>
@@ -10814,7 +10814,7 @@
         <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>1.8</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
         <v>3.5</v>
@@ -10916,7 +10916,7 @@
         <v>2.15</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10925,13 +10925,13 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V65">
         <v>1.56</v>
       </c>
       <c r="W65">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -11076,13 +11076,13 @@
         <v>4.2</v>
       </c>
       <c r="Q66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R66">
         <v>2.49</v>
       </c>
       <c r="S66">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="T66">
         <v>4.65</v>
@@ -11140,7 +11140,7 @@
         <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O67">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="Q67">
         <v>2.44</v>
@@ -11251,13 +11251,13 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="V67">
         <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X67">
         <v>1.01</v>
@@ -11275,7 +11275,7 @@
         <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="AD67">
         <v>1.51</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,10 +11396,10 @@
         <v>2.13</v>
       </c>
       <c r="O68">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P68">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="Q68">
         <v>2.59</v>
@@ -11556,28 +11556,28 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
         <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>2.53</v>
+        <v>2.86</v>
       </c>
       <c r="R69">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S69">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U69">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V69">
         <v>1.51</v>
@@ -11592,13 +11592,13 @@
         <v>1.22</v>
       </c>
       <c r="Z69">
-        <v>4.15</v>
+        <v>4.16</v>
       </c>
       <c r="AA69">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB69">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC69">
         <v>2.56</v>
@@ -11629,7 +11629,7 @@
         <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11755,7 +11755,7 @@
         <v>1.08</v>
       </c>
       <c r="Z70">
-        <v>6.15</v>
+        <v>6.24</v>
       </c>
       <c r="AA70">
         <v>1.36</v>
@@ -11903,13 +11903,13 @@
         <v>3.56</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V71">
         <v>1.62</v>
       </c>
       <c r="W71">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X71">
         <v>1.02</v>
@@ -11927,7 +11927,7 @@
         <v>2.35</v>
       </c>
       <c r="AC71">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD71">
         <v>1.53</v>
@@ -12229,10 +12229,10 @@
         <v>3.7</v>
       </c>
       <c r="U73">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V73">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W73">
         <v>1.15</v>
@@ -12253,10 +12253,10 @@
         <v>2.45</v>
       </c>
       <c r="AC73">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AD73">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE73">
         <v>1.22</v>
@@ -12265,7 +12265,7 @@
         <v>1.44</v>
       </c>
       <c r="AG73">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.22</v>
       </c>
       <c r="AK73">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.47</v>
+        <v>2.38</v>
       </c>
       <c r="O74">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P74">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q74">
-        <v>1.93</v>
+        <v>2.76</v>
       </c>
       <c r="R74">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T74">
-        <v>3.21</v>
+        <v>2.78</v>
       </c>
       <c r="U74">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="V74">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W74">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z74">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA74">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB74">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC74">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AD74">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE74">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG74">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK74">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P75">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="Q75">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="U75">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
+        <v>1.02</v>
+      </c>
+      <c r="Y75">
+        <v>1.22</v>
+      </c>
+      <c r="Z75">
+        <v>3.5</v>
+      </c>
+      <c r="AA75">
+        <v>1.87</v>
+      </c>
+      <c r="AB75">
+        <v>1.9</v>
+      </c>
+      <c r="AC75">
+        <v>3.09</v>
+      </c>
+      <c r="AD75">
+        <v>1.32</v>
+      </c>
+      <c r="AE75">
+        <v>1.14</v>
+      </c>
+      <c r="AF75">
+        <v>1.93</v>
+      </c>
+      <c r="AG75">
+        <v>1.78</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.06</v>
       </c>
-      <c r="Y75">
-        <v>1.36</v>
-      </c>
-      <c r="Z75">
-        <v>3.16</v>
-      </c>
-      <c r="AA75">
-        <v>2.1</v>
-      </c>
-      <c r="AB75">
-        <v>1.73</v>
-      </c>
-      <c r="AC75">
-        <v>3.7</v>
-      </c>
-      <c r="AD75">
-        <v>1.26</v>
-      </c>
-      <c r="AE75">
-        <v>1.07</v>
-      </c>
-      <c r="AF75">
-        <v>1.75</v>
-      </c>
-      <c r="AG75">
-        <v>2</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.4</v>
-      </c>
       <c r="AK75">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12700,7 +12700,7 @@
         <v>3.05</v>
       </c>
       <c r="O76">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="P76">
         <v>2.2</v>
@@ -12718,10 +12718,10 @@
         <v>2.82</v>
       </c>
       <c r="U76">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="V76">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W76">
         <v>1.08</v>
@@ -12866,7 +12866,7 @@
         <v>3.4</v>
       </c>
       <c r="P77">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="Q77">
         <v>2.55</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P79">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="Q79">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R79">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T79">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="U79">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z79">
-        <v>4.32</v>
+        <v>3.92</v>
       </c>
       <c r="AA79">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB79">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC79">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="AD79">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF79">
         <v>1.55</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK79">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P80">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="Q80">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R80">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S80">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T80">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="U80">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W80">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z80">
-        <v>3.92</v>
+        <v>4.32</v>
       </c>
       <c r="AA80">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB80">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC80">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AD80">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE80">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF80">
         <v>1.55</v>
       </c>
       <c r="AG80">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13515,19 +13515,19 @@
         <v>1.68</v>
       </c>
       <c r="O81">
-        <v>4.3</v>
+        <v>3.91</v>
       </c>
       <c r="P81">
         <v>4</v>
       </c>
       <c r="Q81">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R81">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S81">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T81">
         <v>4</v>
@@ -13542,7 +13542,7 @@
         <v>1.2</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
         <v>1.13</v>
@@ -13557,7 +13557,7 @@
         <v>2.7</v>
       </c>
       <c r="AC81">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD81">
         <v>1.67</v>
@@ -13569,7 +13569,7 @@
         <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q82">
         <v>2.55</v>
       </c>
       <c r="R82">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T82">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U82">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="W82">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AA82">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AC82">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="AD82">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="AE82">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG82">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK82">
         <v>1.62</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
+        <v>2.14</v>
+      </c>
+      <c r="O83">
+        <v>3.7</v>
+      </c>
+      <c r="P83">
+        <v>2.62</v>
+      </c>
+      <c r="Q83">
+        <v>2.45</v>
+      </c>
+      <c r="R83">
+        <v>2.5</v>
+      </c>
+      <c r="S83">
+        <v>1.2</v>
+      </c>
+      <c r="T83">
+        <v>4</v>
+      </c>
+      <c r="U83">
         <v>2.05</v>
       </c>
-      <c r="O83">
-        <v>3.6</v>
-      </c>
-      <c r="P83">
-        <v>2.95</v>
-      </c>
-      <c r="Q83">
-        <v>2.6</v>
-      </c>
-      <c r="R83">
-        <v>2.38</v>
-      </c>
-      <c r="S83">
-        <v>1.25</v>
-      </c>
-      <c r="T83">
-        <v>3.5</v>
-      </c>
-      <c r="U83">
-        <v>2.25</v>
-      </c>
       <c r="V83">
+        <v>1.65</v>
+      </c>
+      <c r="W83">
+        <v>1.14</v>
+      </c>
+      <c r="X83">
+        <v>1.02</v>
+      </c>
+      <c r="Y83">
+        <v>1.1</v>
+      </c>
+      <c r="Z83">
+        <v>6</v>
+      </c>
+      <c r="AA83">
+        <v>1.4</v>
+      </c>
+      <c r="AB83">
+        <v>2.75</v>
+      </c>
+      <c r="AC83">
+        <v>2.01</v>
+      </c>
+      <c r="AD83">
+        <v>1.77</v>
+      </c>
+      <c r="AE83">
+        <v>1.28</v>
+      </c>
+      <c r="AF83">
+        <v>1.4</v>
+      </c>
+      <c r="AG83">
+        <v>2.88</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>1.21</v>
+      </c>
+      <c r="AK83">
         <v>1.6</v>
-      </c>
-      <c r="W83">
-        <v>1.15</v>
-      </c>
-      <c r="X83">
-        <v>1.01</v>
-      </c>
-      <c r="Y83">
-        <v>1.15</v>
-      </c>
-      <c r="Z83">
-        <v>4.8</v>
-      </c>
-      <c r="AA83">
-        <v>1.57</v>
-      </c>
-      <c r="AB83">
-        <v>2.38</v>
-      </c>
-      <c r="AC83">
-        <v>2.32</v>
-      </c>
-      <c r="AD83">
-        <v>1.52</v>
-      </c>
-      <c r="AE83">
-        <v>1.18</v>
-      </c>
-      <c r="AF83">
-        <v>1.47</v>
-      </c>
-      <c r="AG83">
-        <v>2.45</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.25</v>
-      </c>
-      <c r="AK83">
-        <v>1.65</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,16 +14001,16 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O84">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P84">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="Q84">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R84">
         <v>2.62</v>
@@ -14046,10 +14046,10 @@
         <v>3.5</v>
       </c>
       <c r="AC84">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD84">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AE84">
         <v>1.44</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK84">
         <v>1.77</v>
@@ -14176,7 +14176,7 @@
         <v>2.37</v>
       </c>
       <c r="R85">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
         <v>1.22</v>
@@ -14209,10 +14209,10 @@
         <v>2.55</v>
       </c>
       <c r="AC85">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AD85">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE85">
         <v>1.2</v>
@@ -14348,10 +14348,10 @@
         <v>3.9</v>
       </c>
       <c r="U86">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V86">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W86">
         <v>1.14</v>
@@ -14375,7 +14375,7 @@
         <v>2.1</v>
       </c>
       <c r="AD86">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE86">
         <v>1.22</v>
@@ -14400,7 +14400,7 @@
         <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14493,10 +14493,10 @@
         <v>1.55</v>
       </c>
       <c r="O87">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P87">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q87">
         <v>2.09</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q88">
         <v>2.62</v>
@@ -14819,10 +14819,10 @@
         <v>3.6</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P89">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
@@ -14834,10 +14834,10 @@
         <v>1.35</v>
       </c>
       <c r="T89">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="U89">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V89">
         <v>1.46</v>
@@ -14852,7 +14852,7 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="AA89">
         <v>1.75</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O90">
         <v>3.25</v>
       </c>
       <c r="P90">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q90">
         <v>2.69</v>
@@ -15052,7 +15052,7 @@
         <v>1.23</v>
       </c>
       <c r="AK90">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15474,7 +15474,7 @@
         <v>5.5</v>
       </c>
       <c r="P93">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="Q93">
         <v>1.55</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="O94">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P94">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q94">
         <v>2.1</v>
@@ -16666,7 +16666,7 @@
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16775,13 +16775,13 @@
         <v>5.25</v>
       </c>
       <c r="O101">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P101">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="Q101">
-        <v>5.78</v>
+        <v>5.95</v>
       </c>
       <c r="R101">
         <v>2.63</v>
@@ -16826,10 +16826,10 @@
         <v>1.25</v>
       </c>
       <c r="AF101">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG101">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="AK101">
         <v>1.09</v>
@@ -16935,19 +16935,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O102">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P102">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="Q102">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R102">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S102">
         <v>1.37</v>
@@ -16956,10 +16956,10 @@
         <v>2.69</v>
       </c>
       <c r="U102">
-        <v>3.07</v>
+        <v>3.02</v>
       </c>
       <c r="V102">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W102">
         <v>1.07</v>
@@ -16974,10 +16974,10 @@
         <v>3.04</v>
       </c>
       <c r="AA102">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB102">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC102">
         <v>3.58</v>
@@ -16989,7 +16989,7 @@
         <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG102">
         <v>1.83</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O103">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P103">
-        <v>6.7</v>
+        <v>6.25</v>
       </c>
       <c r="Q103">
         <v>1.88</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O104">
         <v>3.38</v>
@@ -17273,7 +17273,7 @@
         <v>3</v>
       </c>
       <c r="R104">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S104">
         <v>1.39</v>
@@ -17288,7 +17288,7 @@
         <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X104">
         <v>1.04</v>
@@ -17315,10 +17315,10 @@
         <v>1.12</v>
       </c>
       <c r="AF104">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG104">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>3.25</v>
       </c>
       <c r="U105">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V105">
         <v>1.44</v>
@@ -17466,7 +17466,7 @@
         <v>1.84</v>
       </c>
       <c r="AB105">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC105">
         <v>2.88</v>
@@ -17623,22 +17623,22 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA106">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB106">
         <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD106">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE106">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF106">
         <v>1.93</v>
@@ -17768,7 +17768,7 @@
         <v>1.36</v>
       </c>
       <c r="T107">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="U107">
         <v>2.75</v>
@@ -17795,7 +17795,7 @@
         <v>1.85</v>
       </c>
       <c r="AC107">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD107">
         <v>1.3</v>
@@ -17823,7 +17823,7 @@
         <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O108">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="P108">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="Q108">
         <v>1.67</v>
@@ -17934,7 +17934,7 @@
         <v>4</v>
       </c>
       <c r="U108">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V108">
         <v>1.75</v>
@@ -18094,16 +18094,16 @@
         <v>1.22</v>
       </c>
       <c r="T109">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U109">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V109">
         <v>1.67</v>
       </c>
       <c r="W109">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X109">
         <v>1.02</v>
@@ -18112,19 +18112,19 @@
         <v>1.11</v>
       </c>
       <c r="Z109">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA109">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AB109">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC109">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AD109">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE109">
         <v>1.21</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="O110">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="Q110">
         <v>2.25</v>
@@ -18257,7 +18257,7 @@
         <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U110">
         <v>3</v>
@@ -18275,19 +18275,19 @@
         <v>1.32</v>
       </c>
       <c r="Z110">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="AA110">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB110">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC110">
-        <v>3.99</v>
+        <v>3.93</v>
       </c>
       <c r="AD110">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE110">
         <v>1.04</v>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,19 +18402,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="O111">
         <v>10</v>
       </c>
       <c r="P111">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q111">
         <v>1.3</v>
       </c>
       <c r="R111">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S111">
         <v>1.17</v>
@@ -18435,31 +18435,31 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z111">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB111">
         <v>3.1</v>
       </c>
       <c r="AC111">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD111">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AE111">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF111">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="AG111">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK111">
         <v>8.5</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="O113">
         <v>3.15</v>
@@ -18752,7 +18752,7 @@
         <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W113">
         <v>1.1</v>
@@ -18767,7 +18767,7 @@
         <v>3.5</v>
       </c>
       <c r="AA113">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB113">
         <v>1.93</v>
@@ -18891,7 +18891,7 @@
         </is>
       </c>
       <c r="N114">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="O114">
         <v>4.6</v>
@@ -18921,7 +18921,7 @@
         <v>1.15</v>
       </c>
       <c r="X114">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y114">
         <v>1.11</v>
@@ -19060,7 +19060,7 @@
         <v>3.2</v>
       </c>
       <c r="P115">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q115">
         <v>2.25</v>
@@ -19069,7 +19069,7 @@
         <v>2.15</v>
       </c>
       <c r="S115">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T115">
         <v>2.7</v>
@@ -19081,7 +19081,7 @@
         <v>1.35</v>
       </c>
       <c r="W115">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
         <v>1.02</v>
@@ -19093,13 +19093,13 @@
         <v>2.83</v>
       </c>
       <c r="AA115">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB115">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC115">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AD115">
         <v>1.24</v>
@@ -19217,10 +19217,10 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="O116">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P116">
         <v>3.8</v>
@@ -19256,7 +19256,7 @@
         <v>4.95</v>
       </c>
       <c r="AA116">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB116">
         <v>2.5</v>
@@ -19392,7 +19392,7 @@
         <v>3</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S117">
         <v>1.26</v>
@@ -19401,43 +19401,43 @@
         <v>3.24</v>
       </c>
       <c r="U117">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V117">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X117">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA117">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AB117">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="AC117">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="AD117">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE117">
         <v>1.14</v>
       </c>
       <c r="AF117">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG117">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
         <v>1.44</v>
@@ -19549,7 +19549,7 @@
         <v>3.11</v>
       </c>
       <c r="P118">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="Q118">
         <v>2.8</v>
@@ -19561,13 +19561,13 @@
         <v>1.36</v>
       </c>
       <c r="T118">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="U118">
         <v>2.8</v>
       </c>
       <c r="V118">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W118">
         <v>1.05</v>
@@ -19585,7 +19585,7 @@
         <v>1.99</v>
       </c>
       <c r="AB118">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC118">
         <v>3.8</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O9">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q9">
         <v>3.24</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O13">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="P13">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Q13">
         <v>4.36</v>
@@ -2473,10 +2473,10 @@
         <v>2.45</v>
       </c>
       <c r="AC13">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE13">
         <v>1.2</v>
@@ -2501,7 +2501,7 @@
         <v>2.5</v>
       </c>
       <c r="AK13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>2.1</v>
       </c>
       <c r="S21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T21">
         <v>2.58</v>
       </c>
       <c r="U21">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="V21">
         <v>1.34</v>
@@ -3765,13 +3765,13 @@
         <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z21">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="AA21">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AB21">
         <v>1.7</v>
@@ -4064,7 +4064,7 @@
         <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
         <v>3.42</v>
@@ -5398,7 +5398,7 @@
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>6.08</v>
+        <v>5.67</v>
       </c>
       <c r="AA31">
         <v>1.4</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
         <v>2.8</v>
@@ -5924,7 +5924,7 @@
         <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6183,22 +6183,22 @@
         <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="Q36">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="R36">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="S36">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="U36">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="V36">
         <v>1.38</v>
@@ -6213,19 +6213,19 @@
         <v>1.31</v>
       </c>
       <c r="Z36">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="AA36">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB36">
         <v>1.72</v>
       </c>
       <c r="AC36">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
@@ -6250,7 +6250,7 @@
         <v>1.36</v>
       </c>
       <c r="AK36">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -6379,10 +6379,10 @@
         <v>4.33</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AC37">
         <v>2.7</v>
@@ -6391,7 +6391,7 @@
         <v>1.44</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
         <v>1.9</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK37">
         <v>2.74</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O40">
         <v>3.4</v>
       </c>
       <c r="P40">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q40">
         <v>2.8</v>
@@ -6865,7 +6865,7 @@
         <v>1.14</v>
       </c>
       <c r="Z40">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA40">
         <v>1.58</v>
@@ -6874,10 +6874,10 @@
         <v>2.27</v>
       </c>
       <c r="AC40">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD40">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE40">
         <v>1.2</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK40">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O41">
         <v>3.83</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="O42">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="P42">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q42">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
+        <v>1.22</v>
+      </c>
+      <c r="T42">
+        <v>3.52</v>
+      </c>
+      <c r="U42">
+        <v>1.98</v>
+      </c>
+      <c r="V42">
+        <v>1.78</v>
+      </c>
+      <c r="W42">
         <v>1.17</v>
-      </c>
-      <c r="T42">
-        <v>4.6</v>
-      </c>
-      <c r="U42">
-        <v>1.85</v>
-      </c>
-      <c r="V42">
-        <v>1.85</v>
-      </c>
-      <c r="W42">
-        <v>1.25</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>8</v>
+        <v>5.43</v>
       </c>
       <c r="AA42">
+        <v>1.38</v>
+      </c>
+      <c r="AB42">
+        <v>2.75</v>
+      </c>
+      <c r="AC42">
+        <v>2.01</v>
+      </c>
+      <c r="AD42">
+        <v>1.69</v>
+      </c>
+      <c r="AE42">
         <v>1.29</v>
-      </c>
-      <c r="AB42">
-        <v>3.3</v>
-      </c>
-      <c r="AC42">
-        <v>1.75</v>
-      </c>
-      <c r="AD42">
-        <v>2.05</v>
-      </c>
-      <c r="AE42">
-        <v>1.44</v>
       </c>
       <c r="AF42">
         <v>1.38</v>
       </c>
       <c r="AG42">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="O43">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="Q43">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="S43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T43">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="U43">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="V43">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W43">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z43">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AA43">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AB43">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="AC43">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AD43">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE43">
+        <v>1.4</v>
+      </c>
+      <c r="AF43">
         <v>1.36</v>
       </c>
-      <c r="AF43">
-        <v>1.32</v>
-      </c>
       <c r="AG43">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK43">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O45">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="P45">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q45">
         <v>3.1</v>
@@ -7813,7 +7813,7 @@
         <v>4.25</v>
       </c>
       <c r="P46">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Q46">
         <v>4.21</v>
@@ -7846,10 +7846,10 @@
         <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
         <v>2.38</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AK46">
         <v>1.15</v>
@@ -8474,10 +8474,10 @@
         <v>2.47</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U50">
         <v>2</v>
@@ -8489,7 +8489,7 @@
         <v>1.2</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
         <v>1.1</v>
@@ -8510,7 +8510,7 @@
         <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O51">
         <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q51">
         <v>3.75</v>
@@ -8637,10 +8637,10 @@
         <v>2.12</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="U51">
         <v>2.63</v>
@@ -8664,7 +8664,7 @@
         <v>1.79</v>
       </c>
       <c r="AB51">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC51">
         <v>3.1</v>
@@ -8785,10 +8785,10 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="O52">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P52">
         <v>5.8</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK52">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O54">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P54">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9295,7 +9295,7 @@
         <v>3.6</v>
       </c>
       <c r="U55">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="V55">
         <v>1.57</v>
@@ -9316,7 +9316,7 @@
         <v>1.57</v>
       </c>
       <c r="AB55">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC55">
         <v>2.3</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK55">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9820,7 +9820,7 @@
         <v>1.57</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9929,10 +9929,10 @@
         <v>4</v>
       </c>
       <c r="O59">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P59">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q59">
         <v>4.1</v>
@@ -9974,13 +9974,13 @@
         <v>2.17</v>
       </c>
       <c r="AD59">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE59">
         <v>1.22</v>
       </c>
       <c r="AF59">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
         <v>2.55</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.95</v>
+        <v>1.15</v>
       </c>
       <c r="AK59">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10098,7 +10098,7 @@
         <v>1.27</v>
       </c>
       <c r="Q60">
-        <v>6.57</v>
+        <v>7.5</v>
       </c>
       <c r="R60">
         <v>2.9</v>
@@ -10134,7 +10134,7 @@
         <v>3.21</v>
       </c>
       <c r="AC60">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AD60">
         <v>1.9</v>
@@ -10146,7 +10146,7 @@
         <v>1.68</v>
       </c>
       <c r="AG60">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK60">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="O61">
         <v>3.75</v>
@@ -10261,10 +10261,10 @@
         <v>2.27</v>
       </c>
       <c r="Q61">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="R61">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S61">
         <v>1.22</v>
@@ -10294,7 +10294,7 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC61">
         <v>2.38</v>
@@ -11393,22 +11393,22 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="O68">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="P68">
         <v>3.32</v>
       </c>
       <c r="Q68">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="R68">
         <v>2.08</v>
       </c>
       <c r="S68">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
         <v>3</v>
@@ -11417,7 +11417,7 @@
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W68">
         <v>1.06</v>
@@ -11429,16 +11429,16 @@
         <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="AA68">
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC68">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O71">
         <v>5.1</v>
       </c>
       <c r="P71">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Q71">
         <v>1.64</v>
@@ -11900,10 +11900,10 @@
         <v>1.25</v>
       </c>
       <c r="T71">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V71">
         <v>1.62</v>
@@ -11912,22 +11912,22 @@
         <v>1.14</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z71">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AA71">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB71">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AC71">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AD71">
         <v>1.53</v>
@@ -11936,10 +11936,10 @@
         <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG71">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O72">
         <v>3</v>
@@ -12054,22 +12054,22 @@
         <v>4.6</v>
       </c>
       <c r="Q72">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R72">
         <v>1.91</v>
       </c>
       <c r="S72">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T72">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="U72">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="V72">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W72">
         <v>1.03</v>
@@ -12078,31 +12078,31 @@
         <v>1.07</v>
       </c>
       <c r="Y72">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="Z72">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AA72">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AB72">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AC72">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="AD72">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE72">
         <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG72">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="O73">
+        <v>4.15</v>
+      </c>
+      <c r="P73">
+        <v>6.5</v>
+      </c>
+      <c r="Q73">
+        <v>1.95</v>
+      </c>
+      <c r="R73">
+        <v>2.3</v>
+      </c>
+      <c r="S73">
+        <v>1.3</v>
+      </c>
+      <c r="T73">
+        <v>3.18</v>
+      </c>
+      <c r="U73">
+        <v>2.6</v>
+      </c>
+      <c r="V73">
+        <v>1.44</v>
+      </c>
+      <c r="W73">
+        <v>1.1</v>
+      </c>
+      <c r="X73">
+        <v>1.02</v>
+      </c>
+      <c r="Y73">
+        <v>1.22</v>
+      </c>
+      <c r="Z73">
         <v>3.5</v>
       </c>
-      <c r="P73">
-        <v>3</v>
-      </c>
-      <c r="Q73">
-        <v>2.44</v>
-      </c>
-      <c r="R73">
-        <v>2.28</v>
-      </c>
-      <c r="S73">
-        <v>1.25</v>
-      </c>
-      <c r="T73">
-        <v>3.7</v>
-      </c>
-      <c r="U73">
-        <v>2.19</v>
-      </c>
-      <c r="V73">
-        <v>1.58</v>
-      </c>
-      <c r="W73">
-        <v>1.15</v>
-      </c>
-      <c r="X73">
-        <v>1.01</v>
-      </c>
-      <c r="Y73">
-        <v>1.11</v>
-      </c>
-      <c r="Z73">
-        <v>4.95</v>
-      </c>
       <c r="AA73">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB73">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AC73">
-        <v>2.31</v>
+        <v>3.09</v>
       </c>
       <c r="AD73">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF73">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AG73">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK73">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,80 +12371,80 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="O74">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q74">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="R74">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="S74">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="U74">
-        <v>3.17</v>
+        <v>2.19</v>
       </c>
       <c r="V74">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X74">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="Z74">
-        <v>3.16</v>
+        <v>4.95</v>
       </c>
       <c r="AA74">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AB74">
+        <v>2.45</v>
+      </c>
+      <c r="AC74">
+        <v>2.31</v>
+      </c>
+      <c r="AD74">
+        <v>1.54</v>
+      </c>
+      <c r="AE74">
+        <v>1.22</v>
+      </c>
+      <c r="AF74">
+        <v>1.44</v>
+      </c>
+      <c r="AG74">
+        <v>2.5</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>1.22</v>
+      </c>
+      <c r="AK74">
         <v>1.73</v>
-      </c>
-      <c r="AC74">
-        <v>3.8</v>
-      </c>
-      <c r="AD74">
-        <v>1.26</v>
-      </c>
-      <c r="AE74">
-        <v>1.07</v>
-      </c>
-      <c r="AF74">
-        <v>1.8</v>
-      </c>
-      <c r="AG74">
-        <v>1.91</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>1.36</v>
-      </c>
-      <c r="AK74">
-        <v>1.5</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="O75">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P75">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q75">
-        <v>1.95</v>
+        <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T75">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="U75">
-        <v>2.6</v>
+        <v>3.17</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z75">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="AA75">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB75">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC75">
-        <v>3.09</v>
+        <v>3.8</v>
       </c>
       <c r="AD75">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AG75">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="AK75">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="O78">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q78">
         <v>3.2</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O80">
         <v>3.45</v>
@@ -13364,19 +13364,19 @@
         <v>2.38</v>
       </c>
       <c r="S80">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T80">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U80">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V80">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="O85">
         <v>3.6</v>
       </c>
       <c r="P85">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q85">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S85">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T85">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U85">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V85">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W85">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
         <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="AA85">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AC85">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD85">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AE85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG85">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>1.19</v>
       </c>
       <c r="AK85">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="O86">
         <v>3.6</v>
       </c>
       <c r="P86">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="R86">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S86">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V86">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB86">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC86">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD86">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG86">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.19</v>
       </c>
       <c r="AK86">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="O88">
         <v>3.6</v>
       </c>
       <c r="P88">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q88">
         <v>2.62</v>
@@ -14671,7 +14671,7 @@
         <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U88">
         <v>2.32</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
+        <v>4</v>
+      </c>
+      <c r="O89">
         <v>3.6</v>
       </c>
-      <c r="O89">
-        <v>3.55</v>
-      </c>
       <c r="P89">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q89">
         <v>4.62</v>
@@ -14873,7 +14873,7 @@
         <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK92">
         <v>1.36</v>
@@ -15471,7 +15471,7 @@
         <v>1.25</v>
       </c>
       <c r="O93">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P93">
         <v>9</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O94">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P94">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q94">
         <v>2.1</v>
@@ -15673,7 +15673,7 @@
         <v>1.7</v>
       </c>
       <c r="AB94">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC94">
         <v>2.25</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>1.54</v>
+        <v>2.01</v>
       </c>
       <c r="Q95">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="R95">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB95">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC95">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD95">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF95">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG95">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>3</v>
+        <v>4.65</v>
       </c>
       <c r="O96">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P96">
-        <v>2.06</v>
+        <v>1.57</v>
       </c>
       <c r="Q96">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="R96">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V96">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W96">
         <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
+        <v>1.18</v>
+      </c>
+      <c r="Z96">
+        <v>4.33</v>
+      </c>
+      <c r="AA96">
+        <v>1.64</v>
+      </c>
+      <c r="AB96">
+        <v>2.17</v>
+      </c>
+      <c r="AC96">
+        <v>2.67</v>
+      </c>
+      <c r="AD96">
+        <v>1.42</v>
+      </c>
+      <c r="AE96">
+        <v>1.14</v>
+      </c>
+      <c r="AF96">
+        <v>1.7</v>
+      </c>
+      <c r="AG96">
+        <v>2.04</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.22</v>
+      </c>
+      <c r="AK96">
         <v>1.15</v>
-      </c>
-      <c r="Z96">
-        <v>4.25</v>
-      </c>
-      <c r="AA96">
-        <v>1.62</v>
-      </c>
-      <c r="AB96">
-        <v>2.15</v>
-      </c>
-      <c r="AC96">
-        <v>2.55</v>
-      </c>
-      <c r="AD96">
-        <v>1.45</v>
-      </c>
-      <c r="AE96">
-        <v>1.15</v>
-      </c>
-      <c r="AF96">
-        <v>1.5</v>
-      </c>
-      <c r="AG96">
-        <v>2.38</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.29</v>
-      </c>
-      <c r="AK96">
-        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,19 +16120,19 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O97">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P97">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q97">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="R97">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="S97">
         <v>1.22</v>
@@ -16141,10 +16141,10 @@
         <v>3.8</v>
       </c>
       <c r="U97">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V97">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W97">
         <v>1.17</v>
@@ -16156,19 +16156,19 @@
         <v>1.11</v>
       </c>
       <c r="Z97">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA97">
         <v>1.46</v>
       </c>
       <c r="AB97">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AC97">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD97">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE97">
         <v>1.2</v>
@@ -16283,28 +16283,28 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O98">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P98">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q98">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R98">
         <v>2.18</v>
       </c>
       <c r="S98">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T98">
-        <v>3.28</v>
+        <v>2.87</v>
       </c>
       <c r="U98">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="V98">
         <v>1.47</v>
@@ -16313,31 +16313,31 @@
         <v>1.11</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
         <v>1.24</v>
       </c>
       <c r="Z98">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="AA98">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB98">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC98">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AD98">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AE98">
         <v>1.16</v>
       </c>
       <c r="AF98">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG98">
         <v>2.25</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK98">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16452,7 +16452,7 @@
         <v>3.4</v>
       </c>
       <c r="P99">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q99">
         <v>2.57</v>
@@ -16464,16 +16464,16 @@
         <v>1.3</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U99">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V99">
         <v>1.42</v>
       </c>
       <c r="W99">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16488,7 +16488,7 @@
         <v>1.78</v>
       </c>
       <c r="AB99">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AC99">
         <v>2.88</v>
@@ -16519,7 +16519,7 @@
         <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P100">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q100">
         <v>3.75</v>
@@ -16624,7 +16624,7 @@
         <v>2.09</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
         <v>3.1</v>
@@ -16772,16 +16772,16 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="O101">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P101">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q101">
-        <v>5.95</v>
+        <v>6.03</v>
       </c>
       <c r="R101">
         <v>2.63</v>
@@ -16796,7 +16796,7 @@
         <v>2</v>
       </c>
       <c r="V101">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W101">
         <v>1.18</v>
@@ -16811,25 +16811,25 @@
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB101">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AC101">
         <v>2.1</v>
       </c>
       <c r="AD101">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE101">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF101">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG101">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AK101">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16938,7 +16938,7 @@
         <v>1.9</v>
       </c>
       <c r="O102">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
         <v>4.3</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="O103">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P103">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q103">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R103">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="S103">
         <v>1.25</v>
@@ -17267,16 +17267,16 @@
         <v>3.38</v>
       </c>
       <c r="P104">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="Q104">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R104">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S104">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T104">
         <v>3</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK104">
         <v>1.55</v>
@@ -17451,7 +17451,7 @@
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X105">
         <v>1.03</v>
@@ -17497,7 +17497,7 @@
         <v>1.27</v>
       </c>
       <c r="AK105">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17596,7 +17596,7 @@
         <v>1.28</v>
       </c>
       <c r="Q106">
-        <v>6.09</v>
+        <v>6.38</v>
       </c>
       <c r="R106">
         <v>2.6</v>
@@ -17623,25 +17623,25 @@
         <v>1.14</v>
       </c>
       <c r="Z106">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA106">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB106">
         <v>2.35</v>
       </c>
       <c r="AC106">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AD106">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE106">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF106">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG106">
         <v>1.75</v>
@@ -17753,10 +17753,10 @@
         <v>1.57</v>
       </c>
       <c r="O107">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P107">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q107">
         <v>2.2</v>
@@ -17783,16 +17783,16 @@
         <v>1.04</v>
       </c>
       <c r="Y107">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z107">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA107">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AB107">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC107">
         <v>3.4</v>
@@ -17804,7 +17804,7 @@
         <v>1.1</v>
       </c>
       <c r="AF107">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG107">
         <v>1.83</v>
@@ -17913,10 +17913,10 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O108">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="P108">
         <v>9.6</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O109">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P109">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q109">
         <v>1.8</v>
@@ -18094,46 +18094,46 @@
         <v>1.22</v>
       </c>
       <c r="T109">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U109">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V109">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W109">
         <v>1.17</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
         <v>1.11</v>
       </c>
       <c r="Z109">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA109">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB109">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AC109">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AD109">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE109">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF109">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG109">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18565,13 +18565,13 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O112">
         <v>3.7</v>
       </c>
       <c r="P112">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q112">
         <v>2.3</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O113">
         <v>3.15</v>
@@ -18936,7 +18936,7 @@
         <v>2.38</v>
       </c>
       <c r="AC114">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD114">
         <v>1.56</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
         <v>3.2</v>
@@ -19217,43 +19217,43 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="O116">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q116">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="R116">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S116">
         <v>1.22</v>
       </c>
       <c r="T116">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U116">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="V116">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="W116">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA116">
         <v>1.5</v>
@@ -19262,19 +19262,19 @@
         <v>2.5</v>
       </c>
       <c r="AC116">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AD116">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AE116">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AF116">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG116">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK116">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19546,7 +19546,7 @@
         <v>2.06</v>
       </c>
       <c r="O118">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="P118">
         <v>3.15</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -612,36 +612,36 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O2">
         <v>3.55</v>
       </c>
       <c r="P2">
-        <v>2.95</v>
+        <v>2.31</v>
       </c>
       <c r="Q2">
         <v>2.82</v>
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "88", "90+2"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "88"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>2.19</v>
       </c>
       <c r="AG9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="O11">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q11">
+        <v>1.62</v>
+      </c>
+      <c r="R11">
+        <v>2.88</v>
+      </c>
+      <c r="S11">
+        <v>1.18</v>
+      </c>
+      <c r="T11">
+        <v>3.75</v>
+      </c>
+      <c r="U11">
+        <v>2.1</v>
+      </c>
+      <c r="V11">
         <v>1.67</v>
       </c>
-      <c r="R11">
-        <v>2.7</v>
-      </c>
-      <c r="S11">
-        <v>1.23</v>
-      </c>
-      <c r="T11">
-        <v>3.4</v>
-      </c>
-      <c r="U11">
-        <v>2.25</v>
-      </c>
-      <c r="V11">
-        <v>1.57</v>
-      </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z11">
-        <v>4.45</v>
+        <v>5.49</v>
       </c>
       <c r="AA11">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB11">
-        <v>2.37</v>
+        <v>2.69</v>
       </c>
       <c r="AC11">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AD11">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK11">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="O13">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Q13">
         <v>4.36</v>
@@ -2443,13 +2443,13 @@
         <v>2.5</v>
       </c>
       <c r="S13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
         <v>3.6</v>
       </c>
       <c r="U13">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V13">
         <v>1.6</v>
@@ -2467,10 +2467,10 @@
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB13">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AC13">
         <v>2.38</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AK13">
         <v>1.05</v>
@@ -3569,49 +3569,49 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q20">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="S20">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
         <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z20">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AA20">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC20">
         <v>3.5</v>
@@ -3623,7 +3623,7 @@
         <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AG20">
         <v>1.85</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P21">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q21">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S21">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="T21">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="U21">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="V21">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z21">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AA21">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="AB21">
+        <v>1.5</v>
+      </c>
+      <c r="AC21">
+        <v>4.5</v>
+      </c>
+      <c r="AD21">
+        <v>1.17</v>
+      </c>
+      <c r="AE21">
+        <v>1.02</v>
+      </c>
+      <c r="AF21">
+        <v>2</v>
+      </c>
+      <c r="AG21">
         <v>1.7</v>
-      </c>
-      <c r="AC21">
-        <v>3.8</v>
-      </c>
-      <c r="AD21">
-        <v>1.22</v>
-      </c>
-      <c r="AE21">
-        <v>1.05</v>
-      </c>
-      <c r="AF21">
-        <v>1.75</v>
-      </c>
-      <c r="AG21">
-        <v>1.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.36</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O23">
         <v>2.8</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q23">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="R23">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S23">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T23">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U23">
         <v>3.6</v>
@@ -4097,13 +4097,13 @@
         <v>2.17</v>
       </c>
       <c r="AA23">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AB23">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AC23">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="AD23">
         <v>1.07</v>
@@ -4112,10 +4112,10 @@
         <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG23">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.32</v>
       </c>
       <c r="AK23">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q27">
         <v>2.8</v>
@@ -4725,13 +4725,13 @@
         <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T27">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U27">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V27">
         <v>1.4</v>
@@ -4743,16 +4743,16 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z27">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC27">
         <v>3.28</v>
@@ -4761,13 +4761,13 @@
         <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,31 +4879,31 @@
         <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q28">
         <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
         <v>1.25</v>
@@ -4912,25 +4912,25 @@
         <v>3.5</v>
       </c>
       <c r="AA28">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AC28">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD28">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE28">
         <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,25 +5036,25 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="O29">
         <v>3</v>
       </c>
       <c r="P29">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q29">
-        <v>5.6</v>
+        <v>6.11</v>
       </c>
       <c r="R29">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="S29">
         <v>1.48</v>
       </c>
       <c r="T29">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="U29">
         <v>3.7</v>
@@ -5069,10 +5069,10 @@
         <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Z29">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AA29">
         <v>2.64</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
         <v>1.11</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5697,16 +5697,16 @@
         <v>3.8</v>
       </c>
       <c r="Q33">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="R33">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="S33">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="T33">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U33">
         <v>4</v>
@@ -5724,13 +5724,13 @@
         <v>1.67</v>
       </c>
       <c r="Z33">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AA33">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AB33">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AC33">
         <v>6.8</v>
@@ -5742,10 +5742,10 @@
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="AG33">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
         <v>1.63</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="O34">
         <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="Q34">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R34">
         <v>2.15</v>
@@ -5872,7 +5872,7 @@
         <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V34">
         <v>1.43</v>
@@ -5893,13 +5893,13 @@
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC34">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
         <v>1.08</v>
@@ -5908,7 +5908,7 @@
         <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
         <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z36">
         <v>3.21</v>
@@ -6231,10 +6231,10 @@
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG36">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK36">
         <v>1.3</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O39">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R39">
         <v>2.07</v>
@@ -6684,25 +6684,25 @@
         <v>1.32</v>
       </c>
       <c r="T39">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U39">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="V39">
         <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z39">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AA39">
         <v>1.83</v>
@@ -6711,19 +6711,19 @@
         <v>1.84</v>
       </c>
       <c r="AC39">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE39">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
         <v>1.75</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="O44">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P44">
         <v>6</v>
       </c>
       <c r="Q44">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R44">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U44">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="V44">
         <v>1.36</v>
@@ -7511,28 +7511,28 @@
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z44">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="AA44">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB44">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AC44">
         <v>3.42</v>
       </c>
       <c r="AD44">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE44">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
         <v>2.1</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>3.1</v>
       </c>
       <c r="Q45">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="R45">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="S45">
         <v>1.53</v>
@@ -7665,7 +7665,7 @@
         <v>2.3</v>
       </c>
       <c r="U45">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="V45">
         <v>1.25</v>
@@ -7683,10 +7683,10 @@
         <v>2.31</v>
       </c>
       <c r="AA45">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC45">
         <v>6</v>
@@ -7701,7 +7701,7 @@
         <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7810,10 +7810,10 @@
         <v>5.25</v>
       </c>
       <c r="O46">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="P46">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="Q46">
         <v>4.21</v>
@@ -7825,7 +7825,7 @@
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
         <v>2.3</v>
@@ -7840,25 +7840,25 @@
         <v>1</v>
       </c>
       <c r="Y46">
+        <v>1.15</v>
+      </c>
+      <c r="Z46">
+        <v>4.4</v>
+      </c>
+      <c r="AA46">
+        <v>1.57</v>
+      </c>
+      <c r="AB46">
+        <v>2.38</v>
+      </c>
+      <c r="AC46">
+        <v>2.34</v>
+      </c>
+      <c r="AD46">
+        <v>1.5</v>
+      </c>
+      <c r="AE46">
         <v>1.17</v>
-      </c>
-      <c r="Z46">
-        <v>4.25</v>
-      </c>
-      <c r="AA46">
-        <v>1.6</v>
-      </c>
-      <c r="AB46">
-        <v>2.3</v>
-      </c>
-      <c r="AC46">
-        <v>2.38</v>
-      </c>
-      <c r="AD46">
-        <v>1.47</v>
-      </c>
-      <c r="AE46">
-        <v>1.16</v>
       </c>
       <c r="AF46">
         <v>1.62</v>
@@ -7976,7 +7976,7 @@
         <v>3.55</v>
       </c>
       <c r="P47">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q47">
         <v>2.75</v>
@@ -8009,22 +8009,22 @@
         <v>4.1</v>
       </c>
       <c r="AA47">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB47">
         <v>2.16</v>
       </c>
       <c r="AC47">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="AD47">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE47">
         <v>1.13</v>
       </c>
       <c r="AF47">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
         <v>2.25</v>
@@ -8133,22 +8133,22 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q48">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R48">
         <v>2.24</v>
       </c>
       <c r="S48">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
         <v>3.5</v>
@@ -8163,25 +8163,25 @@
         <v>1.15</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AD48">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE48">
         <v>1.2</v>
@@ -8206,7 +8206,7 @@
         <v>1.44</v>
       </c>
       <c r="AK48">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,10 +8296,10 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O49">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="P49">
         <v>3.5</v>
@@ -8314,31 +8314,31 @@
         <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U49">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
         <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X49">
         <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
         <v>4.1</v>
       </c>
       <c r="AA49">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AB49">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AC49">
         <v>2.75</v>
@@ -8350,10 +8350,10 @@
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>4.3</v>
       </c>
       <c r="P52">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q52">
         <v>1.94</v>
@@ -8800,28 +8800,28 @@
         <v>2.33</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
         <v>2.53</v>
       </c>
       <c r="V52">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z52">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
         <v>1.78</v>
@@ -8830,10 +8830,10 @@
         <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE52">
         <v>1.14</v>
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O54">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="P54">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA54">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB54">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O55">
         <v>3.8</v>
       </c>
       <c r="P55">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q55">
         <v>2.15</v>
@@ -9292,40 +9292,40 @@
         <v>1.25</v>
       </c>
       <c r="T55">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U55">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W55">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X55">
         <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z55">
-        <v>4.78</v>
+        <v>4.46</v>
       </c>
       <c r="AA55">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB55">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC55">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AE55">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF55">
         <v>1.57</v>
@@ -9467,7 +9467,7 @@
         <v>1.18</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
         <v>1.11</v>
@@ -9476,7 +9476,7 @@
         <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB56">
         <v>2.48</v>
@@ -9494,7 +9494,7 @@
         <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
         <v>1.9</v>
       </c>
       <c r="O57">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P57">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9630,7 +9630,7 @@
         <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
         <v>1.2</v>
@@ -9642,7 +9642,7 @@
         <v>1.65</v>
       </c>
       <c r="AB57">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC57">
         <v>2.59</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q58">
         <v>3.4</v>
@@ -9808,19 +9808,19 @@
         <v>2</v>
       </c>
       <c r="AC58">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AD58">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
         <v>1.57</v>
       </c>
       <c r="AG58">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O59">
         <v>3.95</v>
@@ -9935,7 +9935,7 @@
         <v>1.76</v>
       </c>
       <c r="Q59">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R59">
         <v>2.4</v>
@@ -9950,7 +9950,7 @@
         <v>2.15</v>
       </c>
       <c r="V59">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W59">
         <v>1.12</v>
@@ -9974,13 +9974,13 @@
         <v>2.17</v>
       </c>
       <c r="AD59">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE59">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF59">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG59">
         <v>2.55</v>
@@ -10089,22 +10089,22 @@
         </is>
       </c>
       <c r="N60">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="O60">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="P60">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Q60">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="R60">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="S60">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
         <v>4.4</v>
@@ -10122,31 +10122,31 @@
         <v>1</v>
       </c>
       <c r="Y60">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z60">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="AA60">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AB60">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="AC60">
         <v>1.94</v>
       </c>
       <c r="AD60">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE60">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF60">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG60">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.04</v>
+        <v>3.68</v>
       </c>
       <c r="AK60">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,10 +10255,10 @@
         <v>2.71</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="Q61">
         <v>2.94</v>
@@ -10267,49 +10267,49 @@
         <v>2.31</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="U61">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V61">
         <v>1.59</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z61">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA61">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AC61">
+        <v>2.63</v>
+      </c>
+      <c r="AD61">
+        <v>1.47</v>
+      </c>
+      <c r="AE61">
+        <v>1.17</v>
+      </c>
+      <c r="AF61">
+        <v>1.47</v>
+      </c>
+      <c r="AG61">
         <v>2.38</v>
-      </c>
-      <c r="AD61">
-        <v>1.57</v>
-      </c>
-      <c r="AE61">
-        <v>1.22</v>
-      </c>
-      <c r="AF61">
-        <v>1.44</v>
-      </c>
-      <c r="AG61">
-        <v>2.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10759,37 +10759,37 @@
         <v>1.25</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA64">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC64">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AD64">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE64">
         <v>1.2</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK64">
         <v>2.11</v>
@@ -10907,7 +10907,7 @@
         <v>1.8</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
         <v>3.5</v>
@@ -10925,22 +10925,22 @@
         <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z65">
-        <v>4.55</v>
+        <v>5.28</v>
       </c>
       <c r="AA65">
         <v>1.5</v>
@@ -10949,13 +10949,13 @@
         <v>2.4</v>
       </c>
       <c r="AC65">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AD65">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
         <v>1.5</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK65">
         <v>1.97</v>
@@ -11067,28 +11067,28 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P66">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="R66">
         <v>2.49</v>
       </c>
       <c r="S66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T66">
         <v>4.65</v>
       </c>
       <c r="U66">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V66">
         <v>1.88</v>
@@ -11393,22 +11393,22 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="O68">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="P68">
-        <v>3.32</v>
+        <v>2.85</v>
       </c>
       <c r="Q68">
         <v>2.54</v>
       </c>
       <c r="R68">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T68">
         <v>3</v>
@@ -11417,28 +11417,28 @@
         <v>2.62</v>
       </c>
       <c r="V68">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W68">
         <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
         <v>1.29</v>
       </c>
       <c r="Z68">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="AA68">
         <v>1.9</v>
       </c>
       <c r="AB68">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AC68">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="AD68">
         <v>1.34</v>
@@ -11447,7 +11447,7 @@
         <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG68">
         <v>2.05</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK68">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q69">
-        <v>2.86</v>
+        <v>1.9</v>
       </c>
       <c r="R69">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="S69">
+        <v>1.19</v>
+      </c>
+      <c r="T69">
+        <v>4</v>
+      </c>
+      <c r="U69">
+        <v>2</v>
+      </c>
+      <c r="V69">
+        <v>1.73</v>
+      </c>
+      <c r="W69">
+        <v>1.2</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>1.08</v>
+      </c>
+      <c r="Z69">
+        <v>5.97</v>
+      </c>
+      <c r="AA69">
+        <v>1.36</v>
+      </c>
+      <c r="AB69">
+        <v>2.88</v>
+      </c>
+      <c r="AC69">
+        <v>1.95</v>
+      </c>
+      <c r="AD69">
+        <v>1.7</v>
+      </c>
+      <c r="AE69">
         <v>1.3</v>
       </c>
-      <c r="T69">
-        <v>3.3</v>
-      </c>
-      <c r="U69">
-        <v>2.55</v>
-      </c>
-      <c r="V69">
-        <v>1.51</v>
-      </c>
-      <c r="W69">
-        <v>1.12</v>
-      </c>
-      <c r="X69">
-        <v>1.03</v>
-      </c>
-      <c r="Y69">
-        <v>1.22</v>
-      </c>
-      <c r="Z69">
-        <v>4.16</v>
-      </c>
-      <c r="AA69">
-        <v>1.68</v>
-      </c>
-      <c r="AB69">
-        <v>2.02</v>
-      </c>
-      <c r="AC69">
-        <v>2.56</v>
-      </c>
-      <c r="AD69">
-        <v>1.4</v>
-      </c>
-      <c r="AE69">
-        <v>1.18</v>
-      </c>
       <c r="AF69">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG69">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK69">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O70">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q70">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="R70">
-        <v>2.61</v>
+        <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U70">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="V70">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="W70">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z70">
-        <v>6.24</v>
+        <v>3.98</v>
       </c>
       <c r="AA70">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB70">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="AC70">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AD70">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AE70">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AF70">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG70">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AK70">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11903,37 +11903,37 @@
         <v>3.6</v>
       </c>
       <c r="U71">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
         <v>1.62</v>
       </c>
       <c r="W71">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AA71">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AC71">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD71">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE71">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF71">
         <v>1.9</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O72">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P72">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q72">
         <v>2.5</v>
       </c>
       <c r="R72">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="S72">
         <v>1.54</v>
@@ -12075,7 +12075,7 @@
         <v>1.03</v>
       </c>
       <c r="X72">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y72">
         <v>1.51</v>
@@ -12099,10 +12099,10 @@
         <v>1.04</v>
       </c>
       <c r="AF72">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG72">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK72">
         <v>1.85</v>
@@ -12214,7 +12214,7 @@
         <v>4.15</v>
       </c>
       <c r="P73">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q73">
         <v>1.95</v>
@@ -12226,7 +12226,7 @@
         <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="U73">
         <v>2.6</v>
@@ -12253,7 +12253,7 @@
         <v>1.9</v>
       </c>
       <c r="AC73">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="AD73">
         <v>1.32</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q74">
         <v>2.44</v>
@@ -12404,31 +12404,31 @@
         <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z74">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA74">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB74">
+        <v>2.38</v>
+      </c>
+      <c r="AC74">
+        <v>2.53</v>
+      </c>
+      <c r="AD74">
+        <v>1.52</v>
+      </c>
+      <c r="AE74">
+        <v>1.2</v>
+      </c>
+      <c r="AF74">
+        <v>1.5</v>
+      </c>
+      <c r="AG74">
         <v>2.45</v>
-      </c>
-      <c r="AC74">
-        <v>2.31</v>
-      </c>
-      <c r="AD74">
-        <v>1.54</v>
-      </c>
-      <c r="AE74">
-        <v>1.22</v>
-      </c>
-      <c r="AF74">
-        <v>1.44</v>
-      </c>
-      <c r="AG74">
-        <v>2.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12534,10 +12534,10 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O75">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P75">
         <v>2.8</v>
@@ -12546,52 +12546,52 @@
         <v>2.76</v>
       </c>
       <c r="R75">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="S75">
         <v>1.4</v>
       </c>
       <c r="T75">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="U75">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="V75">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W75">
+        <v>1.06</v>
+      </c>
+      <c r="X75">
         <v>1.07</v>
       </c>
-      <c r="X75">
+      <c r="Y75">
+        <v>1.43</v>
+      </c>
+      <c r="Z75">
+        <v>2.89</v>
+      </c>
+      <c r="AA75">
+        <v>2.3</v>
+      </c>
+      <c r="AB75">
+        <v>1.6</v>
+      </c>
+      <c r="AC75">
+        <v>4.1</v>
+      </c>
+      <c r="AD75">
+        <v>1.22</v>
+      </c>
+      <c r="AE75">
         <v>1.06</v>
       </c>
-      <c r="Y75">
-        <v>1.36</v>
-      </c>
-      <c r="Z75">
-        <v>3.16</v>
-      </c>
-      <c r="AA75">
-        <v>2.1</v>
-      </c>
-      <c r="AB75">
-        <v>1.73</v>
-      </c>
-      <c r="AC75">
-        <v>3.8</v>
-      </c>
-      <c r="AD75">
-        <v>1.26</v>
-      </c>
-      <c r="AE75">
-        <v>1.07</v>
-      </c>
       <c r="AF75">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG75">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12709,16 +12709,16 @@
         <v>3.6</v>
       </c>
       <c r="R76">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S76">
         <v>1.41</v>
       </c>
       <c r="T76">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="V76">
         <v>1.39</v>
@@ -12751,10 +12751,10 @@
         <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG76">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P77">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="Q77">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R77">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T77">
-        <v>3.27</v>
+        <v>3.07</v>
       </c>
       <c r="U77">
-        <v>2.65</v>
+        <v>2.86</v>
       </c>
       <c r="V77">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W77">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB77">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC77">
-        <v>2.94</v>
+        <v>3.31</v>
       </c>
       <c r="AD77">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.22</v>
       </c>
       <c r="AK77">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13044,7 +13044,7 @@
         <v>2.31</v>
       </c>
       <c r="U78">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="V78">
         <v>1.25</v>
@@ -13059,13 +13059,13 @@
         <v>1.48</v>
       </c>
       <c r="Z78">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AA78">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC78">
         <v>4.8</v>
@@ -13213,7 +13213,7 @@
         <v>1.5</v>
       </c>
       <c r="W79">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X79">
         <v>1.03</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
         <v>3.45</v>
       </c>
       <c r="P80">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q80">
         <v>2.62</v>
       </c>
       <c r="R80">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="S80">
         <v>1.3</v>
@@ -13379,22 +13379,22 @@
         <v>1.12</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z80">
-        <v>4.32</v>
+        <v>4.05</v>
       </c>
       <c r="AA80">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AB80">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC80">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="AD80">
         <v>1.4</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="O81">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q81">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="R81">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="S81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T81">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U81">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V81">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W81">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z81">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AA81">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AB81">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC81">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AD81">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AE81">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AF81">
         <v>1.47</v>
       </c>
       <c r="AG81">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK81">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="Q82">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="R82">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="S82">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U82">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V82">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z82">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AA82">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB82">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AC82">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AD82">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE82">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF82">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG82">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="P83">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="Q83">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="R83">
         <v>2.5</v>
@@ -13862,40 +13862,40 @@
         <v>2.05</v>
       </c>
       <c r="V83">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W83">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X83">
         <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z83">
         <v>6</v>
       </c>
       <c r="AA83">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB83">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC83">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AD83">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AE83">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF83">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AG83">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14173,7 +14173,7 @@
         <v>2.25</v>
       </c>
       <c r="Q85">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R85">
         <v>2.36</v>
@@ -14182,7 +14182,7 @@
         <v>1.19</v>
       </c>
       <c r="T85">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U85">
         <v>2.05</v>
@@ -14200,7 +14200,7 @@
         <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>5.55</v>
+        <v>5.59</v>
       </c>
       <c r="AA85">
         <v>1.44</v>
@@ -14209,19 +14209,19 @@
         <v>2.6</v>
       </c>
       <c r="AC85">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD85">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AE85">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF85">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG85">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK85">
         <v>1.4</v>
@@ -14327,25 +14327,25 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
         <v>2.8</v>
       </c>
       <c r="Q86">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="R86">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S86">
         <v>1.22</v>
       </c>
       <c r="T86">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="U86">
         <v>2.1</v>
@@ -14372,13 +14372,13 @@
         <v>2.55</v>
       </c>
       <c r="AC86">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AD86">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE86">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF86">
         <v>1.4</v>
@@ -14502,7 +14502,7 @@
         <v>2.09</v>
       </c>
       <c r="R87">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
         <v>1.3</v>
@@ -14520,7 +14520,7 @@
         <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
         <v>1.23</v>
@@ -14541,7 +14541,7 @@
         <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
         <v>1.85</v>
@@ -14563,7 +14563,7 @@
         <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14656,10 +14656,10 @@
         <v>2.16</v>
       </c>
       <c r="O88">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q88">
         <v>2.62</v>
@@ -14680,7 +14680,7 @@
         <v>1.57</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14704,13 +14704,13 @@
         <v>1.53</v>
       </c>
       <c r="AE88">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF88">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG88">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>1.29</v>
       </c>
       <c r="AK88">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,25 +14816,25 @@
         </is>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="O89">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P89">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="Q89">
-        <v>4.62</v>
+        <v>4.89</v>
       </c>
       <c r="R89">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S89">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="U89">
         <v>2.47</v>
@@ -14843,7 +14843,7 @@
         <v>1.46</v>
       </c>
       <c r="W89">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X89">
         <v>1.01</v>
@@ -14852,28 +14852,28 @@
         <v>1.21</v>
       </c>
       <c r="Z89">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA89">
+        <v>1.8</v>
+      </c>
+      <c r="AB89">
+        <v>2</v>
+      </c>
+      <c r="AC89">
+        <v>2.81</v>
+      </c>
+      <c r="AD89">
+        <v>1.33</v>
+      </c>
+      <c r="AE89">
+        <v>1.13</v>
+      </c>
+      <c r="AF89">
         <v>1.75</v>
       </c>
-      <c r="AB89">
-        <v>2.05</v>
-      </c>
-      <c r="AC89">
-        <v>2.74</v>
-      </c>
-      <c r="AD89">
-        <v>1.35</v>
-      </c>
-      <c r="AE89">
-        <v>1.1</v>
-      </c>
-      <c r="AF89">
-        <v>1.67</v>
-      </c>
       <c r="AG89">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14979,16 +14979,16 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O90">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P90">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q90">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="R90">
         <v>2.05</v>
@@ -14997,40 +14997,40 @@
         <v>1.39</v>
       </c>
       <c r="T90">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="U90">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="V90">
         <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z90">
-        <v>3.58</v>
+        <v>3.07</v>
       </c>
       <c r="AA90">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB90">
         <v>1.84</v>
       </c>
       <c r="AC90">
-        <v>3.36</v>
+        <v>4.04</v>
       </c>
       <c r="AD90">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE90">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF90">
         <v>1.75</v>
@@ -15187,10 +15187,10 @@
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4.33</v>
+        <v>3.88</v>
       </c>
       <c r="AD91">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE91">
         <v>1.06</v>
@@ -15317,7 +15317,7 @@
         <v>3.09</v>
       </c>
       <c r="R92">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S92">
         <v>1.22</v>
@@ -15344,10 +15344,10 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB92">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC92">
         <v>2.15</v>
@@ -15362,7 +15362,7 @@
         <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>5.75</v>
       </c>
       <c r="P93">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="Q93">
         <v>1.55</v>
@@ -15489,10 +15489,10 @@
         <v>2.8</v>
       </c>
       <c r="U93">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V93">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="W93">
         <v>1.09</v>
@@ -15507,13 +15507,13 @@
         <v>3.4</v>
       </c>
       <c r="AA93">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AB93">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AC93">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD93">
         <v>1.54</v>
@@ -15522,10 +15522,10 @@
         <v>1.18</v>
       </c>
       <c r="AF93">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AG93">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O94">
         <v>3.8</v>
@@ -15649,16 +15649,16 @@
         <v>1.3</v>
       </c>
       <c r="T94">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U94">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V94">
         <v>1.48</v>
       </c>
       <c r="W94">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X94">
         <v>1.03</v>
@@ -15679,7 +15679,7 @@
         <v>2.25</v>
       </c>
       <c r="AD94">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE94">
         <v>1.16</v>
@@ -15688,7 +15688,7 @@
         <v>1.67</v>
       </c>
       <c r="AG94">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.17</v>
       </c>
       <c r="AK94">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="O95">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P95">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="Q95">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="R95">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
+        <v>1.18</v>
+      </c>
+      <c r="Z95">
+        <v>4.33</v>
+      </c>
+      <c r="AA95">
+        <v>1.64</v>
+      </c>
+      <c r="AB95">
+        <v>2.17</v>
+      </c>
+      <c r="AC95">
+        <v>2.67</v>
+      </c>
+      <c r="AD95">
+        <v>1.42</v>
+      </c>
+      <c r="AE95">
+        <v>1.14</v>
+      </c>
+      <c r="AF95">
+        <v>1.7</v>
+      </c>
+      <c r="AG95">
+        <v>2.04</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.22</v>
+      </c>
+      <c r="AK95">
         <v>1.15</v>
-      </c>
-      <c r="Z95">
-        <v>4.25</v>
-      </c>
-      <c r="AA95">
-        <v>1.62</v>
-      </c>
-      <c r="AB95">
-        <v>2.13</v>
-      </c>
-      <c r="AC95">
-        <v>2.55</v>
-      </c>
-      <c r="AD95">
-        <v>1.45</v>
-      </c>
-      <c r="AE95">
-        <v>1.15</v>
-      </c>
-      <c r="AF95">
-        <v>1.53</v>
-      </c>
-      <c r="AG95">
-        <v>2.3</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.29</v>
-      </c>
-      <c r="AK95">
-        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="O96">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P96">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="Q96">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="R96">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U96">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V96">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W96">
         <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z96">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA96">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB96">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC96">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AD96">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE96">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF96">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG96">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16609,16 +16609,16 @@
         </is>
       </c>
       <c r="N100">
+        <v>4</v>
+      </c>
+      <c r="O100">
         <v>3.5</v>
       </c>
-      <c r="O100">
-        <v>3.38</v>
-      </c>
       <c r="P100">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="Q100">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R100">
         <v>2.09</v>
@@ -16630,13 +16630,13 @@
         <v>3.1</v>
       </c>
       <c r="U100">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V100">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W100">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X100">
         <v>1.02</v>
@@ -16666,7 +16666,7 @@
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16772,19 +16772,19 @@
         </is>
       </c>
       <c r="N101">
-        <v>5.9</v>
+        <v>6.85</v>
       </c>
       <c r="O101">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="P101">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="Q101">
-        <v>6.03</v>
+        <v>6.53</v>
       </c>
       <c r="R101">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="S101">
         <v>1.2</v>
@@ -16796,7 +16796,7 @@
         <v>2</v>
       </c>
       <c r="V101">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W101">
         <v>1.18</v>
@@ -16811,25 +16811,25 @@
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
         <v>2.1</v>
       </c>
       <c r="AD101">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE101">
         <v>1.29</v>
       </c>
       <c r="AF101">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG101">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16935,25 +16935,25 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P102">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q102">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R102">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
         <v>1.37</v>
       </c>
       <c r="T102">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="U102">
         <v>3.02</v>
@@ -16971,7 +16971,7 @@
         <v>1.29</v>
       </c>
       <c r="Z102">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AA102">
         <v>2.12</v>
@@ -16989,7 +16989,7 @@
         <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
         <v>1.83</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK102">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,16 +17101,16 @@
         <v>1.42</v>
       </c>
       <c r="O103">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P103">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q103">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R103">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="S103">
         <v>1.25</v>
@@ -17276,7 +17276,7 @@
         <v>2.05</v>
       </c>
       <c r="S104">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T104">
         <v>3</v>
@@ -17312,7 +17312,7 @@
         <v>1.27</v>
       </c>
       <c r="AE104">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF104">
         <v>1.65</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="O105">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P105">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q105">
+        <v>3.46</v>
+      </c>
+      <c r="R105">
+        <v>2.1</v>
+      </c>
+      <c r="S105">
+        <v>1.33</v>
+      </c>
+      <c r="T105">
         <v>3.1</v>
       </c>
-      <c r="R105">
-        <v>2.2</v>
-      </c>
-      <c r="S105">
-        <v>1.3</v>
-      </c>
-      <c r="T105">
-        <v>3.25</v>
-      </c>
       <c r="U105">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="V105">
         <v>1.44</v>
       </c>
       <c r="W105">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="AA105">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AB105">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AC105">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AD105">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF105">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.27</v>
       </c>
       <c r="AK105">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17590,19 +17590,19 @@
         <v>10</v>
       </c>
       <c r="O106">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="P106">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q106">
         <v>6.38</v>
       </c>
       <c r="R106">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S106">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T106">
         <v>3.32</v>
@@ -17614,34 +17614,34 @@
         <v>1.57</v>
       </c>
       <c r="W106">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X106">
         <v>1.01</v>
       </c>
       <c r="Y106">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z106">
         <v>4.75</v>
       </c>
       <c r="AA106">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB106">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC106">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AD106">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE106">
         <v>1.19</v>
       </c>
       <c r="AF106">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG106">
         <v>1.75</v>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK106">
         <v>1.07</v>
@@ -17795,13 +17795,13 @@
         <v>1.8</v>
       </c>
       <c r="AC107">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD107">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE107">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF107">
         <v>1.85</v>
@@ -17916,7 +17916,7 @@
         <v>1.25</v>
       </c>
       <c r="O108">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="P108">
         <v>9.6</v>
@@ -17958,7 +17958,7 @@
         <v>2.88</v>
       </c>
       <c r="AC108">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AD108">
         <v>1.72</v>
@@ -17970,7 +17970,7 @@
         <v>1.7</v>
       </c>
       <c r="AG108">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>1.17</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y109">
         <v>1.11</v>
@@ -18242,16 +18242,16 @@
         <v>1.7</v>
       </c>
       <c r="O110">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P110">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="Q110">
         <v>2.25</v>
       </c>
       <c r="R110">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S110">
         <v>1.4</v>
@@ -18260,43 +18260,43 @@
         <v>2.62</v>
       </c>
       <c r="U110">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V110">
+        <v>1.3</v>
+      </c>
+      <c r="W110">
+        <v>1.06</v>
+      </c>
+      <c r="X110">
+        <v>1.02</v>
+      </c>
+      <c r="Y110">
         <v>1.35</v>
       </c>
-      <c r="W110">
-        <v>1.07</v>
-      </c>
-      <c r="X110">
+      <c r="Z110">
+        <v>2.77</v>
+      </c>
+      <c r="AA110">
+        <v>2.35</v>
+      </c>
+      <c r="AB110">
+        <v>1.6</v>
+      </c>
+      <c r="AC110">
+        <v>4.31</v>
+      </c>
+      <c r="AD110">
+        <v>1.21</v>
+      </c>
+      <c r="AE110">
         <v>1.01</v>
       </c>
-      <c r="Y110">
-        <v>1.32</v>
-      </c>
-      <c r="Z110">
-        <v>2.98</v>
-      </c>
-      <c r="AA110">
-        <v>2.19</v>
-      </c>
-      <c r="AB110">
-        <v>1.68</v>
-      </c>
-      <c r="AC110">
-        <v>3.93</v>
-      </c>
-      <c r="AD110">
-        <v>1.24</v>
-      </c>
-      <c r="AE110">
-        <v>1.04</v>
-      </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG110">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18568,7 +18568,7 @@
         <v>1.83</v>
       </c>
       <c r="O112">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P112">
         <v>4.2</v>
@@ -18586,22 +18586,22 @@
         <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V112">
         <v>1.4</v>
       </c>
       <c r="W112">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X112">
         <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z112">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA112">
         <v>2</v>
@@ -18610,10 +18610,10 @@
         <v>1.82</v>
       </c>
       <c r="AC112">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD112">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE112">
         <v>1.06</v>
@@ -18638,7 +18638,7 @@
         <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18728,10 +18728,10 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="O113">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="P113">
         <v>3.45</v>
@@ -18746,13 +18746,13 @@
         <v>1.3</v>
       </c>
       <c r="T113">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U113">
         <v>2.4</v>
       </c>
       <c r="V113">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W113">
         <v>1.1</v>
@@ -18761,19 +18761,19 @@
         <v>1.01</v>
       </c>
       <c r="Y113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z113">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA113">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB113">
         <v>1.93</v>
       </c>
       <c r="AC113">
-        <v>2.83</v>
+        <v>3.24</v>
       </c>
       <c r="AD113">
         <v>1.33</v>
@@ -18897,7 +18897,7 @@
         <v>4.6</v>
       </c>
       <c r="P114">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Q114">
         <v>1.75</v>
@@ -18909,7 +18909,7 @@
         <v>1.17</v>
       </c>
       <c r="T114">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U114">
         <v>2.1</v>
@@ -18924,31 +18924,31 @@
         <v>1.02</v>
       </c>
       <c r="Y114">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z114">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AA114">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB114">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC114">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AD114">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE114">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF114">
         <v>1.71</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK114">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="O115">
         <v>3.2</v>
@@ -19063,13 +19063,13 @@
         <v>3.85</v>
       </c>
       <c r="Q115">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R115">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S115">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
         <v>2.7</v>
@@ -19078,40 +19078,40 @@
         <v>3</v>
       </c>
       <c r="V115">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y115">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z115">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AA115">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB115">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC115">
-        <v>3.93</v>
+        <v>4.28</v>
       </c>
       <c r="AD115">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AE115">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF115">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AG115">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK115">
         <v>1.83</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O116">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P116">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q116">
         <v>2.3</v>
@@ -19244,28 +19244,28 @@
         <v>1.59</v>
       </c>
       <c r="W116">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X116">
         <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA116">
+        <v>1.63</v>
+      </c>
+      <c r="AB116">
+        <v>2.35</v>
+      </c>
+      <c r="AC116">
+        <v>2.55</v>
+      </c>
+      <c r="AD116">
         <v>1.5</v>
-      </c>
-      <c r="AB116">
-        <v>2.5</v>
-      </c>
-      <c r="AC116">
-        <v>2.38</v>
-      </c>
-      <c r="AD116">
-        <v>1.57</v>
       </c>
       <c r="AE116">
         <v>1.22</v>
@@ -19287,7 +19287,7 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK116">
         <v>1.91</v>
@@ -19392,7 +19392,7 @@
         <v>3</v>
       </c>
       <c r="R117">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
         <v>1.26</v>
@@ -19410,13 +19410,13 @@
         <v>1.12</v>
       </c>
       <c r="X117">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y117">
         <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA117">
         <v>1.61</v>
@@ -19428,7 +19428,7 @@
         <v>2.49</v>
       </c>
       <c r="AD117">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE117">
         <v>1.14</v>
@@ -19453,7 +19453,7 @@
         <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19570,7 +19570,7 @@
         <v>1.37</v>
       </c>
       <c r="W118">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X118">
         <v>1</v>
@@ -19582,16 +19582,16 @@
         <v>3.1</v>
       </c>
       <c r="AA118">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AB118">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC118">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="AD118">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE118">
         <v>1.05</v>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -938,130 +938,130 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O4">
         <v>3.3</v>
       </c>
       <c r="P4">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q4">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R4">
         <v>2.08</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.92</v>
+        <v>2.61</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
-        <v>3.43</v>
+        <v>2.85</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AJ4">
         <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1116,27 +1116,27 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q5">
         <v>3.12</v>
       </c>
       <c r="R5">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.4</v>
@@ -1163,7 +1163,7 @@
         <v>2.92</v>
       </c>
       <c r="AA5">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB5">
         <v>1.65</v>
@@ -1175,7 +1175,7 @@
         <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
         <v>1.75</v>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1276,42 +1276,42 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="P6">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q6">
         <v>2.6</v>
       </c>
       <c r="R6">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
         <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
         <v>1.08</v>
@@ -1320,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
         <v>3.08</v>
@@ -1338,17 +1338,17 @@
         <v>1.22</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
         <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+9"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1439,14 +1439,14 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1456,25 +1456,25 @@
         <v>4.6</v>
       </c>
       <c r="P7">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q7">
         <v>5</v>
       </c>
       <c r="R7">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="S7">
         <v>1.16</v>
       </c>
       <c r="T7">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="U7">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="V7">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W7">
         <v>1.16</v>
@@ -1486,13 +1486,13 @@
         <v>1.08</v>
       </c>
       <c r="Z7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AA7">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB7">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC7">
         <v>2.1</v>
@@ -1501,7 +1501,7 @@
         <v>1.73</v>
       </c>
       <c r="AE7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF7">
         <v>1.57</v>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+10"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1916,30 +1916,30 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>2.75</v>
@@ -1954,58 +1954,58 @@
         <v>1.8</v>
       </c>
       <c r="S10">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="T10">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="U10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="V10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
         <v>1.01</v>
       </c>
       <c r="X10">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z10">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AA10">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AB10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC10">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE10">
         <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AG10">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "65"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2091,14 +2091,14 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="O12">
-        <v>3.66</v>
+        <v>3.43</v>
       </c>
       <c r="P12">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="Q12">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T12">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
         <v>1.57</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AC12">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AD12">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG12">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P13">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q13">
-        <v>4.36</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>2.5</v>
@@ -2458,34 +2458,34 @@
         <v>1.15</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z13">
         <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD13">
         <v>1.57</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AK13">
         <v>1.05</v>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3558,30 +3558,30 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q20">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="R20">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
         <v>1.41</v>
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48", "83"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71", "78"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3712,23 +3712,23 @@
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3747,10 +3747,10 @@
         <v>2</v>
       </c>
       <c r="S21">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T21">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="U21">
         <v>3.13</v>
@@ -3762,7 +3762,7 @@
         <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
         <v>1.38</v>
@@ -3771,10 +3771,10 @@
         <v>2.78</v>
       </c>
       <c r="AA21">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AB21">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
         <v>4.5</v>
@@ -3783,56 +3783,56 @@
         <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
+        <v>1.93</v>
+      </c>
+      <c r="AG21">
+        <v>1.8</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>["10", "33", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.4</v>
+      </c>
+      <c r="AK21">
+        <v>1.44</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
         <v>2</v>
       </c>
-      <c r="AG21">
-        <v>1.7</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.36</v>
-      </c>
-      <c r="AK21">
-        <v>1.4</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>-1</v>
-      </c>
-      <c r="AN21">
-        <v>-1</v>
-      </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,36 +3872,36 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "47"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O23">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
         <v>3.1</v>
@@ -4091,10 +4091,10 @@
         <v>1.08</v>
       </c>
       <c r="Y23">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Z23">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AA23">
         <v>2.74</v>
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O27">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T27">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="U27">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
+        <v>1.36</v>
+      </c>
+      <c r="Z27">
+        <v>2.88</v>
+      </c>
+      <c r="AA27">
+        <v>2.1</v>
+      </c>
+      <c r="AB27">
+        <v>1.65</v>
+      </c>
+      <c r="AC27">
+        <v>3.8</v>
+      </c>
+      <c r="AD27">
+        <v>1.19</v>
+      </c>
+      <c r="AE27">
+        <v>1.04</v>
+      </c>
+      <c r="AF27">
+        <v>1.85</v>
+      </c>
+      <c r="AG27">
+        <v>1.85</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.3</v>
       </c>
-      <c r="Z27">
-        <v>3.25</v>
-      </c>
-      <c r="AA27">
-        <v>1.91</v>
-      </c>
-      <c r="AB27">
-        <v>1.8</v>
-      </c>
-      <c r="AC27">
-        <v>3.28</v>
-      </c>
-      <c r="AD27">
-        <v>1.25</v>
-      </c>
-      <c r="AE27">
-        <v>1.06</v>
-      </c>
-      <c r="AF27">
-        <v>1.75</v>
-      </c>
-      <c r="AG27">
-        <v>2</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.28</v>
-      </c>
       <c r="AK27">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O28">
         <v>3.25</v>
       </c>
       <c r="P28">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
         <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U28">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -4903,7 +4903,7 @@
         <v>1.1</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.25</v>
@@ -4915,19 +4915,19 @@
         <v>1.85</v>
       </c>
       <c r="AB28">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC28">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE28">
         <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG28">
         <v>2.1</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O29">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P29">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q29">
         <v>6.11</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK30">
         <v>2.52</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="Q31">
         <v>3.4</v>
@@ -5395,7 +5395,7 @@
         <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z31">
         <v>5.67</v>
@@ -5413,7 +5413,7 @@
         <v>1.64</v>
       </c>
       <c r="AE31">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
         <v>1.44</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>2.05</v>
       </c>
       <c r="O33">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P33">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q33">
         <v>2.85</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P34">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="Q34">
         <v>3.2</v>
       </c>
       <c r="R34">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T34">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U34">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
         <v>1.08</v>
@@ -5884,28 +5884,28 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
         <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD34">
         <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
         <v>2.05</v>
@@ -6017,7 +6017,7 @@
         <v>2.9</v>
       </c>
       <c r="O35">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="P35">
         <v>2.35</v>
@@ -6029,13 +6029,13 @@
         <v>1.85</v>
       </c>
       <c r="S35">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T35">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="U35">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="V35">
         <v>1.22</v>
@@ -6044,34 +6044,34 @@
         <v>1.04</v>
       </c>
       <c r="X35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y35">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z35">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AA35">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AB35">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AC35">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AD35">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF35">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AG35">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>1.4</v>
       </c>
       <c r="O37">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P37">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q37">
         <v>1.87</v>
@@ -6355,49 +6355,49 @@
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U37">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V37">
+        <v>1.55</v>
+      </c>
+      <c r="W37">
+        <v>1.12</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.17</v>
+      </c>
+      <c r="Z37">
+        <v>5</v>
+      </c>
+      <c r="AA37">
+        <v>1.57</v>
+      </c>
+      <c r="AB37">
+        <v>2.17</v>
+      </c>
+      <c r="AC37">
+        <v>2.55</v>
+      </c>
+      <c r="AD37">
         <v>1.5</v>
       </c>
-      <c r="W37">
-        <v>1.11</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.2</v>
-      </c>
-      <c r="Z37">
-        <v>4.33</v>
-      </c>
-      <c r="AA37">
-        <v>1.7</v>
-      </c>
-      <c r="AB37">
-        <v>2.06</v>
-      </c>
-      <c r="AC37">
-        <v>2.7</v>
-      </c>
-      <c r="AD37">
-        <v>1.44</v>
-      </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK37">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P39">
         <v>3.6</v>
       </c>
       <c r="Q39">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R39">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U39">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.05</v>
@@ -6705,10 +6705,10 @@
         <v>2.88</v>
       </c>
       <c r="AA39">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="AB39">
-        <v>1.84</v>
+        <v>1.61</v>
       </c>
       <c r="AC39">
         <v>4</v>
@@ -6739,7 +6739,7 @@
         <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V40">
         <v>1.57</v>
@@ -6877,7 +6877,7 @@
         <v>2.38</v>
       </c>
       <c r="AD40">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE40">
         <v>1.2</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,65 +7155,65 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="O42">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="P42">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="Q42">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="R42">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="S42">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T42">
-        <v>3.52</v>
+        <v>4.6</v>
       </c>
       <c r="U42">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W42">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z42">
-        <v>5.43</v>
+        <v>8</v>
       </c>
       <c r="AA42">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AB42">
+        <v>3.6</v>
+      </c>
+      <c r="AC42">
+        <v>1.8</v>
+      </c>
+      <c r="AD42">
+        <v>2</v>
+      </c>
+      <c r="AE42">
+        <v>1.4</v>
+      </c>
+      <c r="AF42">
+        <v>1.36</v>
+      </c>
+      <c r="AG42">
         <v>2.75</v>
       </c>
-      <c r="AC42">
-        <v>2.01</v>
-      </c>
-      <c r="AD42">
-        <v>1.69</v>
-      </c>
-      <c r="AE42">
-        <v>1.29</v>
-      </c>
-      <c r="AF42">
-        <v>1.38</v>
-      </c>
-      <c r="AG42">
-        <v>2.71</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK42">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="O43">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="Q43">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="R43">
-        <v>2.69</v>
+        <v>2.31</v>
       </c>
       <c r="S43">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T43">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="U43">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="V43">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="W43">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>8</v>
+        <v>5.43</v>
       </c>
       <c r="AA43">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AB43">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AC43">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="AD43">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AE43">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
         <v>1.36</v>
       </c>
       <c r="AG43">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="O44">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>2.1</v>
       </c>
       <c r="R44">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
         <v>1.4</v>
@@ -7502,10 +7502,10 @@
         <v>2.7</v>
       </c>
       <c r="U44">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
         <v>1.07</v>
@@ -7514,25 +7514,25 @@
         <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z44">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AA44">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB44">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AD44">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF44">
         <v>2.1</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7647,10 +7647,10 @@
         <v>2.4</v>
       </c>
       <c r="O45">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="P45">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q45">
         <v>3.23</v>
@@ -7677,7 +7677,7 @@
         <v>1.07</v>
       </c>
       <c r="Y45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z45">
         <v>2.31</v>
@@ -7701,7 +7701,7 @@
         <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="O46">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P46">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="Q46">
         <v>4.21</v>
@@ -7825,40 +7825,40 @@
         <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AB46">
+        <v>2.27</v>
+      </c>
+      <c r="AC46">
         <v>2.38</v>
       </c>
-      <c r="AC46">
-        <v>2.34</v>
-      </c>
       <c r="AD46">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
         <v>1.62</v>
@@ -7880,7 +7880,7 @@
         <v>2.33</v>
       </c>
       <c r="AK46">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>2.87</v>
       </c>
       <c r="Q47">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R47">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S47">
         <v>1.3</v>
@@ -7997,37 +7997,37 @@
         <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AB47">
         <v>2.16</v>
       </c>
       <c r="AC47">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="AD47">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG47">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8142,10 +8142,10 @@
         <v>2.75</v>
       </c>
       <c r="Q48">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R48">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
         <v>1.25</v>
@@ -8163,7 +8163,7 @@
         <v>1.15</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
         <v>1.15</v>
@@ -8178,7 +8178,7 @@
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
         <v>1.51</v>
@@ -8190,7 +8190,7 @@
         <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.44</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,43 +8296,43 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O49">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
         <v>3.5</v>
       </c>
       <c r="Q49">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R49">
         <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T49">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
         <v>1.13</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
         <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA49">
         <v>1.62</v>
@@ -8341,13 +8341,13 @@
         <v>2.11</v>
       </c>
       <c r="AC49">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8465,7 +8465,7 @@
         <v>4.4</v>
       </c>
       <c r="P50">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q50">
         <v>1.92</v>
@@ -8489,7 +8489,7 @@
         <v>1.2</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
         <v>1.1</v>
@@ -8498,10 +8498,10 @@
         <v>6</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="AC50">
         <v>1.99</v>
@@ -8510,7 +8510,7 @@
         <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
@@ -8622,25 +8622,25 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O51">
         <v>3.25</v>
       </c>
       <c r="P51">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q51">
-        <v>3.75</v>
+        <v>4.18</v>
       </c>
       <c r="R51">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="U51">
         <v>2.63</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z51">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB51">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC51">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8948,19 +8948,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
         <v>2.8</v>
       </c>
       <c r="P53">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q53">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R53">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S53">
         <v>1.55</v>
@@ -8969,34 +8969,34 @@
         <v>2.3</v>
       </c>
       <c r="U53">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="V53">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W53">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X53">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y53">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z53">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AA53">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="AB53">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AC53">
-        <v>5.35</v>
+        <v>5.65</v>
       </c>
       <c r="AD53">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE53">
         <v>1.01</v>
@@ -9005,7 +9005,7 @@
         <v>2.15</v>
       </c>
       <c r="AG53">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>1.33</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9129,19 +9129,19 @@
         <v>1.29</v>
       </c>
       <c r="T54">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="V54">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
         <v>1.11</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.15</v>
@@ -9156,19 +9156,19 @@
         <v>2.2</v>
       </c>
       <c r="AC54">
-        <v>2.49</v>
+        <v>2.58</v>
       </c>
       <c r="AD54">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
         <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK54">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="O55">
         <v>3.8</v>
       </c>
       <c r="P55">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q55">
         <v>2.15</v>
@@ -9289,19 +9289,19 @@
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U55">
         <v>2.3</v>
       </c>
       <c r="V55">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W55">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9313,25 +9313,25 @@
         <v>4.46</v>
       </c>
       <c r="AA55">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB55">
         <v>2.26</v>
       </c>
       <c r="AC55">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AD55">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE55">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF55">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,25 +9437,25 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O56">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P56">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="Q56">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R56">
         <v>2.4</v>
       </c>
       <c r="S56">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T56">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U56">
         <v>2.1</v>
@@ -9476,16 +9476,16 @@
         <v>5.5</v>
       </c>
       <c r="AA56">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AB56">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AC56">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD56">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE56">
         <v>1.25</v>
@@ -9494,7 +9494,7 @@
         <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O57">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="P57">
-        <v>3.33</v>
+        <v>3.01</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9615,7 +9615,7 @@
         <v>2.18</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T57">
         <v>3.3</v>
@@ -9627,37 +9627,37 @@
         <v>1.52</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z57">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA57">
+        <v>1.75</v>
+      </c>
+      <c r="AB57">
+        <v>2.05</v>
+      </c>
+      <c r="AC57">
+        <v>2.81</v>
+      </c>
+      <c r="AD57">
+        <v>1.4</v>
+      </c>
+      <c r="AE57">
+        <v>1.11</v>
+      </c>
+      <c r="AF57">
         <v>1.65</v>
       </c>
-      <c r="AB57">
-        <v>2.1</v>
-      </c>
-      <c r="AC57">
-        <v>2.59</v>
-      </c>
-      <c r="AD57">
-        <v>1.46</v>
-      </c>
-      <c r="AE57">
-        <v>1.14</v>
-      </c>
-      <c r="AF57">
-        <v>1.57</v>
-      </c>
       <c r="AG57">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9793,7 +9793,7 @@
         <v>1.07</v>
       </c>
       <c r="X58">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
         <v>1.22</v>
@@ -9808,13 +9808,13 @@
         <v>2</v>
       </c>
       <c r="AC58">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AD58">
         <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
         <v>1.57</v>
@@ -9944,16 +9944,16 @@
         <v>1.21</v>
       </c>
       <c r="T59">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U59">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V59">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W59">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X59">
         <v>1.02</v>
@@ -9962,16 +9962,16 @@
         <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>5.68</v>
+        <v>5.8</v>
       </c>
       <c r="AA59">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB59">
         <v>2.63</v>
       </c>
       <c r="AC59">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD59">
         <v>1.66</v>
@@ -9983,7 +9983,7 @@
         <v>1.45</v>
       </c>
       <c r="AG59">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="O62">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P62">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q62">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R62">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="S62">
         <v>1.44</v>
       </c>
       <c r="T62">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="U62">
         <v>3.8</v>
       </c>
       <c r="V62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W62">
         <v>1.05</v>
       </c>
       <c r="X62">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y62">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z62">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="AA62">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB62">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC62">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AD62">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE62">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF62">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG62">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,43 +10578,43 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="O63">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="Q63">
         <v>3.3</v>
       </c>
       <c r="R63">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="S63">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="T63">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U63">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="V63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X63">
         <v>1.1</v>
       </c>
       <c r="Y63">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="Z63">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="AA63">
         <v>2.88</v>
@@ -10623,19 +10623,19 @@
         <v>1.4</v>
       </c>
       <c r="AC63">
-        <v>6.44</v>
+        <v>5.78</v>
       </c>
       <c r="AD63">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE63">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF63">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AG63">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="O66">
-        <v>4.33</v>
+        <v>4.65</v>
       </c>
       <c r="P66">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q66">
         <v>2.01</v>
@@ -11085,16 +11085,16 @@
         <v>1.13</v>
       </c>
       <c r="T66">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="U66">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V66">
         <v>1.88</v>
       </c>
       <c r="W66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X66">
         <v>1</v>
@@ -11106,25 +11106,25 @@
         <v>7.38</v>
       </c>
       <c r="AA66">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AB66">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AC66">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AD66">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="AE66">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AF66">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG66">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="O69">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="R69">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U69">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="V69">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="W69">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z69">
-        <v>5.97</v>
+        <v>3.98</v>
       </c>
       <c r="AA69">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="AB69">
-        <v>2.88</v>
+        <v>2.02</v>
       </c>
       <c r="AC69">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="AD69">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AE69">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AF69">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG69">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AK69">
-        <v>2.29</v>
+        <v>1.53</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,65 +11719,65 @@
         </is>
       </c>
       <c r="N70">
+        <v>1.5</v>
+      </c>
+      <c r="O70">
+        <v>4.2</v>
+      </c>
+      <c r="P70">
+        <v>4.5</v>
+      </c>
+      <c r="Q70">
+        <v>1.9</v>
+      </c>
+      <c r="R70">
+        <v>2.55</v>
+      </c>
+      <c r="S70">
+        <v>1.19</v>
+      </c>
+      <c r="T70">
+        <v>4</v>
+      </c>
+      <c r="U70">
+        <v>2</v>
+      </c>
+      <c r="V70">
+        <v>1.73</v>
+      </c>
+      <c r="W70">
+        <v>1.2</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
+        <v>1.08</v>
+      </c>
+      <c r="Z70">
+        <v>5.97</v>
+      </c>
+      <c r="AA70">
+        <v>1.36</v>
+      </c>
+      <c r="AB70">
+        <v>2.88</v>
+      </c>
+      <c r="AC70">
+        <v>1.95</v>
+      </c>
+      <c r="AD70">
+        <v>1.7</v>
+      </c>
+      <c r="AE70">
+        <v>1.3</v>
+      </c>
+      <c r="AF70">
+        <v>1.5</v>
+      </c>
+      <c r="AG70">
         <v>2.4</v>
       </c>
-      <c r="O70">
-        <v>3.2</v>
-      </c>
-      <c r="P70">
-        <v>2.5</v>
-      </c>
-      <c r="Q70">
-        <v>3.07</v>
-      </c>
-      <c r="R70">
-        <v>2.2</v>
-      </c>
-      <c r="S70">
-        <v>1.3</v>
-      </c>
-      <c r="T70">
-        <v>3.25</v>
-      </c>
-      <c r="U70">
-        <v>2.6</v>
-      </c>
-      <c r="V70">
-        <v>1.47</v>
-      </c>
-      <c r="W70">
-        <v>1.11</v>
-      </c>
-      <c r="X70">
-        <v>1.03</v>
-      </c>
-      <c r="Y70">
-        <v>1.24</v>
-      </c>
-      <c r="Z70">
-        <v>3.98</v>
-      </c>
-      <c r="AA70">
-        <v>1.68</v>
-      </c>
-      <c r="AB70">
-        <v>2.02</v>
-      </c>
-      <c r="AC70">
-        <v>2.56</v>
-      </c>
-      <c r="AD70">
-        <v>1.4</v>
-      </c>
-      <c r="AE70">
-        <v>1.16</v>
-      </c>
-      <c r="AF70">
-        <v>1.55</v>
-      </c>
-      <c r="AG70">
-        <v>2.3</v>
-      </c>
       <c r="AH70" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>2.29</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11918,22 +11918,22 @@
         <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA71">
         <v>1.5</v>
       </c>
       <c r="AB71">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC71">
         <v>2.38</v>
       </c>
       <c r="AD71">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE71">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF71">
         <v>1.9</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="O72">
         <v>2.95</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,80 +12208,80 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.44</v>
+        <v>1.96</v>
       </c>
       <c r="O73">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q73">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.21</v>
+        <v>3.7</v>
       </c>
       <c r="U73">
-        <v>2.6</v>
+        <v>2.19</v>
       </c>
       <c r="V73">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W73">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
+        <v>1.12</v>
+      </c>
+      <c r="Z73">
+        <v>4.7</v>
+      </c>
+      <c r="AA73">
+        <v>1.57</v>
+      </c>
+      <c r="AB73">
+        <v>2.38</v>
+      </c>
+      <c r="AC73">
+        <v>2.53</v>
+      </c>
+      <c r="AD73">
+        <v>1.52</v>
+      </c>
+      <c r="AE73">
+        <v>1.2</v>
+      </c>
+      <c r="AF73">
+        <v>1.5</v>
+      </c>
+      <c r="AG73">
+        <v>2.45</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
         <v>1.22</v>
       </c>
-      <c r="Z73">
-        <v>3.5</v>
-      </c>
-      <c r="AA73">
-        <v>1.87</v>
-      </c>
-      <c r="AB73">
-        <v>1.9</v>
-      </c>
-      <c r="AC73">
-        <v>3.11</v>
-      </c>
-      <c r="AD73">
-        <v>1.32</v>
-      </c>
-      <c r="AE73">
-        <v>1.14</v>
-      </c>
-      <c r="AF73">
-        <v>1.93</v>
-      </c>
-      <c r="AG73">
-        <v>1.78</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ73">
-        <v>1.19</v>
-      </c>
       <c r="AK73">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q74">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="R74">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="T74">
-        <v>3.7</v>
+        <v>2.64</v>
       </c>
       <c r="U74">
-        <v>2.19</v>
+        <v>3.19</v>
       </c>
       <c r="V74">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="W74">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y74">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="Z74">
-        <v>4.7</v>
+        <v>2.89</v>
       </c>
       <c r="AA74">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="AB74">
-        <v>2.38</v>
+        <v>1.6</v>
       </c>
       <c r="AC74">
-        <v>2.53</v>
+        <v>4.4</v>
       </c>
       <c r="AD74">
-        <v>1.52</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AF74">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AG74">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK74">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="O75">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P75">
-        <v>2.8</v>
+        <v>6.1</v>
       </c>
       <c r="Q75">
-        <v>2.76</v>
+        <v>1.95</v>
       </c>
       <c r="R75">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>2.64</v>
+        <v>3.21</v>
       </c>
       <c r="U75">
-        <v>3.19</v>
+        <v>2.6</v>
       </c>
       <c r="V75">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC75">
-        <v>4.1</v>
+        <v>3.11</v>
       </c>
       <c r="AD75">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE75">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG75">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12718,10 +12718,10 @@
         <v>2.88</v>
       </c>
       <c r="U76">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="V76">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
         <v>1.08</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O77">
         <v>3.48</v>
       </c>
       <c r="P77">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="Q77">
         <v>2.6</v>
@@ -12893,13 +12893,13 @@
         <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA77">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
         <v>1.9</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O78">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="P78">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
         <v>3.2</v>
@@ -13059,13 +13059,13 @@
         <v>1.48</v>
       </c>
       <c r="Z78">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="AA78">
         <v>2.5</v>
       </c>
       <c r="AB78">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC78">
         <v>4.8</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="O87">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P87">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q87">
         <v>2.09</v>
@@ -14508,7 +14508,7 @@
         <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U87">
         <v>2.5</v>
@@ -14520,19 +14520,19 @@
         <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA87">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC87">
         <v>3.05</v>
@@ -14541,7 +14541,7 @@
         <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
         <v>1.85</v>
@@ -14659,22 +14659,22 @@
         <v>3.5</v>
       </c>
       <c r="P88">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q88">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R88">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="S88">
         <v>1.25</v>
       </c>
       <c r="T88">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U88">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V88">
         <v>1.57</v>
@@ -14686,10 +14686,10 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z88">
-        <v>5</v>
+        <v>4.97</v>
       </c>
       <c r="AA88">
         <v>1.5</v>
@@ -14704,7 +14704,7 @@
         <v>1.53</v>
       </c>
       <c r="AE88">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF88">
         <v>1.45</v>
@@ -14726,7 +14726,7 @@
         <v>1.29</v>
       </c>
       <c r="AK88">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O89">
         <v>3.7</v>
@@ -14834,16 +14834,16 @@
         <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="U89">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V89">
         <v>1.46</v>
       </c>
       <c r="W89">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
         <v>1.01</v>
@@ -14855,10 +14855,10 @@
         <v>4.1</v>
       </c>
       <c r="AA89">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB89">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC89">
         <v>2.81</v>
@@ -14886,7 +14886,7 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK89">
         <v>1.15</v>
@@ -15187,10 +15187,10 @@
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AD91">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE91">
         <v>1.06</v>
@@ -15311,7 +15311,7 @@
         <v>3.75</v>
       </c>
       <c r="P92">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q92">
         <v>3.09</v>
@@ -15323,13 +15323,13 @@
         <v>1.22</v>
       </c>
       <c r="T92">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U92">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="V92">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W92">
         <v>1.18</v>
@@ -15344,25 +15344,25 @@
         <v>6</v>
       </c>
       <c r="AA92">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB92">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AC92">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD92">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE92">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF92">
         <v>1.44</v>
       </c>
       <c r="AG92">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="O95">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P95">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="Q95">
-        <v>5</v>
+        <v>3.84</v>
       </c>
       <c r="R95">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="S95">
         <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U95">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V95">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
         <v>1.12</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y95">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z95">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA95">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB95">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC95">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="AD95">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE95">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF95">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG95">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK95">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="O96">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P96">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="Q96">
-        <v>3.84</v>
+        <v>5</v>
       </c>
       <c r="R96">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="S96">
         <v>1.3</v>
       </c>
       <c r="T96">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U96">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V96">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W96">
         <v>1.12</v>
       </c>
       <c r="X96">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
+        <v>1.18</v>
+      </c>
+      <c r="Z96">
+        <v>4.33</v>
+      </c>
+      <c r="AA96">
+        <v>1.64</v>
+      </c>
+      <c r="AB96">
+        <v>2.17</v>
+      </c>
+      <c r="AC96">
+        <v>2.67</v>
+      </c>
+      <c r="AD96">
+        <v>1.42</v>
+      </c>
+      <c r="AE96">
+        <v>1.14</v>
+      </c>
+      <c r="AF96">
+        <v>1.7</v>
+      </c>
+      <c r="AG96">
+        <v>2.04</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.22</v>
+      </c>
+      <c r="AK96">
         <v>1.15</v>
-      </c>
-      <c r="Z96">
-        <v>4.25</v>
-      </c>
-      <c r="AA96">
-        <v>1.62</v>
-      </c>
-      <c r="AB96">
-        <v>2.13</v>
-      </c>
-      <c r="AC96">
-        <v>2.55</v>
-      </c>
-      <c r="AD96">
-        <v>1.45</v>
-      </c>
-      <c r="AE96">
-        <v>1.15</v>
-      </c>
-      <c r="AF96">
-        <v>1.53</v>
-      </c>
-      <c r="AG96">
-        <v>2.3</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>1.29</v>
-      </c>
-      <c r="AK96">
-        <v>1.3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16781,7 +16781,7 @@
         <v>1.4</v>
       </c>
       <c r="Q101">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
       <c r="R101">
         <v>2.7</v>
@@ -16811,25 +16811,25 @@
         <v>6.5</v>
       </c>
       <c r="AA101">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB101">
         <v>2.7</v>
       </c>
       <c r="AC101">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD101">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE101">
         <v>1.29</v>
       </c>
       <c r="AF101">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG101">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>

--- a/jogos_2026-10-30.xlsx
+++ b/jogos_2026-10-30.xlsx
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1605,18 +1605,18 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
         <v>1.89</v>
@@ -1628,10 +1628,10 @@
         <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="U8">
         <v>2.63</v>
@@ -1652,10 +1652,10 @@
         <v>2.8</v>
       </c>
       <c r="AA8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
         <v>2.83</v>
@@ -1674,46 +1674,46 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "41"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "61", "65", "71", "85"]</t>
         </is>
       </c>
       <c r="AJ8">
         <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64", "90+3"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2417,14 +2417,14 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,115 +2909,115 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
         <v>3.6</v>
       </c>
       <c r="Q16">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
         <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T16">
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z16">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
         <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AJ16">
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -3069,91 +3069,91 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S17">
+        <v>1.3</v>
+      </c>
+      <c r="T17">
+        <v>3.25</v>
+      </c>
+      <c r="U17">
+        <v>2.4</v>
+      </c>
+      <c r="V17">
+        <v>1.44</v>
+      </c>
+      <c r="W17">
+        <v>1.11</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.21</v>
+      </c>
+      <c r="Z17">
+        <v>3.58</v>
+      </c>
+      <c r="AA17">
+        <v>1.8</v>
+      </c>
+      <c r="AB17">
+        <v>1.95</v>
+      </c>
+      <c r="AC17">
+        <v>2.78</v>
+      </c>
+      <c r="AD17">
         <v>1.33</v>
-      </c>
-      <c r="T17">
-        <v>2.9</v>
-      </c>
-      <c r="U17">
-        <v>2.51</v>
-      </c>
-      <c r="V17">
-        <v>1.4</v>
-      </c>
-      <c r="W17">
-        <v>1.1</v>
-      </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>1.25</v>
-      </c>
-      <c r="Z17">
-        <v>3.8</v>
-      </c>
-      <c r="AA17">
-        <v>1.95</v>
-      </c>
-      <c r="AB17">
-        <v>2</v>
-      </c>
-      <c r="AC17">
-        <v>3.1</v>
-      </c>
-      <c r="AD17">
-        <v>1.36</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>["76"]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ17">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3165,10 +3165,10 @@
         <v>-1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ17">
         <v>0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,66 +3220,66 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
         <v>2.3</v>
       </c>
       <c r="Q18">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA18">
         <v>1.73</v>
@@ -3291,10 +3291,10 @@
         <v>2.88</v>
       </c>
       <c r="AD18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
         <v>1.57</v>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "55", "90+3"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "76"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,48 +3383,48 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O19">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Q19">
         <v>5.5</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
         <v>2.38</v>
@@ -3439,22 +3439,22 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
         <v>1.15</v>
@@ -3467,46 +3467,46 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "90+1"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "47"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85", "90+5"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4217,32 +4217,32 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
+        <v>3.35</v>
+      </c>
+      <c r="P24">
+        <v>2.9</v>
+      </c>
+      <c r="Q24">
         <v>3.25</v>
       </c>
-      <c r="P24">
-        <v>3.9</v>
-      </c>
-      <c r="Q24">
-        <v>2.3</v>
-      </c>
       <c r="R24">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T24">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U24">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4254,31 +4254,31 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z24">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AA24">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AB24">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC24">
-        <v>4.14</v>
+        <v>3.96</v>
       </c>
       <c r="AD24">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
         <v>1.02</v>
       </c>
       <c r="AF24">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AG24">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,37 +4291,37 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4373,30 +4373,30 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.61</v>
+        <v>2.05</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="R25">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="S25">
         <v>1.25</v>
@@ -4405,74 +4405,74 @@
         <v>3.3</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="AA25">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AC25">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AD25">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE25">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AG25">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ25">
         <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ25">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -4539,11 +4539,11 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4553,22 +4553,22 @@
         <v>3.75</v>
       </c>
       <c r="P26">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q26">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
         <v>1.44</v>
@@ -4586,25 +4586,25 @@
         <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC26">
         <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG26">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4613,41 +4613,41 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4702,11 +4702,11 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "45+2"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -4865,11 +4865,11 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+3"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "45+6"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5351,14 +5351,14 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "87"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5502,26 +5502,26 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "30", "67"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "87"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,13 +5665,13 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5828,26 +5828,26 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5", "68"]</t>
         </is>
       </c>
       <c r="AJ34">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -6154,30 +6154,30 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O36">
         <v>3.2</v>
@@ -6192,16 +6192,16 @@
         <v>1.98</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T36">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="U36">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="V36">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W36">
         <v>1.05</v>
@@ -6213,37 +6213,37 @@
         <v>1.35</v>
       </c>
       <c r="Z36">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="AA36">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AB36">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC36">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="AD36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AG36">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12"]</t>
         </is>
       </c>
       <c r="AJ36">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "28", "48", "59", "67", "82"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ37">
@@ -6419,28 +6419,28 @@
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6643,26 +6643,26 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "51"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,26 +6806,26 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "33", "85"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="O41">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="P41">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O42">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P42">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="Q42">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="R42">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="S42">
         <v>1.17</v>
       </c>
       <c r="T42">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U42">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V42">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W42">
         <v>1.25</v>
@@ -7188,7 +7188,7 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z42">
         <v>8</v>
@@ -7200,19 +7200,19 @@
         <v>3.6</v>
       </c>
       <c r="AC42">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE42">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AF42">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG42">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK42">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O43">
+        <v>3.9</v>
+      </c>
+      <c r="P43">
         <v>3.65</v>
       </c>
-      <c r="P43">
-        <v>3.3</v>
-      </c>
       <c r="Q43">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="R43">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
         <v>1.18</v>
@@ -7360,22 +7360,22 @@
         <v>1.33</v>
       </c>
       <c r="AB43">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AC43">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AD43">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF43">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AG43">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="P46">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q46">
         <v>4.21</v>
@@ -7831,7 +7831,7 @@
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W46">
         <v>1.15</v>
@@ -7976,25 +7976,25 @@
         <v>3.55</v>
       </c>
       <c r="P47">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
         <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
         <v>1.11</v>
@@ -8003,28 +8003,28 @@
         <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA47">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB47">
         <v>2.16</v>
       </c>
       <c r="AC47">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD47">
         <v>1.33</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF47">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
         <v>2.15</v>
@@ -8043,7 +8043,7 @@
         <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O48">
         <v>3.4</v>
       </c>
       <c r="P48">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q48">
         <v>3</v>
@@ -8178,7 +8178,7 @@
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD48">
         <v>1.51</v>
@@ -8206,7 +8206,7 @@
         <v>1.44</v>
       </c>
       <c r="AK48">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O49">
+        <v>3.48</v>
+      </c>
+      <c r="P49">
         <v>3.4</v>
       </c>
-      <c r="P49">
-        <v>3.5</v>
-      </c>
       <c r="Q49">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R49">
         <v>2.19</v>
       </c>
       <c r="S49">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
         <v>3.5</v>
       </c>
       <c r="U49">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V49">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W49">
         <v>1.13</v>
@@ -8332,28 +8332,28 @@
         <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AA49">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AD49">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE49">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF49">
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
         <v>1.85</v>
@@ -8468,10 +8468,10 @@
         <v>5</v>
       </c>
       <c r="Q50">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R50">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8492,22 +8492,22 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z50">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
         <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="AC50">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AD50">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE50">
         <v>1.29</v>
@@ -8516,7 +8516,7 @@
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK50">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O51">
         <v>3.25</v>
       </c>
       <c r="P51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q51">
-        <v>4.18</v>
+        <v>4.01</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="S51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T51">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U51">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA51">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AB51">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC51">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
         <v>1.33</v>
       </c>
       <c r="AE51">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,10 +8794,10 @@
         <v>5.9</v>
       </c>
       <c r="Q52">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="R52">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S52">
         <v>1.3</v>
@@ -8806,7 +8806,7 @@
         <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V52">
         <v>1.47</v>
@@ -8818,16 +8818,16 @@
         <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
         <v>4.33</v>
       </c>
       <c r="AA52">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AB52">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AC52">
         <v>2.59</v>
@@ -8836,13 +8836,13 @@
         <v>1.39</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF52">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9437,10 +9437,10 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O56">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P56">
         <v>2.21</v>
@@ -9470,22 +9470,22 @@
         <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z56">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA56">
         <v>1.49</v>
       </c>
       <c r="AB56">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AC56">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD56">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE56">
         <v>1.25</v>
@@ -9494,7 +9494,7 @@
         <v>1.4</v>
       </c>
       <c r="AG56">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9603,10 +9603,10 @@
         <v>1.85</v>
       </c>
       <c r="O57">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P57">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="Q57">
         <v>2.3</v>
@@ -9627,37 +9627,37 @@
         <v>1.52</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA57">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC57">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="AD57">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF57">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG57">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="O58">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q58">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R58">
         <v>2.2</v>
@@ -9814,13 +9814,13 @@
         <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AK58">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9962,13 +9962,13 @@
         <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA59">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB59">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC59">
         <v>2.15</v>
@@ -9980,10 +9980,10 @@
         <v>1.26</v>
       </c>
       <c r="AF59">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG59">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>8</v>
+        <v>2.71</v>
       </c>
       <c r="O60">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q60">
-        <v>6.95</v>
+        <v>2.94</v>
       </c>
       <c r="R60">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T60">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="U60">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="V60">
-        <v>1.91</v>
+        <v>1.59</v>
       </c>
       <c r="W60">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA60">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AB60">
-        <v>3.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC60">
-        <v>1.94</v>
+        <v>2.55</v>
       </c>
       <c r="AD60">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AE60">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AF60">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG60">
-        <v>2.11</v>
+        <v>2.63</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>3.68</v>
+        <v>1.21</v>
       </c>
       <c r="AK60">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.71</v>
+        <v>8.25</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="P61">
-        <v>2.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q61">
-        <v>2.94</v>
+        <v>6.75</v>
       </c>
       <c r="R61">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="V61">
-        <v>1.59</v>
+        <v>1.91</v>
       </c>
       <c r="W61">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z61">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA61">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AB61">
-        <v>2.18</v>
+        <v>2.86</v>
       </c>
       <c r="AC61">
-        <v>2.63</v>
+        <v>1.94</v>
       </c>
       <c r="AD61">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AE61">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>3.5</v>
       </c>
       <c r="AK61">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10744,7 +10744,7 @@
         <v>1.65</v>
       </c>
       <c r="O64">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="P64">
         <v>4.2</v>
@@ -10756,16 +10756,16 @@
         <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T64">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U64">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V64">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W64">
         <v>1.11</v>
@@ -10783,7 +10783,7 @@
         <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC64">
         <v>2.55</v>
@@ -10795,10 +10795,10 @@
         <v>1.2</v>
       </c>
       <c r="AF64">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P65">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q65">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R65">
         <v>2.2</v>
@@ -10943,10 +10943,10 @@
         <v>5.28</v>
       </c>
       <c r="AA65">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB65">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC65">
         <v>2.2</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O66">
         <v>4.65</v>
       </c>
       <c r="P66">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q66">
         <v>2.01</v>
@@ -11082,13 +11082,13 @@
         <v>2.49</v>
       </c>
       <c r="S66">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T66">
-        <v>4.85</v>
+        <v>5.05</v>
       </c>
       <c r="U66">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V66">
         <v>1.88</v>
@@ -11106,25 +11106,25 @@
         <v>7.38</v>
       </c>
       <c r="AA66">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB66">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC66">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD66">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AE66">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="AF66">
         <v>1.3</v>
       </c>
       <c r="AG66">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11233,10 +11233,10 @@
         <v>2.05</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P67">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q67">
         <v>2.44</v>
@@ -11251,7 +11251,7 @@
         <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="V67">
         <v>1.57</v>
@@ -11275,13 +11275,13 @@
         <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AD67">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
         <v>1.5</v>
@@ -11393,22 +11393,22 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O68">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="P68">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="Q68">
         <v>2.54</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S68">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <